--- a/Excel/ItemConfig.xlsx
+++ b/Excel/ItemConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="4"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="技能" sheetId="1" r:id="rId1"/>
@@ -498,7 +498,7 @@
     <t>1001</t>
   </si>
   <si>
-    <t>基础剑术</t>
+    <t>基础心法</t>
   </si>
   <si>
     <t>3</t>
@@ -516,7 +516,7 @@
     <t>1002</t>
   </si>
   <si>
-    <t>流光剑法</t>
+    <t>流光剑诀</t>
   </si>
   <si>
     <t>学习或者升级战士技能流光剑法</t>
@@ -525,7 +525,7 @@
     <t>1003</t>
   </si>
   <si>
-    <t>旋风斩</t>
+    <t>圆月剑诀</t>
   </si>
   <si>
     <t>学习或者升级战士技能旋风斩</t>
@@ -534,7 +534,7 @@
     <t>1004</t>
   </si>
   <si>
-    <t>腾空斩</t>
+    <t>重击剑术</t>
   </si>
   <si>
     <t>学习或者升级战士技能腾空斩</t>
@@ -555,7 +555,7 @@
     <t>1006</t>
   </si>
   <si>
-    <t>武力精通</t>
+    <t>无求易决</t>
   </si>
   <si>
     <t>学习或者升级战士技能武力精通</t>
@@ -564,7 +564,7 @@
     <t>1007</t>
   </si>
   <si>
-    <t>烈焰斩</t>
+    <t>烈焰剑诀</t>
   </si>
   <si>
     <t>学习或者升级战士技能烈焰斩</t>
@@ -618,7 +618,7 @@
     <t>2001</t>
   </si>
   <si>
-    <t>火球术</t>
+    <t>冥想法</t>
   </si>
   <si>
     <t>学习或者升级法师技能火球术</t>
@@ -627,7 +627,7 @@
     <t>2002</t>
   </si>
   <si>
-    <t>落雷术</t>
+    <t>神雷术</t>
   </si>
   <si>
     <t>学习或者升级法师技能落雷术</t>
@@ -636,7 +636,7 @@
     <t>2003</t>
   </si>
   <si>
-    <t>火焰墙</t>
+    <t>烈焰墙</t>
   </si>
   <si>
     <t>学习或者升级法师技能火焰墙</t>
@@ -654,7 +654,7 @@
     <t>2005</t>
   </si>
   <si>
-    <t>法力盾</t>
+    <t>念力盾</t>
   </si>
   <si>
     <t>学习或者升级法师技能法力盾</t>
@@ -663,7 +663,7 @@
     <t>2006</t>
   </si>
   <si>
-    <t>法术精通</t>
+    <t>冰心诀</t>
   </si>
   <si>
     <t>学习或者升级法师技能法术精通</t>
@@ -726,43 +726,43 @@
     <t>3001</t>
   </si>
   <si>
+    <t>祈福术</t>
+  </si>
+  <si>
+    <t>学习或者升级道士技能疗伤术</t>
+  </si>
+  <si>
+    <t>3002</t>
+  </si>
+  <si>
+    <t>灭魔符</t>
+  </si>
+  <si>
+    <t>学习或者升级道士技能驱魔符</t>
+  </si>
+  <si>
+    <t>3003</t>
+  </si>
+  <si>
+    <t>毒咒术</t>
+  </si>
+  <si>
+    <t>学习或者升级道士技能毒咒术</t>
+  </si>
+  <si>
+    <t>3004</t>
+  </si>
+  <si>
     <t>疗伤术</t>
   </si>
   <si>
-    <t>学习或者升级道士技能疗伤术</t>
-  </si>
-  <si>
-    <t>3002</t>
-  </si>
-  <si>
-    <t>驱魔符</t>
-  </si>
-  <si>
-    <t>学习或者升级道士技能驱魔符</t>
-  </si>
-  <si>
-    <t>3003</t>
-  </si>
-  <si>
-    <t>毒咒术</t>
-  </si>
-  <si>
-    <t>学习或者升级道士技能毒咒术</t>
-  </si>
-  <si>
-    <t>3004</t>
-  </si>
-  <si>
-    <t>召唤小兵</t>
-  </si>
-  <si>
     <t>学习或者升级道士技能召唤小兵</t>
   </si>
   <si>
     <t>3005</t>
   </si>
   <si>
-    <t>道力盾</t>
+    <t>护魂盾</t>
   </si>
   <si>
     <t>学习或者升级道士技能道力盾</t>
@@ -771,7 +771,7 @@
     <t>3006</t>
   </si>
   <si>
-    <t>道力精通</t>
+    <t>圣心诀</t>
   </si>
   <si>
     <t>学习或者升级道士技能道力精通</t>
@@ -780,7 +780,7 @@
     <t>3007</t>
   </si>
   <si>
-    <t>召唤魔兽</t>
+    <t>唤神咒</t>
   </si>
   <si>
     <t>学习或者升级道士技能召唤魔兽</t>
@@ -3798,12 +3798,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -4754,7 +4754,7 @@
       <c r="C6" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D6" s="22" t="s">
+      <c r="D6" s="11" t="s">
         <v>24</v>
       </c>
       <c r="E6" s="3" t="s">
@@ -4789,7 +4789,7 @@
       <c r="C7" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D7" s="22" t="s">
+      <c r="D7" s="11" t="s">
         <v>30</v>
       </c>
       <c r="E7" s="3" t="s">
@@ -4824,7 +4824,7 @@
       <c r="C8" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="D8" s="22" t="s">
+      <c r="D8" s="11" t="s">
         <v>33</v>
       </c>
       <c r="E8" s="3" t="s">
@@ -4859,7 +4859,7 @@
       <c r="C9" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="D9" s="22" t="s">
+      <c r="D9" s="11" t="s">
         <v>36</v>
       </c>
       <c r="E9" s="3" t="s">
@@ -4894,7 +4894,7 @@
       <c r="C10" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="D10" s="22" t="s">
+      <c r="D10" s="11" t="s">
         <v>40</v>
       </c>
       <c r="E10" s="3" t="s">
@@ -4929,7 +4929,7 @@
       <c r="C11" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="D11" s="22" t="s">
+      <c r="D11" s="11" t="s">
         <v>43</v>
       </c>
       <c r="E11" s="3" t="s">
@@ -4964,7 +4964,7 @@
       <c r="C12" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D12" s="22" t="s">
+      <c r="D12" s="11" t="s">
         <v>46</v>
       </c>
       <c r="E12" s="3" t="s">
@@ -5174,7 +5174,7 @@
       <c r="C19" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="D19" s="22" t="s">
+      <c r="D19" s="11" t="s">
         <v>64</v>
       </c>
       <c r="E19" s="3" t="s">
@@ -5209,7 +5209,7 @@
       <c r="C20" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="D20" s="22" t="s">
+      <c r="D20" s="11" t="s">
         <v>67</v>
       </c>
       <c r="E20" s="3" t="s">
@@ -5244,7 +5244,7 @@
       <c r="C21" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="D21" s="22" t="s">
+      <c r="D21" s="11" t="s">
         <v>70</v>
       </c>
       <c r="E21" s="3" t="s">
@@ -5279,7 +5279,7 @@
       <c r="C22" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="D22" s="22" t="s">
+      <c r="D22" s="11" t="s">
         <v>73</v>
       </c>
       <c r="E22" s="3" t="s">
@@ -5314,7 +5314,7 @@
       <c r="C23" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="D23" s="22" t="s">
+      <c r="D23" s="11" t="s">
         <v>76</v>
       </c>
       <c r="E23" s="3" t="s">
@@ -5349,7 +5349,7 @@
       <c r="C24" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="D24" s="22" t="s">
+      <c r="D24" s="11" t="s">
         <v>79</v>
       </c>
       <c r="E24" s="3" t="s">
@@ -5384,7 +5384,7 @@
       <c r="C25" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="D25" s="22" t="s">
+      <c r="D25" s="11" t="s">
         <v>82</v>
       </c>
       <c r="E25" s="3" t="s">
@@ -5594,7 +5594,7 @@
       <c r="C32" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="D32" s="22" t="s">
+      <c r="D32" s="11" t="s">
         <v>100</v>
       </c>
       <c r="E32" s="3" t="s">
@@ -5629,7 +5629,7 @@
       <c r="C33" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="D33" s="22" t="s">
+      <c r="D33" s="11" t="s">
         <v>103</v>
       </c>
       <c r="E33" s="3" t="s">
@@ -5664,7 +5664,7 @@
       <c r="C34" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="D34" s="22" t="s">
+      <c r="D34" s="11" t="s">
         <v>106</v>
       </c>
       <c r="E34" s="3" t="s">
@@ -5699,7 +5699,7 @@
       <c r="C35" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="D35" s="22" t="s">
+      <c r="D35" s="11" t="s">
         <v>109</v>
       </c>
       <c r="E35" s="3" t="s">
@@ -5734,7 +5734,7 @@
       <c r="C36" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="D36" s="22" t="s">
+      <c r="D36" s="11" t="s">
         <v>112</v>
       </c>
       <c r="E36" s="3" t="s">
@@ -5769,7 +5769,7 @@
       <c r="C37" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="D37" s="22" t="s">
+      <c r="D37" s="11" t="s">
         <v>115</v>
       </c>
       <c r="E37" s="3" t="s">
@@ -5804,7 +5804,7 @@
       <c r="C38" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="D38" s="22" t="s">
+      <c r="D38" s="11" t="s">
         <v>118</v>
       </c>
       <c r="E38" s="3" t="s">

--- a/Excel/ItemConfig.xlsx
+++ b/Excel/ItemConfig.xlsx
@@ -424,7 +424,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1957" uniqueCount="1041">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1987" uniqueCount="1041">
   <si>
     <t>_Id</t>
   </si>
@@ -525,7 +525,7 @@
     <t>1003</t>
   </si>
   <si>
-    <t>圆月剑诀</t>
+    <t>四方剑阵</t>
   </si>
   <si>
     <t>学习或者升级战士技能旋风斩</t>
@@ -564,12 +564,15 @@
     <t>1007</t>
   </si>
   <si>
-    <t>烈焰剑诀</t>
+    <t>火麟剑诀</t>
   </si>
   <si>
     <t>学习或者升级战士技能烈焰斩</t>
   </si>
   <si>
+    <t>#</t>
+  </si>
+  <si>
     <t>1008</t>
   </si>
   <si>
@@ -618,7 +621,7 @@
     <t>2001</t>
   </si>
   <si>
-    <t>冥想法</t>
+    <t>冥想心法</t>
   </si>
   <si>
     <t>学习或者升级法师技能火球术</t>
@@ -636,7 +639,7 @@
     <t>2003</t>
   </si>
   <si>
-    <t>烈焰墙</t>
+    <t>火海术</t>
   </si>
   <si>
     <t>学习或者升级法师技能火焰墙</t>
@@ -645,7 +648,7 @@
     <t>2004</t>
   </si>
   <si>
-    <t>烈焰环</t>
+    <t>烈焰术</t>
   </si>
   <si>
     <t>学习或者升级法师技能烈焰环</t>
@@ -672,7 +675,7 @@
     <t>2007</t>
   </si>
   <si>
-    <t>冰爆术</t>
+    <t>冰封术</t>
   </si>
   <si>
     <t>学习或者升级法师技能冰爆术</t>
@@ -726,7 +729,7 @@
     <t>3001</t>
   </si>
   <si>
-    <t>祈福术</t>
+    <t>祈福心法</t>
   </si>
   <si>
     <t>学习或者升级道士技能疗伤术</t>
@@ -1036,9 +1039,6 @@
   </si>
   <si>
     <t>升阶传奇专属的材料</t>
-  </si>
-  <si>
-    <t>#</t>
   </si>
   <si>
     <t>不朽废弃</t>
@@ -3798,12 +3798,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -4284,7 +4284,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4311,7 +4311,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="49">
@@ -4632,7 +4631,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:M43"/>
+  <dimension ref="A3:M43"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="3"/>
@@ -4645,7 +4644,7 @@
     <col min="14" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="3" customHeight="1" spans="3:13">
+    <row r="3" customHeight="1" spans="1:13">
       <c r="C3" s="5" t="s">
         <v>0</v>
       </c>
@@ -4680,7 +4679,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" customHeight="1" spans="3:13">
+    <row r="4" customHeight="1" spans="1:13">
       <c r="C4" s="5" t="s">
         <v>11</v>
       </c>
@@ -4715,7 +4714,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" customHeight="1" spans="3:13">
+    <row r="5" customHeight="1" spans="1:13">
       <c r="C5" s="5" t="s">
         <v>20</v>
       </c>
@@ -4750,7 +4749,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" customHeight="1" spans="3:13">
+    <row r="6" customHeight="1" spans="1:13">
       <c r="C6" s="3" t="s">
         <v>23</v>
       </c>
@@ -4785,7 +4784,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" customHeight="1" spans="3:13">
+    <row r="7" customHeight="1" spans="1:13">
       <c r="C7" s="3" t="s">
         <v>29</v>
       </c>
@@ -4820,7 +4819,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" customHeight="1" spans="3:13">
+    <row r="8" customHeight="1" spans="1:13">
       <c r="C8" s="3" t="s">
         <v>32</v>
       </c>
@@ -4855,7 +4854,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" customHeight="1" spans="3:13">
+    <row r="9" customHeight="1" spans="1:13">
       <c r="C9" s="3" t="s">
         <v>35</v>
       </c>
@@ -4890,7 +4889,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" customHeight="1" spans="3:13">
+    <row r="10" customHeight="1" spans="1:13">
       <c r="C10" s="3" t="s">
         <v>39</v>
       </c>
@@ -4925,7 +4924,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" customHeight="1" spans="3:13">
+    <row r="11" customHeight="1" spans="1:13">
       <c r="C11" s="3" t="s">
         <v>42</v>
       </c>
@@ -4960,7 +4959,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" customHeight="1" spans="3:13">
+    <row r="12" customHeight="1" spans="1:13">
       <c r="C12" s="3" t="s">
         <v>45</v>
       </c>
@@ -4995,18 +4994,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" customHeight="1" spans="3:13">
-      <c r="C13" s="23" t="s">
+    <row r="13" customHeight="1" spans="1:13">
+      <c r="A13" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="D13" s="22" t="s">
+      <c r="B13" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C13" s="22" t="s">
         <v>49</v>
+      </c>
+      <c r="D13" s="11" t="s">
+        <v>50</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>38</v>
@@ -5030,18 +5035,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" customHeight="1" spans="3:13">
-      <c r="C14" s="23" t="s">
-        <v>51</v>
-      </c>
-      <c r="D14" s="22" t="s">
+    <row r="14" customHeight="1" spans="1:13">
+      <c r="A14" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C14" s="22" t="s">
         <v>52</v>
+      </c>
+      <c r="D14" s="11" t="s">
+        <v>53</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>38</v>
@@ -5065,18 +5076,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" customHeight="1" spans="3:13">
-      <c r="C15" s="23" t="s">
-        <v>54</v>
-      </c>
-      <c r="D15" s="22" t="s">
+    <row r="15" customHeight="1" spans="1:13">
+      <c r="A15" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C15" s="22" t="s">
         <v>55</v>
+      </c>
+      <c r="D15" s="11" t="s">
+        <v>56</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>38</v>
@@ -5100,18 +5117,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" customHeight="1" spans="3:13">
-      <c r="C16" s="23" t="s">
-        <v>57</v>
-      </c>
-      <c r="D16" s="22" t="s">
+    <row r="16" customHeight="1" spans="1:13">
+      <c r="A16" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C16" s="22" t="s">
         <v>58</v>
+      </c>
+      <c r="D16" s="11" t="s">
+        <v>59</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>38</v>
@@ -5135,18 +5158,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" customHeight="1" spans="3:13">
-      <c r="C17" s="23" t="s">
-        <v>60</v>
-      </c>
-      <c r="D17" s="22" t="s">
+    <row r="17" customHeight="1" spans="1:13">
+      <c r="A17" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C17" s="22" t="s">
         <v>61</v>
+      </c>
+      <c r="D17" s="11" t="s">
+        <v>62</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>38</v>
@@ -5170,18 +5199,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" customHeight="1" spans="3:13">
+    <row r="19" customHeight="1" spans="1:13">
       <c r="C19" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>27</v>
@@ -5205,18 +5234,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" customHeight="1" spans="3:13">
+    <row r="20" customHeight="1" spans="1:13">
       <c r="C20" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>27</v>
@@ -5240,18 +5269,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" customHeight="1" spans="3:13">
+    <row r="21" customHeight="1" spans="1:13">
       <c r="C21" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D21" s="11" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>27</v>
@@ -5275,18 +5304,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" customHeight="1" spans="3:13">
+    <row r="22" customHeight="1" spans="1:13">
       <c r="C22" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>38</v>
@@ -5310,18 +5339,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" customHeight="1" spans="3:13">
+    <row r="23" customHeight="1" spans="1:13">
       <c r="C23" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D23" s="11" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>38</v>
@@ -5345,18 +5374,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" customHeight="1" spans="3:13">
+    <row r="24" customHeight="1" spans="1:13">
       <c r="C24" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D24" s="11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>38</v>
@@ -5380,18 +5409,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" customHeight="1" spans="3:13">
+    <row r="25" customHeight="1" spans="1:13">
       <c r="C25" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D25" s="11" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>38</v>
@@ -5415,18 +5444,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" customHeight="1" spans="3:13">
-      <c r="C26" s="23" t="s">
-        <v>84</v>
-      </c>
-      <c r="D26" s="22" t="s">
+    <row r="26" customHeight="1" spans="1:13">
+      <c r="A26" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C26" s="22" t="s">
         <v>85</v>
+      </c>
+      <c r="D26" s="11" t="s">
+        <v>86</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>38</v>
@@ -5450,18 +5485,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" customHeight="1" spans="3:13">
-      <c r="C27" s="23" t="s">
-        <v>87</v>
-      </c>
-      <c r="D27" s="22" t="s">
+    <row r="27" customHeight="1" spans="1:13">
+      <c r="A27" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C27" s="22" t="s">
         <v>88</v>
+      </c>
+      <c r="D27" s="11" t="s">
+        <v>89</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>38</v>
@@ -5485,18 +5526,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" customHeight="1" spans="3:13">
-      <c r="C28" s="23" t="s">
-        <v>90</v>
-      </c>
-      <c r="D28" s="22" t="s">
+    <row r="28" customHeight="1" spans="1:13">
+      <c r="A28" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C28" s="22" t="s">
         <v>91</v>
+      </c>
+      <c r="D28" s="11" t="s">
+        <v>92</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>38</v>
@@ -5520,18 +5567,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" customHeight="1" spans="3:13">
-      <c r="C29" s="23" t="s">
-        <v>93</v>
-      </c>
-      <c r="D29" s="22" t="s">
+    <row r="29" customHeight="1" spans="1:13">
+      <c r="A29" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C29" s="22" t="s">
         <v>94</v>
+      </c>
+      <c r="D29" s="11" t="s">
+        <v>95</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>38</v>
@@ -5555,18 +5608,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" customHeight="1" spans="3:13">
-      <c r="C30" s="23" t="s">
-        <v>96</v>
-      </c>
-      <c r="D30" s="22" t="s">
+    <row r="30" customHeight="1" spans="1:13">
+      <c r="A30" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C30" s="22" t="s">
         <v>97</v>
+      </c>
+      <c r="D30" s="11" t="s">
+        <v>98</v>
       </c>
       <c r="E30" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G30" s="3" t="s">
         <v>38</v>
@@ -5590,18 +5649,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" customHeight="1" spans="3:13">
+    <row r="32" customHeight="1" spans="1:13">
       <c r="C32" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D32" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>27</v>
@@ -5625,18 +5684,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" customHeight="1" spans="3:13">
+    <row r="33" customHeight="1" spans="1:13">
       <c r="C33" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D33" s="11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E33" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>27</v>
@@ -5660,18 +5719,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" customHeight="1" spans="3:13">
+    <row r="34" customHeight="1" spans="1:13">
       <c r="C34" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D34" s="11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E34" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="G34" s="3" t="s">
         <v>27</v>
@@ -5695,18 +5754,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" customHeight="1" spans="3:13">
+    <row r="35" customHeight="1" spans="1:13">
       <c r="C35" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D35" s="11" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E35" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G35" s="3" t="s">
         <v>38</v>
@@ -5730,18 +5789,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" customHeight="1" spans="3:13">
+    <row r="36" customHeight="1" spans="1:13">
       <c r="C36" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D36" s="11" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E36" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G36" s="3" t="s">
         <v>38</v>
@@ -5765,18 +5824,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" customHeight="1" spans="3:13">
+    <row r="37" customHeight="1" spans="1:13">
       <c r="C37" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D37" s="11" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E37" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G37" s="3" t="s">
         <v>38</v>
@@ -5800,18 +5859,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" customHeight="1" spans="3:13">
+    <row r="38" customHeight="1" spans="1:13">
       <c r="C38" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D38" s="11" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E38" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="G38" s="3" t="s">
         <v>38</v>
@@ -5835,18 +5894,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" customHeight="1" spans="3:13">
-      <c r="C39" s="23" t="s">
-        <v>120</v>
-      </c>
-      <c r="D39" s="22" t="s">
+    <row r="39" customHeight="1" spans="1:13">
+      <c r="A39" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C39" s="22" t="s">
         <v>121</v>
+      </c>
+      <c r="D39" s="11" t="s">
+        <v>122</v>
       </c>
       <c r="E39" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="G39" s="3" t="s">
         <v>38</v>
@@ -5870,18 +5935,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" customHeight="1" spans="3:13">
-      <c r="C40" s="23" t="s">
-        <v>123</v>
-      </c>
-      <c r="D40" s="22" t="s">
+    <row r="40" customHeight="1" spans="1:13">
+      <c r="A40" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C40" s="22" t="s">
         <v>124</v>
+      </c>
+      <c r="D40" s="11" t="s">
+        <v>125</v>
       </c>
       <c r="E40" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G40" s="3" t="s">
         <v>38</v>
@@ -5905,18 +5976,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" customHeight="1" spans="3:13">
-      <c r="C41" s="23" t="s">
-        <v>126</v>
-      </c>
-      <c r="D41" s="22" t="s">
+    <row r="41" customHeight="1" spans="1:13">
+      <c r="A41" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C41" s="22" t="s">
         <v>127</v>
+      </c>
+      <c r="D41" s="11" t="s">
+        <v>128</v>
       </c>
       <c r="E41" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="G41" s="3" t="s">
         <v>38</v>
@@ -5940,18 +6017,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" customHeight="1" spans="3:13">
-      <c r="C42" s="23" t="s">
-        <v>129</v>
-      </c>
-      <c r="D42" s="22" t="s">
+    <row r="42" customHeight="1" spans="1:13">
+      <c r="A42" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C42" s="22" t="s">
         <v>130</v>
+      </c>
+      <c r="D42" s="11" t="s">
+        <v>131</v>
       </c>
       <c r="E42" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="G42" s="3" t="s">
         <v>38</v>
@@ -5975,18 +6058,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" customHeight="1" spans="3:13">
-      <c r="C43" s="23" t="s">
-        <v>132</v>
-      </c>
-      <c r="D43" s="22" t="s">
+    <row r="43" customHeight="1" spans="1:13">
+      <c r="A43" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C43" s="22" t="s">
         <v>133</v>
+      </c>
+      <c r="D43" s="11" t="s">
+        <v>134</v>
       </c>
       <c r="E43" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G43" s="3" t="s">
         <v>38</v>
@@ -6702,13 +6791,13 @@
         <v>4001</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E6" s="3">
         <v>5</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="G6" s="3">
         <v>1</v>
@@ -6734,13 +6823,13 @@
         <v>4002</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E7" s="3">
         <v>5</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="G7" s="3">
         <v>1</v>
@@ -6766,13 +6855,13 @@
         <v>4003</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E8" s="3">
         <v>9</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="G8" s="3">
         <v>1</v>
@@ -6798,13 +6887,13 @@
         <v>4004</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E9" s="3">
         <v>5</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="G9" s="3">
         <v>1</v>
@@ -6830,13 +6919,13 @@
         <v>4005</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E10" s="3">
         <v>5</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="G10" s="3">
         <v>1</v>
@@ -6862,13 +6951,13 @@
         <v>4006</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E11" s="3">
         <v>5</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G11" s="3">
         <v>1</v>
@@ -6897,13 +6986,13 @@
         <v>4007</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E12" s="3">
         <v>5</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="G12" s="3">
         <v>1</v>
@@ -6929,13 +7018,13 @@
         <v>4008</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E13" s="3">
         <v>5</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="G13" s="3">
         <v>1</v>
@@ -6961,13 +7050,13 @@
         <v>4009</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E14" s="3">
         <v>5</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="G14" s="3">
         <v>1</v>
@@ -6993,13 +7082,13 @@
         <v>4010</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E15" s="3">
         <v>5</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="G15" s="3">
         <v>1</v>
@@ -7025,13 +7114,13 @@
         <v>4011</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E16" s="3">
         <v>5</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="G16" s="3">
         <v>1</v>
@@ -7057,13 +7146,13 @@
         <v>4012</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E17" s="3">
         <v>5</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="G17" s="3">
         <v>1</v>
@@ -7089,13 +7178,13 @@
         <v>4013</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E18" s="3">
         <v>9</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="G18" s="3">
         <v>1</v>
@@ -7121,13 +7210,13 @@
         <v>4014</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E19" s="3">
         <v>15</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="G19" s="3">
         <v>1</v>
@@ -7153,13 +7242,13 @@
         <v>4015</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E20" s="3">
         <v>5</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G20" s="3">
         <v>1</v>
@@ -7185,13 +7274,13 @@
         <v>4016</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E21" s="3">
         <v>5</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G21" s="3">
         <v>1</v>
@@ -7217,13 +7306,13 @@
         <v>4017</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E22" s="3">
         <v>9</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="G22" s="3">
         <v>1</v>
@@ -7249,13 +7338,13 @@
         <v>4018</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E23" s="3">
         <v>5</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G23" s="3">
         <v>1</v>
@@ -7281,13 +7370,13 @@
         <v>4019</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E24" s="3">
         <v>5</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="G24" s="3">
         <v>1</v>
@@ -7313,13 +7402,13 @@
         <v>4020</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E25" s="3">
         <v>15</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G25" s="3">
         <v>1</v>
@@ -7348,13 +7437,13 @@
         <v>4021</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E26" s="3">
         <v>5</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="G26" s="3">
         <v>1</v>
@@ -7380,13 +7469,13 @@
         <v>4022</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E27" s="3">
         <v>5</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="G27" s="3">
         <v>1</v>
@@ -7412,13 +7501,13 @@
         <v>4023</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E28" s="3">
         <v>5</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="G28" s="3">
         <v>1</v>
@@ -7444,13 +7533,13 @@
         <v>4024</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E29" s="3">
         <v>5</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="G29" s="3">
         <v>1</v>
@@ -7476,13 +7565,13 @@
         <v>4025</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E30" s="3">
         <v>5</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="G30" s="3">
         <v>1</v>
@@ -7508,13 +7597,13 @@
         <v>4026</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E31" s="3">
         <v>5</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="G31" s="3">
         <v>1</v>
@@ -7540,13 +7629,13 @@
         <v>4027</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E32" s="3">
         <v>5</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="G32" s="3">
         <v>1</v>
@@ -7572,13 +7661,13 @@
         <v>4028</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E33" s="3">
         <v>5</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="G33" s="3">
         <v>1</v>
@@ -7604,13 +7693,13 @@
         <v>4029</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E34" s="3">
         <v>5</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="G34" s="3">
         <v>1</v>
@@ -7636,13 +7725,13 @@
         <v>4030</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E35" s="3">
         <v>5</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="G35" s="3">
         <v>1</v>
@@ -7668,13 +7757,13 @@
         <v>4031</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E36" s="3">
         <v>5</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="G36" s="3">
         <v>1</v>
@@ -7700,13 +7789,13 @@
         <v>4032</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E37" s="3">
         <v>5</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="G37" s="3">
         <v>1</v>
@@ -7732,13 +7821,13 @@
         <v>4033</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E38" s="3">
         <v>5</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G38" s="3">
         <v>1</v>
@@ -7764,13 +7853,13 @@
         <v>4034</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E39" s="3">
         <v>5</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="G39" s="3">
         <v>1</v>
@@ -7796,13 +7885,13 @@
         <v>4035</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E40" s="3">
         <v>5</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="G40" s="3">
         <v>1</v>
@@ -7825,10 +7914,10 @@
     </row>
     <row r="41" s="3" customFormat="1" customHeight="1" spans="1:13">
       <c r="A41" s="3" t="s">
-        <v>204</v>
+        <v>48</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>204</v>
+        <v>48</v>
       </c>
       <c r="C41" s="3">
         <v>4036</v>
@@ -7840,7 +7929,7 @@
         <v>5</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="G41" s="3">
         <v>1</v>
@@ -7968,7 +8057,7 @@
         <v>5</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G45" s="3">
         <v>1</v>
@@ -8204,7 +8293,7 @@
         <v>5</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="G53" s="3">
         <v>1</v>
@@ -8236,7 +8325,7 @@
         <v>5</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="G54" s="3">
         <v>1</v>
@@ -8268,7 +8357,7 @@
         <v>5</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="G55" s="3">
         <v>1</v>

--- a/Excel/ItemConfig.xlsx
+++ b/Excel/ItemConfig.xlsx
@@ -184,7 +184,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="510" uniqueCount="281">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="512" uniqueCount="281">
   <si>
     <t>_Id</t>
   </si>
@@ -591,16 +591,16 @@
     <t>学习或者升级道士技能召唤白虎</t>
   </si>
   <si>
+    <t>精炼石</t>
+  </si>
+  <si>
+    <t>装备精练材料</t>
+  </si>
+  <si>
     <t>魂环碎片</t>
   </si>
   <si>
     <t>合成魂环的材料</t>
-  </si>
-  <si>
-    <t>精炼石</t>
-  </si>
-  <si>
-    <t>装备精练材料</t>
   </si>
   <si>
     <t>装备副本卷</t>
@@ -1696,7 +1696,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1708,6 +1708,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
   </cellXfs>
@@ -2399,7 +2403,7 @@
       <c r="B13" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C13" s="8" t="s">
+      <c r="C13" s="10" t="s">
         <v>48</v>
       </c>
       <c r="D13" s="6" t="s">
@@ -2440,7 +2444,7 @@
       <c r="B14" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C14" s="8" t="s">
+      <c r="C14" s="10" t="s">
         <v>51</v>
       </c>
       <c r="D14" s="6" t="s">
@@ -2481,7 +2485,7 @@
       <c r="B15" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C15" s="8" t="s">
+      <c r="C15" s="10" t="s">
         <v>54</v>
       </c>
       <c r="D15" s="6" t="s">
@@ -2522,7 +2526,7 @@
       <c r="B16" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C16" s="8" t="s">
+      <c r="C16" s="10" t="s">
         <v>57</v>
       </c>
       <c r="D16" s="6" t="s">
@@ -2563,7 +2567,7 @@
       <c r="B17" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C17" s="8" t="s">
+      <c r="C17" s="10" t="s">
         <v>60</v>
       </c>
       <c r="D17" s="6" t="s">
@@ -2849,7 +2853,7 @@
       <c r="B26" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C26" s="8" t="s">
+      <c r="C26" s="10" t="s">
         <v>84</v>
       </c>
       <c r="D26" s="6" t="s">
@@ -2890,7 +2894,7 @@
       <c r="B27" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C27" s="8" t="s">
+      <c r="C27" s="10" t="s">
         <v>87</v>
       </c>
       <c r="D27" s="6" t="s">
@@ -2931,7 +2935,7 @@
       <c r="B28" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C28" s="8" t="s">
+      <c r="C28" s="10" t="s">
         <v>90</v>
       </c>
       <c r="D28" s="6" t="s">
@@ -2972,7 +2976,7 @@
       <c r="B29" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C29" s="8" t="s">
+      <c r="C29" s="10" t="s">
         <v>93</v>
       </c>
       <c r="D29" s="6" t="s">
@@ -3013,7 +3017,7 @@
       <c r="B30" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C30" s="8" t="s">
+      <c r="C30" s="10" t="s">
         <v>96</v>
       </c>
       <c r="D30" s="6" t="s">
@@ -3299,7 +3303,7 @@
       <c r="B39" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C39" s="8" t="s">
+      <c r="C39" s="10" t="s">
         <v>120</v>
       </c>
       <c r="D39" s="6" t="s">
@@ -3340,7 +3344,7 @@
       <c r="B40" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C40" s="8" t="s">
+      <c r="C40" s="10" t="s">
         <v>123</v>
       </c>
       <c r="D40" s="6" t="s">
@@ -3381,7 +3385,7 @@
       <c r="B41" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C41" s="8" t="s">
+      <c r="C41" s="10" t="s">
         <v>126</v>
       </c>
       <c r="D41" s="6" t="s">
@@ -3422,7 +3426,7 @@
       <c r="B42" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C42" s="8" t="s">
+      <c r="C42" s="10" t="s">
         <v>129</v>
       </c>
       <c r="D42" s="6" t="s">
@@ -3463,7 +3467,7 @@
       <c r="B43" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C43" s="8" t="s">
+      <c r="C43" s="10" t="s">
         <v>132</v>
       </c>
       <c r="D43" s="6" t="s">
@@ -3516,7 +3520,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:M102"/>
+  <dimension ref="C3:M112"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="3"/>
@@ -3636,7 +3640,7 @@
     </row>
     <row r="6" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C6" s="3">
-        <v>4001</v>
+        <v>5001</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>135</v>
@@ -3659,6 +3663,7 @@
       <c r="J6" s="3">
         <v>5</v>
       </c>
+      <c r="K6" s="3"/>
       <c r="L6" s="3">
         <v>0</v>
       </c>
@@ -3666,321 +3671,147 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" s="3" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C7" s="3">
-        <v>4002</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="E7" s="3">
-        <v>5</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="G7" s="3">
-        <v>1</v>
-      </c>
-      <c r="H7" s="3">
-        <v>99999999999</v>
-      </c>
-      <c r="I7" s="3">
-        <v>0</v>
-      </c>
-      <c r="J7" s="3">
-        <v>5</v>
-      </c>
-      <c r="L7" s="3">
-        <v>0</v>
-      </c>
-      <c r="M7" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" s="3" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C8" s="3">
-        <v>4003</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="E8" s="3">
-        <v>9</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="G8" s="3">
-        <v>1</v>
-      </c>
-      <c r="H8" s="3">
-        <v>9999999</v>
-      </c>
-      <c r="I8" s="3">
-        <v>0</v>
-      </c>
-      <c r="J8" s="3">
-        <v>5</v>
-      </c>
-      <c r="L8" s="3">
-        <v>0</v>
-      </c>
-      <c r="M8" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" s="3" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C9" s="3">
-        <v>4004</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="E9" s="3">
-        <v>5</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="G9" s="3">
-        <v>1</v>
-      </c>
-      <c r="H9" s="3">
-        <v>9999999</v>
-      </c>
-      <c r="I9" s="3">
-        <v>0</v>
-      </c>
-      <c r="J9" s="3">
-        <v>5</v>
-      </c>
-      <c r="L9" s="3">
-        <v>0</v>
-      </c>
-      <c r="M9" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" s="3" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C10" s="3">
-        <v>4005</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="E10" s="3">
-        <v>5</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="G10" s="3">
-        <v>1</v>
-      </c>
-      <c r="H10" s="3">
-        <v>9999999</v>
-      </c>
-      <c r="I10" s="3">
-        <v>0</v>
-      </c>
-      <c r="J10" s="3">
-        <v>5</v>
-      </c>
-      <c r="L10" s="3">
-        <v>0</v>
-      </c>
-      <c r="M10" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" s="3" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C11" s="3">
-        <v>4006</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="E11" s="3">
-        <v>5</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="G11" s="3">
-        <v>1</v>
-      </c>
-      <c r="H11" s="3">
-        <v>99999999</v>
-      </c>
-      <c r="I11" s="3">
-        <v>0</v>
-      </c>
-      <c r="J11" s="3">
-        <v>5</v>
-      </c>
-      <c r="K11" s="3">
-        <v>50</v>
-      </c>
-      <c r="L11" s="3">
-        <v>0</v>
-      </c>
-      <c r="M11" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" s="3" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C12" s="3">
-        <v>4007</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="E12" s="3">
-        <v>5</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="G12" s="3">
-        <v>1</v>
-      </c>
-      <c r="H12" s="3">
-        <v>9999999999</v>
-      </c>
-      <c r="I12" s="3">
-        <v>0</v>
-      </c>
-      <c r="J12" s="3">
-        <v>5</v>
-      </c>
-      <c r="L12" s="3">
-        <v>0</v>
-      </c>
-      <c r="M12" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" s="3" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C13" s="3">
-        <v>4008</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="E13" s="3">
-        <v>5</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="G13" s="3">
-        <v>1</v>
-      </c>
-      <c r="H13" s="3">
-        <v>9999999</v>
-      </c>
-      <c r="I13" s="3">
-        <v>0</v>
-      </c>
-      <c r="J13" s="3">
-        <v>5</v>
-      </c>
-      <c r="L13" s="3">
-        <v>0</v>
-      </c>
-      <c r="M13" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" s="3" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C14" s="3">
-        <v>4009</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="E14" s="3">
-        <v>5</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="G14" s="3">
-        <v>1</v>
-      </c>
-      <c r="H14" s="3">
-        <v>9999999</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>5</v>
-      </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" s="3" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C15" s="3">
-        <v>4010</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="E15" s="3">
-        <v>5</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="G15" s="3">
-        <v>1</v>
-      </c>
-      <c r="H15" s="3">
-        <v>9999999</v>
-      </c>
-      <c r="I15" s="3">
-        <v>0</v>
-      </c>
-      <c r="J15" s="3">
-        <v>5</v>
-      </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
-      <c r="M15" s="3">
-        <v>0</v>
-      </c>
+    <row r="7" s="7" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C7" s="8"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="8"/>
+      <c r="I7" s="8"/>
+      <c r="J7" s="8"/>
+      <c r="K7" s="8"/>
+      <c r="L7" s="8"/>
+      <c r="M7" s="8"/>
+    </row>
+    <row r="8" s="7" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="8"/>
+      <c r="I8" s="8"/>
+      <c r="J8" s="8"/>
+      <c r="K8" s="8"/>
+      <c r="L8" s="8"/>
+      <c r="M8" s="8"/>
+    </row>
+    <row r="9" s="7" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="8"/>
+      <c r="H9" s="8"/>
+      <c r="I9" s="8"/>
+      <c r="J9" s="8"/>
+      <c r="K9" s="8"/>
+      <c r="L9" s="8"/>
+      <c r="M9" s="8"/>
+    </row>
+    <row r="10" s="7" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C10" s="8"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="8"/>
+      <c r="G10" s="8"/>
+      <c r="H10" s="8"/>
+      <c r="I10" s="8"/>
+      <c r="J10" s="8"/>
+      <c r="K10" s="8"/>
+      <c r="L10" s="8"/>
+      <c r="M10" s="8"/>
+    </row>
+    <row r="11" s="7" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="8"/>
+      <c r="H11" s="8"/>
+      <c r="I11" s="8"/>
+      <c r="J11" s="8"/>
+      <c r="K11" s="8"/>
+      <c r="L11" s="8"/>
+      <c r="M11" s="8"/>
+    </row>
+    <row r="12" s="7" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="8"/>
+      <c r="G12" s="8"/>
+      <c r="H12" s="8"/>
+      <c r="I12" s="8"/>
+      <c r="J12" s="8"/>
+      <c r="K12" s="8"/>
+      <c r="L12" s="8"/>
+      <c r="M12" s="8"/>
+    </row>
+    <row r="13" s="7" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="8"/>
+      <c r="G13" s="8"/>
+      <c r="H13" s="8"/>
+      <c r="I13" s="8"/>
+      <c r="J13" s="8"/>
+      <c r="K13" s="8"/>
+      <c r="L13" s="8"/>
+      <c r="M13" s="8"/>
+    </row>
+    <row r="14" s="7" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C14" s="8"/>
+      <c r="D14" s="8"/>
+      <c r="E14" s="8"/>
+      <c r="F14" s="8"/>
+      <c r="G14" s="8"/>
+      <c r="H14" s="8"/>
+      <c r="I14" s="8"/>
+      <c r="J14" s="8"/>
+      <c r="K14" s="8"/>
+      <c r="L14" s="8"/>
+      <c r="M14" s="8"/>
+    </row>
+    <row r="15" s="7" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C15" s="8"/>
+      <c r="D15" s="8"/>
+      <c r="E15" s="8"/>
+      <c r="F15" s="8"/>
+      <c r="G15" s="8"/>
+      <c r="H15" s="8"/>
+      <c r="I15" s="8"/>
+      <c r="J15" s="8"/>
+      <c r="K15" s="8"/>
+      <c r="L15" s="8"/>
+      <c r="M15" s="8"/>
     </row>
     <row r="16" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C16" s="3">
-        <v>4011</v>
+        <v>4001</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>155</v>
+        <v>137</v>
       </c>
       <c r="E16" s="3">
         <v>5</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>156</v>
+        <v>138</v>
       </c>
       <c r="G16" s="3">
         <v>1</v>
       </c>
       <c r="H16" s="3">
-        <v>9999999</v>
+        <v>99999999999</v>
       </c>
       <c r="I16" s="3">
         <v>0</v>
       </c>
       <c r="J16" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L16" s="3">
         <v>0</v>
@@ -3991,28 +3822,28 @@
     </row>
     <row r="17" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C17" s="3">
-        <v>4012</v>
+        <v>4002</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>157</v>
+        <v>135</v>
       </c>
       <c r="E17" s="3">
         <v>5</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>158</v>
+        <v>136</v>
       </c>
       <c r="G17" s="3">
         <v>1</v>
       </c>
       <c r="H17" s="3">
-        <v>9999999</v>
+        <v>99999999999</v>
       </c>
       <c r="I17" s="3">
         <v>0</v>
       </c>
       <c r="J17" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L17" s="3">
         <v>0</v>
@@ -4023,16 +3854,16 @@
     </row>
     <row r="18" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C18" s="3">
-        <v>4013</v>
+        <v>4003</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>159</v>
+        <v>139</v>
       </c>
       <c r="E18" s="3">
         <v>9</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="G18" s="3">
         <v>1</v>
@@ -4055,16 +3886,16 @@
     </row>
     <row r="19" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C19" s="3">
-        <v>4014</v>
+        <v>4004</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>161</v>
+        <v>141</v>
       </c>
       <c r="E19" s="3">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>162</v>
+        <v>142</v>
       </c>
       <c r="G19" s="3">
         <v>1</v>
@@ -4076,7 +3907,7 @@
         <v>0</v>
       </c>
       <c r="J19" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L19" s="3">
         <v>0</v>
@@ -4087,16 +3918,16 @@
     </row>
     <row r="20" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C20" s="3">
-        <v>4015</v>
+        <v>4005</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>163</v>
+        <v>143</v>
       </c>
       <c r="E20" s="3">
         <v>5</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>164</v>
+        <v>144</v>
       </c>
       <c r="G20" s="3">
         <v>1</v>
@@ -4108,7 +3939,7 @@
         <v>0</v>
       </c>
       <c r="J20" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L20" s="3">
         <v>0</v>
@@ -4119,28 +3950,31 @@
     </row>
     <row r="21" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C21" s="3">
-        <v>4016</v>
+        <v>4006</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>165</v>
+        <v>145</v>
       </c>
       <c r="E21" s="3">
         <v>5</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>166</v>
+        <v>146</v>
       </c>
       <c r="G21" s="3">
         <v>1</v>
       </c>
       <c r="H21" s="3">
-        <v>9999999</v>
+        <v>99999999</v>
       </c>
       <c r="I21" s="3">
         <v>0</v>
       </c>
       <c r="J21" s="3">
-        <v>6</v>
+        <v>5</v>
+      </c>
+      <c r="K21" s="3">
+        <v>50</v>
       </c>
       <c r="L21" s="3">
         <v>0</v>
@@ -4151,22 +3985,22 @@
     </row>
     <row r="22" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C22" s="3">
-        <v>4017</v>
+        <v>4007</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>167</v>
+        <v>147</v>
       </c>
       <c r="E22" s="3">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>168</v>
+        <v>148</v>
       </c>
       <c r="G22" s="3">
         <v>1</v>
       </c>
       <c r="H22" s="3">
-        <v>9999999</v>
+        <v>9999999999</v>
       </c>
       <c r="I22" s="3">
         <v>0</v>
@@ -4183,16 +4017,16 @@
     </row>
     <row r="23" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C23" s="3">
-        <v>4018</v>
+        <v>4008</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>169</v>
+        <v>149</v>
       </c>
       <c r="E23" s="3">
         <v>5</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="G23" s="3">
         <v>1</v>
@@ -4204,7 +4038,7 @@
         <v>0</v>
       </c>
       <c r="J23" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L23" s="3">
         <v>0</v>
@@ -4215,16 +4049,16 @@
     </row>
     <row r="24" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C24" s="3">
-        <v>4019</v>
+        <v>4009</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>171</v>
+        <v>151</v>
       </c>
       <c r="E24" s="3">
         <v>5</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>172</v>
+        <v>152</v>
       </c>
       <c r="G24" s="3">
         <v>1</v>
@@ -4236,7 +4070,7 @@
         <v>0</v>
       </c>
       <c r="J24" s="3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L24" s="3">
         <v>0</v>
@@ -4247,16 +4081,16 @@
     </row>
     <row r="25" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C25" s="3">
-        <v>4020</v>
+        <v>4010</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>173</v>
+        <v>153</v>
       </c>
       <c r="E25" s="3">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>174</v>
+        <v>154</v>
       </c>
       <c r="G25" s="3">
         <v>1</v>
@@ -4268,10 +4102,7 @@
         <v>0</v>
       </c>
       <c r="J25" s="3">
-        <v>7</v>
-      </c>
-      <c r="K25" s="3">
-        <v>500</v>
+        <v>5</v>
       </c>
       <c r="L25" s="3">
         <v>0</v>
@@ -4282,16 +4113,16 @@
     </row>
     <row r="26" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C26" s="3">
-        <v>4021</v>
+        <v>4011</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>175</v>
+        <v>155</v>
       </c>
       <c r="E26" s="3">
         <v>5</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>176</v>
+        <v>156</v>
       </c>
       <c r="G26" s="3">
         <v>1</v>
@@ -4314,16 +4145,16 @@
     </row>
     <row r="27" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C27" s="3">
-        <v>4022</v>
+        <v>4012</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>177</v>
+        <v>157</v>
       </c>
       <c r="E27" s="3">
         <v>5</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>178</v>
+        <v>158</v>
       </c>
       <c r="G27" s="3">
         <v>1</v>
@@ -4335,7 +4166,7 @@
         <v>0</v>
       </c>
       <c r="J27" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L27" s="3">
         <v>0</v>
@@ -4346,16 +4177,16 @@
     </row>
     <row r="28" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C28" s="3">
-        <v>4023</v>
+        <v>4013</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>179</v>
+        <v>159</v>
       </c>
       <c r="E28" s="3">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="G28" s="3">
         <v>1</v>
@@ -4378,16 +4209,16 @@
     </row>
     <row r="29" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C29" s="3">
-        <v>4024</v>
+        <v>4014</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>181</v>
+        <v>161</v>
       </c>
       <c r="E29" s="3">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>182</v>
+        <v>162</v>
       </c>
       <c r="G29" s="3">
         <v>1</v>
@@ -4410,16 +4241,16 @@
     </row>
     <row r="30" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C30" s="3">
-        <v>4025</v>
+        <v>4015</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>183</v>
+        <v>163</v>
       </c>
       <c r="E30" s="3">
         <v>5</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>184</v>
+        <v>164</v>
       </c>
       <c r="G30" s="3">
         <v>1</v>
@@ -4431,7 +4262,7 @@
         <v>0</v>
       </c>
       <c r="J30" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L30" s="3">
         <v>0</v>
@@ -4442,16 +4273,16 @@
     </row>
     <row r="31" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C31" s="3">
-        <v>4026</v>
+        <v>4016</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>185</v>
+        <v>165</v>
       </c>
       <c r="E31" s="3">
         <v>5</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>186</v>
+        <v>166</v>
       </c>
       <c r="G31" s="3">
         <v>1</v>
@@ -4463,7 +4294,7 @@
         <v>0</v>
       </c>
       <c r="J31" s="3">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L31" s="3">
         <v>0</v>
@@ -4474,16 +4305,16 @@
     </row>
     <row r="32" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C32" s="3">
-        <v>4027</v>
+        <v>4017</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>187</v>
+        <v>167</v>
       </c>
       <c r="E32" s="3">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>188</v>
+        <v>168</v>
       </c>
       <c r="G32" s="3">
         <v>1</v>
@@ -4495,7 +4326,7 @@
         <v>0</v>
       </c>
       <c r="J32" s="3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L32" s="3">
         <v>0</v>
@@ -4506,16 +4337,16 @@
     </row>
     <row r="33" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C33" s="3">
-        <v>4028</v>
+        <v>4018</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="E33" s="3">
         <v>5</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>190</v>
+        <v>170</v>
       </c>
       <c r="G33" s="3">
         <v>1</v>
@@ -4527,7 +4358,7 @@
         <v>0</v>
       </c>
       <c r="J33" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L33" s="3">
         <v>0</v>
@@ -4538,16 +4369,16 @@
     </row>
     <row r="34" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C34" s="3">
-        <v>4029</v>
+        <v>4019</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>191</v>
+        <v>171</v>
       </c>
       <c r="E34" s="3">
         <v>5</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>192</v>
+        <v>172</v>
       </c>
       <c r="G34" s="3">
         <v>1</v>
@@ -4570,16 +4401,16 @@
     </row>
     <row r="35" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C35" s="3">
-        <v>4030</v>
+        <v>4020</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>193</v>
+        <v>173</v>
       </c>
       <c r="E35" s="3">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>194</v>
+        <v>174</v>
       </c>
       <c r="G35" s="3">
         <v>1</v>
@@ -4593,6 +4424,9 @@
       <c r="J35" s="3">
         <v>7</v>
       </c>
+      <c r="K35" s="3">
+        <v>500</v>
+      </c>
       <c r="L35" s="3">
         <v>0</v>
       </c>
@@ -4602,16 +4436,16 @@
     </row>
     <row r="36" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C36" s="3">
-        <v>4031</v>
+        <v>4021</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>195</v>
+        <v>175</v>
       </c>
       <c r="E36" s="3">
         <v>5</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>196</v>
+        <v>176</v>
       </c>
       <c r="G36" s="3">
         <v>1</v>
@@ -4623,7 +4457,7 @@
         <v>0</v>
       </c>
       <c r="J36" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L36" s="3">
         <v>0</v>
@@ -4634,16 +4468,16 @@
     </row>
     <row r="37" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C37" s="3">
-        <v>4032</v>
+        <v>4022</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>197</v>
+        <v>177</v>
       </c>
       <c r="E37" s="3">
         <v>5</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>198</v>
+        <v>178</v>
       </c>
       <c r="G37" s="3">
         <v>1</v>
@@ -4655,7 +4489,7 @@
         <v>0</v>
       </c>
       <c r="J37" s="3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L37" s="3">
         <v>0</v>
@@ -4666,16 +4500,16 @@
     </row>
     <row r="38" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C38" s="3">
-        <v>4033</v>
+        <v>4023</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>199</v>
+        <v>179</v>
       </c>
       <c r="E38" s="3">
         <v>5</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>166</v>
+        <v>180</v>
       </c>
       <c r="G38" s="3">
         <v>1</v>
@@ -4687,7 +4521,7 @@
         <v>0</v>
       </c>
       <c r="J38" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L38" s="3">
         <v>0</v>
@@ -4698,16 +4532,16 @@
     </row>
     <row r="39" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C39" s="3">
-        <v>4034</v>
+        <v>4024</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>200</v>
+        <v>181</v>
       </c>
       <c r="E39" s="3">
         <v>5</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>201</v>
+        <v>182</v>
       </c>
       <c r="G39" s="3">
         <v>1</v>
@@ -4719,7 +4553,7 @@
         <v>0</v>
       </c>
       <c r="J39" s="3">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L39" s="3">
         <v>0</v>
@@ -4730,16 +4564,16 @@
     </row>
     <row r="40" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C40" s="3">
-        <v>4035</v>
+        <v>4025</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>202</v>
+        <v>183</v>
       </c>
       <c r="E40" s="3">
         <v>5</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>203</v>
+        <v>184</v>
       </c>
       <c r="G40" s="3">
         <v>1</v>
@@ -4762,16 +4596,16 @@
     </row>
     <row r="41" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C41" s="3">
-        <v>4037</v>
+        <v>4026</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>204</v>
+        <v>185</v>
       </c>
       <c r="E41" s="3">
         <v>5</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>205</v>
+        <v>186</v>
       </c>
       <c r="G41" s="3">
         <v>1</v>
@@ -4783,7 +4617,7 @@
         <v>0</v>
       </c>
       <c r="J41" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L41" s="3">
         <v>0</v>
@@ -4794,16 +4628,16 @@
     </row>
     <row r="42" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C42" s="3">
-        <v>4038</v>
+        <v>4027</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>206</v>
+        <v>187</v>
       </c>
       <c r="E42" s="3">
         <v>5</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>207</v>
+        <v>188</v>
       </c>
       <c r="G42" s="3">
         <v>1</v>
@@ -4815,7 +4649,7 @@
         <v>0</v>
       </c>
       <c r="J42" s="3">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L42" s="3">
         <v>0</v>
@@ -4826,16 +4660,16 @@
     </row>
     <row r="43" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C43" s="3">
-        <v>4039</v>
+        <v>4028</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>208</v>
+        <v>189</v>
       </c>
       <c r="E43" s="3">
         <v>5</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>209</v>
+        <v>190</v>
       </c>
       <c r="G43" s="3">
         <v>1</v>
@@ -4847,7 +4681,7 @@
         <v>0</v>
       </c>
       <c r="J43" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L43" s="3">
         <v>0</v>
@@ -4858,16 +4692,16 @@
     </row>
     <row r="44" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C44" s="3">
-        <v>4040</v>
+        <v>4029</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>210</v>
+        <v>191</v>
       </c>
       <c r="E44" s="3">
         <v>5</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>166</v>
+        <v>192</v>
       </c>
       <c r="G44" s="3">
         <v>1</v>
@@ -4879,7 +4713,7 @@
         <v>0</v>
       </c>
       <c r="J44" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -4890,16 +4724,16 @@
     </row>
     <row r="45" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C45" s="3">
-        <v>4041</v>
+        <v>4030</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>211</v>
+        <v>193</v>
       </c>
       <c r="E45" s="3">
         <v>5</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>212</v>
+        <v>194</v>
       </c>
       <c r="G45" s="3">
         <v>1</v>
@@ -4911,7 +4745,7 @@
         <v>0</v>
       </c>
       <c r="J45" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L45" s="3">
         <v>0</v>
@@ -4922,28 +4756,28 @@
     </row>
     <row r="46" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C46" s="3">
-        <v>4042</v>
+        <v>4031</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>213</v>
+        <v>195</v>
       </c>
       <c r="E46" s="3">
         <v>5</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>214</v>
+        <v>196</v>
       </c>
       <c r="G46" s="3">
         <v>1</v>
       </c>
       <c r="H46" s="3">
-        <v>1999999999</v>
+        <v>9999999</v>
       </c>
       <c r="I46" s="3">
         <v>0</v>
       </c>
       <c r="J46" s="3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L46" s="3">
         <v>0</v>
@@ -4954,16 +4788,16 @@
     </row>
     <row r="47" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C47" s="3">
-        <v>4043</v>
+        <v>4032</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>215</v>
+        <v>197</v>
       </c>
       <c r="E47" s="3">
         <v>5</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>214</v>
+        <v>198</v>
       </c>
       <c r="G47" s="3">
         <v>1</v>
@@ -4986,16 +4820,16 @@
     </row>
     <row r="48" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C48" s="3">
-        <v>4044</v>
+        <v>4033</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>216</v>
+        <v>199</v>
       </c>
       <c r="E48" s="3">
         <v>5</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>217</v>
+        <v>166</v>
       </c>
       <c r="G48" s="3">
         <v>1</v>
@@ -5007,7 +4841,7 @@
         <v>0</v>
       </c>
       <c r="J48" s="3">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="L48" s="3">
         <v>0</v>
@@ -5016,30 +4850,50 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C49" s="3"/>
-      <c r="D49" s="3"/>
-      <c r="E49" s="3"/>
-      <c r="F49" s="3"/>
-      <c r="G49" s="3"/>
-      <c r="H49" s="3"/>
-      <c r="I49" s="3"/>
-      <c r="J49" s="3"/>
-      <c r="L49" s="3"/>
-      <c r="M49" s="3"/>
+    <row r="49" s="3" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C49" s="3">
+        <v>4034</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="E49" s="3">
+        <v>5</v>
+      </c>
+      <c r="F49" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="G49" s="3">
+        <v>1</v>
+      </c>
+      <c r="H49" s="3">
+        <v>9999999</v>
+      </c>
+      <c r="I49" s="3">
+        <v>0</v>
+      </c>
+      <c r="J49" s="3">
+        <v>8</v>
+      </c>
+      <c r="L49" s="3">
+        <v>0</v>
+      </c>
+      <c r="M49" s="3">
+        <v>0</v>
+      </c>
     </row>
     <row r="50" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C50" s="3">
-        <v>4101</v>
+        <v>4035</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>218</v>
+        <v>202</v>
       </c>
       <c r="E50" s="3">
         <v>5</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>219</v>
+        <v>203</v>
       </c>
       <c r="G50" s="3">
         <v>1</v>
@@ -5051,7 +4905,7 @@
         <v>0</v>
       </c>
       <c r="J50" s="3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L50" s="3">
         <v>0</v>
@@ -5062,16 +4916,16 @@
     </row>
     <row r="51" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C51" s="3">
-        <v>4111</v>
+        <v>4037</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>220</v>
+        <v>204</v>
       </c>
       <c r="E51" s="3">
         <v>5</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>221</v>
+        <v>205</v>
       </c>
       <c r="G51" s="3">
         <v>1</v>
@@ -5083,7 +4937,7 @@
         <v>0</v>
       </c>
       <c r="J51" s="3">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L51" s="3">
         <v>0</v>
@@ -5094,16 +4948,16 @@
     </row>
     <row r="52" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C52" s="3">
-        <v>4112</v>
+        <v>4038</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>222</v>
+        <v>206</v>
       </c>
       <c r="E52" s="3">
         <v>5</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>223</v>
+        <v>207</v>
       </c>
       <c r="G52" s="3">
         <v>1</v>
@@ -5115,7 +4969,7 @@
         <v>0</v>
       </c>
       <c r="J52" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L52" s="3">
         <v>0</v>
@@ -5126,16 +4980,16 @@
     </row>
     <row r="53" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C53" s="3">
-        <v>4113</v>
+        <v>4039</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>224</v>
+        <v>208</v>
       </c>
       <c r="E53" s="3">
         <v>5</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>225</v>
+        <v>209</v>
       </c>
       <c r="G53" s="3">
         <v>1</v>
@@ -5147,7 +5001,7 @@
         <v>0</v>
       </c>
       <c r="J53" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L53" s="3">
         <v>0</v>
@@ -5156,62 +5010,190 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C54" s="3"/>
-      <c r="D54" s="3"/>
-      <c r="E54" s="3"/>
-      <c r="F54" s="3"/>
-      <c r="G54" s="3"/>
-      <c r="H54" s="3"/>
-      <c r="I54" s="3"/>
-      <c r="J54" s="3"/>
-      <c r="L54" s="3"/>
-      <c r="M54" s="3"/>
+    <row r="54" s="3" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C54" s="3">
+        <v>4040</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="E54" s="3">
+        <v>5</v>
+      </c>
+      <c r="F54" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="G54" s="3">
+        <v>1</v>
+      </c>
+      <c r="H54" s="3">
+        <v>9999999</v>
+      </c>
+      <c r="I54" s="3">
+        <v>0</v>
+      </c>
+      <c r="J54" s="3">
+        <v>6</v>
+      </c>
+      <c r="L54" s="3">
+        <v>0</v>
+      </c>
+      <c r="M54" s="3">
+        <v>0</v>
+      </c>
     </row>
     <row r="55" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C55" s="3">
-        <v>4201</v>
+        <v>4041</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="E55" s="3">
         <v>5</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>227</v>
+        <v>212</v>
       </c>
       <c r="G55" s="3">
         <v>1</v>
       </c>
       <c r="H55" s="3">
-        <v>99999999</v>
+        <v>9999999</v>
       </c>
       <c r="I55" s="3">
         <v>0</v>
       </c>
       <c r="J55" s="3">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="L55" s="3">
-        <v>4002</v>
+        <v>0</v>
       </c>
       <c r="M55" s="3">
-        <v>1000</v>
-      </c>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" s="3" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C56" s="3">
+        <v>4042</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="E56" s="3">
+        <v>5</v>
+      </c>
+      <c r="F56" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="G56" s="3">
+        <v>1</v>
+      </c>
+      <c r="H56" s="3">
+        <v>1999999999</v>
+      </c>
+      <c r="I56" s="3">
+        <v>0</v>
+      </c>
+      <c r="J56" s="3">
+        <v>5</v>
+      </c>
+      <c r="L56" s="3">
+        <v>0</v>
+      </c>
+      <c r="M56" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" s="3" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C57" s="3">
+        <v>4043</v>
+      </c>
+      <c r="D57" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="E57" s="3">
+        <v>5</v>
+      </c>
+      <c r="F57" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="G57" s="3">
+        <v>1</v>
+      </c>
+      <c r="H57" s="3">
+        <v>9999999</v>
+      </c>
+      <c r="I57" s="3">
+        <v>0</v>
+      </c>
+      <c r="J57" s="3">
+        <v>7</v>
+      </c>
+      <c r="L57" s="3">
+        <v>0</v>
+      </c>
+      <c r="M57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" s="3" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C58" s="3">
+        <v>4044</v>
+      </c>
+      <c r="D58" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="E58" s="3">
+        <v>5</v>
+      </c>
+      <c r="F58" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="G58" s="3">
+        <v>1</v>
+      </c>
+      <c r="H58" s="3">
+        <v>9999999</v>
+      </c>
+      <c r="I58" s="3">
+        <v>0</v>
+      </c>
+      <c r="J58" s="3">
+        <v>9</v>
+      </c>
+      <c r="L58" s="3">
+        <v>0</v>
+      </c>
+      <c r="M58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C59" s="3"/>
+      <c r="D59" s="3"/>
+      <c r="E59" s="3"/>
+      <c r="F59" s="3"/>
+      <c r="G59" s="3"/>
+      <c r="H59" s="3"/>
+      <c r="I59" s="3"/>
+      <c r="J59" s="3"/>
+      <c r="L59" s="3"/>
+      <c r="M59" s="3"/>
     </row>
     <row r="60" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C60" s="3">
-        <v>8001</v>
+        <v>4101</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>228</v>
+        <v>218</v>
       </c>
       <c r="E60" s="3">
         <v>5</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
       <c r="G60" s="3">
         <v>1</v>
@@ -5223,7 +5205,7 @@
         <v>0</v>
       </c>
       <c r="J60" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L60" s="3">
         <v>0</v>
@@ -5234,16 +5216,16 @@
     </row>
     <row r="61" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C61" s="3">
-        <v>8002</v>
+        <v>4111</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="E61" s="3">
         <v>5</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="G61" s="3">
         <v>1</v>
@@ -5255,7 +5237,7 @@
         <v>0</v>
       </c>
       <c r="J61" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L61" s="3">
         <v>0</v>
@@ -5266,16 +5248,16 @@
     </row>
     <row r="62" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C62" s="3">
-        <v>8003</v>
+        <v>4112</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>231</v>
+        <v>222</v>
       </c>
       <c r="E62" s="3">
         <v>5</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="G62" s="3">
         <v>1</v>
@@ -5287,7 +5269,7 @@
         <v>0</v>
       </c>
       <c r="J62" s="3">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L62" s="3">
         <v>0</v>
@@ -5298,16 +5280,16 @@
     </row>
     <row r="63" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C63" s="3">
-        <v>8004</v>
+        <v>4113</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="E63" s="3">
         <v>5</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="G63" s="3">
         <v>1</v>
@@ -5319,7 +5301,7 @@
         <v>0</v>
       </c>
       <c r="J63" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L63" s="3">
         <v>0</v>
@@ -5328,210 +5310,94 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" s="3" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C64" s="3">
-        <v>8005</v>
-      </c>
-      <c r="D64" s="3" t="s">
-        <v>233</v>
-      </c>
-      <c r="E64" s="3">
-        <v>5</v>
-      </c>
-      <c r="F64" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="G64" s="3">
-        <v>1</v>
-      </c>
-      <c r="H64" s="3">
-        <v>9999999</v>
-      </c>
-      <c r="I64" s="3">
-        <v>0</v>
-      </c>
-      <c r="J64" s="3">
-        <v>6</v>
-      </c>
-      <c r="L64" s="3">
-        <v>0</v>
-      </c>
-      <c r="M64" s="3">
-        <v>0</v>
-      </c>
+    <row r="64" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C64" s="3"/>
+      <c r="D64" s="3"/>
+      <c r="E64" s="3"/>
+      <c r="F64" s="3"/>
+      <c r="G64" s="3"/>
+      <c r="H64" s="3"/>
+      <c r="I64" s="3"/>
+      <c r="J64" s="3"/>
+      <c r="L64" s="3"/>
+      <c r="M64" s="3"/>
     </row>
     <row r="65" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C65" s="3">
-        <v>8006</v>
+        <v>4201</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="E65" s="3">
         <v>5</v>
       </c>
       <c r="F65" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="G65" s="3">
+        <v>1</v>
+      </c>
+      <c r="H65" s="3">
+        <v>99999999</v>
+      </c>
+      <c r="I65" s="3">
+        <v>0</v>
+      </c>
+      <c r="J65" s="3">
+        <v>5</v>
+      </c>
+      <c r="L65" s="3">
+        <v>4002</v>
+      </c>
+      <c r="M65" s="3">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="70" s="3" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C70" s="3">
+        <v>8001</v>
+      </c>
+      <c r="D70" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="E70" s="3">
+        <v>5</v>
+      </c>
+      <c r="F70" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="G65" s="3">
-        <v>1</v>
-      </c>
-      <c r="H65" s="3">
+      <c r="G70" s="3">
+        <v>1</v>
+      </c>
+      <c r="H70" s="3">
         <v>9999999</v>
       </c>
-      <c r="I65" s="3">
-        <v>0</v>
-      </c>
-      <c r="J65" s="3">
+      <c r="I70" s="3">
+        <v>0</v>
+      </c>
+      <c r="J70" s="3">
         <v>6</v>
       </c>
-      <c r="L65" s="3">
-        <v>0</v>
-      </c>
-      <c r="M65" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" s="3" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C66" s="3">
-        <v>8007</v>
-      </c>
-      <c r="D66" s="3" t="s">
-        <v>235</v>
-      </c>
-      <c r="E66" s="3">
-        <v>5</v>
-      </c>
-      <c r="F66" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="G66" s="3">
-        <v>1</v>
-      </c>
-      <c r="H66" s="3">
-        <v>9999999</v>
-      </c>
-      <c r="I66" s="3">
-        <v>0</v>
-      </c>
-      <c r="J66" s="3">
-        <v>6</v>
-      </c>
-      <c r="L66" s="3">
-        <v>0</v>
-      </c>
-      <c r="M66" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" s="3" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C67" s="3">
-        <v>8008</v>
-      </c>
-      <c r="D67" s="3" t="s">
-        <v>236</v>
-      </c>
-      <c r="E67" s="3">
-        <v>5</v>
-      </c>
-      <c r="F67" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="G67" s="3">
-        <v>1</v>
-      </c>
-      <c r="H67" s="3">
-        <v>9999999</v>
-      </c>
-      <c r="I67" s="3">
-        <v>0</v>
-      </c>
-      <c r="J67" s="3">
-        <v>6</v>
-      </c>
-      <c r="L67" s="3">
-        <v>0</v>
-      </c>
-      <c r="M67" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" s="3" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C68" s="3">
-        <v>8009</v>
-      </c>
-      <c r="D68" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="E68" s="3">
-        <v>5</v>
-      </c>
-      <c r="F68" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="G68" s="3">
-        <v>1</v>
-      </c>
-      <c r="H68" s="3">
-        <v>9999999</v>
-      </c>
-      <c r="I68" s="3">
-        <v>0</v>
-      </c>
-      <c r="J68" s="3">
-        <v>6</v>
-      </c>
-      <c r="L68" s="3">
-        <v>0</v>
-      </c>
-      <c r="M68" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" s="3" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C69" s="3">
-        <v>8010</v>
-      </c>
-      <c r="D69" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="E69" s="3">
-        <v>5</v>
-      </c>
-      <c r="F69" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="G69" s="3">
-        <v>1</v>
-      </c>
-      <c r="H69" s="3">
-        <v>9999999</v>
-      </c>
-      <c r="I69" s="3">
-        <v>0</v>
-      </c>
-      <c r="J69" s="3">
-        <v>6</v>
-      </c>
-      <c r="L69" s="3">
-        <v>0</v>
-      </c>
-      <c r="M69" s="3">
+      <c r="L70" s="3">
+        <v>0</v>
+      </c>
+      <c r="M70" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="71" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C71" s="3">
-        <v>8101</v>
-      </c>
-      <c r="D71" s="7" t="s">
-        <v>239</v>
+        <v>8002</v>
+      </c>
+      <c r="D71" s="3" t="s">
+        <v>230</v>
       </c>
       <c r="E71" s="3">
         <v>5</v>
       </c>
       <c r="F71" s="3" t="s">
-        <v>240</v>
+        <v>229</v>
       </c>
       <c r="G71" s="3">
         <v>1</v>
@@ -5543,7 +5409,7 @@
         <v>0</v>
       </c>
       <c r="J71" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L71" s="3">
         <v>0</v>
@@ -5554,16 +5420,16 @@
     </row>
     <row r="72" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C72" s="3">
-        <v>8102</v>
-      </c>
-      <c r="D72" s="7" t="s">
-        <v>241</v>
+        <v>8003</v>
+      </c>
+      <c r="D72" s="3" t="s">
+        <v>231</v>
       </c>
       <c r="E72" s="3">
         <v>5</v>
       </c>
       <c r="F72" s="3" t="s">
-        <v>240</v>
+        <v>229</v>
       </c>
       <c r="G72" s="3">
         <v>1</v>
@@ -5575,7 +5441,7 @@
         <v>0</v>
       </c>
       <c r="J72" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L72" s="3">
         <v>0</v>
@@ -5586,16 +5452,16 @@
     </row>
     <row r="73" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C73" s="3">
-        <v>8103</v>
-      </c>
-      <c r="D73" s="7" t="s">
-        <v>242</v>
+        <v>8004</v>
+      </c>
+      <c r="D73" s="3" t="s">
+        <v>232</v>
       </c>
       <c r="E73" s="3">
         <v>5</v>
       </c>
       <c r="F73" s="3" t="s">
-        <v>240</v>
+        <v>229</v>
       </c>
       <c r="G73" s="3">
         <v>1</v>
@@ -5607,7 +5473,7 @@
         <v>0</v>
       </c>
       <c r="J73" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L73" s="3">
         <v>0</v>
@@ -5618,16 +5484,16 @@
     </row>
     <row r="74" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C74" s="3">
-        <v>8104</v>
-      </c>
-      <c r="D74" s="7" t="s">
-        <v>243</v>
+        <v>8005</v>
+      </c>
+      <c r="D74" s="3" t="s">
+        <v>233</v>
       </c>
       <c r="E74" s="3">
         <v>5</v>
       </c>
       <c r="F74" s="3" t="s">
-        <v>240</v>
+        <v>229</v>
       </c>
       <c r="G74" s="3">
         <v>1</v>
@@ -5639,7 +5505,7 @@
         <v>0</v>
       </c>
       <c r="J74" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L74" s="3">
         <v>0</v>
@@ -5650,16 +5516,16 @@
     </row>
     <row r="75" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C75" s="3">
-        <v>8105</v>
-      </c>
-      <c r="D75" s="7" t="s">
-        <v>244</v>
+        <v>8006</v>
+      </c>
+      <c r="D75" s="3" t="s">
+        <v>234</v>
       </c>
       <c r="E75" s="3">
         <v>5</v>
       </c>
       <c r="F75" s="3" t="s">
-        <v>240</v>
+        <v>229</v>
       </c>
       <c r="G75" s="3">
         <v>1</v>
@@ -5671,7 +5537,7 @@
         <v>0</v>
       </c>
       <c r="J75" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L75" s="3">
         <v>0</v>
@@ -5682,16 +5548,16 @@
     </row>
     <row r="76" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C76" s="3">
-        <v>8106</v>
-      </c>
-      <c r="D76" s="7" t="s">
-        <v>245</v>
+        <v>8007</v>
+      </c>
+      <c r="D76" s="3" t="s">
+        <v>235</v>
       </c>
       <c r="E76" s="3">
         <v>5</v>
       </c>
       <c r="F76" s="3" t="s">
-        <v>240</v>
+        <v>229</v>
       </c>
       <c r="G76" s="3">
         <v>1</v>
@@ -5703,7 +5569,7 @@
         <v>0</v>
       </c>
       <c r="J76" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L76" s="3">
         <v>0</v>
@@ -5714,16 +5580,16 @@
     </row>
     <row r="77" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C77" s="3">
-        <v>8107</v>
-      </c>
-      <c r="D77" s="7" t="s">
-        <v>246</v>
+        <v>8008</v>
+      </c>
+      <c r="D77" s="3" t="s">
+        <v>236</v>
       </c>
       <c r="E77" s="3">
         <v>5</v>
       </c>
       <c r="F77" s="3" t="s">
-        <v>240</v>
+        <v>229</v>
       </c>
       <c r="G77" s="3">
         <v>1</v>
@@ -5735,7 +5601,7 @@
         <v>0</v>
       </c>
       <c r="J77" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L77" s="3">
         <v>0</v>
@@ -5746,16 +5612,16 @@
     </row>
     <row r="78" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C78" s="3">
-        <v>8108</v>
-      </c>
-      <c r="D78" s="7" t="s">
-        <v>247</v>
+        <v>8009</v>
+      </c>
+      <c r="D78" s="3" t="s">
+        <v>237</v>
       </c>
       <c r="E78" s="3">
         <v>5</v>
       </c>
       <c r="F78" s="3" t="s">
-        <v>240</v>
+        <v>229</v>
       </c>
       <c r="G78" s="3">
         <v>1</v>
@@ -5767,78 +5633,72 @@
         <v>0</v>
       </c>
       <c r="J78" s="3">
+        <v>6</v>
+      </c>
+      <c r="L78" s="3">
+        <v>0</v>
+      </c>
+      <c r="M78" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" s="3" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C79" s="3">
+        <v>8010</v>
+      </c>
+      <c r="D79" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="E79" s="3">
+        <v>5</v>
+      </c>
+      <c r="F79" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="G79" s="3">
+        <v>1</v>
+      </c>
+      <c r="H79" s="3">
+        <v>9999999</v>
+      </c>
+      <c r="I79" s="3">
+        <v>0</v>
+      </c>
+      <c r="J79" s="3">
+        <v>6</v>
+      </c>
+      <c r="L79" s="3">
+        <v>0</v>
+      </c>
+      <c r="M79" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" s="3" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C81" s="3">
+        <v>8101</v>
+      </c>
+      <c r="D81" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="E81" s="3">
+        <v>5</v>
+      </c>
+      <c r="F81" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="G81" s="3">
+        <v>1</v>
+      </c>
+      <c r="H81" s="3">
+        <v>9999999</v>
+      </c>
+      <c r="I81" s="3">
+        <v>0</v>
+      </c>
+      <c r="J81" s="3">
         <v>7</v>
       </c>
-      <c r="L78" s="3">
-        <v>0</v>
-      </c>
-      <c r="M78" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80" customHeight="1" spans="3:13">
-      <c r="C80" s="3">
-        <v>8201</v>
-      </c>
-      <c r="D80" s="7" t="s">
-        <v>248</v>
-      </c>
-      <c r="E80" s="3">
-        <v>16</v>
-      </c>
-      <c r="F80" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="G80" s="3">
-        <v>1</v>
-      </c>
-      <c r="H80" s="3">
-        <v>1</v>
-      </c>
-      <c r="I80" s="3">
-        <v>0</v>
-      </c>
-      <c r="J80" s="3">
-        <v>1</v>
-      </c>
-      <c r="K80" s="3">
-        <v>0</v>
-      </c>
-      <c r="L80" s="3">
-        <v>0</v>
-      </c>
-      <c r="M80" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="81" customHeight="1" spans="3:13">
-      <c r="C81" s="3">
-        <v>8202</v>
-      </c>
-      <c r="D81" s="7" t="s">
-        <v>250</v>
-      </c>
-      <c r="E81" s="3">
-        <v>16</v>
-      </c>
-      <c r="F81" s="3" t="s">
-        <v>251</v>
-      </c>
-      <c r="G81" s="3">
-        <v>1</v>
-      </c>
-      <c r="H81" s="3">
-        <v>1</v>
-      </c>
-      <c r="I81" s="3">
-        <v>0</v>
-      </c>
-      <c r="J81" s="3">
-        <v>2</v>
-      </c>
-      <c r="K81" s="3">
-        <v>0</v>
-      </c>
       <c r="L81" s="3">
         <v>0</v>
       </c>
@@ -5846,33 +5706,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" customHeight="1" spans="3:13">
+    <row r="82" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C82" s="3">
-        <v>8203</v>
-      </c>
-      <c r="D82" s="7" t="s">
-        <v>252</v>
+        <v>8102</v>
+      </c>
+      <c r="D82" s="9" t="s">
+        <v>241</v>
       </c>
       <c r="E82" s="3">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="F82" s="3" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="G82" s="3">
         <v>1</v>
       </c>
       <c r="H82" s="3">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="I82" s="3">
         <v>0</v>
       </c>
       <c r="J82" s="3">
-        <v>3</v>
-      </c>
-      <c r="K82" s="3">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L82" s="3">
         <v>0</v>
@@ -5881,33 +5738,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" customHeight="1" spans="3:13">
+    <row r="83" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C83" s="3">
-        <v>8204</v>
-      </c>
-      <c r="D83" s="7" t="s">
-        <v>254</v>
+        <v>8103</v>
+      </c>
+      <c r="D83" s="9" t="s">
+        <v>242</v>
       </c>
       <c r="E83" s="3">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="F83" s="3" t="s">
-        <v>255</v>
+        <v>240</v>
       </c>
       <c r="G83" s="3">
         <v>1</v>
       </c>
       <c r="H83" s="3">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="I83" s="3">
         <v>0</v>
       </c>
       <c r="J83" s="3">
-        <v>4</v>
-      </c>
-      <c r="K83" s="3">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L83" s="3">
         <v>0</v>
@@ -5916,33 +5770,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" customHeight="1" spans="3:13">
+    <row r="84" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C84" s="3">
-        <v>8205</v>
-      </c>
-      <c r="D84" s="7" t="s">
-        <v>256</v>
+        <v>8104</v>
+      </c>
+      <c r="D84" s="9" t="s">
+        <v>243</v>
       </c>
       <c r="E84" s="3">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="F84" s="3" t="s">
-        <v>257</v>
+        <v>240</v>
       </c>
       <c r="G84" s="3">
         <v>1</v>
       </c>
       <c r="H84" s="3">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="I84" s="3">
         <v>0</v>
       </c>
       <c r="J84" s="3">
-        <v>5</v>
-      </c>
-      <c r="K84" s="3">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L84" s="3">
         <v>0</v>
@@ -5951,33 +5802,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" customHeight="1" spans="3:13">
+    <row r="85" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C85" s="3">
-        <v>8206</v>
-      </c>
-      <c r="D85" s="7" t="s">
-        <v>258</v>
+        <v>8105</v>
+      </c>
+      <c r="D85" s="9" t="s">
+        <v>244</v>
       </c>
       <c r="E85" s="3">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="F85" s="3" t="s">
-        <v>259</v>
+        <v>240</v>
       </c>
       <c r="G85" s="3">
         <v>1</v>
       </c>
       <c r="H85" s="3">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="I85" s="3">
         <v>0</v>
       </c>
       <c r="J85" s="3">
-        <v>6</v>
-      </c>
-      <c r="K85" s="3">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L85" s="3">
         <v>0</v>
@@ -5986,24 +5834,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" customHeight="1" spans="3:13">
+    <row r="86" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C86" s="3">
-        <v>8207</v>
-      </c>
-      <c r="D86" s="7" t="s">
-        <v>260</v>
+        <v>8106</v>
+      </c>
+      <c r="D86" s="9" t="s">
+        <v>245</v>
       </c>
       <c r="E86" s="3">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="F86" s="3" t="s">
-        <v>261</v>
+        <v>240</v>
       </c>
       <c r="G86" s="3">
         <v>1</v>
       </c>
       <c r="H86" s="3">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="I86" s="3">
         <v>0</v>
@@ -6011,9 +5859,6 @@
       <c r="J86" s="3">
         <v>7</v>
       </c>
-      <c r="K86" s="3">
-        <v>0</v>
-      </c>
       <c r="L86" s="3">
         <v>0</v>
       </c>
@@ -6021,54 +5866,363 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" customHeight="1" spans="3:13">
-      <c r="D88" s="7"/>
-    </row>
-    <row r="89" customHeight="1" spans="3:13">
-      <c r="D89" s="7"/>
+    <row r="87" s="3" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C87" s="3">
+        <v>8107</v>
+      </c>
+      <c r="D87" s="9" t="s">
+        <v>246</v>
+      </c>
+      <c r="E87" s="3">
+        <v>5</v>
+      </c>
+      <c r="F87" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="G87" s="3">
+        <v>1</v>
+      </c>
+      <c r="H87" s="3">
+        <v>9999999</v>
+      </c>
+      <c r="I87" s="3">
+        <v>0</v>
+      </c>
+      <c r="J87" s="3">
+        <v>7</v>
+      </c>
+      <c r="L87" s="3">
+        <v>0</v>
+      </c>
+      <c r="M87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" s="3" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C88" s="3">
+        <v>8108</v>
+      </c>
+      <c r="D88" s="9" t="s">
+        <v>247</v>
+      </c>
+      <c r="E88" s="3">
+        <v>5</v>
+      </c>
+      <c r="F88" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="G88" s="3">
+        <v>1</v>
+      </c>
+      <c r="H88" s="3">
+        <v>9999999</v>
+      </c>
+      <c r="I88" s="3">
+        <v>0</v>
+      </c>
+      <c r="J88" s="3">
+        <v>7</v>
+      </c>
+      <c r="L88" s="3">
+        <v>0</v>
+      </c>
+      <c r="M88" s="3">
+        <v>0</v>
+      </c>
     </row>
     <row r="90" customHeight="1" spans="3:13">
-      <c r="D90" s="7"/>
+      <c r="C90" s="3">
+        <v>8201</v>
+      </c>
+      <c r="D90" s="9" t="s">
+        <v>248</v>
+      </c>
+      <c r="E90" s="3">
+        <v>16</v>
+      </c>
+      <c r="F90" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="G90" s="3">
+        <v>1</v>
+      </c>
+      <c r="H90" s="3">
+        <v>1</v>
+      </c>
+      <c r="I90" s="3">
+        <v>0</v>
+      </c>
+      <c r="J90" s="3">
+        <v>1</v>
+      </c>
+      <c r="K90" s="3">
+        <v>0</v>
+      </c>
+      <c r="L90" s="3">
+        <v>0</v>
+      </c>
+      <c r="M90" s="3">
+        <v>0</v>
+      </c>
     </row>
     <row r="91" customHeight="1" spans="3:13">
-      <c r="D91" s="7"/>
+      <c r="C91" s="3">
+        <v>8202</v>
+      </c>
+      <c r="D91" s="9" t="s">
+        <v>250</v>
+      </c>
+      <c r="E91" s="3">
+        <v>16</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="G91" s="3">
+        <v>1</v>
+      </c>
+      <c r="H91" s="3">
+        <v>1</v>
+      </c>
+      <c r="I91" s="3">
+        <v>0</v>
+      </c>
+      <c r="J91" s="3">
+        <v>2</v>
+      </c>
+      <c r="K91" s="3">
+        <v>0</v>
+      </c>
+      <c r="L91" s="3">
+        <v>0</v>
+      </c>
+      <c r="M91" s="3">
+        <v>0</v>
+      </c>
     </row>
     <row r="92" customHeight="1" spans="3:13">
-      <c r="D92" s="7"/>
+      <c r="C92" s="3">
+        <v>8203</v>
+      </c>
+      <c r="D92" s="9" t="s">
+        <v>252</v>
+      </c>
+      <c r="E92" s="3">
+        <v>16</v>
+      </c>
+      <c r="F92" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="G92" s="3">
+        <v>1</v>
+      </c>
+      <c r="H92" s="3">
+        <v>1</v>
+      </c>
+      <c r="I92" s="3">
+        <v>0</v>
+      </c>
+      <c r="J92" s="3">
+        <v>3</v>
+      </c>
+      <c r="K92" s="3">
+        <v>0</v>
+      </c>
+      <c r="L92" s="3">
+        <v>0</v>
+      </c>
+      <c r="M92" s="3">
+        <v>0</v>
+      </c>
     </row>
     <row r="93" customHeight="1" spans="3:13">
-      <c r="D93" s="7"/>
+      <c r="C93" s="3">
+        <v>8204</v>
+      </c>
+      <c r="D93" s="9" t="s">
+        <v>254</v>
+      </c>
+      <c r="E93" s="3">
+        <v>16</v>
+      </c>
+      <c r="F93" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="G93" s="3">
+        <v>1</v>
+      </c>
+      <c r="H93" s="3">
+        <v>1</v>
+      </c>
+      <c r="I93" s="3">
+        <v>0</v>
+      </c>
+      <c r="J93" s="3">
+        <v>4</v>
+      </c>
+      <c r="K93" s="3">
+        <v>0</v>
+      </c>
+      <c r="L93" s="3">
+        <v>0</v>
+      </c>
+      <c r="M93" s="3">
+        <v>0</v>
+      </c>
     </row>
     <row r="94" customHeight="1" spans="3:13">
-      <c r="D94" s="7"/>
+      <c r="C94" s="3">
+        <v>8205</v>
+      </c>
+      <c r="D94" s="9" t="s">
+        <v>256</v>
+      </c>
+      <c r="E94" s="3">
+        <v>16</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="G94" s="3">
+        <v>1</v>
+      </c>
+      <c r="H94" s="3">
+        <v>1</v>
+      </c>
+      <c r="I94" s="3">
+        <v>0</v>
+      </c>
+      <c r="J94" s="3">
+        <v>5</v>
+      </c>
+      <c r="K94" s="3">
+        <v>0</v>
+      </c>
+      <c r="L94" s="3">
+        <v>0</v>
+      </c>
+      <c r="M94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" customHeight="1" spans="3:13">
+      <c r="C95" s="3">
+        <v>8206</v>
+      </c>
+      <c r="D95" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="E95" s="3">
+        <v>16</v>
+      </c>
+      <c r="F95" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="G95" s="3">
+        <v>1</v>
+      </c>
+      <c r="H95" s="3">
+        <v>1</v>
+      </c>
+      <c r="I95" s="3">
+        <v>0</v>
+      </c>
+      <c r="J95" s="3">
+        <v>6</v>
+      </c>
+      <c r="K95" s="3">
+        <v>0</v>
+      </c>
+      <c r="L95" s="3">
+        <v>0</v>
+      </c>
+      <c r="M95" s="3">
+        <v>0</v>
+      </c>
     </row>
     <row r="96" customHeight="1" spans="3:13">
-      <c r="D96" s="7"/>
-    </row>
-    <row r="97" customHeight="1" spans="4:4">
-      <c r="D97" s="7"/>
+      <c r="C96" s="3">
+        <v>8207</v>
+      </c>
+      <c r="D96" s="9" t="s">
+        <v>260</v>
+      </c>
+      <c r="E96" s="3">
+        <v>16</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="G96" s="3">
+        <v>1</v>
+      </c>
+      <c r="H96" s="3">
+        <v>1</v>
+      </c>
+      <c r="I96" s="3">
+        <v>0</v>
+      </c>
+      <c r="J96" s="3">
+        <v>7</v>
+      </c>
+      <c r="K96" s="3">
+        <v>0</v>
+      </c>
+      <c r="L96" s="3">
+        <v>0</v>
+      </c>
+      <c r="M96" s="3">
+        <v>0</v>
+      </c>
     </row>
     <row r="98" customHeight="1" spans="4:4">
-      <c r="D98" s="7"/>
+      <c r="D98" s="9"/>
     </row>
     <row r="99" customHeight="1" spans="4:4">
-      <c r="D99" s="7"/>
+      <c r="D99" s="9"/>
     </row>
     <row r="100" customHeight="1" spans="4:4">
-      <c r="D100" s="7"/>
+      <c r="D100" s="9"/>
     </row>
     <row r="101" customHeight="1" spans="4:4">
-      <c r="D101" s="7"/>
+      <c r="D101" s="9"/>
     </row>
     <row r="102" customHeight="1" spans="4:4">
-      <c r="D102" s="7"/>
+      <c r="D102" s="9"/>
+    </row>
+    <row r="103" customHeight="1" spans="4:4">
+      <c r="D103" s="9"/>
+    </row>
+    <row r="104" customHeight="1" spans="4:4">
+      <c r="D104" s="9"/>
+    </row>
+    <row r="106" customHeight="1" spans="4:4">
+      <c r="D106" s="9"/>
+    </row>
+    <row r="107" customHeight="1" spans="4:4">
+      <c r="D107" s="9"/>
+    </row>
+    <row r="108" customHeight="1" spans="4:4">
+      <c r="D108" s="9"/>
+    </row>
+    <row r="109" customHeight="1" spans="4:4">
+      <c r="D109" s="9"/>
+    </row>
+    <row r="110" customHeight="1" spans="4:4">
+      <c r="D110" s="9"/>
+    </row>
+    <row r="111" customHeight="1" spans="4:4">
+      <c r="D111" s="9"/>
+    </row>
+    <row r="112" customHeight="1" spans="4:4">
+      <c r="D112" s="9"/>
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="L3:M5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="L3:M5 L7:M15" errorStyle="warning">
       <formula1>COUNTIF($A:$A,L3)&lt;2</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:D5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:D5 C7:D15" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/ItemConfig.xlsx
+++ b/Excel/ItemConfig.xlsx
@@ -184,7 +184,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="512" uniqueCount="281">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="284">
   <si>
     <t>_Id</t>
   </si>
@@ -591,16 +591,25 @@
     <t>学习或者升级道士技能召唤白虎</t>
   </si>
   <si>
+    <t>铁矿石</t>
+  </si>
+  <si>
+    <t>装备强化材料</t>
+  </si>
+  <si>
+    <t>黑铁石</t>
+  </si>
+  <si>
+    <t>魂环碎片</t>
+  </si>
+  <si>
+    <t>合成魂环的材料</t>
+  </si>
+  <si>
     <t>精炼石</t>
   </si>
   <si>
     <t>装备精练材料</t>
-  </si>
-  <si>
-    <t>魂环碎片</t>
-  </si>
-  <si>
-    <t>合成魂环的材料</t>
   </si>
   <si>
     <t>装备副本卷</t>
@@ -1696,7 +1705,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1707,7 +1716,6 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2403,7 +2411,7 @@
       <c r="B13" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C13" s="10" t="s">
+      <c r="C13" s="9" t="s">
         <v>48</v>
       </c>
       <c r="D13" s="6" t="s">
@@ -2444,7 +2452,7 @@
       <c r="B14" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C14" s="10" t="s">
+      <c r="C14" s="9" t="s">
         <v>51</v>
       </c>
       <c r="D14" s="6" t="s">
@@ -2485,7 +2493,7 @@
       <c r="B15" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C15" s="10" t="s">
+      <c r="C15" s="9" t="s">
         <v>54</v>
       </c>
       <c r="D15" s="6" t="s">
@@ -2526,7 +2534,7 @@
       <c r="B16" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C16" s="10" t="s">
+      <c r="C16" s="9" t="s">
         <v>57</v>
       </c>
       <c r="D16" s="6" t="s">
@@ -2567,7 +2575,7 @@
       <c r="B17" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C17" s="10" t="s">
+      <c r="C17" s="9" t="s">
         <v>60</v>
       </c>
       <c r="D17" s="6" t="s">
@@ -2853,7 +2861,7 @@
       <c r="B26" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C26" s="10" t="s">
+      <c r="C26" s="9" t="s">
         <v>84</v>
       </c>
       <c r="D26" s="6" t="s">
@@ -2894,7 +2902,7 @@
       <c r="B27" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C27" s="10" t="s">
+      <c r="C27" s="9" t="s">
         <v>87</v>
       </c>
       <c r="D27" s="6" t="s">
@@ -2935,7 +2943,7 @@
       <c r="B28" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C28" s="10" t="s">
+      <c r="C28" s="9" t="s">
         <v>90</v>
       </c>
       <c r="D28" s="6" t="s">
@@ -2976,7 +2984,7 @@
       <c r="B29" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C29" s="10" t="s">
+      <c r="C29" s="9" t="s">
         <v>93</v>
       </c>
       <c r="D29" s="6" t="s">
@@ -3017,7 +3025,7 @@
       <c r="B30" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C30" s="10" t="s">
+      <c r="C30" s="9" t="s">
         <v>96</v>
       </c>
       <c r="D30" s="6" t="s">
@@ -3303,7 +3311,7 @@
       <c r="B39" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C39" s="10" t="s">
+      <c r="C39" s="9" t="s">
         <v>120</v>
       </c>
       <c r="D39" s="6" t="s">
@@ -3344,7 +3352,7 @@
       <c r="B40" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C40" s="10" t="s">
+      <c r="C40" s="9" t="s">
         <v>123</v>
       </c>
       <c r="D40" s="6" t="s">
@@ -3385,7 +3393,7 @@
       <c r="B41" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C41" s="10" t="s">
+      <c r="C41" s="9" t="s">
         <v>126</v>
       </c>
       <c r="D41" s="6" t="s">
@@ -3426,7 +3434,7 @@
       <c r="B42" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C42" s="10" t="s">
+      <c r="C42" s="9" t="s">
         <v>129</v>
       </c>
       <c r="D42" s="6" t="s">
@@ -3467,7 +3475,7 @@
       <c r="B43" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C43" s="10" t="s">
+      <c r="C43" s="9" t="s">
         <v>132</v>
       </c>
       <c r="D43" s="6" t="s">
@@ -3671,135 +3679,155 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" s="7" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
-      <c r="H7" s="8"/>
-      <c r="I7" s="8"/>
-      <c r="J7" s="8"/>
-      <c r="K7" s="8"/>
-      <c r="L7" s="8"/>
-      <c r="M7" s="8"/>
-    </row>
-    <row r="8" s="7" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C8" s="8"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="8"/>
-      <c r="G8" s="8"/>
-      <c r="H8" s="8"/>
-      <c r="I8" s="8"/>
-      <c r="J8" s="8"/>
-      <c r="K8" s="8"/>
-      <c r="L8" s="8"/>
-      <c r="M8" s="8"/>
-    </row>
-    <row r="9" s="7" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C9" s="8"/>
-      <c r="D9" s="8"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="8"/>
-      <c r="G9" s="8"/>
-      <c r="H9" s="8"/>
-      <c r="I9" s="8"/>
-      <c r="J9" s="8"/>
-      <c r="K9" s="8"/>
-      <c r="L9" s="8"/>
-      <c r="M9" s="8"/>
-    </row>
-    <row r="10" s="7" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="8"/>
-      <c r="H10" s="8"/>
-      <c r="I10" s="8"/>
-      <c r="J10" s="8"/>
-      <c r="K10" s="8"/>
-      <c r="L10" s="8"/>
-      <c r="M10" s="8"/>
-    </row>
-    <row r="11" s="7" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C11" s="8"/>
-      <c r="D11" s="8"/>
-      <c r="E11" s="8"/>
-      <c r="F11" s="8"/>
-      <c r="G11" s="8"/>
-      <c r="H11" s="8"/>
-      <c r="I11" s="8"/>
-      <c r="J11" s="8"/>
-      <c r="K11" s="8"/>
-      <c r="L11" s="8"/>
-      <c r="M11" s="8"/>
-    </row>
-    <row r="12" s="7" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C12" s="8"/>
-      <c r="D12" s="8"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="8"/>
-      <c r="G12" s="8"/>
-      <c r="H12" s="8"/>
-      <c r="I12" s="8"/>
-      <c r="J12" s="8"/>
-      <c r="K12" s="8"/>
-      <c r="L12" s="8"/>
-      <c r="M12" s="8"/>
-    </row>
-    <row r="13" s="7" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C13" s="8"/>
-      <c r="D13" s="8"/>
-      <c r="E13" s="8"/>
-      <c r="F13" s="8"/>
-      <c r="G13" s="8"/>
-      <c r="H13" s="8"/>
-      <c r="I13" s="8"/>
-      <c r="J13" s="8"/>
-      <c r="K13" s="8"/>
-      <c r="L13" s="8"/>
-      <c r="M13" s="8"/>
-    </row>
-    <row r="14" s="7" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C14" s="8"/>
-      <c r="D14" s="8"/>
-      <c r="E14" s="8"/>
-      <c r="F14" s="8"/>
-      <c r="G14" s="8"/>
-      <c r="H14" s="8"/>
-      <c r="I14" s="8"/>
-      <c r="J14" s="8"/>
-      <c r="K14" s="8"/>
-      <c r="L14" s="8"/>
-      <c r="M14" s="8"/>
-    </row>
-    <row r="15" s="7" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C15" s="8"/>
-      <c r="D15" s="8"/>
-      <c r="E15" s="8"/>
-      <c r="F15" s="8"/>
-      <c r="G15" s="8"/>
-      <c r="H15" s="8"/>
-      <c r="I15" s="8"/>
-      <c r="J15" s="8"/>
-      <c r="K15" s="8"/>
-      <c r="L15" s="8"/>
-      <c r="M15" s="8"/>
+    <row r="7" s="6" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C7" s="3">
+        <v>5002</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="E7" s="3">
+        <v>5</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="G7" s="3">
+        <v>1</v>
+      </c>
+      <c r="H7" s="3">
+        <v>99999999999</v>
+      </c>
+      <c r="I7" s="3">
+        <v>0</v>
+      </c>
+      <c r="J7" s="3">
+        <v>5</v>
+      </c>
+      <c r="K7" s="3"/>
+      <c r="L7" s="3">
+        <v>0</v>
+      </c>
+      <c r="M7" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" s="6" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C8" s="7"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="7"/>
+      <c r="G8" s="7"/>
+      <c r="H8" s="7"/>
+      <c r="I8" s="7"/>
+      <c r="J8" s="7"/>
+      <c r="K8" s="7"/>
+      <c r="L8" s="7"/>
+      <c r="M8" s="7"/>
+    </row>
+    <row r="9" s="6" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C9" s="7"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="7"/>
+      <c r="G9" s="7"/>
+      <c r="H9" s="7"/>
+      <c r="I9" s="7"/>
+      <c r="J9" s="7"/>
+      <c r="K9" s="7"/>
+      <c r="L9" s="7"/>
+      <c r="M9" s="7"/>
+    </row>
+    <row r="10" s="6" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C10" s="7"/>
+      <c r="D10" s="7"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="7"/>
+      <c r="G10" s="7"/>
+      <c r="H10" s="7"/>
+      <c r="I10" s="7"/>
+      <c r="J10" s="7"/>
+      <c r="K10" s="7"/>
+      <c r="L10" s="7"/>
+      <c r="M10" s="7"/>
+    </row>
+    <row r="11" s="6" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C11" s="7"/>
+      <c r="D11" s="7"/>
+      <c r="E11" s="7"/>
+      <c r="F11" s="7"/>
+      <c r="G11" s="7"/>
+      <c r="H11" s="7"/>
+      <c r="I11" s="7"/>
+      <c r="J11" s="7"/>
+      <c r="K11" s="7"/>
+      <c r="L11" s="7"/>
+      <c r="M11" s="7"/>
+    </row>
+    <row r="12" s="6" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C12" s="7"/>
+      <c r="D12" s="7"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="7"/>
+      <c r="G12" s="7"/>
+      <c r="H12" s="7"/>
+      <c r="I12" s="7"/>
+      <c r="J12" s="7"/>
+      <c r="K12" s="7"/>
+      <c r="L12" s="7"/>
+      <c r="M12" s="7"/>
+    </row>
+    <row r="13" s="6" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C13" s="7"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="7"/>
+      <c r="G13" s="7"/>
+      <c r="H13" s="7"/>
+      <c r="I13" s="7"/>
+      <c r="J13" s="7"/>
+      <c r="K13" s="7"/>
+      <c r="L13" s="7"/>
+      <c r="M13" s="7"/>
+    </row>
+    <row r="14" s="6" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C14" s="7"/>
+      <c r="D14" s="7"/>
+      <c r="E14" s="7"/>
+      <c r="F14" s="7"/>
+      <c r="G14" s="7"/>
+      <c r="H14" s="7"/>
+      <c r="I14" s="7"/>
+      <c r="J14" s="7"/>
+      <c r="K14" s="7"/>
+      <c r="L14" s="7"/>
+      <c r="M14" s="7"/>
+    </row>
+    <row r="15" s="6" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C15" s="7"/>
+      <c r="D15" s="7"/>
+      <c r="E15" s="7"/>
+      <c r="F15" s="7"/>
+      <c r="G15" s="7"/>
+      <c r="H15" s="7"/>
+      <c r="I15" s="7"/>
+      <c r="J15" s="7"/>
+      <c r="K15" s="7"/>
+      <c r="L15" s="7"/>
+      <c r="M15" s="7"/>
     </row>
     <row r="16" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C16" s="3">
         <v>4001</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E16" s="3">
         <v>5</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="G16" s="3">
         <v>1</v>
@@ -3825,13 +3853,13 @@
         <v>4002</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="E17" s="3">
         <v>5</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="G17" s="3">
         <v>1</v>
@@ -3857,13 +3885,13 @@
         <v>4003</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="E18" s="3">
         <v>9</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="G18" s="3">
         <v>1</v>
@@ -3889,13 +3917,13 @@
         <v>4004</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="E19" s="3">
         <v>5</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="G19" s="3">
         <v>1</v>
@@ -3921,13 +3949,13 @@
         <v>4005</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="E20" s="3">
         <v>5</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="G20" s="3">
         <v>1</v>
@@ -3953,13 +3981,13 @@
         <v>4006</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="E21" s="3">
         <v>5</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="G21" s="3">
         <v>1</v>
@@ -3988,13 +4016,13 @@
         <v>4007</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="E22" s="3">
         <v>5</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="G22" s="3">
         <v>1</v>
@@ -4020,13 +4048,13 @@
         <v>4008</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="E23" s="3">
         <v>5</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="G23" s="3">
         <v>1</v>
@@ -4052,13 +4080,13 @@
         <v>4009</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="E24" s="3">
         <v>5</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="G24" s="3">
         <v>1</v>
@@ -4084,13 +4112,13 @@
         <v>4010</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="E25" s="3">
         <v>5</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="G25" s="3">
         <v>1</v>
@@ -4116,13 +4144,13 @@
         <v>4011</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="E26" s="3">
         <v>5</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="G26" s="3">
         <v>1</v>
@@ -4148,13 +4176,13 @@
         <v>4012</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="E27" s="3">
         <v>5</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="G27" s="3">
         <v>1</v>
@@ -4180,13 +4208,13 @@
         <v>4013</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="E28" s="3">
         <v>9</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="G28" s="3">
         <v>1</v>
@@ -4212,13 +4240,13 @@
         <v>4014</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="E29" s="3">
         <v>15</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="G29" s="3">
         <v>1</v>
@@ -4244,13 +4272,13 @@
         <v>4015</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="E30" s="3">
         <v>5</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="G30" s="3">
         <v>1</v>
@@ -4276,13 +4304,13 @@
         <v>4016</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="E31" s="3">
         <v>5</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="G31" s="3">
         <v>1</v>
@@ -4308,13 +4336,13 @@
         <v>4017</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="E32" s="3">
         <v>9</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="G32" s="3">
         <v>1</v>
@@ -4340,13 +4368,13 @@
         <v>4018</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="E33" s="3">
         <v>5</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="G33" s="3">
         <v>1</v>
@@ -4372,13 +4400,13 @@
         <v>4019</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="E34" s="3">
         <v>5</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="G34" s="3">
         <v>1</v>
@@ -4404,13 +4432,13 @@
         <v>4020</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="E35" s="3">
         <v>15</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="G35" s="3">
         <v>1</v>
@@ -4439,13 +4467,13 @@
         <v>4021</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="E36" s="3">
         <v>5</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="G36" s="3">
         <v>1</v>
@@ -4471,13 +4499,13 @@
         <v>4022</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="E37" s="3">
         <v>5</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="G37" s="3">
         <v>1</v>
@@ -4503,13 +4531,13 @@
         <v>4023</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="E38" s="3">
         <v>5</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="G38" s="3">
         <v>1</v>
@@ -4535,13 +4563,13 @@
         <v>4024</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="E39" s="3">
         <v>5</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="G39" s="3">
         <v>1</v>
@@ -4567,13 +4595,13 @@
         <v>4025</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="E40" s="3">
         <v>5</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="G40" s="3">
         <v>1</v>
@@ -4599,13 +4627,13 @@
         <v>4026</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="E41" s="3">
         <v>5</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="G41" s="3">
         <v>1</v>
@@ -4631,13 +4659,13 @@
         <v>4027</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="E42" s="3">
         <v>5</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="G42" s="3">
         <v>1</v>
@@ -4663,13 +4691,13 @@
         <v>4028</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="E43" s="3">
         <v>5</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="G43" s="3">
         <v>1</v>
@@ -4695,13 +4723,13 @@
         <v>4029</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="E44" s="3">
         <v>5</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="G44" s="3">
         <v>1</v>
@@ -4727,13 +4755,13 @@
         <v>4030</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="E45" s="3">
         <v>5</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="G45" s="3">
         <v>1</v>
@@ -4759,13 +4787,13 @@
         <v>4031</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="E46" s="3">
         <v>5</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="G46" s="3">
         <v>1</v>
@@ -4791,13 +4819,13 @@
         <v>4032</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="E47" s="3">
         <v>5</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="G47" s="3">
         <v>1</v>
@@ -4823,13 +4851,13 @@
         <v>4033</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="E48" s="3">
         <v>5</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="G48" s="3">
         <v>1</v>
@@ -4855,13 +4883,13 @@
         <v>4034</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="E49" s="3">
         <v>5</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="G49" s="3">
         <v>1</v>
@@ -4887,13 +4915,13 @@
         <v>4035</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="E50" s="3">
         <v>5</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="G50" s="3">
         <v>1</v>
@@ -4919,13 +4947,13 @@
         <v>4037</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="E51" s="3">
         <v>5</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="G51" s="3">
         <v>1</v>
@@ -4951,13 +4979,13 @@
         <v>4038</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="E52" s="3">
         <v>5</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="G52" s="3">
         <v>1</v>
@@ -4983,13 +5011,13 @@
         <v>4039</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="E53" s="3">
         <v>5</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="G53" s="3">
         <v>1</v>
@@ -5015,13 +5043,13 @@
         <v>4040</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="E54" s="3">
         <v>5</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="G54" s="3">
         <v>1</v>
@@ -5047,13 +5075,13 @@
         <v>4041</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="E55" s="3">
         <v>5</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="G55" s="3">
         <v>1</v>
@@ -5079,13 +5107,13 @@
         <v>4042</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="E56" s="3">
         <v>5</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="G56" s="3">
         <v>1</v>
@@ -5111,13 +5139,13 @@
         <v>4043</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="E57" s="3">
         <v>5</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="G57" s="3">
         <v>1</v>
@@ -5143,13 +5171,13 @@
         <v>4044</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="E58" s="3">
         <v>5</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="G58" s="3">
         <v>1</v>
@@ -5187,13 +5215,13 @@
         <v>4101</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="E60" s="3">
         <v>5</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="G60" s="3">
         <v>1</v>
@@ -5219,13 +5247,13 @@
         <v>4111</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="E61" s="3">
         <v>5</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="G61" s="3">
         <v>1</v>
@@ -5251,13 +5279,13 @@
         <v>4112</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="E62" s="3">
         <v>5</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="G62" s="3">
         <v>1</v>
@@ -5283,13 +5311,13 @@
         <v>4113</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E63" s="3">
         <v>5</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="G63" s="3">
         <v>1</v>
@@ -5327,13 +5355,13 @@
         <v>4201</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="E65" s="3">
         <v>5</v>
       </c>
       <c r="F65" s="3" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="G65" s="3">
         <v>1</v>
@@ -5359,13 +5387,13 @@
         <v>8001</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="E70" s="3">
         <v>5</v>
       </c>
       <c r="F70" s="3" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="G70" s="3">
         <v>1</v>
@@ -5391,13 +5419,13 @@
         <v>8002</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="E71" s="3">
         <v>5</v>
       </c>
       <c r="F71" s="3" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="G71" s="3">
         <v>1</v>
@@ -5423,13 +5451,13 @@
         <v>8003</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="E72" s="3">
         <v>5</v>
       </c>
       <c r="F72" s="3" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="G72" s="3">
         <v>1</v>
@@ -5455,13 +5483,13 @@
         <v>8004</v>
       </c>
       <c r="D73" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="E73" s="3">
+        <v>5</v>
+      </c>
+      <c r="F73" s="3" t="s">
         <v>232</v>
-      </c>
-      <c r="E73" s="3">
-        <v>5</v>
-      </c>
-      <c r="F73" s="3" t="s">
-        <v>229</v>
       </c>
       <c r="G73" s="3">
         <v>1</v>
@@ -5487,13 +5515,13 @@
         <v>8005</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="E74" s="3">
         <v>5</v>
       </c>
       <c r="F74" s="3" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="G74" s="3">
         <v>1</v>
@@ -5519,13 +5547,13 @@
         <v>8006</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="E75" s="3">
         <v>5</v>
       </c>
       <c r="F75" s="3" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="G75" s="3">
         <v>1</v>
@@ -5551,13 +5579,13 @@
         <v>8007</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="E76" s="3">
         <v>5</v>
       </c>
       <c r="F76" s="3" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="G76" s="3">
         <v>1</v>
@@ -5583,13 +5611,13 @@
         <v>8008</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="E77" s="3">
         <v>5</v>
       </c>
       <c r="F77" s="3" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="G77" s="3">
         <v>1</v>
@@ -5615,13 +5643,13 @@
         <v>8009</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="E78" s="3">
         <v>5</v>
       </c>
       <c r="F78" s="3" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="G78" s="3">
         <v>1</v>
@@ -5647,13 +5675,13 @@
         <v>8010</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="E79" s="3">
         <v>5</v>
       </c>
       <c r="F79" s="3" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="G79" s="3">
         <v>1</v>
@@ -5678,14 +5706,14 @@
       <c r="C81" s="3">
         <v>8101</v>
       </c>
-      <c r="D81" s="9" t="s">
-        <v>239</v>
+      <c r="D81" s="8" t="s">
+        <v>242</v>
       </c>
       <c r="E81" s="3">
         <v>5</v>
       </c>
       <c r="F81" s="3" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="G81" s="3">
         <v>1</v>
@@ -5710,14 +5738,14 @@
       <c r="C82" s="3">
         <v>8102</v>
       </c>
-      <c r="D82" s="9" t="s">
-        <v>241</v>
+      <c r="D82" s="8" t="s">
+        <v>244</v>
       </c>
       <c r="E82" s="3">
         <v>5</v>
       </c>
       <c r="F82" s="3" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="G82" s="3">
         <v>1</v>
@@ -5742,14 +5770,14 @@
       <c r="C83" s="3">
         <v>8103</v>
       </c>
-      <c r="D83" s="9" t="s">
-        <v>242</v>
+      <c r="D83" s="8" t="s">
+        <v>245</v>
       </c>
       <c r="E83" s="3">
         <v>5</v>
       </c>
       <c r="F83" s="3" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="G83" s="3">
         <v>1</v>
@@ -5774,14 +5802,14 @@
       <c r="C84" s="3">
         <v>8104</v>
       </c>
-      <c r="D84" s="9" t="s">
+      <c r="D84" s="8" t="s">
+        <v>246</v>
+      </c>
+      <c r="E84" s="3">
+        <v>5</v>
+      </c>
+      <c r="F84" s="3" t="s">
         <v>243</v>
-      </c>
-      <c r="E84" s="3">
-        <v>5</v>
-      </c>
-      <c r="F84" s="3" t="s">
-        <v>240</v>
       </c>
       <c r="G84" s="3">
         <v>1</v>
@@ -5806,14 +5834,14 @@
       <c r="C85" s="3">
         <v>8105</v>
       </c>
-      <c r="D85" s="9" t="s">
-        <v>244</v>
+      <c r="D85" s="8" t="s">
+        <v>247</v>
       </c>
       <c r="E85" s="3">
         <v>5</v>
       </c>
       <c r="F85" s="3" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="G85" s="3">
         <v>1</v>
@@ -5838,14 +5866,14 @@
       <c r="C86" s="3">
         <v>8106</v>
       </c>
-      <c r="D86" s="9" t="s">
-        <v>245</v>
+      <c r="D86" s="8" t="s">
+        <v>248</v>
       </c>
       <c r="E86" s="3">
         <v>5</v>
       </c>
       <c r="F86" s="3" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="G86" s="3">
         <v>1</v>
@@ -5870,14 +5898,14 @@
       <c r="C87" s="3">
         <v>8107</v>
       </c>
-      <c r="D87" s="9" t="s">
-        <v>246</v>
+      <c r="D87" s="8" t="s">
+        <v>249</v>
       </c>
       <c r="E87" s="3">
         <v>5</v>
       </c>
       <c r="F87" s="3" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="G87" s="3">
         <v>1</v>
@@ -5902,14 +5930,14 @@
       <c r="C88" s="3">
         <v>8108</v>
       </c>
-      <c r="D88" s="9" t="s">
-        <v>247</v>
+      <c r="D88" s="8" t="s">
+        <v>250</v>
       </c>
       <c r="E88" s="3">
         <v>5</v>
       </c>
       <c r="F88" s="3" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="G88" s="3">
         <v>1</v>
@@ -5934,14 +5962,14 @@
       <c r="C90" s="3">
         <v>8201</v>
       </c>
-      <c r="D90" s="9" t="s">
-        <v>248</v>
+      <c r="D90" s="8" t="s">
+        <v>251</v>
       </c>
       <c r="E90" s="3">
         <v>16</v>
       </c>
       <c r="F90" s="3" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="G90" s="3">
         <v>1</v>
@@ -5969,14 +5997,14 @@
       <c r="C91" s="3">
         <v>8202</v>
       </c>
-      <c r="D91" s="9" t="s">
-        <v>250</v>
+      <c r="D91" s="8" t="s">
+        <v>253</v>
       </c>
       <c r="E91" s="3">
         <v>16</v>
       </c>
       <c r="F91" s="3" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="G91" s="3">
         <v>1</v>
@@ -6004,14 +6032,14 @@
       <c r="C92" s="3">
         <v>8203</v>
       </c>
-      <c r="D92" s="9" t="s">
-        <v>252</v>
+      <c r="D92" s="8" t="s">
+        <v>255</v>
       </c>
       <c r="E92" s="3">
         <v>16</v>
       </c>
       <c r="F92" s="3" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="G92" s="3">
         <v>1</v>
@@ -6039,14 +6067,14 @@
       <c r="C93" s="3">
         <v>8204</v>
       </c>
-      <c r="D93" s="9" t="s">
-        <v>254</v>
+      <c r="D93" s="8" t="s">
+        <v>257</v>
       </c>
       <c r="E93" s="3">
         <v>16</v>
       </c>
       <c r="F93" s="3" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="G93" s="3">
         <v>1</v>
@@ -6074,14 +6102,14 @@
       <c r="C94" s="3">
         <v>8205</v>
       </c>
-      <c r="D94" s="9" t="s">
-        <v>256</v>
+      <c r="D94" s="8" t="s">
+        <v>259</v>
       </c>
       <c r="E94" s="3">
         <v>16</v>
       </c>
       <c r="F94" s="3" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="G94" s="3">
         <v>1</v>
@@ -6109,14 +6137,14 @@
       <c r="C95" s="3">
         <v>8206</v>
       </c>
-      <c r="D95" s="9" t="s">
-        <v>258</v>
+      <c r="D95" s="8" t="s">
+        <v>261</v>
       </c>
       <c r="E95" s="3">
         <v>16</v>
       </c>
       <c r="F95" s="3" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="G95" s="3">
         <v>1</v>
@@ -6144,14 +6172,14 @@
       <c r="C96" s="3">
         <v>8207</v>
       </c>
-      <c r="D96" s="9" t="s">
-        <v>260</v>
+      <c r="D96" s="8" t="s">
+        <v>263</v>
       </c>
       <c r="E96" s="3">
         <v>16</v>
       </c>
       <c r="F96" s="3" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="G96" s="3">
         <v>1</v>
@@ -6176,53 +6204,53 @@
       </c>
     </row>
     <row r="98" customHeight="1" spans="4:4">
-      <c r="D98" s="9"/>
+      <c r="D98" s="8"/>
     </row>
     <row r="99" customHeight="1" spans="4:4">
-      <c r="D99" s="9"/>
+      <c r="D99" s="8"/>
     </row>
     <row r="100" customHeight="1" spans="4:4">
-      <c r="D100" s="9"/>
+      <c r="D100" s="8"/>
     </row>
     <row r="101" customHeight="1" spans="4:4">
-      <c r="D101" s="9"/>
+      <c r="D101" s="8"/>
     </row>
     <row r="102" customHeight="1" spans="4:4">
-      <c r="D102" s="9"/>
+      <c r="D102" s="8"/>
     </row>
     <row r="103" customHeight="1" spans="4:4">
-      <c r="D103" s="9"/>
+      <c r="D103" s="8"/>
     </row>
     <row r="104" customHeight="1" spans="4:4">
-      <c r="D104" s="9"/>
+      <c r="D104" s="8"/>
     </row>
     <row r="106" customHeight="1" spans="4:4">
-      <c r="D106" s="9"/>
+      <c r="D106" s="8"/>
     </row>
     <row r="107" customHeight="1" spans="4:4">
-      <c r="D107" s="9"/>
+      <c r="D107" s="8"/>
     </row>
     <row r="108" customHeight="1" spans="4:4">
-      <c r="D108" s="9"/>
+      <c r="D108" s="8"/>
     </row>
     <row r="109" customHeight="1" spans="4:4">
-      <c r="D109" s="9"/>
+      <c r="D109" s="8"/>
     </row>
     <row r="110" customHeight="1" spans="4:4">
-      <c r="D110" s="9"/>
+      <c r="D110" s="8"/>
     </row>
     <row r="111" customHeight="1" spans="4:4">
-      <c r="D111" s="9"/>
+      <c r="D111" s="8"/>
     </row>
     <row r="112" customHeight="1" spans="4:4">
-      <c r="D112" s="9"/>
+      <c r="D112" s="8"/>
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="L3:M5 L7:M15" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="L3:M5 L8:M15" errorStyle="warning">
       <formula1>COUNTIF($A:$A,L3)&lt;2</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:D5 C7:D15" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:D5 C8:D15" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>
@@ -6361,13 +6389,13 @@
         <v>1999001</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="E6" s="2">
         <v>6</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="G6" s="2">
         <v>1</v>
@@ -6390,13 +6418,13 @@
         <v>1999002</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="E7" s="2">
         <v>6</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="G7" s="2">
         <v>1</v>
@@ -6419,13 +6447,13 @@
         <v>1999003</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="E8" s="2">
         <v>6</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="G8" s="2">
         <v>1</v>
@@ -6448,13 +6476,13 @@
         <v>1999004</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="E9" s="2">
         <v>6</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="G9" s="2">
         <v>1</v>
@@ -6477,13 +6505,13 @@
         <v>1999005</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="E10" s="2">
         <v>6</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="G10" s="2">
         <v>1</v>
@@ -6506,13 +6534,13 @@
         <v>1999006</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="E11" s="2">
         <v>6</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="G11" s="2">
         <v>1</v>
@@ -6534,13 +6562,13 @@
         <v>1999007</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="E12" s="2">
         <v>6</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="G12" s="2">
         <v>1</v>
@@ -6562,13 +6590,13 @@
         <v>1999008</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="E13" s="2">
         <v>6</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="G13" s="2">
         <v>1</v>
@@ -6590,13 +6618,13 @@
         <v>1999009</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="E14" s="2">
         <v>6</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="G14" s="2">
         <v>1</v>
@@ -6618,13 +6646,13 @@
         <v>1999010</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="E15" s="2">
         <v>6</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="G15" s="2">
         <v>1</v>
@@ -6646,13 +6674,13 @@
         <v>1999011</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="E16" s="2">
         <v>6</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="G16" s="2">
         <v>1</v>
@@ -6824,13 +6852,13 @@
         <v>40000001</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="E6" s="2">
         <v>6</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="G6" s="2">
         <v>1</v>
@@ -6851,13 +6879,13 @@
         <v>40000002</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="E7" s="2">
         <v>6</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="G7" s="2">
         <v>1</v>
@@ -6878,13 +6906,13 @@
         <v>40000003</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="E8" s="2">
         <v>6</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="G8" s="2">
         <v>1</v>
@@ -6905,13 +6933,13 @@
         <v>40000004</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="E9" s="2">
         <v>6</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="G9" s="2">
         <v>1</v>
@@ -6932,13 +6960,13 @@
         <v>40000005</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="E10" s="2">
         <v>6</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="G10" s="2">
         <v>1</v>
@@ -6959,13 +6987,13 @@
         <v>40000006</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="E11" s="2">
         <v>6</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="G11" s="2">
         <v>1</v>

--- a/Excel/ItemConfig.xlsx
+++ b/Excel/ItemConfig.xlsx
@@ -184,7 +184,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="284">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="292">
   <si>
     <t>_Id</t>
   </si>
@@ -598,6 +598,30 @@
   </si>
   <si>
     <t>黑铁石</t>
+  </si>
+  <si>
+    <t>灵盾碎片</t>
+  </si>
+  <si>
+    <t>灵盾进阶材料</t>
+  </si>
+  <si>
+    <t>灵符碎片</t>
+  </si>
+  <si>
+    <t>灵符进阶材料</t>
+  </si>
+  <si>
+    <t>灵玉碎片</t>
+  </si>
+  <si>
+    <t>灵玉进阶材料</t>
+  </si>
+  <si>
+    <t>灵珠碎片</t>
+  </si>
+  <si>
+    <t>灵珠进阶材料</t>
   </si>
   <si>
     <t>魂环碎片</t>
@@ -1705,7 +1729,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1720,7 +1744,13 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="49">
@@ -2411,7 +2441,7 @@
       <c r="B13" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C13" s="9" t="s">
+      <c r="C13" s="11" t="s">
         <v>48</v>
       </c>
       <c r="D13" s="6" t="s">
@@ -2452,7 +2482,7 @@
       <c r="B14" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C14" s="9" t="s">
+      <c r="C14" s="11" t="s">
         <v>51</v>
       </c>
       <c r="D14" s="6" t="s">
@@ -2493,7 +2523,7 @@
       <c r="B15" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C15" s="9" t="s">
+      <c r="C15" s="11" t="s">
         <v>54</v>
       </c>
       <c r="D15" s="6" t="s">
@@ -2534,7 +2564,7 @@
       <c r="B16" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C16" s="9" t="s">
+      <c r="C16" s="11" t="s">
         <v>57</v>
       </c>
       <c r="D16" s="6" t="s">
@@ -2575,7 +2605,7 @@
       <c r="B17" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C17" s="9" t="s">
+      <c r="C17" s="11" t="s">
         <v>60</v>
       </c>
       <c r="D17" s="6" t="s">
@@ -2861,7 +2891,7 @@
       <c r="B26" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C26" s="9" t="s">
+      <c r="C26" s="11" t="s">
         <v>84</v>
       </c>
       <c r="D26" s="6" t="s">
@@ -2902,7 +2932,7 @@
       <c r="B27" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C27" s="9" t="s">
+      <c r="C27" s="11" t="s">
         <v>87</v>
       </c>
       <c r="D27" s="6" t="s">
@@ -2943,7 +2973,7 @@
       <c r="B28" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C28" s="9" t="s">
+      <c r="C28" s="11" t="s">
         <v>90</v>
       </c>
       <c r="D28" s="6" t="s">
@@ -2984,7 +3014,7 @@
       <c r="B29" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C29" s="9" t="s">
+      <c r="C29" s="11" t="s">
         <v>93</v>
       </c>
       <c r="D29" s="6" t="s">
@@ -3025,7 +3055,7 @@
       <c r="B30" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C30" s="9" t="s">
+      <c r="C30" s="11" t="s">
         <v>96</v>
       </c>
       <c r="D30" s="6" t="s">
@@ -3311,7 +3341,7 @@
       <c r="B39" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C39" s="9" t="s">
+      <c r="C39" s="11" t="s">
         <v>120</v>
       </c>
       <c r="D39" s="6" t="s">
@@ -3352,7 +3382,7 @@
       <c r="B40" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C40" s="9" t="s">
+      <c r="C40" s="11" t="s">
         <v>123</v>
       </c>
       <c r="D40" s="6" t="s">
@@ -3393,7 +3423,7 @@
       <c r="B41" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C41" s="9" t="s">
+      <c r="C41" s="11" t="s">
         <v>126</v>
       </c>
       <c r="D41" s="6" t="s">
@@ -3434,7 +3464,7 @@
       <c r="B42" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C42" s="9" t="s">
+      <c r="C42" s="11" t="s">
         <v>129</v>
       </c>
       <c r="D42" s="6" t="s">
@@ -3475,7 +3505,7 @@
       <c r="B43" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C43" s="9" t="s">
+      <c r="C43" s="11" t="s">
         <v>132</v>
       </c>
       <c r="D43" s="6" t="s">
@@ -3716,66 +3746,146 @@
       <c r="C8" s="7"/>
       <c r="D8" s="7"/>
       <c r="E8" s="7"/>
-      <c r="F8" s="7"/>
-      <c r="G8" s="7"/>
-      <c r="H8" s="7"/>
-      <c r="I8" s="7"/>
-      <c r="J8" s="7"/>
-      <c r="K8" s="7"/>
-      <c r="L8" s="7"/>
-      <c r="M8" s="7"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3"/>
+      <c r="H8" s="3"/>
+      <c r="I8" s="3"/>
+      <c r="J8" s="3"/>
+      <c r="K8" s="3"/>
+      <c r="L8" s="3"/>
+      <c r="M8" s="3"/>
     </row>
     <row r="9" s="6" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
-      <c r="H9" s="7"/>
-      <c r="I9" s="7"/>
-      <c r="J9" s="7"/>
-      <c r="K9" s="7"/>
-      <c r="L9" s="7"/>
-      <c r="M9" s="7"/>
+      <c r="C9" s="8">
+        <v>5011</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="E9" s="10">
+        <v>5</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="G9" s="3">
+        <v>1</v>
+      </c>
+      <c r="H9" s="3">
+        <v>99999999999</v>
+      </c>
+      <c r="I9" s="3">
+        <v>0</v>
+      </c>
+      <c r="J9" s="3">
+        <v>3</v>
+      </c>
+      <c r="K9" s="3"/>
+      <c r="L9" s="3">
+        <v>0</v>
+      </c>
+      <c r="M9" s="3">
+        <v>0</v>
+      </c>
     </row>
     <row r="10" s="6" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C10" s="7"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="7"/>
-      <c r="G10" s="7"/>
-      <c r="H10" s="7"/>
-      <c r="I10" s="7"/>
-      <c r="J10" s="7"/>
-      <c r="K10" s="7"/>
-      <c r="L10" s="7"/>
-      <c r="M10" s="7"/>
+      <c r="C10" s="8">
+        <v>5012</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="E10" s="10">
+        <v>5</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="G10" s="3">
+        <v>1</v>
+      </c>
+      <c r="H10" s="3">
+        <v>99999999999</v>
+      </c>
+      <c r="I10" s="3">
+        <v>0</v>
+      </c>
+      <c r="J10" s="3">
+        <v>3</v>
+      </c>
+      <c r="K10" s="3"/>
+      <c r="L10" s="3">
+        <v>0</v>
+      </c>
+      <c r="M10" s="3">
+        <v>0</v>
+      </c>
     </row>
     <row r="11" s="6" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C11" s="7"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="7"/>
-      <c r="G11" s="7"/>
-      <c r="H11" s="7"/>
-      <c r="I11" s="7"/>
-      <c r="J11" s="7"/>
-      <c r="K11" s="7"/>
-      <c r="L11" s="7"/>
-      <c r="M11" s="7"/>
+      <c r="C11" s="8">
+        <v>5013</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="E11" s="10">
+        <v>5</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="G11" s="3">
+        <v>1</v>
+      </c>
+      <c r="H11" s="3">
+        <v>99999999999</v>
+      </c>
+      <c r="I11" s="3">
+        <v>0</v>
+      </c>
+      <c r="J11" s="3">
+        <v>3</v>
+      </c>
+      <c r="K11" s="3"/>
+      <c r="L11" s="3">
+        <v>0</v>
+      </c>
+      <c r="M11" s="3">
+        <v>0</v>
+      </c>
     </row>
     <row r="12" s="6" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C12" s="7"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="7"/>
-      <c r="G12" s="7"/>
-      <c r="H12" s="7"/>
-      <c r="I12" s="7"/>
-      <c r="J12" s="7"/>
-      <c r="K12" s="7"/>
-      <c r="L12" s="7"/>
-      <c r="M12" s="7"/>
+      <c r="C12" s="8">
+        <v>5014</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="E12" s="10">
+        <v>5</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="G12" s="3">
+        <v>1</v>
+      </c>
+      <c r="H12" s="3">
+        <v>99999999999</v>
+      </c>
+      <c r="I12" s="3">
+        <v>0</v>
+      </c>
+      <c r="J12" s="3">
+        <v>3</v>
+      </c>
+      <c r="K12" s="3"/>
+      <c r="L12" s="3">
+        <v>0</v>
+      </c>
+      <c r="M12" s="3">
+        <v>0</v>
+      </c>
     </row>
     <row r="13" s="6" customFormat="1" customHeight="1" spans="3:13">
       <c r="C13" s="7"/>
@@ -3821,13 +3931,13 @@
         <v>4001</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="E16" s="3">
         <v>5</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="G16" s="3">
         <v>1</v>
@@ -3853,13 +3963,13 @@
         <v>4002</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="E17" s="3">
         <v>5</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="G17" s="3">
         <v>1</v>
@@ -3885,13 +3995,13 @@
         <v>4003</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="E18" s="3">
         <v>9</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="G18" s="3">
         <v>1</v>
@@ -3917,13 +4027,13 @@
         <v>4004</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="E19" s="3">
         <v>5</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="G19" s="3">
         <v>1</v>
@@ -3949,13 +4059,13 @@
         <v>4005</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="E20" s="3">
         <v>5</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="G20" s="3">
         <v>1</v>
@@ -3981,13 +4091,13 @@
         <v>4006</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="E21" s="3">
         <v>5</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="G21" s="3">
         <v>1</v>
@@ -4016,13 +4126,13 @@
         <v>4007</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="E22" s="3">
         <v>5</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="G22" s="3">
         <v>1</v>
@@ -4048,13 +4158,13 @@
         <v>4008</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="E23" s="3">
         <v>5</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="G23" s="3">
         <v>1</v>
@@ -4080,13 +4190,13 @@
         <v>4009</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="E24" s="3">
         <v>5</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="G24" s="3">
         <v>1</v>
@@ -4112,13 +4222,13 @@
         <v>4010</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="E25" s="3">
         <v>5</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="G25" s="3">
         <v>1</v>
@@ -4144,13 +4254,13 @@
         <v>4011</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="E26" s="3">
         <v>5</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="G26" s="3">
         <v>1</v>
@@ -4176,13 +4286,13 @@
         <v>4012</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="E27" s="3">
         <v>5</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="G27" s="3">
         <v>1</v>
@@ -4208,13 +4318,13 @@
         <v>4013</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="E28" s="3">
         <v>9</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="G28" s="3">
         <v>1</v>
@@ -4240,13 +4350,13 @@
         <v>4014</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="E29" s="3">
         <v>15</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="G29" s="3">
         <v>1</v>
@@ -4272,13 +4382,13 @@
         <v>4015</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="E30" s="3">
         <v>5</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="G30" s="3">
         <v>1</v>
@@ -4304,13 +4414,13 @@
         <v>4016</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="E31" s="3">
         <v>5</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="G31" s="3">
         <v>1</v>
@@ -4336,13 +4446,13 @@
         <v>4017</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="E32" s="3">
         <v>9</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="G32" s="3">
         <v>1</v>
@@ -4368,13 +4478,13 @@
         <v>4018</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="E33" s="3">
         <v>5</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="G33" s="3">
         <v>1</v>
@@ -4400,13 +4510,13 @@
         <v>4019</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="E34" s="3">
         <v>5</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="G34" s="3">
         <v>1</v>
@@ -4432,13 +4542,13 @@
         <v>4020</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="E35" s="3">
         <v>15</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="G35" s="3">
         <v>1</v>
@@ -4467,13 +4577,13 @@
         <v>4021</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="E36" s="3">
         <v>5</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="G36" s="3">
         <v>1</v>
@@ -4499,13 +4609,13 @@
         <v>4022</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="E37" s="3">
         <v>5</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="G37" s="3">
         <v>1</v>
@@ -4531,13 +4641,13 @@
         <v>4023</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="E38" s="3">
         <v>5</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="G38" s="3">
         <v>1</v>
@@ -4563,13 +4673,13 @@
         <v>4024</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="E39" s="3">
         <v>5</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="G39" s="3">
         <v>1</v>
@@ -4595,13 +4705,13 @@
         <v>4025</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="E40" s="3">
         <v>5</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="G40" s="3">
         <v>1</v>
@@ -4627,13 +4737,13 @@
         <v>4026</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="E41" s="3">
         <v>5</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="G41" s="3">
         <v>1</v>
@@ -4659,13 +4769,13 @@
         <v>4027</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="E42" s="3">
         <v>5</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="G42" s="3">
         <v>1</v>
@@ -4691,13 +4801,13 @@
         <v>4028</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="E43" s="3">
         <v>5</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="G43" s="3">
         <v>1</v>
@@ -4723,13 +4833,13 @@
         <v>4029</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="E44" s="3">
         <v>5</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="G44" s="3">
         <v>1</v>
@@ -4755,13 +4865,13 @@
         <v>4030</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="E45" s="3">
         <v>5</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="G45" s="3">
         <v>1</v>
@@ -4787,13 +4897,13 @@
         <v>4031</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="E46" s="3">
         <v>5</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="G46" s="3">
         <v>1</v>
@@ -4819,13 +4929,13 @@
         <v>4032</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="E47" s="3">
         <v>5</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="G47" s="3">
         <v>1</v>
@@ -4851,13 +4961,13 @@
         <v>4033</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="E48" s="3">
         <v>5</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="G48" s="3">
         <v>1</v>
@@ -4883,13 +4993,13 @@
         <v>4034</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="E49" s="3">
         <v>5</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="G49" s="3">
         <v>1</v>
@@ -4915,13 +5025,13 @@
         <v>4035</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="E50" s="3">
         <v>5</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="G50" s="3">
         <v>1</v>
@@ -4947,13 +5057,13 @@
         <v>4037</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="E51" s="3">
         <v>5</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="G51" s="3">
         <v>1</v>
@@ -4979,13 +5089,13 @@
         <v>4038</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="E52" s="3">
         <v>5</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="G52" s="3">
         <v>1</v>
@@ -5011,13 +5121,13 @@
         <v>4039</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="E53" s="3">
         <v>5</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="G53" s="3">
         <v>1</v>
@@ -5043,13 +5153,13 @@
         <v>4040</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="E54" s="3">
         <v>5</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="G54" s="3">
         <v>1</v>
@@ -5075,13 +5185,13 @@
         <v>4041</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="E55" s="3">
         <v>5</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="G55" s="3">
         <v>1</v>
@@ -5107,13 +5217,13 @@
         <v>4042</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="E56" s="3">
         <v>5</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="G56" s="3">
         <v>1</v>
@@ -5139,13 +5249,13 @@
         <v>4043</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="E57" s="3">
         <v>5</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="G57" s="3">
         <v>1</v>
@@ -5171,13 +5281,13 @@
         <v>4044</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="E58" s="3">
         <v>5</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="G58" s="3">
         <v>1</v>
@@ -5215,13 +5325,13 @@
         <v>4101</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="E60" s="3">
         <v>5</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="G60" s="3">
         <v>1</v>
@@ -5247,13 +5357,13 @@
         <v>4111</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="E61" s="3">
         <v>5</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="G61" s="3">
         <v>1</v>
@@ -5279,13 +5389,13 @@
         <v>4112</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="E62" s="3">
         <v>5</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="G62" s="3">
         <v>1</v>
@@ -5311,13 +5421,13 @@
         <v>4113</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="E63" s="3">
         <v>5</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="G63" s="3">
         <v>1</v>
@@ -5355,13 +5465,13 @@
         <v>4201</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="E65" s="3">
         <v>5</v>
       </c>
       <c r="F65" s="3" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="G65" s="3">
         <v>1</v>
@@ -5387,13 +5497,13 @@
         <v>8001</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="E70" s="3">
         <v>5</v>
       </c>
       <c r="F70" s="3" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="G70" s="3">
         <v>1</v>
@@ -5419,13 +5529,13 @@
         <v>8002</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="E71" s="3">
         <v>5</v>
       </c>
       <c r="F71" s="3" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="G71" s="3">
         <v>1</v>
@@ -5451,13 +5561,13 @@
         <v>8003</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>234</v>
+        <v>242</v>
       </c>
       <c r="E72" s="3">
         <v>5</v>
       </c>
       <c r="F72" s="3" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="G72" s="3">
         <v>1</v>
@@ -5483,13 +5593,13 @@
         <v>8004</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="E73" s="3">
         <v>5</v>
       </c>
       <c r="F73" s="3" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="G73" s="3">
         <v>1</v>
@@ -5515,13 +5625,13 @@
         <v>8005</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="E74" s="3">
         <v>5</v>
       </c>
       <c r="F74" s="3" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="G74" s="3">
         <v>1</v>
@@ -5547,13 +5657,13 @@
         <v>8006</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="E75" s="3">
         <v>5</v>
       </c>
       <c r="F75" s="3" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="G75" s="3">
         <v>1</v>
@@ -5579,13 +5689,13 @@
         <v>8007</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="E76" s="3">
         <v>5</v>
       </c>
       <c r="F76" s="3" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="G76" s="3">
         <v>1</v>
@@ -5611,13 +5721,13 @@
         <v>8008</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="E77" s="3">
         <v>5</v>
       </c>
       <c r="F77" s="3" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="G77" s="3">
         <v>1</v>
@@ -5643,13 +5753,13 @@
         <v>8009</v>
       </c>
       <c r="D78" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="E78" s="3">
+        <v>5</v>
+      </c>
+      <c r="F78" s="3" t="s">
         <v>240</v>
-      </c>
-      <c r="E78" s="3">
-        <v>5</v>
-      </c>
-      <c r="F78" s="3" t="s">
-        <v>232</v>
       </c>
       <c r="G78" s="3">
         <v>1</v>
@@ -5675,13 +5785,13 @@
         <v>8010</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="E79" s="3">
         <v>5</v>
       </c>
       <c r="F79" s="3" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="G79" s="3">
         <v>1</v>
@@ -5706,14 +5816,14 @@
       <c r="C81" s="3">
         <v>8101</v>
       </c>
-      <c r="D81" s="8" t="s">
-        <v>242</v>
+      <c r="D81" s="9" t="s">
+        <v>250</v>
       </c>
       <c r="E81" s="3">
         <v>5</v>
       </c>
       <c r="F81" s="3" t="s">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="G81" s="3">
         <v>1</v>
@@ -5738,14 +5848,14 @@
       <c r="C82" s="3">
         <v>8102</v>
       </c>
-      <c r="D82" s="8" t="s">
-        <v>244</v>
+      <c r="D82" s="9" t="s">
+        <v>252</v>
       </c>
       <c r="E82" s="3">
         <v>5</v>
       </c>
       <c r="F82" s="3" t="s">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="G82" s="3">
         <v>1</v>
@@ -5770,14 +5880,14 @@
       <c r="C83" s="3">
         <v>8103</v>
       </c>
-      <c r="D83" s="8" t="s">
-        <v>245</v>
+      <c r="D83" s="9" t="s">
+        <v>253</v>
       </c>
       <c r="E83" s="3">
         <v>5</v>
       </c>
       <c r="F83" s="3" t="s">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="G83" s="3">
         <v>1</v>
@@ -5802,14 +5912,14 @@
       <c r="C84" s="3">
         <v>8104</v>
       </c>
-      <c r="D84" s="8" t="s">
-        <v>246</v>
+      <c r="D84" s="9" t="s">
+        <v>254</v>
       </c>
       <c r="E84" s="3">
         <v>5</v>
       </c>
       <c r="F84" s="3" t="s">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="G84" s="3">
         <v>1</v>
@@ -5834,14 +5944,14 @@
       <c r="C85" s="3">
         <v>8105</v>
       </c>
-      <c r="D85" s="8" t="s">
-        <v>247</v>
+      <c r="D85" s="9" t="s">
+        <v>255</v>
       </c>
       <c r="E85" s="3">
         <v>5</v>
       </c>
       <c r="F85" s="3" t="s">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="G85" s="3">
         <v>1</v>
@@ -5866,14 +5976,14 @@
       <c r="C86" s="3">
         <v>8106</v>
       </c>
-      <c r="D86" s="8" t="s">
-        <v>248</v>
+      <c r="D86" s="9" t="s">
+        <v>256</v>
       </c>
       <c r="E86" s="3">
         <v>5</v>
       </c>
       <c r="F86" s="3" t="s">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="G86" s="3">
         <v>1</v>
@@ -5898,14 +6008,14 @@
       <c r="C87" s="3">
         <v>8107</v>
       </c>
-      <c r="D87" s="8" t="s">
-        <v>249</v>
+      <c r="D87" s="9" t="s">
+        <v>257</v>
       </c>
       <c r="E87" s="3">
         <v>5</v>
       </c>
       <c r="F87" s="3" t="s">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="G87" s="3">
         <v>1</v>
@@ -5930,14 +6040,14 @@
       <c r="C88" s="3">
         <v>8108</v>
       </c>
-      <c r="D88" s="8" t="s">
-        <v>250</v>
+      <c r="D88" s="9" t="s">
+        <v>258</v>
       </c>
       <c r="E88" s="3">
         <v>5</v>
       </c>
       <c r="F88" s="3" t="s">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="G88" s="3">
         <v>1</v>
@@ -5962,14 +6072,14 @@
       <c r="C90" s="3">
         <v>8201</v>
       </c>
-      <c r="D90" s="8" t="s">
-        <v>251</v>
+      <c r="D90" s="9" t="s">
+        <v>259</v>
       </c>
       <c r="E90" s="3">
         <v>16</v>
       </c>
       <c r="F90" s="3" t="s">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="G90" s="3">
         <v>1</v>
@@ -5997,14 +6107,14 @@
       <c r="C91" s="3">
         <v>8202</v>
       </c>
-      <c r="D91" s="8" t="s">
-        <v>253</v>
+      <c r="D91" s="9" t="s">
+        <v>261</v>
       </c>
       <c r="E91" s="3">
         <v>16</v>
       </c>
       <c r="F91" s="3" t="s">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="G91" s="3">
         <v>1</v>
@@ -6032,14 +6142,14 @@
       <c r="C92" s="3">
         <v>8203</v>
       </c>
-      <c r="D92" s="8" t="s">
-        <v>255</v>
+      <c r="D92" s="9" t="s">
+        <v>263</v>
       </c>
       <c r="E92" s="3">
         <v>16</v>
       </c>
       <c r="F92" s="3" t="s">
-        <v>256</v>
+        <v>264</v>
       </c>
       <c r="G92" s="3">
         <v>1</v>
@@ -6067,14 +6177,14 @@
       <c r="C93" s="3">
         <v>8204</v>
       </c>
-      <c r="D93" s="8" t="s">
-        <v>257</v>
+      <c r="D93" s="9" t="s">
+        <v>265</v>
       </c>
       <c r="E93" s="3">
         <v>16</v>
       </c>
       <c r="F93" s="3" t="s">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="G93" s="3">
         <v>1</v>
@@ -6102,14 +6212,14 @@
       <c r="C94" s="3">
         <v>8205</v>
       </c>
-      <c r="D94" s="8" t="s">
-        <v>259</v>
+      <c r="D94" s="9" t="s">
+        <v>267</v>
       </c>
       <c r="E94" s="3">
         <v>16</v>
       </c>
       <c r="F94" s="3" t="s">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="G94" s="3">
         <v>1</v>
@@ -6137,14 +6247,14 @@
       <c r="C95" s="3">
         <v>8206</v>
       </c>
-      <c r="D95" s="8" t="s">
-        <v>261</v>
+      <c r="D95" s="9" t="s">
+        <v>269</v>
       </c>
       <c r="E95" s="3">
         <v>16</v>
       </c>
       <c r="F95" s="3" t="s">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="G95" s="3">
         <v>1</v>
@@ -6172,14 +6282,14 @@
       <c r="C96" s="3">
         <v>8207</v>
       </c>
-      <c r="D96" s="8" t="s">
-        <v>263</v>
+      <c r="D96" s="9" t="s">
+        <v>271</v>
       </c>
       <c r="E96" s="3">
         <v>16</v>
       </c>
       <c r="F96" s="3" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="G96" s="3">
         <v>1</v>
@@ -6204,54 +6314,54 @@
       </c>
     </row>
     <row r="98" customHeight="1" spans="4:4">
-      <c r="D98" s="8"/>
+      <c r="D98" s="9"/>
     </row>
     <row r="99" customHeight="1" spans="4:4">
-      <c r="D99" s="8"/>
+      <c r="D99" s="9"/>
     </row>
     <row r="100" customHeight="1" spans="4:4">
-      <c r="D100" s="8"/>
+      <c r="D100" s="9"/>
     </row>
     <row r="101" customHeight="1" spans="4:4">
-      <c r="D101" s="8"/>
+      <c r="D101" s="9"/>
     </row>
     <row r="102" customHeight="1" spans="4:4">
-      <c r="D102" s="8"/>
+      <c r="D102" s="9"/>
     </row>
     <row r="103" customHeight="1" spans="4:4">
-      <c r="D103" s="8"/>
+      <c r="D103" s="9"/>
     </row>
     <row r="104" customHeight="1" spans="4:4">
-      <c r="D104" s="8"/>
+      <c r="D104" s="9"/>
     </row>
     <row r="106" customHeight="1" spans="4:4">
-      <c r="D106" s="8"/>
+      <c r="D106" s="9"/>
     </row>
     <row r="107" customHeight="1" spans="4:4">
-      <c r="D107" s="8"/>
+      <c r="D107" s="9"/>
     </row>
     <row r="108" customHeight="1" spans="4:4">
-      <c r="D108" s="8"/>
+      <c r="D108" s="9"/>
     </row>
     <row r="109" customHeight="1" spans="4:4">
-      <c r="D109" s="8"/>
+      <c r="D109" s="9"/>
     </row>
     <row r="110" customHeight="1" spans="4:4">
-      <c r="D110" s="8"/>
+      <c r="D110" s="9"/>
     </row>
     <row r="111" customHeight="1" spans="4:4">
-      <c r="D111" s="8"/>
+      <c r="D111" s="9"/>
     </row>
     <row r="112" customHeight="1" spans="4:4">
-      <c r="D112" s="8"/>
+      <c r="D112" s="9"/>
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="L3:M5 L8:M15" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C8:D8 C9:C12 C13:D15 C3:D5" errorStyle="warning">
+      <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="L3:M5 L13:M15" errorStyle="warning">
       <formula1>COUNTIF($A:$A,L3)&lt;2</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:D5 C8:D15" errorStyle="warning">
-      <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6389,13 +6499,13 @@
         <v>1999001</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
       <c r="E6" s="2">
         <v>6</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>266</v>
+        <v>274</v>
       </c>
       <c r="G6" s="2">
         <v>1</v>
@@ -6418,13 +6528,13 @@
         <v>1999002</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="E7" s="2">
         <v>6</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>266</v>
+        <v>274</v>
       </c>
       <c r="G7" s="2">
         <v>1</v>
@@ -6447,13 +6557,13 @@
         <v>1999003</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="E8" s="2">
         <v>6</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>266</v>
+        <v>274</v>
       </c>
       <c r="G8" s="2">
         <v>1</v>
@@ -6476,13 +6586,13 @@
         <v>1999004</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="E9" s="2">
         <v>6</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>266</v>
+        <v>274</v>
       </c>
       <c r="G9" s="2">
         <v>1</v>
@@ -6505,13 +6615,13 @@
         <v>1999005</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="E10" s="2">
         <v>6</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>266</v>
+        <v>274</v>
       </c>
       <c r="G10" s="2">
         <v>1</v>
@@ -6534,13 +6644,13 @@
         <v>1999006</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="E11" s="2">
         <v>6</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>266</v>
+        <v>274</v>
       </c>
       <c r="G11" s="2">
         <v>1</v>
@@ -6562,13 +6672,13 @@
         <v>1999007</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="E12" s="2">
         <v>6</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>266</v>
+        <v>274</v>
       </c>
       <c r="G12" s="2">
         <v>1</v>
@@ -6590,13 +6700,13 @@
         <v>1999008</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>273</v>
+        <v>281</v>
       </c>
       <c r="E13" s="2">
         <v>6</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>266</v>
+        <v>274</v>
       </c>
       <c r="G13" s="2">
         <v>1</v>
@@ -6618,13 +6728,13 @@
         <v>1999009</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>274</v>
+        <v>282</v>
       </c>
       <c r="E14" s="2">
         <v>6</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>266</v>
+        <v>274</v>
       </c>
       <c r="G14" s="2">
         <v>1</v>
@@ -6646,13 +6756,13 @@
         <v>1999010</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="E15" s="2">
         <v>6</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>266</v>
+        <v>274</v>
       </c>
       <c r="G15" s="2">
         <v>1</v>
@@ -6674,13 +6784,13 @@
         <v>1999011</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="E16" s="2">
         <v>6</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>266</v>
+        <v>274</v>
       </c>
       <c r="G16" s="2">
         <v>1</v>
@@ -6852,13 +6962,13 @@
         <v>40000001</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="E6" s="2">
         <v>6</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="G6" s="2">
         <v>1</v>
@@ -6879,13 +6989,13 @@
         <v>40000002</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="E7" s="2">
         <v>6</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="G7" s="2">
         <v>1</v>
@@ -6906,13 +7016,13 @@
         <v>40000003</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="E8" s="2">
         <v>6</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="G8" s="2">
         <v>1</v>
@@ -6933,13 +7043,13 @@
         <v>40000004</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="E9" s="2">
         <v>6</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="G9" s="2">
         <v>1</v>
@@ -6960,13 +7070,13 @@
         <v>40000005</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>282</v>
+        <v>290</v>
       </c>
       <c r="E10" s="2">
         <v>6</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="G10" s="2">
         <v>1</v>
@@ -6987,13 +7097,13 @@
         <v>40000006</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>283</v>
+        <v>291</v>
       </c>
       <c r="E11" s="2">
         <v>6</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="G11" s="2">
         <v>1</v>

--- a/Excel/ItemConfig.xlsx
+++ b/Excel/ItemConfig.xlsx
@@ -3693,7 +3693,7 @@
         <v>1</v>
       </c>
       <c r="H6" s="3">
-        <v>99999999999</v>
+        <v>99999999</v>
       </c>
       <c r="I6" s="3">
         <v>0</v>
@@ -3726,7 +3726,7 @@
         <v>1</v>
       </c>
       <c r="H7" s="3">
-        <v>99999999999</v>
+        <v>99999999</v>
       </c>
       <c r="I7" s="3">
         <v>0</v>
@@ -3772,7 +3772,7 @@
         <v>1</v>
       </c>
       <c r="H9" s="3">
-        <v>99999999999</v>
+        <v>99999999</v>
       </c>
       <c r="I9" s="3">
         <v>0</v>
@@ -3805,7 +3805,7 @@
         <v>1</v>
       </c>
       <c r="H10" s="3">
-        <v>99999999999</v>
+        <v>99999999</v>
       </c>
       <c r="I10" s="3">
         <v>0</v>
@@ -3838,7 +3838,7 @@
         <v>1</v>
       </c>
       <c r="H11" s="3">
-        <v>99999999999</v>
+        <v>99999999</v>
       </c>
       <c r="I11" s="3">
         <v>0</v>
@@ -3871,7 +3871,7 @@
         <v>1</v>
       </c>
       <c r="H12" s="3">
-        <v>99999999999</v>
+        <v>99999999</v>
       </c>
       <c r="I12" s="3">
         <v>0</v>
@@ -4112,7 +4112,7 @@
         <v>5</v>
       </c>
       <c r="K21" s="3">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="L21" s="3">
         <v>0</v>
@@ -4563,7 +4563,7 @@
         <v>7</v>
       </c>
       <c r="K35" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="L35" s="3">
         <v>0</v>
@@ -6357,7 +6357,7 @@
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C8:D8 C9:C12 C13:D15 C3:D5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C8:D8 C9:C12 C3:D5 C13:D15" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
     <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="L3:M5 L13:M15" errorStyle="warning">

--- a/Excel/ItemConfig.xlsx
+++ b/Excel/ItemConfig.xlsx
@@ -591,7 +591,7 @@
     <t>学习或者升级道士技能召唤白虎</t>
   </si>
   <si>
-    <t>铁矿石</t>
+    <t>铜矿石</t>
   </si>
   <si>
     <t>装备强化材料</t>

--- a/Excel/ItemConfig.xlsx
+++ b/Excel/ItemConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="1"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="技能" sheetId="1" r:id="rId1"/>
@@ -184,7 +184,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="292">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="498" uniqueCount="291">
   <si>
     <t>_Id</t>
   </si>
@@ -267,9 +267,6 @@
     <t>10000</t>
   </si>
   <si>
-    <t>50</t>
-  </si>
-  <si>
     <t>1002</t>
   </si>
   <si>
@@ -624,6 +621,18 @@
     <t>灵珠进阶材料</t>
   </si>
   <si>
+    <t>等级丹</t>
+  </si>
+  <si>
+    <t>人物等级+1</t>
+  </si>
+  <si>
+    <t>天赋秘籍</t>
+  </si>
+  <si>
+    <t>天赋经验+500</t>
+  </si>
+  <si>
     <t>魂环碎片</t>
   </si>
   <si>
@@ -702,12 +711,6 @@
     <t>传世挑战次数+1</t>
   </si>
   <si>
-    <t>等级丹</t>
-  </si>
-  <si>
-    <t>人物等级+1</t>
-  </si>
-  <si>
     <t>红装粉尘</t>
   </si>
   <si>
@@ -736,12 +739,6 @@
   </si>
   <si>
     <t>分解金装获取，金装升阶材料</t>
-  </si>
-  <si>
-    <t>天赋秘籍</t>
-  </si>
-  <si>
-    <t>天赋经验+500</t>
   </si>
   <si>
     <t>改造石</t>
@@ -2209,13 +2206,13 @@
         <v>99999999</v>
       </c>
       <c r="I6" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" s="3">
         <v>3</v>
       </c>
-      <c r="K6" s="3" t="s">
-        <v>27</v>
+      <c r="K6" s="3">
+        <v>0</v>
       </c>
       <c r="L6" s="3">
         <v>0</v>
@@ -2226,16 +2223,16 @@
     </row>
     <row r="7" customHeight="1" spans="1:13">
       <c r="C7" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D7" s="6" t="s">
         <v>28</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>29</v>
       </c>
       <c r="E7" s="3">
         <v>4</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>26</v>
@@ -2244,13 +2241,13 @@
         <v>99999999</v>
       </c>
       <c r="I7" s="3">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J7" s="3">
         <v>3</v>
       </c>
-      <c r="K7" s="3" t="s">
-        <v>27</v>
+      <c r="K7" s="3">
+        <v>0</v>
       </c>
       <c r="L7" s="3">
         <v>0</v>
@@ -2261,16 +2258,16 @@
     </row>
     <row r="8" customHeight="1" spans="1:13">
       <c r="C8" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" s="6" t="s">
         <v>31</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>32</v>
       </c>
       <c r="E8" s="3">
         <v>4</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>26</v>
@@ -2279,13 +2276,13 @@
         <v>99999999</v>
       </c>
       <c r="I8" s="3">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="J8" s="3">
         <v>3</v>
       </c>
-      <c r="K8" s="3" t="s">
-        <v>27</v>
+      <c r="K8" s="3">
+        <v>0</v>
       </c>
       <c r="L8" s="3">
         <v>0</v>
@@ -2296,31 +2293,31 @@
     </row>
     <row r="9" customHeight="1" spans="1:13">
       <c r="C9" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D9" s="6" t="s">
         <v>34</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>35</v>
       </c>
       <c r="E9" s="3">
         <v>4</v>
       </c>
       <c r="F9" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G9" s="3" t="s">
         <v>36</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>37</v>
       </c>
       <c r="H9" s="3">
         <v>99999999</v>
       </c>
       <c r="I9" s="3">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="J9" s="3">
         <v>3</v>
       </c>
-      <c r="K9" s="3" t="s">
-        <v>27</v>
+      <c r="K9" s="3">
+        <v>0</v>
       </c>
       <c r="L9" s="3">
         <v>0</v>
@@ -2331,31 +2328,31 @@
     </row>
     <row r="10" customHeight="1" spans="1:13">
       <c r="C10" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D10" s="6" t="s">
         <v>38</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>39</v>
       </c>
       <c r="E10" s="3">
         <v>4</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H10" s="3">
         <v>99999999</v>
       </c>
       <c r="I10" s="3">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="J10" s="3">
         <v>4</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>27</v>
+      <c r="K10" s="3">
+        <v>0</v>
       </c>
       <c r="L10" s="3">
         <v>0</v>
@@ -2366,31 +2363,31 @@
     </row>
     <row r="11" customHeight="1" spans="1:13">
       <c r="C11" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D11" s="6" t="s">
         <v>41</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>42</v>
       </c>
       <c r="E11" s="3">
         <v>4</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H11" s="3">
         <v>99999999</v>
       </c>
       <c r="I11" s="3">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="J11" s="3">
         <v>4</v>
       </c>
-      <c r="K11" s="3" t="s">
-        <v>27</v>
+      <c r="K11" s="3">
+        <v>0</v>
       </c>
       <c r="L11" s="3">
         <v>0</v>
@@ -2401,31 +2398,31 @@
     </row>
     <row r="12" customHeight="1" spans="1:13">
       <c r="C12" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D12" s="6" t="s">
         <v>44</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>45</v>
       </c>
       <c r="E12" s="3">
         <v>4</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H12" s="3">
         <v>99999999</v>
       </c>
       <c r="I12" s="3">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="J12" s="3">
         <v>4</v>
       </c>
-      <c r="K12" s="3" t="s">
-        <v>27</v>
+      <c r="K12" s="3">
+        <v>0</v>
       </c>
       <c r="L12" s="3">
         <v>0</v>
@@ -2436,37 +2433,37 @@
     </row>
     <row r="13" customHeight="1" spans="1:13">
       <c r="A13" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C13" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="B13" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="C13" s="11" t="s">
+      <c r="D13" s="6" t="s">
         <v>48</v>
-      </c>
-      <c r="D13" s="6" t="s">
-        <v>49</v>
       </c>
       <c r="E13" s="3">
         <v>4</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H13" s="3">
         <v>99999999</v>
       </c>
       <c r="I13" s="3">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="J13" s="3">
         <v>5</v>
       </c>
-      <c r="K13" s="3" t="s">
-        <v>27</v>
+      <c r="K13" s="3">
+        <v>0</v>
       </c>
       <c r="L13" s="3">
         <v>0</v>
@@ -2477,25 +2474,25 @@
     </row>
     <row r="14" customHeight="1" spans="1:13">
       <c r="A14" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C14" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="D14" s="6" t="s">
         <v>51</v>
-      </c>
-      <c r="D14" s="6" t="s">
-        <v>52</v>
       </c>
       <c r="E14" s="3">
         <v>4</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H14" s="3">
         <v>99999999</v>
@@ -2507,7 +2504,7 @@
         <v>5</v>
       </c>
       <c r="K14" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="L14" s="3">
         <v>0</v>
@@ -2518,25 +2515,25 @@
     </row>
     <row r="15" customHeight="1" spans="1:13">
       <c r="A15" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C15" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="D15" s="6" t="s">
         <v>54</v>
-      </c>
-      <c r="D15" s="6" t="s">
-        <v>55</v>
       </c>
       <c r="E15" s="3">
         <v>4</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H15" s="3">
         <v>99999999</v>
@@ -2548,7 +2545,7 @@
         <v>6</v>
       </c>
       <c r="K15" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="L15" s="3">
         <v>0</v>
@@ -2559,25 +2556,25 @@
     </row>
     <row r="16" customHeight="1" spans="1:13">
       <c r="A16" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C16" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="D16" s="6" t="s">
         <v>57</v>
-      </c>
-      <c r="D16" s="6" t="s">
-        <v>58</v>
       </c>
       <c r="E16" s="3">
         <v>4</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H16" s="3">
         <v>99999999</v>
@@ -2589,7 +2586,7 @@
         <v>7</v>
       </c>
       <c r="K16" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="L16" s="3">
         <v>0</v>
@@ -2600,25 +2597,25 @@
     </row>
     <row r="17" customHeight="1" spans="1:13">
       <c r="A17" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C17" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="D17" s="6" t="s">
         <v>60</v>
-      </c>
-      <c r="D17" s="6" t="s">
-        <v>61</v>
       </c>
       <c r="E17" s="3">
         <v>4</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H17" s="3">
         <v>99999999</v>
@@ -2630,7 +2627,7 @@
         <v>8</v>
       </c>
       <c r="K17" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="L17" s="3">
         <v>0</v>
@@ -2641,16 +2638,16 @@
     </row>
     <row r="19" customHeight="1" spans="1:13">
       <c r="C19" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D19" s="6" t="s">
         <v>63</v>
-      </c>
-      <c r="D19" s="6" t="s">
-        <v>64</v>
       </c>
       <c r="E19" s="3">
         <v>4</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>26</v>
@@ -2659,13 +2656,13 @@
         <v>99999999</v>
       </c>
       <c r="I19" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J19" s="3">
         <v>3</v>
       </c>
-      <c r="K19" s="3" t="s">
-        <v>27</v>
+      <c r="K19" s="3">
+        <v>0</v>
       </c>
       <c r="L19" s="3">
         <v>0</v>
@@ -2676,16 +2673,16 @@
     </row>
     <row r="20" customHeight="1" spans="1:13">
       <c r="C20" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D20" s="6" t="s">
         <v>66</v>
-      </c>
-      <c r="D20" s="6" t="s">
-        <v>67</v>
       </c>
       <c r="E20" s="3">
         <v>4</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>26</v>
@@ -2694,13 +2691,13 @@
         <v>99999999</v>
       </c>
       <c r="I20" s="3">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J20" s="3">
         <v>3</v>
       </c>
-      <c r="K20" s="3" t="s">
-        <v>27</v>
+      <c r="K20" s="3">
+        <v>0</v>
       </c>
       <c r="L20" s="3">
         <v>0</v>
@@ -2711,16 +2708,16 @@
     </row>
     <row r="21" customHeight="1" spans="1:13">
       <c r="C21" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D21" s="6" t="s">
         <v>69</v>
-      </c>
-      <c r="D21" s="6" t="s">
-        <v>70</v>
       </c>
       <c r="E21" s="3">
         <v>4</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>26</v>
@@ -2729,13 +2726,13 @@
         <v>99999999</v>
       </c>
       <c r="I21" s="3">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="J21" s="3">
         <v>3</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>27</v>
+      <c r="K21" s="3">
+        <v>0</v>
       </c>
       <c r="L21" s="3">
         <v>0</v>
@@ -2746,31 +2743,31 @@
     </row>
     <row r="22" customHeight="1" spans="1:13">
       <c r="C22" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="D22" s="6" t="s">
         <v>72</v>
-      </c>
-      <c r="D22" s="6" t="s">
-        <v>73</v>
       </c>
       <c r="E22" s="3">
         <v>4</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H22" s="3">
         <v>99999999</v>
       </c>
       <c r="I22" s="3">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="J22" s="3">
         <v>3</v>
       </c>
-      <c r="K22" s="3" t="s">
-        <v>27</v>
+      <c r="K22" s="3">
+        <v>0</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
@@ -2781,31 +2778,31 @@
     </row>
     <row r="23" customHeight="1" spans="1:13">
       <c r="C23" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D23" s="6" t="s">
         <v>75</v>
-      </c>
-      <c r="D23" s="6" t="s">
-        <v>76</v>
       </c>
       <c r="E23" s="3">
         <v>4</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H23" s="3">
         <v>99999999</v>
       </c>
       <c r="I23" s="3">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="J23" s="3">
         <v>4</v>
       </c>
-      <c r="K23" s="3" t="s">
-        <v>27</v>
+      <c r="K23" s="3">
+        <v>0</v>
       </c>
       <c r="L23" s="3">
         <v>0</v>
@@ -2816,31 +2813,31 @@
     </row>
     <row r="24" customHeight="1" spans="1:13">
       <c r="C24" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="D24" s="6" t="s">
         <v>78</v>
-      </c>
-      <c r="D24" s="6" t="s">
-        <v>79</v>
       </c>
       <c r="E24" s="3">
         <v>4</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H24" s="3">
         <v>99999999</v>
       </c>
       <c r="I24" s="3">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="J24" s="3">
         <v>4</v>
       </c>
-      <c r="K24" s="3" t="s">
-        <v>27</v>
+      <c r="K24" s="3">
+        <v>0</v>
       </c>
       <c r="L24" s="3">
         <v>0</v>
@@ -2851,31 +2848,31 @@
     </row>
     <row r="25" customHeight="1" spans="1:13">
       <c r="C25" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="D25" s="6" t="s">
         <v>81</v>
-      </c>
-      <c r="D25" s="6" t="s">
-        <v>82</v>
       </c>
       <c r="E25" s="3">
         <v>4</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H25" s="3">
         <v>99999999</v>
       </c>
       <c r="I25" s="3">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="J25" s="3">
         <v>4</v>
       </c>
-      <c r="K25" s="3" t="s">
-        <v>27</v>
+      <c r="K25" s="3">
+        <v>0</v>
       </c>
       <c r="L25" s="3">
         <v>0</v>
@@ -2886,37 +2883,37 @@
     </row>
     <row r="26" customHeight="1" spans="1:13">
       <c r="A26" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C26" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="D26" s="6" t="s">
         <v>84</v>
-      </c>
-      <c r="D26" s="6" t="s">
-        <v>85</v>
       </c>
       <c r="E26" s="3">
         <v>4</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H26" s="3">
         <v>99999999</v>
       </c>
       <c r="I26" s="3">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="J26" s="3">
         <v>5</v>
       </c>
-      <c r="K26" s="3" t="s">
-        <v>27</v>
+      <c r="K26" s="3">
+        <v>0</v>
       </c>
       <c r="L26" s="3">
         <v>0</v>
@@ -2927,25 +2924,25 @@
     </row>
     <row r="27" customHeight="1" spans="1:13">
       <c r="A27" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C27" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="D27" s="6" t="s">
         <v>87</v>
-      </c>
-      <c r="D27" s="6" t="s">
-        <v>88</v>
       </c>
       <c r="E27" s="3">
         <v>4</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H27" s="3">
         <v>99999999</v>
@@ -2957,7 +2954,7 @@
         <v>5</v>
       </c>
       <c r="K27" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="L27" s="3">
         <v>0</v>
@@ -2968,25 +2965,25 @@
     </row>
     <row r="28" customHeight="1" spans="1:13">
       <c r="A28" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C28" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="D28" s="6" t="s">
         <v>90</v>
-      </c>
-      <c r="D28" s="6" t="s">
-        <v>91</v>
       </c>
       <c r="E28" s="3">
         <v>4</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H28" s="3">
         <v>99999999</v>
@@ -2998,7 +2995,7 @@
         <v>6</v>
       </c>
       <c r="K28" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="L28" s="3">
         <v>0</v>
@@ -3009,25 +3006,25 @@
     </row>
     <row r="29" customHeight="1" spans="1:13">
       <c r="A29" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C29" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="D29" s="6" t="s">
         <v>93</v>
-      </c>
-      <c r="D29" s="6" t="s">
-        <v>94</v>
       </c>
       <c r="E29" s="3">
         <v>4</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H29" s="3">
         <v>99999999</v>
@@ -3039,7 +3036,7 @@
         <v>7</v>
       </c>
       <c r="K29" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="L29" s="3">
         <v>0</v>
@@ -3050,25 +3047,25 @@
     </row>
     <row r="30" customHeight="1" spans="1:13">
       <c r="A30" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C30" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="D30" s="6" t="s">
         <v>96</v>
-      </c>
-      <c r="D30" s="6" t="s">
-        <v>97</v>
       </c>
       <c r="E30" s="3">
         <v>4</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H30" s="3">
         <v>99999999</v>
@@ -3080,7 +3077,7 @@
         <v>8</v>
       </c>
       <c r="K30" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="L30" s="3">
         <v>0</v>
@@ -3091,16 +3088,16 @@
     </row>
     <row r="32" customHeight="1" spans="1:13">
       <c r="C32" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="D32" s="6" t="s">
         <v>99</v>
-      </c>
-      <c r="D32" s="6" t="s">
-        <v>100</v>
       </c>
       <c r="E32" s="3">
         <v>4</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>26</v>
@@ -3109,13 +3106,13 @@
         <v>99999999</v>
       </c>
       <c r="I32" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J32" s="3">
         <v>3</v>
       </c>
-      <c r="K32" s="3" t="s">
-        <v>27</v>
+      <c r="K32" s="3">
+        <v>0</v>
       </c>
       <c r="L32" s="3">
         <v>0</v>
@@ -3126,16 +3123,16 @@
     </row>
     <row r="33" customHeight="1" spans="1:13">
       <c r="C33" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="D33" s="6" t="s">
         <v>102</v>
-      </c>
-      <c r="D33" s="6" t="s">
-        <v>103</v>
       </c>
       <c r="E33" s="3">
         <v>4</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>26</v>
@@ -3144,13 +3141,13 @@
         <v>99999999</v>
       </c>
       <c r="I33" s="3">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J33" s="3">
         <v>3</v>
       </c>
-      <c r="K33" s="3" t="s">
-        <v>27</v>
+      <c r="K33" s="3">
+        <v>0</v>
       </c>
       <c r="L33" s="3">
         <v>0</v>
@@ -3161,16 +3158,16 @@
     </row>
     <row r="34" customHeight="1" spans="1:13">
       <c r="C34" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="D34" s="6" t="s">
         <v>105</v>
-      </c>
-      <c r="D34" s="6" t="s">
-        <v>106</v>
       </c>
       <c r="E34" s="3">
         <v>4</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G34" s="3" t="s">
         <v>26</v>
@@ -3179,13 +3176,13 @@
         <v>99999999</v>
       </c>
       <c r="I34" s="3">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="J34" s="3">
         <v>3</v>
       </c>
-      <c r="K34" s="3" t="s">
-        <v>27</v>
+      <c r="K34" s="3">
+        <v>0</v>
       </c>
       <c r="L34" s="3">
         <v>0</v>
@@ -3196,31 +3193,31 @@
     </row>
     <row r="35" customHeight="1" spans="1:13">
       <c r="C35" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="D35" s="6" t="s">
         <v>108</v>
-      </c>
-      <c r="D35" s="6" t="s">
-        <v>109</v>
       </c>
       <c r="E35" s="3">
         <v>4</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H35" s="3">
         <v>99999999</v>
       </c>
       <c r="I35" s="3">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="J35" s="3">
         <v>3</v>
       </c>
-      <c r="K35" s="3" t="s">
-        <v>27</v>
+      <c r="K35" s="3">
+        <v>0</v>
       </c>
       <c r="L35" s="3">
         <v>0</v>
@@ -3231,31 +3228,31 @@
     </row>
     <row r="36" customHeight="1" spans="1:13">
       <c r="C36" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="D36" s="6" t="s">
         <v>111</v>
-      </c>
-      <c r="D36" s="6" t="s">
-        <v>112</v>
       </c>
       <c r="E36" s="3">
         <v>4</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H36" s="3">
         <v>99999999</v>
       </c>
       <c r="I36" s="3">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="J36" s="3">
         <v>4</v>
       </c>
-      <c r="K36" s="3" t="s">
-        <v>27</v>
+      <c r="K36" s="3">
+        <v>0</v>
       </c>
       <c r="L36" s="3">
         <v>0</v>
@@ -3266,31 +3263,31 @@
     </row>
     <row r="37" customHeight="1" spans="1:13">
       <c r="C37" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="D37" s="6" t="s">
         <v>114</v>
-      </c>
-      <c r="D37" s="6" t="s">
-        <v>115</v>
       </c>
       <c r="E37" s="3">
         <v>4</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H37" s="3">
         <v>99999999</v>
       </c>
       <c r="I37" s="3">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="J37" s="3">
         <v>4</v>
       </c>
-      <c r="K37" s="3" t="s">
-        <v>27</v>
+      <c r="K37" s="3">
+        <v>0</v>
       </c>
       <c r="L37" s="3">
         <v>0</v>
@@ -3301,31 +3298,31 @@
     </row>
     <row r="38" customHeight="1" spans="1:13">
       <c r="C38" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="D38" s="6" t="s">
         <v>117</v>
-      </c>
-      <c r="D38" s="6" t="s">
-        <v>118</v>
       </c>
       <c r="E38" s="3">
         <v>4</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H38" s="3">
         <v>99999999</v>
       </c>
       <c r="I38" s="3">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="J38" s="3">
         <v>4</v>
       </c>
-      <c r="K38" s="3" t="s">
-        <v>27</v>
+      <c r="K38" s="3">
+        <v>0</v>
       </c>
       <c r="L38" s="3">
         <v>0</v>
@@ -3336,37 +3333,37 @@
     </row>
     <row r="39" customHeight="1" spans="1:13">
       <c r="A39" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C39" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="D39" s="6" t="s">
         <v>120</v>
-      </c>
-      <c r="D39" s="6" t="s">
-        <v>121</v>
       </c>
       <c r="E39" s="3">
         <v>4</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H39" s="3">
         <v>99999999</v>
       </c>
       <c r="I39" s="3">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="J39" s="3">
         <v>5</v>
       </c>
-      <c r="K39" s="3" t="s">
-        <v>27</v>
+      <c r="K39" s="3">
+        <v>0</v>
       </c>
       <c r="L39" s="3">
         <v>0</v>
@@ -3377,25 +3374,25 @@
     </row>
     <row r="40" customHeight="1" spans="1:13">
       <c r="A40" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C40" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="D40" s="6" t="s">
         <v>123</v>
-      </c>
-      <c r="D40" s="6" t="s">
-        <v>124</v>
       </c>
       <c r="E40" s="3">
         <v>4</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H40" s="3">
         <v>99999999</v>
@@ -3407,7 +3404,7 @@
         <v>5</v>
       </c>
       <c r="K40" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="L40" s="3">
         <v>0</v>
@@ -3418,25 +3415,25 @@
     </row>
     <row r="41" customHeight="1" spans="1:13">
       <c r="A41" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C41" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="D41" s="6" t="s">
         <v>126</v>
-      </c>
-      <c r="D41" s="6" t="s">
-        <v>127</v>
       </c>
       <c r="E41" s="3">
         <v>4</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H41" s="3">
         <v>99999999</v>
@@ -3448,7 +3445,7 @@
         <v>6</v>
       </c>
       <c r="K41" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="L41" s="3">
         <v>0</v>
@@ -3459,25 +3456,25 @@
     </row>
     <row r="42" customHeight="1" spans="1:13">
       <c r="A42" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C42" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="D42" s="6" t="s">
         <v>129</v>
-      </c>
-      <c r="D42" s="6" t="s">
-        <v>130</v>
       </c>
       <c r="E42" s="3">
         <v>4</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H42" s="3">
         <v>99999999</v>
@@ -3489,7 +3486,7 @@
         <v>7</v>
       </c>
       <c r="K42" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="L42" s="3">
         <v>0</v>
@@ -3500,25 +3497,25 @@
     </row>
     <row r="43" customHeight="1" spans="1:13">
       <c r="A43" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C43" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="D43" s="6" t="s">
         <v>132</v>
-      </c>
-      <c r="D43" s="6" t="s">
-        <v>133</v>
       </c>
       <c r="E43" s="3">
         <v>4</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H43" s="3">
         <v>99999999</v>
@@ -3530,7 +3527,7 @@
         <v>8</v>
       </c>
       <c r="K43" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="L43" s="3">
         <v>0</v>
@@ -3681,13 +3678,13 @@
         <v>5001</v>
       </c>
       <c r="D6" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="E6" s="3">
+        <v>5</v>
+      </c>
+      <c r="F6" s="3" t="s">
         <v>135</v>
-      </c>
-      <c r="E6" s="3">
-        <v>5</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>136</v>
       </c>
       <c r="G6" s="3">
         <v>1</v>
@@ -3714,13 +3711,13 @@
         <v>5002</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E7" s="3">
         <v>5</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G7" s="3">
         <v>1</v>
@@ -3760,13 +3757,13 @@
         <v>5011</v>
       </c>
       <c r="D9" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="E9" s="10">
+        <v>5</v>
+      </c>
+      <c r="F9" s="3" t="s">
         <v>138</v>
-      </c>
-      <c r="E9" s="10">
-        <v>5</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>139</v>
       </c>
       <c r="G9" s="3">
         <v>1</v>
@@ -3793,13 +3790,13 @@
         <v>5012</v>
       </c>
       <c r="D10" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="E10" s="10">
+        <v>5</v>
+      </c>
+      <c r="F10" s="3" t="s">
         <v>140</v>
-      </c>
-      <c r="E10" s="10">
-        <v>5</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>141</v>
       </c>
       <c r="G10" s="3">
         <v>1</v>
@@ -3826,13 +3823,13 @@
         <v>5013</v>
       </c>
       <c r="D11" s="9" t="s">
+        <v>141</v>
+      </c>
+      <c r="E11" s="10">
+        <v>5</v>
+      </c>
+      <c r="F11" s="3" t="s">
         <v>142</v>
-      </c>
-      <c r="E11" s="10">
-        <v>5</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>143</v>
       </c>
       <c r="G11" s="3">
         <v>1</v>
@@ -3859,13 +3856,13 @@
         <v>5014</v>
       </c>
       <c r="D12" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="E12" s="10">
+        <v>5</v>
+      </c>
+      <c r="F12" s="3" t="s">
         <v>144</v>
-      </c>
-      <c r="E12" s="10">
-        <v>5</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>145</v>
       </c>
       <c r="G12" s="3">
         <v>1</v>
@@ -3900,76 +3897,85 @@
       <c r="L13" s="7"/>
       <c r="M13" s="7"/>
     </row>
-    <row r="14" s="6" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C14" s="7"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="7"/>
-      <c r="G14" s="7"/>
-      <c r="H14" s="7"/>
-      <c r="I14" s="7"/>
-      <c r="J14" s="7"/>
-      <c r="K14" s="7"/>
-      <c r="L14" s="7"/>
-      <c r="M14" s="7"/>
-    </row>
-    <row r="15" s="6" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C15" s="7"/>
-      <c r="D15" s="7"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="7"/>
-      <c r="G15" s="7"/>
-      <c r="H15" s="7"/>
-      <c r="I15" s="7"/>
-      <c r="J15" s="7"/>
-      <c r="K15" s="7"/>
-      <c r="L15" s="7"/>
-      <c r="M15" s="7"/>
-    </row>
-    <row r="16" s="3" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C16" s="3">
-        <v>4001</v>
-      </c>
-      <c r="D16" s="3" t="s">
+    <row r="14" s="3" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C14" s="3">
+        <v>5101</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="E14" s="3">
+        <v>7</v>
+      </c>
+      <c r="F14" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="E16" s="3">
-        <v>5</v>
-      </c>
-      <c r="F16" s="3" t="s">
+      <c r="G14" s="3">
+        <v>1</v>
+      </c>
+      <c r="H14" s="3">
+        <v>9999999</v>
+      </c>
+      <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3">
+        <v>6</v>
+      </c>
+      <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" s="3" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C15" s="3">
+        <v>5102</v>
+      </c>
+      <c r="D15" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="G16" s="3">
-        <v>1</v>
-      </c>
-      <c r="H16" s="3">
-        <v>99999999999</v>
-      </c>
-      <c r="I16" s="3">
-        <v>0</v>
-      </c>
-      <c r="J16" s="3">
-        <v>5</v>
-      </c>
-      <c r="L16" s="3">
-        <v>0</v>
-      </c>
-      <c r="M16" s="3">
+      <c r="E15" s="3">
+        <v>15</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="G15" s="3">
+        <v>1</v>
+      </c>
+      <c r="H15" s="3">
+        <v>9999999</v>
+      </c>
+      <c r="I15" s="3">
+        <v>0</v>
+      </c>
+      <c r="J15" s="3">
+        <v>7</v>
+      </c>
+      <c r="K15" s="3">
+        <v>0</v>
+      </c>
+      <c r="L15" s="3">
+        <v>0</v>
+      </c>
+      <c r="M15" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="17" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C17" s="3">
-        <v>4002</v>
+        <v>4001</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E17" s="3">
         <v>5</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G17" s="3">
         <v>1</v>
@@ -3992,22 +3998,22 @@
     </row>
     <row r="18" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C18" s="3">
-        <v>4003</v>
+        <v>4002</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E18" s="3">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="G18" s="3">
         <v>1</v>
       </c>
       <c r="H18" s="3">
-        <v>9999999</v>
+        <v>99999999999</v>
       </c>
       <c r="I18" s="3">
         <v>0</v>
@@ -4024,16 +4030,16 @@
     </row>
     <row r="19" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C19" s="3">
-        <v>4004</v>
+        <v>4003</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E19" s="3">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="G19" s="3">
         <v>1</v>
@@ -4056,16 +4062,16 @@
     </row>
     <row r="20" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C20" s="3">
-        <v>4005</v>
+        <v>4004</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E20" s="3">
         <v>5</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="G20" s="3">
         <v>1</v>
@@ -4088,31 +4094,28 @@
     </row>
     <row r="21" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C21" s="3">
-        <v>4006</v>
+        <v>4005</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E21" s="3">
         <v>5</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G21" s="3">
         <v>1</v>
       </c>
       <c r="H21" s="3">
-        <v>99999999</v>
+        <v>9999999</v>
       </c>
       <c r="I21" s="3">
         <v>0</v>
       </c>
       <c r="J21" s="3">
         <v>5</v>
-      </c>
-      <c r="K21" s="3">
-        <v>0</v>
       </c>
       <c r="L21" s="3">
         <v>0</v>
@@ -4123,28 +4126,31 @@
     </row>
     <row r="22" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C22" s="3">
-        <v>4007</v>
+        <v>4006</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E22" s="3">
         <v>5</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G22" s="3">
         <v>1</v>
       </c>
       <c r="H22" s="3">
-        <v>9999999999</v>
+        <v>99999999</v>
       </c>
       <c r="I22" s="3">
         <v>0</v>
       </c>
       <c r="J22" s="3">
         <v>5</v>
+      </c>
+      <c r="K22" s="3">
+        <v>0</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
@@ -4155,22 +4161,22 @@
     </row>
     <row r="23" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C23" s="3">
-        <v>4008</v>
+        <v>4007</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E23" s="3">
         <v>5</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="G23" s="3">
         <v>1</v>
       </c>
       <c r="H23" s="3">
-        <v>9999999</v>
+        <v>9999999999</v>
       </c>
       <c r="I23" s="3">
         <v>0</v>
@@ -4187,16 +4193,16 @@
     </row>
     <row r="24" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C24" s="3">
-        <v>4009</v>
+        <v>4008</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E24" s="3">
         <v>5</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="G24" s="3">
         <v>1</v>
@@ -4219,16 +4225,16 @@
     </row>
     <row r="25" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C25" s="3">
-        <v>4010</v>
+        <v>4009</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E25" s="3">
         <v>5</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="G25" s="3">
         <v>1</v>
@@ -4251,16 +4257,16 @@
     </row>
     <row r="26" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C26" s="3">
-        <v>4011</v>
+        <v>4010</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E26" s="3">
         <v>5</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="G26" s="3">
         <v>1</v>
@@ -4272,7 +4278,7 @@
         <v>0</v>
       </c>
       <c r="J26" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L26" s="3">
         <v>0</v>
@@ -4283,16 +4289,16 @@
     </row>
     <row r="27" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C27" s="3">
-        <v>4012</v>
+        <v>4011</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E27" s="3">
         <v>5</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="G27" s="3">
         <v>1</v>
@@ -4315,16 +4321,16 @@
     </row>
     <row r="28" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C28" s="3">
-        <v>4013</v>
+        <v>4012</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E28" s="3">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="G28" s="3">
         <v>1</v>
@@ -4336,7 +4342,7 @@
         <v>0</v>
       </c>
       <c r="J28" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L28" s="3">
         <v>0</v>
@@ -4347,16 +4353,16 @@
     </row>
     <row r="29" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C29" s="3">
-        <v>4014</v>
+        <v>4013</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E29" s="3">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="G29" s="3">
         <v>1</v>
@@ -4368,7 +4374,7 @@
         <v>0</v>
       </c>
       <c r="J29" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L29" s="3">
         <v>0</v>
@@ -4382,13 +4388,13 @@
         <v>4015</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E30" s="3">
         <v>5</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="G30" s="3">
         <v>1</v>
@@ -4414,13 +4420,13 @@
         <v>4016</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E31" s="3">
         <v>5</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="G31" s="3">
         <v>1</v>
@@ -4446,13 +4452,13 @@
         <v>4017</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E32" s="3">
         <v>9</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="G32" s="3">
         <v>1</v>
@@ -4478,13 +4484,13 @@
         <v>4018</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E33" s="3">
         <v>5</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G33" s="3">
         <v>1</v>
@@ -4510,13 +4516,13 @@
         <v>4019</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E34" s="3">
         <v>5</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="G34" s="3">
         <v>1</v>
@@ -4534,41 +4540,6 @@
         <v>0</v>
       </c>
       <c r="M34" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" s="3" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C35" s="3">
-        <v>4020</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="E35" s="3">
-        <v>15</v>
-      </c>
-      <c r="F35" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="G35" s="3">
-        <v>1</v>
-      </c>
-      <c r="H35" s="3">
-        <v>9999999</v>
-      </c>
-      <c r="I35" s="3">
-        <v>0</v>
-      </c>
-      <c r="J35" s="3">
-        <v>7</v>
-      </c>
-      <c r="K35" s="3">
-        <v>0</v>
-      </c>
-      <c r="L35" s="3">
-        <v>0</v>
-      </c>
-      <c r="M35" s="3">
         <v>0</v>
       </c>
     </row>
@@ -4577,13 +4548,13 @@
         <v>4021</v>
       </c>
       <c r="D36" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="E36" s="3">
+        <v>5</v>
+      </c>
+      <c r="F36" s="3" t="s">
         <v>186</v>
-      </c>
-      <c r="E36" s="3">
-        <v>5</v>
-      </c>
-      <c r="F36" s="3" t="s">
-        <v>187</v>
       </c>
       <c r="G36" s="3">
         <v>1</v>
@@ -4609,13 +4580,13 @@
         <v>4022</v>
       </c>
       <c r="D37" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="E37" s="3">
+        <v>5</v>
+      </c>
+      <c r="F37" s="3" t="s">
         <v>188</v>
-      </c>
-      <c r="E37" s="3">
-        <v>5</v>
-      </c>
-      <c r="F37" s="3" t="s">
-        <v>189</v>
       </c>
       <c r="G37" s="3">
         <v>1</v>
@@ -4641,13 +4612,13 @@
         <v>4023</v>
       </c>
       <c r="D38" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="E38" s="3">
+        <v>5</v>
+      </c>
+      <c r="F38" s="3" t="s">
         <v>190</v>
-      </c>
-      <c r="E38" s="3">
-        <v>5</v>
-      </c>
-      <c r="F38" s="3" t="s">
-        <v>191</v>
       </c>
       <c r="G38" s="3">
         <v>1</v>
@@ -4673,13 +4644,13 @@
         <v>4024</v>
       </c>
       <c r="D39" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="E39" s="3">
+        <v>5</v>
+      </c>
+      <c r="F39" s="3" t="s">
         <v>192</v>
-      </c>
-      <c r="E39" s="3">
-        <v>5</v>
-      </c>
-      <c r="F39" s="3" t="s">
-        <v>193</v>
       </c>
       <c r="G39" s="3">
         <v>1</v>
@@ -4705,13 +4676,13 @@
         <v>4025</v>
       </c>
       <c r="D40" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="E40" s="3">
+        <v>5</v>
+      </c>
+      <c r="F40" s="3" t="s">
         <v>194</v>
-      </c>
-      <c r="E40" s="3">
-        <v>5</v>
-      </c>
-      <c r="F40" s="3" t="s">
-        <v>195</v>
       </c>
       <c r="G40" s="3">
         <v>1</v>
@@ -4737,13 +4708,13 @@
         <v>4026</v>
       </c>
       <c r="D41" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="E41" s="3">
+        <v>5</v>
+      </c>
+      <c r="F41" s="3" t="s">
         <v>196</v>
-      </c>
-      <c r="E41" s="3">
-        <v>5</v>
-      </c>
-      <c r="F41" s="3" t="s">
-        <v>197</v>
       </c>
       <c r="G41" s="3">
         <v>1</v>
@@ -4769,13 +4740,13 @@
         <v>4027</v>
       </c>
       <c r="D42" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="E42" s="3">
+        <v>5</v>
+      </c>
+      <c r="F42" s="3" t="s">
         <v>198</v>
-      </c>
-      <c r="E42" s="3">
-        <v>5</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>199</v>
       </c>
       <c r="G42" s="3">
         <v>1</v>
@@ -4801,13 +4772,13 @@
         <v>4028</v>
       </c>
       <c r="D43" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="E43" s="3">
+        <v>5</v>
+      </c>
+      <c r="F43" s="3" t="s">
         <v>200</v>
-      </c>
-      <c r="E43" s="3">
-        <v>5</v>
-      </c>
-      <c r="F43" s="3" t="s">
-        <v>201</v>
       </c>
       <c r="G43" s="3">
         <v>1</v>
@@ -4833,13 +4804,13 @@
         <v>4029</v>
       </c>
       <c r="D44" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="E44" s="3">
+        <v>5</v>
+      </c>
+      <c r="F44" s="3" t="s">
         <v>202</v>
-      </c>
-      <c r="E44" s="3">
-        <v>5</v>
-      </c>
-      <c r="F44" s="3" t="s">
-        <v>203</v>
       </c>
       <c r="G44" s="3">
         <v>1</v>
@@ -4865,13 +4836,13 @@
         <v>4030</v>
       </c>
       <c r="D45" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="E45" s="3">
+        <v>5</v>
+      </c>
+      <c r="F45" s="3" t="s">
         <v>204</v>
-      </c>
-      <c r="E45" s="3">
-        <v>5</v>
-      </c>
-      <c r="F45" s="3" t="s">
-        <v>205</v>
       </c>
       <c r="G45" s="3">
         <v>1</v>
@@ -4897,13 +4868,13 @@
         <v>4031</v>
       </c>
       <c r="D46" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="E46" s="3">
+        <v>5</v>
+      </c>
+      <c r="F46" s="3" t="s">
         <v>206</v>
-      </c>
-      <c r="E46" s="3">
-        <v>5</v>
-      </c>
-      <c r="F46" s="3" t="s">
-        <v>207</v>
       </c>
       <c r="G46" s="3">
         <v>1</v>
@@ -4929,13 +4900,13 @@
         <v>4032</v>
       </c>
       <c r="D47" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="E47" s="3">
+        <v>5</v>
+      </c>
+      <c r="F47" s="3" t="s">
         <v>208</v>
-      </c>
-      <c r="E47" s="3">
-        <v>5</v>
-      </c>
-      <c r="F47" s="3" t="s">
-        <v>209</v>
       </c>
       <c r="G47" s="3">
         <v>1</v>
@@ -4961,13 +4932,13 @@
         <v>4033</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E48" s="3">
         <v>5</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="G48" s="3">
         <v>1</v>
@@ -4993,13 +4964,13 @@
         <v>4034</v>
       </c>
       <c r="D49" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="E49" s="3">
+        <v>5</v>
+      </c>
+      <c r="F49" s="3" t="s">
         <v>211</v>
-      </c>
-      <c r="E49" s="3">
-        <v>5</v>
-      </c>
-      <c r="F49" s="3" t="s">
-        <v>212</v>
       </c>
       <c r="G49" s="3">
         <v>1</v>
@@ -5025,13 +4996,13 @@
         <v>4035</v>
       </c>
       <c r="D50" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="E50" s="3">
+        <v>5</v>
+      </c>
+      <c r="F50" s="3" t="s">
         <v>213</v>
-      </c>
-      <c r="E50" s="3">
-        <v>5</v>
-      </c>
-      <c r="F50" s="3" t="s">
-        <v>214</v>
       </c>
       <c r="G50" s="3">
         <v>1</v>
@@ -5057,13 +5028,13 @@
         <v>4037</v>
       </c>
       <c r="D51" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="E51" s="3">
+        <v>5</v>
+      </c>
+      <c r="F51" s="3" t="s">
         <v>215</v>
-      </c>
-      <c r="E51" s="3">
-        <v>5</v>
-      </c>
-      <c r="F51" s="3" t="s">
-        <v>216</v>
       </c>
       <c r="G51" s="3">
         <v>1</v>
@@ -5089,13 +5060,13 @@
         <v>4038</v>
       </c>
       <c r="D52" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="E52" s="3">
+        <v>5</v>
+      </c>
+      <c r="F52" s="3" t="s">
         <v>217</v>
-      </c>
-      <c r="E52" s="3">
-        <v>5</v>
-      </c>
-      <c r="F52" s="3" t="s">
-        <v>218</v>
       </c>
       <c r="G52" s="3">
         <v>1</v>
@@ -5121,13 +5092,13 @@
         <v>4039</v>
       </c>
       <c r="D53" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="E53" s="3">
+        <v>5</v>
+      </c>
+      <c r="F53" s="3" t="s">
         <v>219</v>
-      </c>
-      <c r="E53" s="3">
-        <v>5</v>
-      </c>
-      <c r="F53" s="3" t="s">
-        <v>220</v>
       </c>
       <c r="G53" s="3">
         <v>1</v>
@@ -5153,13 +5124,13 @@
         <v>4040</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E54" s="3">
         <v>5</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="G54" s="3">
         <v>1</v>
@@ -5185,13 +5156,13 @@
         <v>4041</v>
       </c>
       <c r="D55" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="E55" s="3">
+        <v>5</v>
+      </c>
+      <c r="F55" s="3" t="s">
         <v>222</v>
-      </c>
-      <c r="E55" s="3">
-        <v>5</v>
-      </c>
-      <c r="F55" s="3" t="s">
-        <v>223</v>
       </c>
       <c r="G55" s="3">
         <v>1</v>
@@ -5217,13 +5188,13 @@
         <v>4042</v>
       </c>
       <c r="D56" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="E56" s="3">
+        <v>5</v>
+      </c>
+      <c r="F56" s="3" t="s">
         <v>224</v>
-      </c>
-      <c r="E56" s="3">
-        <v>5</v>
-      </c>
-      <c r="F56" s="3" t="s">
-        <v>225</v>
       </c>
       <c r="G56" s="3">
         <v>1</v>
@@ -5249,13 +5220,13 @@
         <v>4043</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E57" s="3">
         <v>5</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="G57" s="3">
         <v>1</v>
@@ -5281,13 +5252,13 @@
         <v>4044</v>
       </c>
       <c r="D58" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="E58" s="3">
+        <v>5</v>
+      </c>
+      <c r="F58" s="3" t="s">
         <v>227</v>
-      </c>
-      <c r="E58" s="3">
-        <v>5</v>
-      </c>
-      <c r="F58" s="3" t="s">
-        <v>228</v>
       </c>
       <c r="G58" s="3">
         <v>1</v>
@@ -5325,13 +5296,13 @@
         <v>4101</v>
       </c>
       <c r="D60" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="E60" s="3">
+        <v>5</v>
+      </c>
+      <c r="F60" s="3" t="s">
         <v>229</v>
-      </c>
-      <c r="E60" s="3">
-        <v>5</v>
-      </c>
-      <c r="F60" s="3" t="s">
-        <v>230</v>
       </c>
       <c r="G60" s="3">
         <v>1</v>
@@ -5357,13 +5328,13 @@
         <v>4111</v>
       </c>
       <c r="D61" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="E61" s="3">
+        <v>5</v>
+      </c>
+      <c r="F61" s="3" t="s">
         <v>231</v>
-      </c>
-      <c r="E61" s="3">
-        <v>5</v>
-      </c>
-      <c r="F61" s="3" t="s">
-        <v>232</v>
       </c>
       <c r="G61" s="3">
         <v>1</v>
@@ -5389,13 +5360,13 @@
         <v>4112</v>
       </c>
       <c r="D62" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="E62" s="3">
+        <v>5</v>
+      </c>
+      <c r="F62" s="3" t="s">
         <v>233</v>
-      </c>
-      <c r="E62" s="3">
-        <v>5</v>
-      </c>
-      <c r="F62" s="3" t="s">
-        <v>234</v>
       </c>
       <c r="G62" s="3">
         <v>1</v>
@@ -5421,13 +5392,13 @@
         <v>4113</v>
       </c>
       <c r="D63" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="E63" s="3">
+        <v>5</v>
+      </c>
+      <c r="F63" s="3" t="s">
         <v>235</v>
-      </c>
-      <c r="E63" s="3">
-        <v>5</v>
-      </c>
-      <c r="F63" s="3" t="s">
-        <v>236</v>
       </c>
       <c r="G63" s="3">
         <v>1</v>
@@ -5465,13 +5436,13 @@
         <v>4201</v>
       </c>
       <c r="D65" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="E65" s="3">
+        <v>5</v>
+      </c>
+      <c r="F65" s="3" t="s">
         <v>237</v>
-      </c>
-      <c r="E65" s="3">
-        <v>5</v>
-      </c>
-      <c r="F65" s="3" t="s">
-        <v>238</v>
       </c>
       <c r="G65" s="3">
         <v>1</v>
@@ -5497,13 +5468,13 @@
         <v>8001</v>
       </c>
       <c r="D70" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="E70" s="3">
+        <v>5</v>
+      </c>
+      <c r="F70" s="3" t="s">
         <v>239</v>
-      </c>
-      <c r="E70" s="3">
-        <v>5</v>
-      </c>
-      <c r="F70" s="3" t="s">
-        <v>240</v>
       </c>
       <c r="G70" s="3">
         <v>1</v>
@@ -5529,13 +5500,13 @@
         <v>8002</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E71" s="3">
         <v>5</v>
       </c>
       <c r="F71" s="3" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="G71" s="3">
         <v>1</v>
@@ -5561,13 +5532,13 @@
         <v>8003</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E72" s="3">
         <v>5</v>
       </c>
       <c r="F72" s="3" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="G72" s="3">
         <v>1</v>
@@ -5593,13 +5564,13 @@
         <v>8004</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E73" s="3">
         <v>5</v>
       </c>
       <c r="F73" s="3" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="G73" s="3">
         <v>1</v>
@@ -5625,13 +5596,13 @@
         <v>8005</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="E74" s="3">
         <v>5</v>
       </c>
       <c r="F74" s="3" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="G74" s="3">
         <v>1</v>
@@ -5657,13 +5628,13 @@
         <v>8006</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="E75" s="3">
         <v>5</v>
       </c>
       <c r="F75" s="3" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="G75" s="3">
         <v>1</v>
@@ -5689,13 +5660,13 @@
         <v>8007</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E76" s="3">
         <v>5</v>
       </c>
       <c r="F76" s="3" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="G76" s="3">
         <v>1</v>
@@ -5721,13 +5692,13 @@
         <v>8008</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="E77" s="3">
         <v>5</v>
       </c>
       <c r="F77" s="3" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="G77" s="3">
         <v>1</v>
@@ -5753,13 +5724,13 @@
         <v>8009</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E78" s="3">
         <v>5</v>
       </c>
       <c r="F78" s="3" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="G78" s="3">
         <v>1</v>
@@ -5785,13 +5756,13 @@
         <v>8010</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E79" s="3">
         <v>5</v>
       </c>
       <c r="F79" s="3" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="G79" s="3">
         <v>1</v>
@@ -5817,13 +5788,13 @@
         <v>8101</v>
       </c>
       <c r="D81" s="9" t="s">
+        <v>249</v>
+      </c>
+      <c r="E81" s="3">
+        <v>5</v>
+      </c>
+      <c r="F81" s="3" t="s">
         <v>250</v>
-      </c>
-      <c r="E81" s="3">
-        <v>5</v>
-      </c>
-      <c r="F81" s="3" t="s">
-        <v>251</v>
       </c>
       <c r="G81" s="3">
         <v>1</v>
@@ -5849,13 +5820,13 @@
         <v>8102</v>
       </c>
       <c r="D82" s="9" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E82" s="3">
         <v>5</v>
       </c>
       <c r="F82" s="3" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="G82" s="3">
         <v>1</v>
@@ -5881,13 +5852,13 @@
         <v>8103</v>
       </c>
       <c r="D83" s="9" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="E83" s="3">
         <v>5</v>
       </c>
       <c r="F83" s="3" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="G83" s="3">
         <v>1</v>
@@ -5913,13 +5884,13 @@
         <v>8104</v>
       </c>
       <c r="D84" s="9" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="E84" s="3">
         <v>5</v>
       </c>
       <c r="F84" s="3" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="G84" s="3">
         <v>1</v>
@@ -5945,13 +5916,13 @@
         <v>8105</v>
       </c>
       <c r="D85" s="9" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="E85" s="3">
         <v>5</v>
       </c>
       <c r="F85" s="3" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="G85" s="3">
         <v>1</v>
@@ -5977,13 +5948,13 @@
         <v>8106</v>
       </c>
       <c r="D86" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E86" s="3">
         <v>5</v>
       </c>
       <c r="F86" s="3" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="G86" s="3">
         <v>1</v>
@@ -6009,13 +5980,13 @@
         <v>8107</v>
       </c>
       <c r="D87" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E87" s="3">
         <v>5</v>
       </c>
       <c r="F87" s="3" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="G87" s="3">
         <v>1</v>
@@ -6041,13 +6012,13 @@
         <v>8108</v>
       </c>
       <c r="D88" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E88" s="3">
         <v>5</v>
       </c>
       <c r="F88" s="3" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="G88" s="3">
         <v>1</v>
@@ -6073,13 +6044,13 @@
         <v>8201</v>
       </c>
       <c r="D90" s="9" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E90" s="3">
         <v>16</v>
       </c>
       <c r="F90" s="3" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="G90" s="3">
         <v>1</v>
@@ -6108,13 +6079,13 @@
         <v>8202</v>
       </c>
       <c r="D91" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E91" s="3">
         <v>16</v>
       </c>
       <c r="F91" s="3" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="G91" s="3">
         <v>1</v>
@@ -6143,13 +6114,13 @@
         <v>8203</v>
       </c>
       <c r="D92" s="9" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E92" s="3">
         <v>16</v>
       </c>
       <c r="F92" s="3" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="G92" s="3">
         <v>1</v>
@@ -6178,13 +6149,13 @@
         <v>8204</v>
       </c>
       <c r="D93" s="9" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E93" s="3">
         <v>16</v>
       </c>
       <c r="F93" s="3" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G93" s="3">
         <v>1</v>
@@ -6213,13 +6184,13 @@
         <v>8205</v>
       </c>
       <c r="D94" s="9" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E94" s="3">
         <v>16</v>
       </c>
       <c r="F94" s="3" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="G94" s="3">
         <v>1</v>
@@ -6248,13 +6219,13 @@
         <v>8206</v>
       </c>
       <c r="D95" s="9" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E95" s="3">
         <v>16</v>
       </c>
       <c r="F95" s="3" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="G95" s="3">
         <v>1</v>
@@ -6283,13 +6254,13 @@
         <v>8207</v>
       </c>
       <c r="D96" s="9" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E96" s="3">
         <v>16</v>
       </c>
       <c r="F96" s="3" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G96" s="3">
         <v>1</v>
@@ -6357,10 +6328,10 @@
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C8:D8 C9:C12 C3:D5 C13:D15" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C8:D8 C13:D13 C9:C12 C3:D5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="L3:M5 L13:M15" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="L13:M13 L3:M5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,L3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>
@@ -6499,13 +6470,13 @@
         <v>1999001</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E6" s="2">
         <v>6</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="G6" s="2">
         <v>1</v>
@@ -6528,13 +6499,13 @@
         <v>1999002</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E7" s="2">
         <v>6</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="G7" s="2">
         <v>1</v>
@@ -6557,13 +6528,13 @@
         <v>1999003</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E8" s="2">
         <v>6</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="G8" s="2">
         <v>1</v>
@@ -6586,13 +6557,13 @@
         <v>1999004</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="E9" s="2">
         <v>6</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="G9" s="2">
         <v>1</v>
@@ -6615,13 +6586,13 @@
         <v>1999005</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E10" s="2">
         <v>6</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="G10" s="2">
         <v>1</v>
@@ -6644,13 +6615,13 @@
         <v>1999006</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E11" s="2">
         <v>6</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="G11" s="2">
         <v>1</v>
@@ -6672,13 +6643,13 @@
         <v>1999007</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E12" s="2">
         <v>6</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="G12" s="2">
         <v>1</v>
@@ -6700,13 +6671,13 @@
         <v>1999008</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E13" s="2">
         <v>6</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="G13" s="2">
         <v>1</v>
@@ -6728,13 +6699,13 @@
         <v>1999009</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="E14" s="2">
         <v>6</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="G14" s="2">
         <v>1</v>
@@ -6756,13 +6727,13 @@
         <v>1999010</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="E15" s="2">
         <v>6</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="G15" s="2">
         <v>1</v>
@@ -6784,13 +6755,13 @@
         <v>1999011</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="E16" s="2">
         <v>6</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="G16" s="2">
         <v>1</v>
@@ -6962,13 +6933,13 @@
         <v>40000001</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E6" s="2">
         <v>6</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="G6" s="2">
         <v>1</v>
@@ -6989,13 +6960,13 @@
         <v>40000002</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E7" s="2">
         <v>6</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="G7" s="2">
         <v>1</v>
@@ -7016,13 +6987,13 @@
         <v>40000003</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E8" s="2">
         <v>6</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="G8" s="2">
         <v>1</v>
@@ -7043,13 +7014,13 @@
         <v>40000004</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="E9" s="2">
         <v>6</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="G9" s="2">
         <v>1</v>
@@ -7070,13 +7041,13 @@
         <v>40000005</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="E10" s="2">
         <v>6</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="G10" s="2">
         <v>1</v>
@@ -7097,13 +7068,13 @@
         <v>40000006</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="E11" s="2">
         <v>6</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="G11" s="2">
         <v>1</v>

--- a/Excel/ItemConfig.xlsx
+++ b/Excel/ItemConfig.xlsx
@@ -4,13 +4,14 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView windowHeight="17680" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="技能" sheetId="1" r:id="rId1"/>
     <sheet name="定制配置" sheetId="2" r:id="rId2"/>
     <sheet name="图鉴" sheetId="3" r:id="rId3"/>
-    <sheet name="珍宝材料" sheetId="5" r:id="rId4"/>
+    <sheet name="时装" sheetId="6" r:id="rId4"/>
+    <sheet name="珍宝材料" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -183,8 +184,47 @@
 </comments>
 </file>
 
+<file path=xl/comments5.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>admin</author>
+  </authors>
+  <commentList>
+    <comment ref="E3" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>admin:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+1 金币
+2 装备
+3 技能书
+4.礼包
+5.材料
+6.buff
+7,金币收益
+8,经验收益</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="498" uniqueCount="291">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="541" uniqueCount="297">
   <si>
     <t>_Id</t>
   </si>
@@ -597,6 +637,12 @@
     <t>黑铁石</t>
   </si>
   <si>
+    <t>皮肤碎片</t>
+  </si>
+  <si>
+    <t>激活皮肤的材料</t>
+  </si>
+  <si>
     <t>灵盾碎片</t>
   </si>
   <si>
@@ -1036,6 +1082,18 @@
   </si>
   <si>
     <t>神鉴·红</t>
+  </si>
+  <si>
+    <t>Tap玩家</t>
+  </si>
+  <si>
+    <t>QQ玩家</t>
+  </si>
+  <si>
+    <t>老玩家</t>
+  </si>
+  <si>
+    <t>大佬再临</t>
   </si>
   <si>
     <t>鸡毛</t>
@@ -3555,7 +3613,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:M112"/>
+  <dimension ref="C3:M114"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="3"/>
@@ -3740,54 +3798,54 @@
       </c>
     </row>
     <row r="8" s="6" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
-      <c r="J8" s="3"/>
+      <c r="C8" s="3">
+        <v>5003</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="E8" s="3">
+        <v>5</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="G8" s="3">
+        <v>1</v>
+      </c>
+      <c r="H8" s="3">
+        <v>99999999</v>
+      </c>
+      <c r="I8" s="3">
+        <v>0</v>
+      </c>
+      <c r="J8" s="3">
+        <v>5</v>
+      </c>
       <c r="K8" s="3"/>
-      <c r="L8" s="3"/>
-      <c r="M8" s="3"/>
+      <c r="L8" s="3">
+        <v>0</v>
+      </c>
+      <c r="M8" s="3">
+        <v>0</v>
+      </c>
     </row>
     <row r="9" s="6" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C9" s="8">
-        <v>5011</v>
-      </c>
-      <c r="D9" s="9" t="s">
-        <v>137</v>
-      </c>
-      <c r="E9" s="10">
-        <v>5</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="G9" s="3">
-        <v>1</v>
-      </c>
-      <c r="H9" s="3">
-        <v>99999999</v>
-      </c>
-      <c r="I9" s="3">
-        <v>0</v>
-      </c>
-      <c r="J9" s="3">
-        <v>3</v>
-      </c>
+      <c r="C9" s="7"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="3"/>
+      <c r="H9" s="3"/>
+      <c r="I9" s="3"/>
+      <c r="J9" s="3"/>
       <c r="K9" s="3"/>
-      <c r="L9" s="3">
-        <v>0</v>
-      </c>
-      <c r="M9" s="3">
-        <v>0</v>
-      </c>
+      <c r="L9" s="3"/>
+      <c r="M9" s="3"/>
     </row>
     <row r="10" s="6" customFormat="1" customHeight="1" spans="3:13">
       <c r="C10" s="8">
-        <v>5012</v>
+        <v>5011</v>
       </c>
       <c r="D10" s="9" t="s">
         <v>139</v>
@@ -3820,7 +3878,7 @@
     </row>
     <row r="11" s="6" customFormat="1" customHeight="1" spans="3:13">
       <c r="C11" s="8">
-        <v>5013</v>
+        <v>5012</v>
       </c>
       <c r="D11" s="9" t="s">
         <v>141</v>
@@ -3853,7 +3911,7 @@
     </row>
     <row r="12" s="6" customFormat="1" customHeight="1" spans="3:13">
       <c r="C12" s="8">
-        <v>5014</v>
+        <v>5013</v>
       </c>
       <c r="D12" s="9" t="s">
         <v>143</v>
@@ -3885,59 +3943,60 @@
       </c>
     </row>
     <row r="13" s="6" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C13" s="7"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="7"/>
-      <c r="G13" s="7"/>
-      <c r="H13" s="7"/>
-      <c r="I13" s="7"/>
-      <c r="J13" s="7"/>
-      <c r="K13" s="7"/>
-      <c r="L13" s="7"/>
-      <c r="M13" s="7"/>
-    </row>
-    <row r="14" s="3" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C14" s="3">
-        <v>5101</v>
-      </c>
-      <c r="D14" s="3" t="s">
+      <c r="C13" s="8">
+        <v>5014</v>
+      </c>
+      <c r="D13" s="9" t="s">
         <v>145</v>
       </c>
-      <c r="E14" s="3">
-        <v>7</v>
-      </c>
-      <c r="F14" s="3" t="s">
+      <c r="E13" s="10">
+        <v>5</v>
+      </c>
+      <c r="F13" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="G14" s="3">
-        <v>1</v>
-      </c>
-      <c r="H14" s="3">
-        <v>9999999</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>6</v>
-      </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
+      <c r="G13" s="3">
+        <v>1</v>
+      </c>
+      <c r="H13" s="3">
+        <v>99999999</v>
+      </c>
+      <c r="I13" s="3">
+        <v>0</v>
+      </c>
+      <c r="J13" s="3">
+        <v>3</v>
+      </c>
+      <c r="K13" s="3"/>
+      <c r="L13" s="3">
+        <v>0</v>
+      </c>
+      <c r="M13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" s="6" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C14" s="7"/>
+      <c r="D14" s="7"/>
+      <c r="E14" s="7"/>
+      <c r="F14" s="7"/>
+      <c r="G14" s="7"/>
+      <c r="H14" s="7"/>
+      <c r="I14" s="7"/>
+      <c r="J14" s="7"/>
+      <c r="K14" s="7"/>
+      <c r="L14" s="7"/>
+      <c r="M14" s="7"/>
     </row>
     <row r="15" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C15" s="3">
-        <v>5102</v>
+        <v>7001</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>147</v>
       </c>
       <c r="E15" s="3">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="F15" s="3" t="s">
         <v>148</v>
@@ -3952,100 +4011,80 @@
         <v>0</v>
       </c>
       <c r="J15" s="3">
+        <v>6</v>
+      </c>
+      <c r="L15" s="3">
+        <v>0</v>
+      </c>
+      <c r="M15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" s="3" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C16" s="3">
+        <v>7002</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="E16" s="3">
         <v>7</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
-      <c r="M15" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" s="3" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C17" s="3">
-        <v>4001</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="E17" s="3">
-        <v>5</v>
-      </c>
-      <c r="F17" s="3" t="s">
+      <c r="F16" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="G17" s="3">
-        <v>1</v>
-      </c>
-      <c r="H17" s="3">
-        <v>99999999999</v>
-      </c>
-      <c r="I17" s="3">
-        <v>0</v>
-      </c>
-      <c r="J17" s="3">
-        <v>5</v>
-      </c>
-      <c r="L17" s="3">
-        <v>0</v>
-      </c>
-      <c r="M17" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" s="3" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C18" s="3">
-        <v>4002</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="E18" s="3">
-        <v>5</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="G18" s="3">
-        <v>1</v>
-      </c>
-      <c r="H18" s="3">
-        <v>99999999999</v>
-      </c>
-      <c r="I18" s="3">
-        <v>0</v>
-      </c>
-      <c r="J18" s="3">
-        <v>5</v>
-      </c>
-      <c r="L18" s="3">
-        <v>0</v>
-      </c>
-      <c r="M18" s="3">
-        <v>0</v>
-      </c>
+      <c r="G16" s="3">
+        <v>1</v>
+      </c>
+      <c r="H16" s="3">
+        <v>9999999</v>
+      </c>
+      <c r="I16" s="3">
+        <v>0</v>
+      </c>
+      <c r="J16" s="3">
+        <v>7</v>
+      </c>
+      <c r="K16" s="3">
+        <v>0</v>
+      </c>
+      <c r="L16" s="3">
+        <v>0</v>
+      </c>
+      <c r="M16" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C18" s="3"/>
+      <c r="D18" s="3"/>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
+      <c r="G18" s="3"/>
+      <c r="H18" s="3"/>
+      <c r="I18" s="3"/>
+      <c r="J18" s="3"/>
+      <c r="L18" s="3"/>
+      <c r="M18" s="3"/>
     </row>
     <row r="19" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C19" s="3">
-        <v>4003</v>
+        <v>4001</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="E19" s="3">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="G19" s="3">
         <v>1</v>
       </c>
       <c r="H19" s="3">
-        <v>9999999</v>
+        <v>99999999999</v>
       </c>
       <c r="I19" s="3">
         <v>0</v>
@@ -4062,22 +4101,22 @@
     </row>
     <row r="20" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C20" s="3">
-        <v>4004</v>
+        <v>4002</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="E20" s="3">
         <v>5</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="G20" s="3">
         <v>1</v>
       </c>
       <c r="H20" s="3">
-        <v>9999999</v>
+        <v>99999999999</v>
       </c>
       <c r="I20" s="3">
         <v>0</v>
@@ -4094,16 +4133,16 @@
     </row>
     <row r="21" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C21" s="3">
-        <v>4005</v>
+        <v>4003</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E21" s="3">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="G21" s="3">
         <v>1</v>
@@ -4126,31 +4165,28 @@
     </row>
     <row r="22" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C22" s="3">
-        <v>4006</v>
+        <v>4004</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="E22" s="3">
         <v>5</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="G22" s="3">
         <v>1</v>
       </c>
       <c r="H22" s="3">
-        <v>99999999</v>
+        <v>9999999</v>
       </c>
       <c r="I22" s="3">
         <v>0</v>
       </c>
       <c r="J22" s="3">
         <v>5</v>
-      </c>
-      <c r="K22" s="3">
-        <v>0</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
@@ -4161,22 +4197,22 @@
     </row>
     <row r="23" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C23" s="3">
-        <v>4007</v>
+        <v>4005</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="E23" s="3">
         <v>5</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="G23" s="3">
         <v>1</v>
       </c>
       <c r="H23" s="3">
-        <v>9999999999</v>
+        <v>9999999</v>
       </c>
       <c r="I23" s="3">
         <v>0</v>
@@ -4193,28 +4229,31 @@
     </row>
     <row r="24" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C24" s="3">
-        <v>4008</v>
+        <v>4006</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="E24" s="3">
         <v>5</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="G24" s="3">
         <v>1</v>
       </c>
       <c r="H24" s="3">
-        <v>9999999</v>
+        <v>99999999</v>
       </c>
       <c r="I24" s="3">
         <v>0</v>
       </c>
       <c r="J24" s="3">
         <v>5</v>
+      </c>
+      <c r="K24" s="3">
+        <v>0</v>
       </c>
       <c r="L24" s="3">
         <v>0</v>
@@ -4225,22 +4264,22 @@
     </row>
     <row r="25" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C25" s="3">
-        <v>4009</v>
+        <v>4007</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="E25" s="3">
         <v>5</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="G25" s="3">
         <v>1</v>
       </c>
       <c r="H25" s="3">
-        <v>9999999</v>
+        <v>9999999999</v>
       </c>
       <c r="I25" s="3">
         <v>0</v>
@@ -4257,16 +4296,16 @@
     </row>
     <row r="26" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C26" s="3">
-        <v>4010</v>
+        <v>4008</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="E26" s="3">
         <v>5</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="G26" s="3">
         <v>1</v>
@@ -4289,16 +4328,16 @@
     </row>
     <row r="27" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C27" s="3">
-        <v>4011</v>
+        <v>4009</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E27" s="3">
         <v>5</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="G27" s="3">
         <v>1</v>
@@ -4310,7 +4349,7 @@
         <v>0</v>
       </c>
       <c r="J27" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L27" s="3">
         <v>0</v>
@@ -4321,16 +4360,16 @@
     </row>
     <row r="28" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C28" s="3">
-        <v>4012</v>
+        <v>4010</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="E28" s="3">
         <v>5</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="G28" s="3">
         <v>1</v>
@@ -4342,7 +4381,7 @@
         <v>0</v>
       </c>
       <c r="J28" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L28" s="3">
         <v>0</v>
@@ -4353,16 +4392,16 @@
     </row>
     <row r="29" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C29" s="3">
-        <v>4013</v>
+        <v>4011</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E29" s="3">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="G29" s="3">
         <v>1</v>
@@ -4374,7 +4413,7 @@
         <v>0</v>
       </c>
       <c r="J29" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L29" s="3">
         <v>0</v>
@@ -4385,16 +4424,16 @@
     </row>
     <row r="30" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C30" s="3">
-        <v>4015</v>
+        <v>4012</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="E30" s="3">
         <v>5</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="G30" s="3">
         <v>1</v>
@@ -4417,16 +4456,16 @@
     </row>
     <row r="31" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C31" s="3">
-        <v>4016</v>
+        <v>4013</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="E31" s="3">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="G31" s="3">
         <v>1</v>
@@ -4438,7 +4477,7 @@
         <v>0</v>
       </c>
       <c r="J31" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L31" s="3">
         <v>0</v>
@@ -4449,16 +4488,16 @@
     </row>
     <row r="32" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C32" s="3">
-        <v>4017</v>
+        <v>4015</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="E32" s="3">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="G32" s="3">
         <v>1</v>
@@ -4470,7 +4509,7 @@
         <v>0</v>
       </c>
       <c r="J32" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L32" s="3">
         <v>0</v>
@@ -4481,16 +4520,16 @@
     </row>
     <row r="33" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C33" s="3">
-        <v>4018</v>
+        <v>4016</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="E33" s="3">
         <v>5</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="G33" s="3">
         <v>1</v>
@@ -4513,16 +4552,16 @@
     </row>
     <row r="34" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C34" s="3">
-        <v>4019</v>
+        <v>4017</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="E34" s="3">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="G34" s="3">
         <v>1</v>
@@ -4534,18 +4573,50 @@
         <v>0</v>
       </c>
       <c r="J34" s="3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L34" s="3">
         <v>0</v>
       </c>
       <c r="M34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" s="3" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C35" s="3">
+        <v>4018</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="E35" s="3">
+        <v>5</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="G35" s="3">
+        <v>1</v>
+      </c>
+      <c r="H35" s="3">
+        <v>9999999</v>
+      </c>
+      <c r="I35" s="3">
+        <v>0</v>
+      </c>
+      <c r="J35" s="3">
+        <v>6</v>
+      </c>
+      <c r="L35" s="3">
+        <v>0</v>
+      </c>
+      <c r="M35" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="36" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C36" s="3">
-        <v>4021</v>
+        <v>4019</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>185</v>
@@ -4566,59 +4637,27 @@
         <v>0</v>
       </c>
       <c r="J36" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L36" s="3">
         <v>0</v>
       </c>
       <c r="M36" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" s="3" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C37" s="3">
-        <v>4022</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="E37" s="3">
-        <v>5</v>
-      </c>
-      <c r="F37" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="G37" s="3">
-        <v>1</v>
-      </c>
-      <c r="H37" s="3">
-        <v>9999999</v>
-      </c>
-      <c r="I37" s="3">
-        <v>0</v>
-      </c>
-      <c r="J37" s="3">
-        <v>5</v>
-      </c>
-      <c r="L37" s="3">
-        <v>0</v>
-      </c>
-      <c r="M37" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="38" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C38" s="3">
-        <v>4023</v>
+        <v>4021</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="E38" s="3">
         <v>5</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="G38" s="3">
         <v>1</v>
@@ -4630,7 +4669,7 @@
         <v>0</v>
       </c>
       <c r="J38" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L38" s="3">
         <v>0</v>
@@ -4641,16 +4680,16 @@
     </row>
     <row r="39" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C39" s="3">
-        <v>4024</v>
+        <v>4022</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E39" s="3">
         <v>5</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="G39" s="3">
         <v>1</v>
@@ -4662,7 +4701,7 @@
         <v>0</v>
       </c>
       <c r="J39" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L39" s="3">
         <v>0</v>
@@ -4673,16 +4712,16 @@
     </row>
     <row r="40" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C40" s="3">
-        <v>4025</v>
+        <v>4023</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="E40" s="3">
         <v>5</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="G40" s="3">
         <v>1</v>
@@ -4694,7 +4733,7 @@
         <v>0</v>
       </c>
       <c r="J40" s="3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L40" s="3">
         <v>0</v>
@@ -4705,16 +4744,16 @@
     </row>
     <row r="41" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C41" s="3">
-        <v>4026</v>
+        <v>4024</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="E41" s="3">
         <v>5</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="G41" s="3">
         <v>1</v>
@@ -4726,7 +4765,7 @@
         <v>0</v>
       </c>
       <c r="J41" s="3">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L41" s="3">
         <v>0</v>
@@ -4737,16 +4776,16 @@
     </row>
     <row r="42" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C42" s="3">
-        <v>4027</v>
+        <v>4025</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="E42" s="3">
         <v>5</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="G42" s="3">
         <v>1</v>
@@ -4769,16 +4808,16 @@
     </row>
     <row r="43" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C43" s="3">
-        <v>4028</v>
+        <v>4026</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="E43" s="3">
         <v>5</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="G43" s="3">
         <v>1</v>
@@ -4790,7 +4829,7 @@
         <v>0</v>
       </c>
       <c r="J43" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L43" s="3">
         <v>0</v>
@@ -4801,16 +4840,16 @@
     </row>
     <row r="44" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C44" s="3">
-        <v>4029</v>
+        <v>4027</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="E44" s="3">
         <v>5</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="G44" s="3">
         <v>1</v>
@@ -4833,16 +4872,16 @@
     </row>
     <row r="45" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C45" s="3">
-        <v>4030</v>
+        <v>4028</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E45" s="3">
         <v>5</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="G45" s="3">
         <v>1</v>
@@ -4865,16 +4904,16 @@
     </row>
     <row r="46" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C46" s="3">
-        <v>4031</v>
+        <v>4029</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E46" s="3">
         <v>5</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="G46" s="3">
         <v>1</v>
@@ -4897,16 +4936,16 @@
     </row>
     <row r="47" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C47" s="3">
-        <v>4032</v>
+        <v>4030</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="E47" s="3">
         <v>5</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="G47" s="3">
         <v>1</v>
@@ -4929,16 +4968,16 @@
     </row>
     <row r="48" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C48" s="3">
-        <v>4033</v>
+        <v>4031</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="E48" s="3">
         <v>5</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>178</v>
+        <v>208</v>
       </c>
       <c r="G48" s="3">
         <v>1</v>
@@ -4950,7 +4989,7 @@
         <v>0</v>
       </c>
       <c r="J48" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L48" s="3">
         <v>0</v>
@@ -4961,16 +5000,16 @@
     </row>
     <row r="49" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C49" s="3">
-        <v>4034</v>
+        <v>4032</v>
       </c>
       <c r="D49" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="E49" s="3">
+        <v>5</v>
+      </c>
+      <c r="F49" s="3" t="s">
         <v>210</v>
-      </c>
-      <c r="E49" s="3">
-        <v>5</v>
-      </c>
-      <c r="F49" s="3" t="s">
-        <v>211</v>
       </c>
       <c r="G49" s="3">
         <v>1</v>
@@ -4982,7 +5021,7 @@
         <v>0</v>
       </c>
       <c r="J49" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L49" s="3">
         <v>0</v>
@@ -4993,16 +5032,16 @@
     </row>
     <row r="50" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C50" s="3">
-        <v>4035</v>
+        <v>4033</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E50" s="3">
         <v>5</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>213</v>
+        <v>180</v>
       </c>
       <c r="G50" s="3">
         <v>1</v>
@@ -5014,7 +5053,7 @@
         <v>0</v>
       </c>
       <c r="J50" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L50" s="3">
         <v>0</v>
@@ -5025,16 +5064,16 @@
     </row>
     <row r="51" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C51" s="3">
-        <v>4037</v>
+        <v>4034</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="E51" s="3">
         <v>5</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="G51" s="3">
         <v>1</v>
@@ -5046,7 +5085,7 @@
         <v>0</v>
       </c>
       <c r="J51" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L51" s="3">
         <v>0</v>
@@ -5057,16 +5096,16 @@
     </row>
     <row r="52" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C52" s="3">
-        <v>4038</v>
+        <v>4035</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="E52" s="3">
         <v>5</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="G52" s="3">
         <v>1</v>
@@ -5078,7 +5117,7 @@
         <v>0</v>
       </c>
       <c r="J52" s="3">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L52" s="3">
         <v>0</v>
@@ -5089,16 +5128,16 @@
     </row>
     <row r="53" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C53" s="3">
-        <v>4039</v>
+        <v>4037</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="E53" s="3">
         <v>5</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="G53" s="3">
         <v>1</v>
@@ -5110,7 +5149,7 @@
         <v>0</v>
       </c>
       <c r="J53" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L53" s="3">
         <v>0</v>
@@ -5121,16 +5160,16 @@
     </row>
     <row r="54" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C54" s="3">
-        <v>4040</v>
+        <v>4038</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="E54" s="3">
         <v>5</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>178</v>
+        <v>219</v>
       </c>
       <c r="G54" s="3">
         <v>1</v>
@@ -5142,7 +5181,7 @@
         <v>0</v>
       </c>
       <c r="J54" s="3">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="L54" s="3">
         <v>0</v>
@@ -5153,16 +5192,16 @@
     </row>
     <row r="55" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C55" s="3">
-        <v>4041</v>
+        <v>4039</v>
       </c>
       <c r="D55" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="E55" s="3">
+        <v>5</v>
+      </c>
+      <c r="F55" s="3" t="s">
         <v>221</v>
-      </c>
-      <c r="E55" s="3">
-        <v>5</v>
-      </c>
-      <c r="F55" s="3" t="s">
-        <v>222</v>
       </c>
       <c r="G55" s="3">
         <v>1</v>
@@ -5185,28 +5224,28 @@
     </row>
     <row r="56" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C56" s="3">
-        <v>4042</v>
+        <v>4040</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E56" s="3">
         <v>5</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>224</v>
+        <v>180</v>
       </c>
       <c r="G56" s="3">
         <v>1</v>
       </c>
       <c r="H56" s="3">
-        <v>1999999999</v>
+        <v>9999999</v>
       </c>
       <c r="I56" s="3">
         <v>0</v>
       </c>
       <c r="J56" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L56" s="3">
         <v>0</v>
@@ -5217,10 +5256,10 @@
     </row>
     <row r="57" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C57" s="3">
-        <v>4043</v>
+        <v>4041</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="E57" s="3">
         <v>5</v>
@@ -5238,7 +5277,7 @@
         <v>0</v>
       </c>
       <c r="J57" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L57" s="3">
         <v>0</v>
@@ -5249,51 +5288,71 @@
     </row>
     <row r="58" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C58" s="3">
-        <v>4044</v>
+        <v>4042</v>
       </c>
       <c r="D58" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="E58" s="3">
+        <v>5</v>
+      </c>
+      <c r="F58" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="E58" s="3">
-        <v>5</v>
-      </c>
-      <c r="F58" s="3" t="s">
+      <c r="G58" s="3">
+        <v>1</v>
+      </c>
+      <c r="H58" s="3">
+        <v>1999999999</v>
+      </c>
+      <c r="I58" s="3">
+        <v>0</v>
+      </c>
+      <c r="J58" s="3">
+        <v>5</v>
+      </c>
+      <c r="L58" s="3">
+        <v>0</v>
+      </c>
+      <c r="M58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" s="3" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C59" s="3">
+        <v>4043</v>
+      </c>
+      <c r="D59" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="G58" s="3">
-        <v>1</v>
-      </c>
-      <c r="H58" s="3">
+      <c r="E59" s="3">
+        <v>5</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="G59" s="3">
+        <v>1</v>
+      </c>
+      <c r="H59" s="3">
         <v>9999999</v>
       </c>
-      <c r="I58" s="3">
-        <v>0</v>
-      </c>
-      <c r="J58" s="3">
-        <v>9</v>
-      </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
-      <c r="M58" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C59" s="3"/>
-      <c r="D59" s="3"/>
-      <c r="E59" s="3"/>
-      <c r="F59" s="3"/>
-      <c r="G59" s="3"/>
-      <c r="H59" s="3"/>
-      <c r="I59" s="3"/>
-      <c r="J59" s="3"/>
-      <c r="L59" s="3"/>
-      <c r="M59" s="3"/>
+      <c r="I59" s="3">
+        <v>0</v>
+      </c>
+      <c r="J59" s="3">
+        <v>7</v>
+      </c>
+      <c r="L59" s="3">
+        <v>0</v>
+      </c>
+      <c r="M59" s="3">
+        <v>0</v>
+      </c>
     </row>
     <row r="60" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C60" s="3">
-        <v>4101</v>
+        <v>4044</v>
       </c>
       <c r="D60" s="3" t="s">
         <v>228</v>
@@ -5314,7 +5373,7 @@
         <v>0</v>
       </c>
       <c r="J60" s="3">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L60" s="3">
         <v>0</v>
@@ -5323,50 +5382,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" s="3" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C61" s="3">
-        <v>4111</v>
-      </c>
-      <c r="D61" s="3" t="s">
-        <v>230</v>
-      </c>
-      <c r="E61" s="3">
-        <v>5</v>
-      </c>
-      <c r="F61" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="G61" s="3">
-        <v>1</v>
-      </c>
-      <c r="H61" s="3">
-        <v>9999999</v>
-      </c>
-      <c r="I61" s="3">
-        <v>0</v>
-      </c>
-      <c r="J61" s="3">
-        <v>5</v>
-      </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
+    <row r="61" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C61" s="3"/>
+      <c r="D61" s="3"/>
+      <c r="E61" s="3"/>
+      <c r="F61" s="3"/>
+      <c r="G61" s="3"/>
+      <c r="H61" s="3"/>
+      <c r="I61" s="3"/>
+      <c r="J61" s="3"/>
+      <c r="L61" s="3"/>
+      <c r="M61" s="3"/>
     </row>
     <row r="62" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C62" s="3">
-        <v>4112</v>
+        <v>4101</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="E62" s="3">
         <v>5</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="G62" s="3">
         <v>1</v>
@@ -5378,7 +5417,7 @@
         <v>0</v>
       </c>
       <c r="J62" s="3">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="L62" s="3">
         <v>0</v>
@@ -5389,16 +5428,16 @@
     </row>
     <row r="63" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C63" s="3">
-        <v>4113</v>
+        <v>4111</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E63" s="3">
         <v>5</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="G63" s="3">
         <v>1</v>
@@ -5410,7 +5449,7 @@
         <v>0</v>
       </c>
       <c r="J63" s="3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L63" s="3">
         <v>0</v>
@@ -5419,21 +5458,41 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C64" s="3"/>
-      <c r="D64" s="3"/>
-      <c r="E64" s="3"/>
-      <c r="F64" s="3"/>
-      <c r="G64" s="3"/>
-      <c r="H64" s="3"/>
-      <c r="I64" s="3"/>
-      <c r="J64" s="3"/>
-      <c r="L64" s="3"/>
-      <c r="M64" s="3"/>
+    <row r="64" s="3" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C64" s="3">
+        <v>4112</v>
+      </c>
+      <c r="D64" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="E64" s="3">
+        <v>5</v>
+      </c>
+      <c r="F64" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="G64" s="3">
+        <v>1</v>
+      </c>
+      <c r="H64" s="3">
+        <v>9999999</v>
+      </c>
+      <c r="I64" s="3">
+        <v>0</v>
+      </c>
+      <c r="J64" s="3">
+        <v>8</v>
+      </c>
+      <c r="L64" s="3">
+        <v>0</v>
+      </c>
+      <c r="M64" s="3">
+        <v>0</v>
+      </c>
     </row>
     <row r="65" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C65" s="3">
-        <v>4201</v>
+        <v>4113</v>
       </c>
       <c r="D65" s="3" t="s">
         <v>236</v>
@@ -5448,97 +5507,77 @@
         <v>1</v>
       </c>
       <c r="H65" s="3">
+        <v>9999999</v>
+      </c>
+      <c r="I65" s="3">
+        <v>0</v>
+      </c>
+      <c r="J65" s="3">
+        <v>7</v>
+      </c>
+      <c r="L65" s="3">
+        <v>0</v>
+      </c>
+      <c r="M65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C66" s="3"/>
+      <c r="D66" s="3"/>
+      <c r="E66" s="3"/>
+      <c r="F66" s="3"/>
+      <c r="G66" s="3"/>
+      <c r="H66" s="3"/>
+      <c r="I66" s="3"/>
+      <c r="J66" s="3"/>
+      <c r="L66" s="3"/>
+      <c r="M66" s="3"/>
+    </row>
+    <row r="67" s="3" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C67" s="3">
+        <v>4201</v>
+      </c>
+      <c r="D67" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="E67" s="3">
+        <v>5</v>
+      </c>
+      <c r="F67" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="G67" s="3">
+        <v>1</v>
+      </c>
+      <c r="H67" s="3">
         <v>99999999</v>
       </c>
-      <c r="I65" s="3">
-        <v>0</v>
-      </c>
-      <c r="J65" s="3">
-        <v>5</v>
-      </c>
-      <c r="L65" s="3">
+      <c r="I67" s="3">
+        <v>0</v>
+      </c>
+      <c r="J67" s="3">
+        <v>5</v>
+      </c>
+      <c r="L67" s="3">
         <v>4002</v>
       </c>
-      <c r="M65" s="3">
+      <c r="M67" s="3">
         <v>1000</v>
-      </c>
-    </row>
-    <row r="70" s="3" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C70" s="3">
-        <v>8001</v>
-      </c>
-      <c r="D70" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="E70" s="3">
-        <v>5</v>
-      </c>
-      <c r="F70" s="3" t="s">
-        <v>239</v>
-      </c>
-      <c r="G70" s="3">
-        <v>1</v>
-      </c>
-      <c r="H70" s="3">
-        <v>9999999</v>
-      </c>
-      <c r="I70" s="3">
-        <v>0</v>
-      </c>
-      <c r="J70" s="3">
-        <v>6</v>
-      </c>
-      <c r="L70" s="3">
-        <v>0</v>
-      </c>
-      <c r="M70" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" s="3" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C71" s="3">
-        <v>8002</v>
-      </c>
-      <c r="D71" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="E71" s="3">
-        <v>5</v>
-      </c>
-      <c r="F71" s="3" t="s">
-        <v>239</v>
-      </c>
-      <c r="G71" s="3">
-        <v>1</v>
-      </c>
-      <c r="H71" s="3">
-        <v>9999999</v>
-      </c>
-      <c r="I71" s="3">
-        <v>0</v>
-      </c>
-      <c r="J71" s="3">
-        <v>6</v>
-      </c>
-      <c r="L71" s="3">
-        <v>0</v>
-      </c>
-      <c r="M71" s="3">
-        <v>0</v>
       </c>
     </row>
     <row r="72" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C72" s="3">
-        <v>8003</v>
+        <v>8001</v>
       </c>
       <c r="D72" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="E72" s="3">
+        <v>5</v>
+      </c>
+      <c r="F72" s="3" t="s">
         <v>241</v>
-      </c>
-      <c r="E72" s="3">
-        <v>5</v>
-      </c>
-      <c r="F72" s="3" t="s">
-        <v>239</v>
       </c>
       <c r="G72" s="3">
         <v>1</v>
@@ -5561,7 +5600,7 @@
     </row>
     <row r="73" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C73" s="3">
-        <v>8004</v>
+        <v>8002</v>
       </c>
       <c r="D73" s="3" t="s">
         <v>242</v>
@@ -5570,7 +5609,7 @@
         <v>5</v>
       </c>
       <c r="F73" s="3" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="G73" s="3">
         <v>1</v>
@@ -5593,7 +5632,7 @@
     </row>
     <row r="74" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C74" s="3">
-        <v>8005</v>
+        <v>8003</v>
       </c>
       <c r="D74" s="3" t="s">
         <v>243</v>
@@ -5602,7 +5641,7 @@
         <v>5</v>
       </c>
       <c r="F74" s="3" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="G74" s="3">
         <v>1</v>
@@ -5625,7 +5664,7 @@
     </row>
     <row r="75" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C75" s="3">
-        <v>8006</v>
+        <v>8004</v>
       </c>
       <c r="D75" s="3" t="s">
         <v>244</v>
@@ -5634,7 +5673,7 @@
         <v>5</v>
       </c>
       <c r="F75" s="3" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="G75" s="3">
         <v>1</v>
@@ -5657,7 +5696,7 @@
     </row>
     <row r="76" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C76" s="3">
-        <v>8007</v>
+        <v>8005</v>
       </c>
       <c r="D76" s="3" t="s">
         <v>245</v>
@@ -5666,7 +5705,7 @@
         <v>5</v>
       </c>
       <c r="F76" s="3" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="G76" s="3">
         <v>1</v>
@@ -5689,7 +5728,7 @@
     </row>
     <row r="77" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C77" s="3">
-        <v>8008</v>
+        <v>8006</v>
       </c>
       <c r="D77" s="3" t="s">
         <v>246</v>
@@ -5698,7 +5737,7 @@
         <v>5</v>
       </c>
       <c r="F77" s="3" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="G77" s="3">
         <v>1</v>
@@ -5721,7 +5760,7 @@
     </row>
     <row r="78" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C78" s="3">
-        <v>8009</v>
+        <v>8007</v>
       </c>
       <c r="D78" s="3" t="s">
         <v>247</v>
@@ -5730,7 +5769,7 @@
         <v>5</v>
       </c>
       <c r="F78" s="3" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="G78" s="3">
         <v>1</v>
@@ -5753,7 +5792,7 @@
     </row>
     <row r="79" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C79" s="3">
-        <v>8010</v>
+        <v>8008</v>
       </c>
       <c r="D79" s="3" t="s">
         <v>248</v>
@@ -5762,7 +5801,7 @@
         <v>5</v>
       </c>
       <c r="F79" s="3" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="G79" s="3">
         <v>1</v>
@@ -5783,18 +5822,50 @@
         <v>0</v>
       </c>
     </row>
+    <row r="80" s="3" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C80" s="3">
+        <v>8009</v>
+      </c>
+      <c r="D80" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="E80" s="3">
+        <v>5</v>
+      </c>
+      <c r="F80" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="G80" s="3">
+        <v>1</v>
+      </c>
+      <c r="H80" s="3">
+        <v>9999999</v>
+      </c>
+      <c r="I80" s="3">
+        <v>0</v>
+      </c>
+      <c r="J80" s="3">
+        <v>6</v>
+      </c>
+      <c r="L80" s="3">
+        <v>0</v>
+      </c>
+      <c r="M80" s="3">
+        <v>0</v>
+      </c>
+    </row>
     <row r="81" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C81" s="3">
-        <v>8101</v>
-      </c>
-      <c r="D81" s="9" t="s">
-        <v>249</v>
+        <v>8010</v>
+      </c>
+      <c r="D81" s="3" t="s">
+        <v>250</v>
       </c>
       <c r="E81" s="3">
         <v>5</v>
       </c>
       <c r="F81" s="3" t="s">
-        <v>250</v>
+        <v>241</v>
       </c>
       <c r="G81" s="3">
         <v>1</v>
@@ -5806,59 +5877,27 @@
         <v>0</v>
       </c>
       <c r="J81" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L81" s="3">
         <v>0</v>
       </c>
       <c r="M81" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" s="3" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C82" s="3">
-        <v>8102</v>
-      </c>
-      <c r="D82" s="9" t="s">
-        <v>251</v>
-      </c>
-      <c r="E82" s="3">
-        <v>5</v>
-      </c>
-      <c r="F82" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="G82" s="3">
-        <v>1</v>
-      </c>
-      <c r="H82" s="3">
-        <v>9999999</v>
-      </c>
-      <c r="I82" s="3">
-        <v>0</v>
-      </c>
-      <c r="J82" s="3">
-        <v>7</v>
-      </c>
-      <c r="L82" s="3">
-        <v>0</v>
-      </c>
-      <c r="M82" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="83" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C83" s="3">
-        <v>8103</v>
+        <v>8101</v>
       </c>
       <c r="D83" s="9" t="s">
+        <v>251</v>
+      </c>
+      <c r="E83" s="3">
+        <v>5</v>
+      </c>
+      <c r="F83" s="3" t="s">
         <v>252</v>
-      </c>
-      <c r="E83" s="3">
-        <v>5</v>
-      </c>
-      <c r="F83" s="3" t="s">
-        <v>250</v>
       </c>
       <c r="G83" s="3">
         <v>1</v>
@@ -5881,7 +5920,7 @@
     </row>
     <row r="84" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C84" s="3">
-        <v>8104</v>
+        <v>8102</v>
       </c>
       <c r="D84" s="9" t="s">
         <v>253</v>
@@ -5890,7 +5929,7 @@
         <v>5</v>
       </c>
       <c r="F84" s="3" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="G84" s="3">
         <v>1</v>
@@ -5913,7 +5952,7 @@
     </row>
     <row r="85" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C85" s="3">
-        <v>8105</v>
+        <v>8103</v>
       </c>
       <c r="D85" s="9" t="s">
         <v>254</v>
@@ -5922,7 +5961,7 @@
         <v>5</v>
       </c>
       <c r="F85" s="3" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="G85" s="3">
         <v>1</v>
@@ -5945,7 +5984,7 @@
     </row>
     <row r="86" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C86" s="3">
-        <v>8106</v>
+        <v>8104</v>
       </c>
       <c r="D86" s="9" t="s">
         <v>255</v>
@@ -5954,7 +5993,7 @@
         <v>5</v>
       </c>
       <c r="F86" s="3" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="G86" s="3">
         <v>1</v>
@@ -5977,7 +6016,7 @@
     </row>
     <row r="87" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C87" s="3">
-        <v>8107</v>
+        <v>8105</v>
       </c>
       <c r="D87" s="9" t="s">
         <v>256</v>
@@ -5986,7 +6025,7 @@
         <v>5</v>
       </c>
       <c r="F87" s="3" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="G87" s="3">
         <v>1</v>
@@ -6009,7 +6048,7 @@
     </row>
     <row r="88" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C88" s="3">
-        <v>8108</v>
+        <v>8106</v>
       </c>
       <c r="D88" s="9" t="s">
         <v>257</v>
@@ -6018,7 +6057,7 @@
         <v>5</v>
       </c>
       <c r="F88" s="3" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="G88" s="3">
         <v>1</v>
@@ -6039,88 +6078,82 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" customHeight="1" spans="3:13">
+    <row r="89" s="3" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C89" s="3">
+        <v>8107</v>
+      </c>
+      <c r="D89" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="E89" s="3">
+        <v>5</v>
+      </c>
+      <c r="F89" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="G89" s="3">
+        <v>1</v>
+      </c>
+      <c r="H89" s="3">
+        <v>9999999</v>
+      </c>
+      <c r="I89" s="3">
+        <v>0</v>
+      </c>
+      <c r="J89" s="3">
+        <v>7</v>
+      </c>
+      <c r="L89" s="3">
+        <v>0</v>
+      </c>
+      <c r="M89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C90" s="3">
-        <v>8201</v>
+        <v>8108</v>
       </c>
       <c r="D90" s="9" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E90" s="3">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="F90" s="3" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="G90" s="3">
         <v>1</v>
       </c>
       <c r="H90" s="3">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="I90" s="3">
         <v>0</v>
       </c>
       <c r="J90" s="3">
-        <v>1</v>
-      </c>
-      <c r="K90" s="3">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L90" s="3">
         <v>0</v>
       </c>
       <c r="M90" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="91" customHeight="1" spans="3:13">
-      <c r="C91" s="3">
-        <v>8202</v>
-      </c>
-      <c r="D91" s="9" t="s">
-        <v>260</v>
-      </c>
-      <c r="E91" s="3">
-        <v>16</v>
-      </c>
-      <c r="F91" s="3" t="s">
-        <v>261</v>
-      </c>
-      <c r="G91" s="3">
-        <v>1</v>
-      </c>
-      <c r="H91" s="3">
-        <v>1</v>
-      </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
-      <c r="J91" s="3">
-        <v>2</v>
-      </c>
-      <c r="K91" s="3">
-        <v>0</v>
-      </c>
-      <c r="L91" s="3">
-        <v>0</v>
-      </c>
-      <c r="M91" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="92" customHeight="1" spans="3:13">
       <c r="C92" s="3">
-        <v>8203</v>
+        <v>8201</v>
       </c>
       <c r="D92" s="9" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="E92" s="3">
         <v>16</v>
       </c>
       <c r="F92" s="3" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="G92" s="3">
         <v>1</v>
@@ -6132,7 +6165,7 @@
         <v>0</v>
       </c>
       <c r="J92" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K92" s="3">
         <v>0</v>
@@ -6146,16 +6179,16 @@
     </row>
     <row r="93" customHeight="1" spans="3:13">
       <c r="C93" s="3">
-        <v>8204</v>
+        <v>8202</v>
       </c>
       <c r="D93" s="9" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="E93" s="3">
         <v>16</v>
       </c>
       <c r="F93" s="3" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="G93" s="3">
         <v>1</v>
@@ -6167,7 +6200,7 @@
         <v>0</v>
       </c>
       <c r="J93" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K93" s="3">
         <v>0</v>
@@ -6181,16 +6214,16 @@
     </row>
     <row r="94" customHeight="1" spans="3:13">
       <c r="C94" s="3">
-        <v>8205</v>
+        <v>8203</v>
       </c>
       <c r="D94" s="9" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="E94" s="3">
         <v>16</v>
       </c>
       <c r="F94" s="3" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="G94" s="3">
         <v>1</v>
@@ -6202,7 +6235,7 @@
         <v>0</v>
       </c>
       <c r="J94" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K94" s="3">
         <v>0</v>
@@ -6216,16 +6249,16 @@
     </row>
     <row r="95" customHeight="1" spans="3:13">
       <c r="C95" s="3">
-        <v>8206</v>
+        <v>8204</v>
       </c>
       <c r="D95" s="9" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="E95" s="3">
         <v>16</v>
       </c>
       <c r="F95" s="3" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="G95" s="3">
         <v>1</v>
@@ -6237,7 +6270,7 @@
         <v>0</v>
       </c>
       <c r="J95" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K95" s="3">
         <v>0</v>
@@ -6251,87 +6284,157 @@
     </row>
     <row r="96" customHeight="1" spans="3:13">
       <c r="C96" s="3">
-        <v>8207</v>
+        <v>8205</v>
       </c>
       <c r="D96" s="9" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="E96" s="3">
         <v>16</v>
       </c>
       <c r="F96" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="G96" s="3">
+        <v>1</v>
+      </c>
+      <c r="H96" s="3">
+        <v>1</v>
+      </c>
+      <c r="I96" s="3">
+        <v>0</v>
+      </c>
+      <c r="J96" s="3">
+        <v>5</v>
+      </c>
+      <c r="K96" s="3">
+        <v>0</v>
+      </c>
+      <c r="L96" s="3">
+        <v>0</v>
+      </c>
+      <c r="M96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" customHeight="1" spans="3:13">
+      <c r="C97" s="3">
+        <v>8206</v>
+      </c>
+      <c r="D97" s="9" t="s">
+        <v>270</v>
+      </c>
+      <c r="E97" s="3">
+        <v>16</v>
+      </c>
+      <c r="F97" s="3" t="s">
         <v>271</v>
       </c>
-      <c r="G96" s="3">
-        <v>1</v>
-      </c>
-      <c r="H96" s="3">
-        <v>1</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
+      <c r="G97" s="3">
+        <v>1</v>
+      </c>
+      <c r="H97" s="3">
+        <v>1</v>
+      </c>
+      <c r="I97" s="3">
+        <v>0</v>
+      </c>
+      <c r="J97" s="3">
+        <v>6</v>
+      </c>
+      <c r="K97" s="3">
+        <v>0</v>
+      </c>
+      <c r="L97" s="3">
+        <v>0</v>
+      </c>
+      <c r="M97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" customHeight="1" spans="3:13">
+      <c r="C98" s="3">
+        <v>8207</v>
+      </c>
+      <c r="D98" s="9" t="s">
+        <v>272</v>
+      </c>
+      <c r="E98" s="3">
+        <v>16</v>
+      </c>
+      <c r="F98" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="G98" s="3">
+        <v>1</v>
+      </c>
+      <c r="H98" s="3">
+        <v>1</v>
+      </c>
+      <c r="I98" s="3">
+        <v>0</v>
+      </c>
+      <c r="J98" s="3">
         <v>7</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
-      <c r="L96" s="3">
-        <v>0</v>
-      </c>
-      <c r="M96" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="98" customHeight="1" spans="4:4">
-      <c r="D98" s="9"/>
-    </row>
-    <row r="99" customHeight="1" spans="4:4">
-      <c r="D99" s="9"/>
-    </row>
-    <row r="100" customHeight="1" spans="4:4">
+      <c r="K98" s="3">
+        <v>0</v>
+      </c>
+      <c r="L98" s="3">
+        <v>0</v>
+      </c>
+      <c r="M98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" customHeight="1" spans="3:13">
       <c r="D100" s="9"/>
     </row>
-    <row r="101" customHeight="1" spans="4:4">
+    <row r="101" customHeight="1" spans="3:13">
       <c r="D101" s="9"/>
     </row>
-    <row r="102" customHeight="1" spans="4:4">
+    <row r="102" customHeight="1" spans="3:13">
       <c r="D102" s="9"/>
     </row>
-    <row r="103" customHeight="1" spans="4:4">
+    <row r="103" customHeight="1" spans="3:13">
       <c r="D103" s="9"/>
     </row>
-    <row r="104" customHeight="1" spans="4:4">
+    <row r="104" customHeight="1" spans="3:13">
       <c r="D104" s="9"/>
     </row>
-    <row r="106" customHeight="1" spans="4:4">
+    <row r="105" customHeight="1" spans="3:13">
+      <c r="D105" s="9"/>
+    </row>
+    <row r="106" customHeight="1" spans="3:13">
       <c r="D106" s="9"/>
     </row>
-    <row r="107" customHeight="1" spans="4:4">
-      <c r="D107" s="9"/>
-    </row>
-    <row r="108" customHeight="1" spans="4:4">
+    <row r="108" customHeight="1" spans="3:13">
       <c r="D108" s="9"/>
     </row>
-    <row r="109" customHeight="1" spans="4:4">
+    <row r="109" customHeight="1" spans="3:13">
       <c r="D109" s="9"/>
     </row>
-    <row r="110" customHeight="1" spans="4:4">
+    <row r="110" customHeight="1" spans="3:13">
       <c r="D110" s="9"/>
     </row>
-    <row r="111" customHeight="1" spans="4:4">
+    <row r="111" customHeight="1" spans="3:13">
       <c r="D111" s="9"/>
     </row>
-    <row r="112" customHeight="1" spans="4:4">
+    <row r="112" customHeight="1" spans="3:13">
       <c r="D112" s="9"/>
+    </row>
+    <row r="113" customHeight="1" spans="4:4">
+      <c r="D113" s="9"/>
+    </row>
+    <row r="114" customHeight="1" spans="4:4">
+      <c r="D114" s="9"/>
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C8:D8 C13:D13 C9:C12 C3:D5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C9:D9 C14:D14 C10:C13 C3:D5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="L13:M13 L3:M5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="L14:M14 L3:M5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,L3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>
@@ -6467,16 +6570,16 @@
     </row>
     <row r="6" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C6" s="2">
-        <v>1999001</v>
+        <v>9001</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="E6" s="2">
         <v>6</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="G6" s="2">
         <v>1</v>
@@ -6496,16 +6599,16 @@
     </row>
     <row r="7" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C7" s="2">
-        <v>1999002</v>
+        <v>9002</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="E7" s="2">
         <v>6</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="G7" s="2">
         <v>1</v>
@@ -6525,16 +6628,16 @@
     </row>
     <row r="8" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C8" s="2">
-        <v>1999003</v>
+        <v>9003</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="E8" s="2">
         <v>6</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="G8" s="2">
         <v>1</v>
@@ -6554,16 +6657,16 @@
     </row>
     <row r="9" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C9" s="2">
-        <v>1999004</v>
+        <v>9004</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="E9" s="2">
         <v>6</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="G9" s="2">
         <v>1</v>
@@ -6583,16 +6686,16 @@
     </row>
     <row r="10" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C10" s="2">
-        <v>1999005</v>
+        <v>9005</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E10" s="2">
         <v>6</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="G10" s="2">
         <v>1</v>
@@ -6612,16 +6715,16 @@
     </row>
     <row r="11" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C11" s="2">
-        <v>1999006</v>
+        <v>9006</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="E11" s="2">
         <v>6</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="G11" s="2">
         <v>1</v>
@@ -6640,16 +6743,16 @@
     </row>
     <row r="12" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C12" s="2">
-        <v>1999007</v>
+        <v>9007</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E12" s="2">
         <v>6</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="G12" s="2">
         <v>1</v>
@@ -6668,16 +6771,16 @@
     </row>
     <row r="13" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C13" s="2">
-        <v>1999008</v>
+        <v>9008</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="E13" s="2">
         <v>6</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="G13" s="2">
         <v>1</v>
@@ -6696,16 +6799,16 @@
     </row>
     <row r="14" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C14" s="2">
-        <v>1999009</v>
+        <v>9009</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E14" s="2">
         <v>6</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="G14" s="2">
         <v>1</v>
@@ -6724,16 +6827,16 @@
     </row>
     <row r="15" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C15" s="2">
-        <v>1999010</v>
+        <v>9010</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="E15" s="2">
         <v>6</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="G15" s="2">
         <v>1</v>
@@ -6752,16 +6855,16 @@
     </row>
     <row r="16" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C16" s="2">
-        <v>1999011</v>
+        <v>9011</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="E16" s="2">
         <v>6</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="G16" s="2">
         <v>1</v>
@@ -6799,6 +6902,339 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="C1:M17"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
+  <cols>
+    <col min="4" max="4" width="9.625" customWidth="1"/>
+    <col min="6" max="6" width="15.375" customWidth="1"/>
+    <col min="12" max="13" width="13.5083333333333" style="3" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="3:13">
+      <c r="L1" s="3"/>
+      <c r="M1" s="3"/>
+    </row>
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="3:13">
+      <c r="L2" s="3"/>
+      <c r="M2" s="3"/>
+    </row>
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C3" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="K3" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="L3" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="M3" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C4" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="K4" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="L4" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="M4" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C5" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="K5" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="L5" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="M5" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" s="2" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C6" s="2">
+        <v>10001</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="E6" s="2">
+        <v>5</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="G6" s="2">
+        <v>1</v>
+      </c>
+      <c r="H6" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I6" s="2">
+        <v>0</v>
+      </c>
+      <c r="J6" s="2">
+        <v>4</v>
+      </c>
+      <c r="L6" s="3"/>
+      <c r="M6" s="3"/>
+    </row>
+    <row r="7" s="2" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C7" s="2">
+        <v>10002</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="E7" s="2">
+        <v>5</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="G7" s="2">
+        <v>1</v>
+      </c>
+      <c r="H7" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I7" s="2">
+        <v>0</v>
+      </c>
+      <c r="J7" s="2">
+        <v>4</v>
+      </c>
+      <c r="L7" s="3"/>
+      <c r="M7" s="3"/>
+    </row>
+    <row r="8" s="2" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C8" s="2">
+        <v>10003</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="E8" s="2">
+        <v>5</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="G8" s="2">
+        <v>1</v>
+      </c>
+      <c r="H8" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I8" s="2">
+        <v>0</v>
+      </c>
+      <c r="J8" s="2">
+        <v>4</v>
+      </c>
+      <c r="L8" s="3"/>
+      <c r="M8" s="3"/>
+    </row>
+    <row r="9" s="2" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C9" s="2">
+        <v>10004</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="E9" s="2">
+        <v>5</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="G9" s="2">
+        <v>1</v>
+      </c>
+      <c r="H9" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I9" s="2">
+        <v>0</v>
+      </c>
+      <c r="J9" s="2">
+        <v>5</v>
+      </c>
+      <c r="L9" s="3"/>
+      <c r="M9" s="3"/>
+    </row>
+    <row r="10" s="2" customFormat="1" customHeight="1" spans="3:13">
+      <c r="D10" s="3"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+      <c r="J10" s="2"/>
+      <c r="L10" s="3"/>
+      <c r="M10" s="3"/>
+    </row>
+    <row r="11" s="2" customFormat="1" customHeight="1" spans="3:13">
+      <c r="D11" s="3"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+      <c r="J11" s="2"/>
+      <c r="L11" s="3"/>
+      <c r="M11" s="3"/>
+    </row>
+    <row r="12" s="2" customFormat="1" customHeight="1" spans="3:13">
+      <c r="D12" s="3"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="2"/>
+      <c r="L12" s="3"/>
+      <c r="M12" s="3"/>
+    </row>
+    <row r="13" s="2" customFormat="1" customHeight="1" spans="3:13">
+      <c r="D13" s="3"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
+      <c r="J13" s="2"/>
+      <c r="L13" s="3"/>
+      <c r="M13" s="3"/>
+    </row>
+    <row r="14" s="2" customFormat="1" customHeight="1" spans="3:13">
+      <c r="D14" s="3"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="2"/>
+      <c r="L14" s="3"/>
+      <c r="M14" s="3"/>
+    </row>
+    <row r="15" s="2" customFormat="1" customHeight="1" spans="3:13">
+      <c r="D15" s="3"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="2"/>
+      <c r="L15" s="3"/>
+      <c r="M15" s="3"/>
+    </row>
+    <row r="16" s="2" customFormat="1" customHeight="1" spans="3:13">
+      <c r="D16" s="3"/>
+      <c r="E16" s="2"/>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
+      <c r="I16" s="2"/>
+      <c r="J16" s="2"/>
+      <c r="L16" s="3"/>
+      <c r="M16" s="3"/>
+    </row>
+    <row r="17" s="2" customFormat="1" customHeight="1" spans="4:13">
+      <c r="D17" s="3"/>
+      <c r="L17" s="3"/>
+      <c r="M17" s="3"/>
+    </row>
+  </sheetData>
+  <dataValidations count="2">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="L3:M5" errorStyle="warning">
+      <formula1>COUNTIF($A:$A,L3)&lt;2</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:D5" errorStyle="warning">
+      <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="C1:M11"/>
@@ -6933,13 +7369,13 @@
         <v>40000001</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="E6" s="2">
         <v>6</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="G6" s="2">
         <v>1</v>
@@ -6960,13 +7396,13 @@
         <v>40000002</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="E7" s="2">
         <v>6</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="G7" s="2">
         <v>1</v>
@@ -6987,13 +7423,13 @@
         <v>40000003</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="E8" s="2">
         <v>6</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="G8" s="2">
         <v>1</v>
@@ -7014,13 +7450,13 @@
         <v>40000004</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="E9" s="2">
         <v>6</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="G9" s="2">
         <v>1</v>
@@ -7041,13 +7477,13 @@
         <v>40000005</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="E10" s="2">
         <v>6</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="G10" s="2">
         <v>1</v>
@@ -7068,13 +7504,13 @@
         <v>40000006</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="E11" s="2">
         <v>6</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="G11" s="2">
         <v>1</v>

--- a/Excel/ItemConfig.xlsx
+++ b/Excel/ItemConfig.xlsx
@@ -224,7 +224,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="541" uniqueCount="297">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="541" uniqueCount="298">
   <si>
     <t>_Id</t>
   </si>
@@ -1085,6 +1085,9 @@
   </si>
   <si>
     <t>Tap玩家</t>
+  </si>
+  <si>
+    <t>激活对应特殊时装</t>
   </si>
   <si>
     <t>QQ玩家</t>
@@ -7036,7 +7039,7 @@
         <v>5</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>275</v>
+        <v>287</v>
       </c>
       <c r="G6" s="2">
         <v>1</v>
@@ -7050,21 +7053,25 @@
       <c r="J6" s="2">
         <v>4</v>
       </c>
-      <c r="L6" s="3"/>
-      <c r="M6" s="3"/>
+      <c r="L6" s="3">
+        <v>5003</v>
+      </c>
+      <c r="M6" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="7" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C7" s="2">
         <v>10002</v>
       </c>
       <c r="D7" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="E7" s="2">
+        <v>5</v>
+      </c>
+      <c r="F7" s="2" t="s">
         <v>287</v>
-      </c>
-      <c r="E7" s="2">
-        <v>5</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>275</v>
       </c>
       <c r="G7" s="2">
         <v>1</v>
@@ -7078,21 +7085,25 @@
       <c r="J7" s="2">
         <v>4</v>
       </c>
-      <c r="L7" s="3"/>
-      <c r="M7" s="3"/>
+      <c r="L7" s="3">
+        <v>5003</v>
+      </c>
+      <c r="M7" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="8" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C8" s="2">
         <v>10003</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E8" s="2">
         <v>5</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>275</v>
+        <v>287</v>
       </c>
       <c r="G8" s="2">
         <v>1</v>
@@ -7106,21 +7117,25 @@
       <c r="J8" s="2">
         <v>4</v>
       </c>
-      <c r="L8" s="3"/>
-      <c r="M8" s="3"/>
+      <c r="L8" s="3">
+        <v>5003</v>
+      </c>
+      <c r="M8" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="9" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C9" s="2">
         <v>10004</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="E9" s="2">
         <v>5</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>275</v>
+        <v>287</v>
       </c>
       <c r="G9" s="2">
         <v>1</v>
@@ -7134,8 +7149,12 @@
       <c r="J9" s="2">
         <v>5</v>
       </c>
-      <c r="L9" s="3"/>
-      <c r="M9" s="3"/>
+      <c r="L9" s="3">
+        <v>5003</v>
+      </c>
+      <c r="M9" s="3">
+        <v>10</v>
+      </c>
     </row>
     <row r="10" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="D10" s="3"/>
@@ -7369,13 +7388,13 @@
         <v>40000001</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="E6" s="2">
         <v>6</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="G6" s="2">
         <v>1</v>
@@ -7396,13 +7415,13 @@
         <v>40000002</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E7" s="2">
         <v>6</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="G7" s="2">
         <v>1</v>
@@ -7423,13 +7442,13 @@
         <v>40000003</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="E8" s="2">
         <v>6</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="G8" s="2">
         <v>1</v>
@@ -7450,13 +7469,13 @@
         <v>40000004</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="E9" s="2">
         <v>6</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="G9" s="2">
         <v>1</v>
@@ -7477,13 +7496,13 @@
         <v>40000005</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="E10" s="2">
         <v>6</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="G10" s="2">
         <v>1</v>
@@ -7504,13 +7523,13 @@
         <v>40000006</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="E11" s="2">
         <v>6</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="G11" s="2">
         <v>1</v>

--- a/Excel/ItemConfig.xlsx
+++ b/Excel/ItemConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="3"/>
+    <workbookView windowHeight="17680" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="技能" sheetId="1" r:id="rId1"/>
@@ -224,7 +224,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="541" uniqueCount="298">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="543" uniqueCount="300">
   <si>
     <t>_Id</t>
   </si>
@@ -641,6 +641,12 @@
   </si>
   <si>
     <t>激活皮肤的材料</t>
+  </si>
+  <si>
+    <t>宠物口粮</t>
+  </si>
+  <si>
+    <t>宠物升级的材料</t>
   </si>
   <si>
     <t>灵盾碎片</t>
@@ -1322,12 +1328,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -3616,7 +3622,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:M114"/>
+  <dimension ref="C3:M115"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="3"/>
@@ -3834,54 +3840,54 @@
       </c>
     </row>
     <row r="9" s="6" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
-      <c r="J9" s="3"/>
+      <c r="C9" s="3">
+        <v>5004</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="E9" s="3">
+        <v>5</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="G9" s="3">
+        <v>1</v>
+      </c>
+      <c r="H9" s="3">
+        <v>99999999</v>
+      </c>
+      <c r="I9" s="3">
+        <v>0</v>
+      </c>
+      <c r="J9" s="3">
+        <v>5</v>
+      </c>
       <c r="K9" s="3"/>
-      <c r="L9" s="3"/>
-      <c r="M9" s="3"/>
+      <c r="L9" s="3">
+        <v>0</v>
+      </c>
+      <c r="M9" s="3">
+        <v>0</v>
+      </c>
     </row>
     <row r="10" s="6" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C10" s="8">
-        <v>5011</v>
-      </c>
-      <c r="D10" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="E10" s="10">
-        <v>5</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="G10" s="3">
-        <v>1</v>
-      </c>
-      <c r="H10" s="3">
-        <v>99999999</v>
-      </c>
-      <c r="I10" s="3">
-        <v>0</v>
-      </c>
-      <c r="J10" s="3">
-        <v>3</v>
-      </c>
+      <c r="C10" s="7"/>
+      <c r="D10" s="7"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="3"/>
+      <c r="H10" s="3"/>
+      <c r="I10" s="3"/>
+      <c r="J10" s="3"/>
       <c r="K10" s="3"/>
-      <c r="L10" s="3">
-        <v>0</v>
-      </c>
-      <c r="M10" s="3">
-        <v>0</v>
-      </c>
+      <c r="L10" s="3"/>
+      <c r="M10" s="3"/>
     </row>
     <row r="11" s="6" customFormat="1" customHeight="1" spans="3:13">
       <c r="C11" s="8">
-        <v>5012</v>
+        <v>5011</v>
       </c>
       <c r="D11" s="9" t="s">
         <v>141</v>
@@ -3914,7 +3920,7 @@
     </row>
     <row r="12" s="6" customFormat="1" customHeight="1" spans="3:13">
       <c r="C12" s="8">
-        <v>5013</v>
+        <v>5012</v>
       </c>
       <c r="D12" s="9" t="s">
         <v>143</v>
@@ -3947,7 +3953,7 @@
     </row>
     <row r="13" s="6" customFormat="1" customHeight="1" spans="3:13">
       <c r="C13" s="8">
-        <v>5014</v>
+        <v>5013</v>
       </c>
       <c r="D13" s="9" t="s">
         <v>145</v>
@@ -3979,53 +3985,54 @@
       </c>
     </row>
     <row r="14" s="6" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C14" s="7"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="7"/>
-      <c r="G14" s="7"/>
-      <c r="H14" s="7"/>
-      <c r="I14" s="7"/>
-      <c r="J14" s="7"/>
-      <c r="K14" s="7"/>
-      <c r="L14" s="7"/>
-      <c r="M14" s="7"/>
-    </row>
-    <row r="15" s="3" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C15" s="3">
-        <v>7001</v>
-      </c>
-      <c r="D15" s="3" t="s">
+      <c r="C14" s="8">
+        <v>5014</v>
+      </c>
+      <c r="D14" s="9" t="s">
         <v>147</v>
       </c>
-      <c r="E15" s="3">
-        <v>7</v>
-      </c>
-      <c r="F15" s="3" t="s">
+      <c r="E14" s="10">
+        <v>5</v>
+      </c>
+      <c r="F14" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="G15" s="3">
-        <v>1</v>
-      </c>
-      <c r="H15" s="3">
-        <v>9999999</v>
-      </c>
-      <c r="I15" s="3">
-        <v>0</v>
-      </c>
-      <c r="J15" s="3">
-        <v>6</v>
-      </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
-      <c r="M15" s="3">
-        <v>0</v>
-      </c>
+      <c r="G14" s="3">
+        <v>1</v>
+      </c>
+      <c r="H14" s="3">
+        <v>99999999</v>
+      </c>
+      <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3">
+        <v>3</v>
+      </c>
+      <c r="K14" s="3"/>
+      <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" s="6" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C15" s="7"/>
+      <c r="D15" s="7"/>
+      <c r="E15" s="7"/>
+      <c r="F15" s="7"/>
+      <c r="G15" s="7"/>
+      <c r="H15" s="7"/>
+      <c r="I15" s="7"/>
+      <c r="J15" s="7"/>
+      <c r="K15" s="7"/>
+      <c r="L15" s="7"/>
+      <c r="M15" s="7"/>
     </row>
     <row r="16" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C16" s="3">
-        <v>7002</v>
+        <v>7001</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>149</v>
@@ -4046,65 +4053,65 @@
         <v>0</v>
       </c>
       <c r="J16" s="3">
+        <v>6</v>
+      </c>
+      <c r="L16" s="3">
+        <v>0</v>
+      </c>
+      <c r="M16" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" s="3" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C17" s="3">
+        <v>7002</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="E17" s="3">
         <v>7</v>
       </c>
-      <c r="K16" s="3">
-        <v>0</v>
-      </c>
-      <c r="L16" s="3">
-        <v>0</v>
-      </c>
-      <c r="M16" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C18" s="3"/>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-      <c r="G18" s="3"/>
-      <c r="H18" s="3"/>
-      <c r="I18" s="3"/>
-      <c r="J18" s="3"/>
-      <c r="L18" s="3"/>
-      <c r="M18" s="3"/>
-    </row>
-    <row r="19" s="3" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C19" s="3">
-        <v>4001</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="E19" s="3">
-        <v>5</v>
-      </c>
-      <c r="F19" s="3" t="s">
+      <c r="F17" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="G19" s="3">
-        <v>1</v>
-      </c>
-      <c r="H19" s="3">
-        <v>99999999999</v>
-      </c>
-      <c r="I19" s="3">
-        <v>0</v>
-      </c>
-      <c r="J19" s="3">
-        <v>5</v>
-      </c>
-      <c r="L19" s="3">
-        <v>0</v>
-      </c>
-      <c r="M19" s="3">
-        <v>0</v>
-      </c>
+      <c r="G17" s="3">
+        <v>1</v>
+      </c>
+      <c r="H17" s="3">
+        <v>9999999</v>
+      </c>
+      <c r="I17" s="3">
+        <v>0</v>
+      </c>
+      <c r="J17" s="3">
+        <v>7</v>
+      </c>
+      <c r="K17" s="3">
+        <v>0</v>
+      </c>
+      <c r="L17" s="3">
+        <v>0</v>
+      </c>
+      <c r="M17" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C19" s="3"/>
+      <c r="D19" s="3"/>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="3"/>
+      <c r="H19" s="3"/>
+      <c r="I19" s="3"/>
+      <c r="J19" s="3"/>
+      <c r="L19" s="3"/>
+      <c r="M19" s="3"/>
     </row>
     <row r="20" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C20" s="3">
-        <v>4002</v>
+        <v>4001</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>153</v>
@@ -4136,13 +4143,13 @@
     </row>
     <row r="21" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C21" s="3">
-        <v>4003</v>
+        <v>4002</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>155</v>
       </c>
       <c r="E21" s="3">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F21" s="3" t="s">
         <v>156</v>
@@ -4151,7 +4158,7 @@
         <v>1</v>
       </c>
       <c r="H21" s="3">
-        <v>9999999</v>
+        <v>99999999999</v>
       </c>
       <c r="I21" s="3">
         <v>0</v>
@@ -4168,13 +4175,13 @@
     </row>
     <row r="22" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C22" s="3">
-        <v>4004</v>
+        <v>4003</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>157</v>
       </c>
       <c r="E22" s="3">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F22" s="3" t="s">
         <v>158</v>
@@ -4200,7 +4207,7 @@
     </row>
     <row r="23" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C23" s="3">
-        <v>4005</v>
+        <v>4004</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>159</v>
@@ -4232,7 +4239,7 @@
     </row>
     <row r="24" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C24" s="3">
-        <v>4006</v>
+        <v>4005</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>161</v>
@@ -4247,16 +4254,13 @@
         <v>1</v>
       </c>
       <c r="H24" s="3">
-        <v>99999999</v>
+        <v>9999999</v>
       </c>
       <c r="I24" s="3">
         <v>0</v>
       </c>
       <c r="J24" s="3">
         <v>5</v>
-      </c>
-      <c r="K24" s="3">
-        <v>0</v>
       </c>
       <c r="L24" s="3">
         <v>0</v>
@@ -4267,7 +4271,7 @@
     </row>
     <row r="25" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C25" s="3">
-        <v>4007</v>
+        <v>4006</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>163</v>
@@ -4282,13 +4286,16 @@
         <v>1</v>
       </c>
       <c r="H25" s="3">
-        <v>9999999999</v>
+        <v>99999999</v>
       </c>
       <c r="I25" s="3">
         <v>0</v>
       </c>
       <c r="J25" s="3">
         <v>5</v>
+      </c>
+      <c r="K25" s="3">
+        <v>0</v>
       </c>
       <c r="L25" s="3">
         <v>0</v>
@@ -4299,7 +4306,7 @@
     </row>
     <row r="26" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C26" s="3">
-        <v>4008</v>
+        <v>4007</v>
       </c>
       <c r="D26" s="3" t="s">
         <v>165</v>
@@ -4314,7 +4321,7 @@
         <v>1</v>
       </c>
       <c r="H26" s="3">
-        <v>9999999</v>
+        <v>9999999999</v>
       </c>
       <c r="I26" s="3">
         <v>0</v>
@@ -4331,7 +4338,7 @@
     </row>
     <row r="27" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C27" s="3">
-        <v>4009</v>
+        <v>4008</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>167</v>
@@ -4363,7 +4370,7 @@
     </row>
     <row r="28" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C28" s="3">
-        <v>4010</v>
+        <v>4009</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>169</v>
@@ -4395,7 +4402,7 @@
     </row>
     <row r="29" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C29" s="3">
-        <v>4011</v>
+        <v>4010</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>171</v>
@@ -4416,7 +4423,7 @@
         <v>0</v>
       </c>
       <c r="J29" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L29" s="3">
         <v>0</v>
@@ -4427,7 +4434,7 @@
     </row>
     <row r="30" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C30" s="3">
-        <v>4012</v>
+        <v>4011</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>173</v>
@@ -4459,13 +4466,13 @@
     </row>
     <row r="31" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C31" s="3">
-        <v>4013</v>
+        <v>4012</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>175</v>
       </c>
       <c r="E31" s="3">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F31" s="3" t="s">
         <v>176</v>
@@ -4480,7 +4487,7 @@
         <v>0</v>
       </c>
       <c r="J31" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L31" s="3">
         <v>0</v>
@@ -4491,13 +4498,13 @@
     </row>
     <row r="32" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C32" s="3">
-        <v>4015</v>
+        <v>4013</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>177</v>
       </c>
       <c r="E32" s="3">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F32" s="3" t="s">
         <v>178</v>
@@ -4512,7 +4519,7 @@
         <v>0</v>
       </c>
       <c r="J32" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L32" s="3">
         <v>0</v>
@@ -4523,7 +4530,7 @@
     </row>
     <row r="33" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C33" s="3">
-        <v>4016</v>
+        <v>4015</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>179</v>
@@ -4555,13 +4562,13 @@
     </row>
     <row r="34" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C34" s="3">
-        <v>4017</v>
+        <v>4016</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>181</v>
       </c>
       <c r="E34" s="3">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F34" s="3" t="s">
         <v>182</v>
@@ -4576,7 +4583,7 @@
         <v>0</v>
       </c>
       <c r="J34" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L34" s="3">
         <v>0</v>
@@ -4587,13 +4594,13 @@
     </row>
     <row r="35" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C35" s="3">
-        <v>4018</v>
+        <v>4017</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>183</v>
       </c>
       <c r="E35" s="3">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F35" s="3" t="s">
         <v>184</v>
@@ -4608,7 +4615,7 @@
         <v>0</v>
       </c>
       <c r="J35" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L35" s="3">
         <v>0</v>
@@ -4619,7 +4626,7 @@
     </row>
     <row r="36" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C36" s="3">
-        <v>4019</v>
+        <v>4018</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>185</v>
@@ -4640,50 +4647,50 @@
         <v>0</v>
       </c>
       <c r="J36" s="3">
+        <v>6</v>
+      </c>
+      <c r="L36" s="3">
+        <v>0</v>
+      </c>
+      <c r="M36" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" s="3" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C37" s="3">
+        <v>4019</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="E37" s="3">
+        <v>5</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="G37" s="3">
+        <v>1</v>
+      </c>
+      <c r="H37" s="3">
+        <v>9999999</v>
+      </c>
+      <c r="I37" s="3">
+        <v>0</v>
+      </c>
+      <c r="J37" s="3">
         <v>7</v>
       </c>
-      <c r="L36" s="3">
-        <v>0</v>
-      </c>
-      <c r="M36" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" s="3" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C38" s="3">
-        <v>4021</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="E38" s="3">
-        <v>5</v>
-      </c>
-      <c r="F38" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="G38" s="3">
-        <v>1</v>
-      </c>
-      <c r="H38" s="3">
-        <v>9999999</v>
-      </c>
-      <c r="I38" s="3">
-        <v>0</v>
-      </c>
-      <c r="J38" s="3">
-        <v>6</v>
-      </c>
-      <c r="L38" s="3">
-        <v>0</v>
-      </c>
-      <c r="M38" s="3">
+      <c r="L37" s="3">
+        <v>0</v>
+      </c>
+      <c r="M37" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="39" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C39" s="3">
-        <v>4022</v>
+        <v>4021</v>
       </c>
       <c r="D39" s="3" t="s">
         <v>189</v>
@@ -4704,7 +4711,7 @@
         <v>0</v>
       </c>
       <c r="J39" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L39" s="3">
         <v>0</v>
@@ -4715,7 +4722,7 @@
     </row>
     <row r="40" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C40" s="3">
-        <v>4023</v>
+        <v>4022</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>191</v>
@@ -4747,7 +4754,7 @@
     </row>
     <row r="41" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C41" s="3">
-        <v>4024</v>
+        <v>4023</v>
       </c>
       <c r="D41" s="3" t="s">
         <v>193</v>
@@ -4768,7 +4775,7 @@
         <v>0</v>
       </c>
       <c r="J41" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L41" s="3">
         <v>0</v>
@@ -4779,7 +4786,7 @@
     </row>
     <row r="42" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C42" s="3">
-        <v>4025</v>
+        <v>4024</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>195</v>
@@ -4800,7 +4807,7 @@
         <v>0</v>
       </c>
       <c r="J42" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L42" s="3">
         <v>0</v>
@@ -4811,7 +4818,7 @@
     </row>
     <row r="43" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C43" s="3">
-        <v>4026</v>
+        <v>4025</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>197</v>
@@ -4832,7 +4839,7 @@
         <v>0</v>
       </c>
       <c r="J43" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L43" s="3">
         <v>0</v>
@@ -4843,7 +4850,7 @@
     </row>
     <row r="44" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C44" s="3">
-        <v>4027</v>
+        <v>4026</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>199</v>
@@ -4864,7 +4871,7 @@
         <v>0</v>
       </c>
       <c r="J44" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -4875,7 +4882,7 @@
     </row>
     <row r="45" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C45" s="3">
-        <v>4028</v>
+        <v>4027</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>201</v>
@@ -4907,7 +4914,7 @@
     </row>
     <row r="46" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C46" s="3">
-        <v>4029</v>
+        <v>4028</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>203</v>
@@ -4939,7 +4946,7 @@
     </row>
     <row r="47" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C47" s="3">
-        <v>4030</v>
+        <v>4029</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>205</v>
@@ -4971,7 +4978,7 @@
     </row>
     <row r="48" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C48" s="3">
-        <v>4031</v>
+        <v>4030</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>207</v>
@@ -5003,7 +5010,7 @@
     </row>
     <row r="49" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C49" s="3">
-        <v>4032</v>
+        <v>4031</v>
       </c>
       <c r="D49" s="3" t="s">
         <v>209</v>
@@ -5035,7 +5042,7 @@
     </row>
     <row r="50" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C50" s="3">
-        <v>4033</v>
+        <v>4032</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>211</v>
@@ -5044,7 +5051,7 @@
         <v>5</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>180</v>
+        <v>212</v>
       </c>
       <c r="G50" s="3">
         <v>1</v>
@@ -5056,7 +5063,7 @@
         <v>0</v>
       </c>
       <c r="J50" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L50" s="3">
         <v>0</v>
@@ -5067,16 +5074,16 @@
     </row>
     <row r="51" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C51" s="3">
-        <v>4034</v>
+        <v>4033</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E51" s="3">
         <v>5</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>213</v>
+        <v>182</v>
       </c>
       <c r="G51" s="3">
         <v>1</v>
@@ -5088,7 +5095,7 @@
         <v>0</v>
       </c>
       <c r="J51" s="3">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L51" s="3">
         <v>0</v>
@@ -5099,7 +5106,7 @@
     </row>
     <row r="52" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C52" s="3">
-        <v>4035</v>
+        <v>4034</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>214</v>
@@ -5120,7 +5127,7 @@
         <v>0</v>
       </c>
       <c r="J52" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L52" s="3">
         <v>0</v>
@@ -5131,7 +5138,7 @@
     </row>
     <row r="53" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C53" s="3">
-        <v>4037</v>
+        <v>4035</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>216</v>
@@ -5152,7 +5159,7 @@
         <v>0</v>
       </c>
       <c r="J53" s="3">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L53" s="3">
         <v>0</v>
@@ -5163,7 +5170,7 @@
     </row>
     <row r="54" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C54" s="3">
-        <v>4038</v>
+        <v>4037</v>
       </c>
       <c r="D54" s="3" t="s">
         <v>218</v>
@@ -5195,7 +5202,7 @@
     </row>
     <row r="55" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C55" s="3">
-        <v>4039</v>
+        <v>4038</v>
       </c>
       <c r="D55" s="3" t="s">
         <v>220</v>
@@ -5216,7 +5223,7 @@
         <v>0</v>
       </c>
       <c r="J55" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L55" s="3">
         <v>0</v>
@@ -5227,7 +5234,7 @@
     </row>
     <row r="56" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C56" s="3">
-        <v>4040</v>
+        <v>4039</v>
       </c>
       <c r="D56" s="3" t="s">
         <v>222</v>
@@ -5236,7 +5243,7 @@
         <v>5</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>180</v>
+        <v>223</v>
       </c>
       <c r="G56" s="3">
         <v>1</v>
@@ -5248,7 +5255,7 @@
         <v>0</v>
       </c>
       <c r="J56" s="3">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L56" s="3">
         <v>0</v>
@@ -5259,16 +5266,16 @@
     </row>
     <row r="57" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C57" s="3">
-        <v>4041</v>
+        <v>4040</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E57" s="3">
         <v>5</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>224</v>
+        <v>182</v>
       </c>
       <c r="G57" s="3">
         <v>1</v>
@@ -5280,7 +5287,7 @@
         <v>0</v>
       </c>
       <c r="J57" s="3">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L57" s="3">
         <v>0</v>
@@ -5291,7 +5298,7 @@
     </row>
     <row r="58" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C58" s="3">
-        <v>4042</v>
+        <v>4041</v>
       </c>
       <c r="D58" s="3" t="s">
         <v>225</v>
@@ -5306,13 +5313,13 @@
         <v>1</v>
       </c>
       <c r="H58" s="3">
-        <v>1999999999</v>
+        <v>9999999</v>
       </c>
       <c r="I58" s="3">
         <v>0</v>
       </c>
       <c r="J58" s="3">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="L58" s="3">
         <v>0</v>
@@ -5323,7 +5330,7 @@
     </row>
     <row r="59" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C59" s="3">
-        <v>4043</v>
+        <v>4042</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>227</v>
@@ -5332,19 +5339,19 @@
         <v>5</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="G59" s="3">
         <v>1</v>
       </c>
       <c r="H59" s="3">
-        <v>9999999</v>
+        <v>1999999999</v>
       </c>
       <c r="I59" s="3">
         <v>0</v>
       </c>
       <c r="J59" s="3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L59" s="3">
         <v>0</v>
@@ -5355,16 +5362,16 @@
     </row>
     <row r="60" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C60" s="3">
-        <v>4044</v>
+        <v>4043</v>
       </c>
       <c r="D60" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="E60" s="3">
+        <v>5</v>
+      </c>
+      <c r="F60" s="3" t="s">
         <v>228</v>
-      </c>
-      <c r="E60" s="3">
-        <v>5</v>
-      </c>
-      <c r="F60" s="3" t="s">
-        <v>229</v>
       </c>
       <c r="G60" s="3">
         <v>1</v>
@@ -5376,62 +5383,62 @@
         <v>0</v>
       </c>
       <c r="J60" s="3">
+        <v>7</v>
+      </c>
+      <c r="L60" s="3">
+        <v>0</v>
+      </c>
+      <c r="M60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" s="3" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C61" s="3">
+        <v>4044</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="E61" s="3">
+        <v>5</v>
+      </c>
+      <c r="F61" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="G61" s="3">
+        <v>1</v>
+      </c>
+      <c r="H61" s="3">
+        <v>9999999</v>
+      </c>
+      <c r="I61" s="3">
+        <v>0</v>
+      </c>
+      <c r="J61" s="3">
         <v>9</v>
       </c>
-      <c r="L60" s="3">
-        <v>0</v>
-      </c>
-      <c r="M60" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C61" s="3"/>
-      <c r="D61" s="3"/>
-      <c r="E61" s="3"/>
-      <c r="F61" s="3"/>
-      <c r="G61" s="3"/>
-      <c r="H61" s="3"/>
-      <c r="I61" s="3"/>
-      <c r="J61" s="3"/>
-      <c r="L61" s="3"/>
-      <c r="M61" s="3"/>
-    </row>
-    <row r="62" s="3" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C62" s="3">
-        <v>4101</v>
-      </c>
-      <c r="D62" s="3" t="s">
-        <v>230</v>
-      </c>
-      <c r="E62" s="3">
-        <v>5</v>
-      </c>
-      <c r="F62" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="G62" s="3">
-        <v>1</v>
-      </c>
-      <c r="H62" s="3">
-        <v>9999999</v>
-      </c>
-      <c r="I62" s="3">
-        <v>0</v>
-      </c>
-      <c r="J62" s="3">
-        <v>5</v>
-      </c>
-      <c r="L62" s="3">
-        <v>0</v>
-      </c>
-      <c r="M62" s="3">
-        <v>0</v>
-      </c>
+      <c r="L61" s="3">
+        <v>0</v>
+      </c>
+      <c r="M61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C62" s="3"/>
+      <c r="D62" s="3"/>
+      <c r="E62" s="3"/>
+      <c r="F62" s="3"/>
+      <c r="G62" s="3"/>
+      <c r="H62" s="3"/>
+      <c r="I62" s="3"/>
+      <c r="J62" s="3"/>
+      <c r="L62" s="3"/>
+      <c r="M62" s="3"/>
     </row>
     <row r="63" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C63" s="3">
-        <v>4111</v>
+        <v>4101</v>
       </c>
       <c r="D63" s="3" t="s">
         <v>232</v>
@@ -5463,7 +5470,7 @@
     </row>
     <row r="64" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C64" s="3">
-        <v>4112</v>
+        <v>4111</v>
       </c>
       <c r="D64" s="3" t="s">
         <v>234</v>
@@ -5484,7 +5491,7 @@
         <v>0</v>
       </c>
       <c r="J64" s="3">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="L64" s="3">
         <v>0</v>
@@ -5495,7 +5502,7 @@
     </row>
     <row r="65" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C65" s="3">
-        <v>4113</v>
+        <v>4112</v>
       </c>
       <c r="D65" s="3" t="s">
         <v>236</v>
@@ -5516,94 +5523,94 @@
         <v>0</v>
       </c>
       <c r="J65" s="3">
+        <v>8</v>
+      </c>
+      <c r="L65" s="3">
+        <v>0</v>
+      </c>
+      <c r="M65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" s="3" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C66" s="3">
+        <v>4113</v>
+      </c>
+      <c r="D66" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="E66" s="3">
+        <v>5</v>
+      </c>
+      <c r="F66" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="G66" s="3">
+        <v>1</v>
+      </c>
+      <c r="H66" s="3">
+        <v>9999999</v>
+      </c>
+      <c r="I66" s="3">
+        <v>0</v>
+      </c>
+      <c r="J66" s="3">
         <v>7</v>
       </c>
-      <c r="L65" s="3">
-        <v>0</v>
-      </c>
-      <c r="M65" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C66" s="3"/>
-      <c r="D66" s="3"/>
-      <c r="E66" s="3"/>
-      <c r="F66" s="3"/>
-      <c r="G66" s="3"/>
-      <c r="H66" s="3"/>
-      <c r="I66" s="3"/>
-      <c r="J66" s="3"/>
-      <c r="L66" s="3"/>
-      <c r="M66" s="3"/>
-    </row>
-    <row r="67" s="3" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C67" s="3">
+      <c r="L66" s="3">
+        <v>0</v>
+      </c>
+      <c r="M66" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C67" s="3"/>
+      <c r="D67" s="3"/>
+      <c r="E67" s="3"/>
+      <c r="F67" s="3"/>
+      <c r="G67" s="3"/>
+      <c r="H67" s="3"/>
+      <c r="I67" s="3"/>
+      <c r="J67" s="3"/>
+      <c r="L67" s="3"/>
+      <c r="M67" s="3"/>
+    </row>
+    <row r="68" s="3" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C68" s="3">
         <v>4201</v>
       </c>
-      <c r="D67" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="E67" s="3">
-        <v>5</v>
-      </c>
-      <c r="F67" s="3" t="s">
-        <v>239</v>
-      </c>
-      <c r="G67" s="3">
-        <v>1</v>
-      </c>
-      <c r="H67" s="3">
+      <c r="D68" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="E68" s="3">
+        <v>5</v>
+      </c>
+      <c r="F68" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="G68" s="3">
+        <v>1</v>
+      </c>
+      <c r="H68" s="3">
         <v>99999999</v>
       </c>
-      <c r="I67" s="3">
-        <v>0</v>
-      </c>
-      <c r="J67" s="3">
-        <v>5</v>
-      </c>
-      <c r="L67" s="3">
+      <c r="I68" s="3">
+        <v>0</v>
+      </c>
+      <c r="J68" s="3">
+        <v>5</v>
+      </c>
+      <c r="L68" s="3">
         <v>4002</v>
       </c>
-      <c r="M67" s="3">
+      <c r="M68" s="3">
         <v>1000</v>
-      </c>
-    </row>
-    <row r="72" s="3" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C72" s="3">
-        <v>8001</v>
-      </c>
-      <c r="D72" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="E72" s="3">
-        <v>5</v>
-      </c>
-      <c r="F72" s="3" t="s">
-        <v>241</v>
-      </c>
-      <c r="G72" s="3">
-        <v>1</v>
-      </c>
-      <c r="H72" s="3">
-        <v>9999999</v>
-      </c>
-      <c r="I72" s="3">
-        <v>0</v>
-      </c>
-      <c r="J72" s="3">
-        <v>6</v>
-      </c>
-      <c r="L72" s="3">
-        <v>0</v>
-      </c>
-      <c r="M72" s="3">
-        <v>0</v>
       </c>
     </row>
     <row r="73" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C73" s="3">
-        <v>8002</v>
+        <v>8001</v>
       </c>
       <c r="D73" s="3" t="s">
         <v>242</v>
@@ -5612,7 +5619,7 @@
         <v>5</v>
       </c>
       <c r="F73" s="3" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="G73" s="3">
         <v>1</v>
@@ -5635,16 +5642,16 @@
     </row>
     <row r="74" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C74" s="3">
-        <v>8003</v>
+        <v>8002</v>
       </c>
       <c r="D74" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="E74" s="3">
+        <v>5</v>
+      </c>
+      <c r="F74" s="3" t="s">
         <v>243</v>
-      </c>
-      <c r="E74" s="3">
-        <v>5</v>
-      </c>
-      <c r="F74" s="3" t="s">
-        <v>241</v>
       </c>
       <c r="G74" s="3">
         <v>1</v>
@@ -5667,16 +5674,16 @@
     </row>
     <row r="75" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C75" s="3">
-        <v>8004</v>
+        <v>8003</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E75" s="3">
         <v>5</v>
       </c>
       <c r="F75" s="3" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="G75" s="3">
         <v>1</v>
@@ -5699,16 +5706,16 @@
     </row>
     <row r="76" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C76" s="3">
-        <v>8005</v>
+        <v>8004</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E76" s="3">
         <v>5</v>
       </c>
       <c r="F76" s="3" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="G76" s="3">
         <v>1</v>
@@ -5731,16 +5738,16 @@
     </row>
     <row r="77" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C77" s="3">
-        <v>8006</v>
+        <v>8005</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E77" s="3">
         <v>5</v>
       </c>
       <c r="F77" s="3" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="G77" s="3">
         <v>1</v>
@@ -5763,16 +5770,16 @@
     </row>
     <row r="78" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C78" s="3">
-        <v>8007</v>
+        <v>8006</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E78" s="3">
         <v>5</v>
       </c>
       <c r="F78" s="3" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="G78" s="3">
         <v>1</v>
@@ -5795,16 +5802,16 @@
     </row>
     <row r="79" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C79" s="3">
-        <v>8008</v>
+        <v>8007</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E79" s="3">
         <v>5</v>
       </c>
       <c r="F79" s="3" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="G79" s="3">
         <v>1</v>
@@ -5827,16 +5834,16 @@
     </row>
     <row r="80" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C80" s="3">
-        <v>8009</v>
+        <v>8008</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E80" s="3">
         <v>5</v>
       </c>
       <c r="F80" s="3" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="G80" s="3">
         <v>1</v>
@@ -5859,16 +5866,16 @@
     </row>
     <row r="81" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C81" s="3">
-        <v>8010</v>
+        <v>8009</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="E81" s="3">
         <v>5</v>
       </c>
       <c r="F81" s="3" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="G81" s="3">
         <v>1</v>
@@ -5889,41 +5896,41 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" s="3" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C83" s="3">
-        <v>8101</v>
-      </c>
-      <c r="D83" s="9" t="s">
-        <v>251</v>
-      </c>
-      <c r="E83" s="3">
-        <v>5</v>
-      </c>
-      <c r="F83" s="3" t="s">
+    <row r="82" s="3" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C82" s="3">
+        <v>8010</v>
+      </c>
+      <c r="D82" s="3" t="s">
         <v>252</v>
       </c>
-      <c r="G83" s="3">
-        <v>1</v>
-      </c>
-      <c r="H83" s="3">
+      <c r="E82" s="3">
+        <v>5</v>
+      </c>
+      <c r="F82" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="G82" s="3">
+        <v>1</v>
+      </c>
+      <c r="H82" s="3">
         <v>9999999</v>
       </c>
-      <c r="I83" s="3">
-        <v>0</v>
-      </c>
-      <c r="J83" s="3">
-        <v>7</v>
-      </c>
-      <c r="L83" s="3">
-        <v>0</v>
-      </c>
-      <c r="M83" s="3">
+      <c r="I82" s="3">
+        <v>0</v>
+      </c>
+      <c r="J82" s="3">
+        <v>6</v>
+      </c>
+      <c r="L82" s="3">
+        <v>0</v>
+      </c>
+      <c r="M82" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="84" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C84" s="3">
-        <v>8102</v>
+        <v>8101</v>
       </c>
       <c r="D84" s="9" t="s">
         <v>253</v>
@@ -5932,7 +5939,7 @@
         <v>5</v>
       </c>
       <c r="F84" s="3" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="G84" s="3">
         <v>1</v>
@@ -5955,16 +5962,16 @@
     </row>
     <row r="85" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C85" s="3">
-        <v>8103</v>
+        <v>8102</v>
       </c>
       <c r="D85" s="9" t="s">
+        <v>255</v>
+      </c>
+      <c r="E85" s="3">
+        <v>5</v>
+      </c>
+      <c r="F85" s="3" t="s">
         <v>254</v>
-      </c>
-      <c r="E85" s="3">
-        <v>5</v>
-      </c>
-      <c r="F85" s="3" t="s">
-        <v>252</v>
       </c>
       <c r="G85" s="3">
         <v>1</v>
@@ -5987,16 +5994,16 @@
     </row>
     <row r="86" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C86" s="3">
-        <v>8104</v>
+        <v>8103</v>
       </c>
       <c r="D86" s="9" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E86" s="3">
         <v>5</v>
       </c>
       <c r="F86" s="3" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="G86" s="3">
         <v>1</v>
@@ -6019,16 +6026,16 @@
     </row>
     <row r="87" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C87" s="3">
-        <v>8105</v>
+        <v>8104</v>
       </c>
       <c r="D87" s="9" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E87" s="3">
         <v>5</v>
       </c>
       <c r="F87" s="3" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="G87" s="3">
         <v>1</v>
@@ -6051,16 +6058,16 @@
     </row>
     <row r="88" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C88" s="3">
-        <v>8106</v>
+        <v>8105</v>
       </c>
       <c r="D88" s="9" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E88" s="3">
         <v>5</v>
       </c>
       <c r="F88" s="3" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="G88" s="3">
         <v>1</v>
@@ -6083,16 +6090,16 @@
     </row>
     <row r="89" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C89" s="3">
-        <v>8107</v>
+        <v>8106</v>
       </c>
       <c r="D89" s="9" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E89" s="3">
         <v>5</v>
       </c>
       <c r="F89" s="3" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="G89" s="3">
         <v>1</v>
@@ -6115,16 +6122,16 @@
     </row>
     <row r="90" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C90" s="3">
-        <v>8108</v>
+        <v>8107</v>
       </c>
       <c r="D90" s="9" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E90" s="3">
         <v>5</v>
       </c>
       <c r="F90" s="3" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="G90" s="3">
         <v>1</v>
@@ -6145,44 +6152,41 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" customHeight="1" spans="3:13">
-      <c r="C92" s="3">
-        <v>8201</v>
-      </c>
-      <c r="D92" s="9" t="s">
-        <v>260</v>
-      </c>
-      <c r="E92" s="3">
-        <v>16</v>
-      </c>
-      <c r="F92" s="3" t="s">
+    <row r="91" s="3" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C91" s="3">
+        <v>8108</v>
+      </c>
+      <c r="D91" s="9" t="s">
         <v>261</v>
       </c>
-      <c r="G92" s="3">
-        <v>1</v>
-      </c>
-      <c r="H92" s="3">
-        <v>1</v>
-      </c>
-      <c r="I92" s="3">
-        <v>0</v>
-      </c>
-      <c r="J92" s="3">
-        <v>1</v>
-      </c>
-      <c r="K92" s="3">
-        <v>0</v>
-      </c>
-      <c r="L92" s="3">
-        <v>0</v>
-      </c>
-      <c r="M92" s="3">
+      <c r="E91" s="3">
+        <v>5</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="G91" s="3">
+        <v>1</v>
+      </c>
+      <c r="H91" s="3">
+        <v>9999999</v>
+      </c>
+      <c r="I91" s="3">
+        <v>0</v>
+      </c>
+      <c r="J91" s="3">
+        <v>7</v>
+      </c>
+      <c r="L91" s="3">
+        <v>0</v>
+      </c>
+      <c r="M91" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="93" customHeight="1" spans="3:13">
       <c r="C93" s="3">
-        <v>8202</v>
+        <v>8201</v>
       </c>
       <c r="D93" s="9" t="s">
         <v>262</v>
@@ -6203,7 +6207,7 @@
         <v>0</v>
       </c>
       <c r="J93" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K93" s="3">
         <v>0</v>
@@ -6217,7 +6221,7 @@
     </row>
     <row r="94" customHeight="1" spans="3:13">
       <c r="C94" s="3">
-        <v>8203</v>
+        <v>8202</v>
       </c>
       <c r="D94" s="9" t="s">
         <v>264</v>
@@ -6238,7 +6242,7 @@
         <v>0</v>
       </c>
       <c r="J94" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K94" s="3">
         <v>0</v>
@@ -6252,7 +6256,7 @@
     </row>
     <row r="95" customHeight="1" spans="3:13">
       <c r="C95" s="3">
-        <v>8204</v>
+        <v>8203</v>
       </c>
       <c r="D95" s="9" t="s">
         <v>266</v>
@@ -6273,7 +6277,7 @@
         <v>0</v>
       </c>
       <c r="J95" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K95" s="3">
         <v>0</v>
@@ -6287,7 +6291,7 @@
     </row>
     <row r="96" customHeight="1" spans="3:13">
       <c r="C96" s="3">
-        <v>8205</v>
+        <v>8204</v>
       </c>
       <c r="D96" s="9" t="s">
         <v>268</v>
@@ -6308,7 +6312,7 @@
         <v>0</v>
       </c>
       <c r="J96" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -6322,7 +6326,7 @@
     </row>
     <row r="97" customHeight="1" spans="3:13">
       <c r="C97" s="3">
-        <v>8206</v>
+        <v>8205</v>
       </c>
       <c r="D97" s="9" t="s">
         <v>270</v>
@@ -6343,7 +6347,7 @@
         <v>0</v>
       </c>
       <c r="J97" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K97" s="3">
         <v>0</v>
@@ -6357,7 +6361,7 @@
     </row>
     <row r="98" customHeight="1" spans="3:13">
       <c r="C98" s="3">
-        <v>8207</v>
+        <v>8206</v>
       </c>
       <c r="D98" s="9" t="s">
         <v>272</v>
@@ -6378,20 +6382,52 @@
         <v>0</v>
       </c>
       <c r="J98" s="3">
+        <v>6</v>
+      </c>
+      <c r="K98" s="3">
+        <v>0</v>
+      </c>
+      <c r="L98" s="3">
+        <v>0</v>
+      </c>
+      <c r="M98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" customHeight="1" spans="3:13">
+      <c r="C99" s="3">
+        <v>8207</v>
+      </c>
+      <c r="D99" s="9" t="s">
+        <v>274</v>
+      </c>
+      <c r="E99" s="3">
+        <v>16</v>
+      </c>
+      <c r="F99" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="G99" s="3">
+        <v>1</v>
+      </c>
+      <c r="H99" s="3">
+        <v>1</v>
+      </c>
+      <c r="I99" s="3">
+        <v>0</v>
+      </c>
+      <c r="J99" s="3">
         <v>7</v>
       </c>
-      <c r="K98" s="3">
-        <v>0</v>
-      </c>
-      <c r="L98" s="3">
-        <v>0</v>
-      </c>
-      <c r="M98" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="100" customHeight="1" spans="3:13">
-      <c r="D100" s="9"/>
+      <c r="K99" s="3">
+        <v>0</v>
+      </c>
+      <c r="L99" s="3">
+        <v>0</v>
+      </c>
+      <c r="M99" s="3">
+        <v>0</v>
+      </c>
     </row>
     <row r="101" customHeight="1" spans="3:13">
       <c r="D101" s="9"/>
@@ -6411,8 +6447,8 @@
     <row r="106" customHeight="1" spans="3:13">
       <c r="D106" s="9"/>
     </row>
-    <row r="108" customHeight="1" spans="3:13">
-      <c r="D108" s="9"/>
+    <row r="107" customHeight="1" spans="3:13">
+      <c r="D107" s="9"/>
     </row>
     <row r="109" customHeight="1" spans="3:13">
       <c r="D109" s="9"/>
@@ -6432,12 +6468,15 @@
     <row r="114" customHeight="1" spans="4:4">
       <c r="D114" s="9"/>
     </row>
+    <row r="115" customHeight="1" spans="4:4">
+      <c r="D115" s="9"/>
+    </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C9:D9 C14:D14 C10:C13 C3:D5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C10:D10 C15:D15 C11:C14 C3:D5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="L14:M14 L3:M5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="L15:M15 L3:M5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,L3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>
@@ -6576,13 +6615,13 @@
         <v>9001</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="E6" s="2">
         <v>6</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="G6" s="2">
         <v>1</v>
@@ -6605,13 +6644,13 @@
         <v>9002</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="E7" s="2">
         <v>6</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="G7" s="2">
         <v>1</v>
@@ -6634,13 +6673,13 @@
         <v>9003</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E8" s="2">
         <v>6</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="G8" s="2">
         <v>1</v>
@@ -6663,13 +6702,13 @@
         <v>9004</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="E9" s="2">
         <v>6</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="G9" s="2">
         <v>1</v>
@@ -6692,13 +6731,13 @@
         <v>9005</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E10" s="2">
         <v>6</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="G10" s="2">
         <v>1</v>
@@ -6721,13 +6760,13 @@
         <v>9006</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="E11" s="2">
         <v>6</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="G11" s="2">
         <v>1</v>
@@ -6749,13 +6788,13 @@
         <v>9007</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E12" s="2">
         <v>6</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="G12" s="2">
         <v>1</v>
@@ -6777,13 +6816,13 @@
         <v>9008</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="E13" s="2">
         <v>6</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="G13" s="2">
         <v>1</v>
@@ -6805,13 +6844,13 @@
         <v>9009</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="E14" s="2">
         <v>6</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="G14" s="2">
         <v>1</v>
@@ -6833,13 +6872,13 @@
         <v>9010</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="E15" s="2">
         <v>6</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="G15" s="2">
         <v>1</v>
@@ -6861,13 +6900,13 @@
         <v>9011</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="E16" s="2">
         <v>6</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="G16" s="2">
         <v>1</v>
@@ -7033,13 +7072,13 @@
         <v>10001</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="E6" s="2">
         <v>5</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="G6" s="2">
         <v>1</v>
@@ -7065,13 +7104,13 @@
         <v>10002</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="E7" s="2">
         <v>5</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="G7" s="2">
         <v>1</v>
@@ -7097,13 +7136,13 @@
         <v>10003</v>
       </c>
       <c r="D8" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="E8" s="2">
+        <v>5</v>
+      </c>
+      <c r="F8" s="2" t="s">
         <v>289</v>
-      </c>
-      <c r="E8" s="2">
-        <v>5</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>287</v>
       </c>
       <c r="G8" s="2">
         <v>1</v>
@@ -7129,13 +7168,13 @@
         <v>10004</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="E9" s="2">
         <v>5</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="G9" s="2">
         <v>1</v>
@@ -7388,13 +7427,13 @@
         <v>40000001</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="E6" s="2">
         <v>6</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="G6" s="2">
         <v>1</v>
@@ -7415,13 +7454,13 @@
         <v>40000002</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="E7" s="2">
         <v>6</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="G7" s="2">
         <v>1</v>
@@ -7442,13 +7481,13 @@
         <v>40000003</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="E8" s="2">
         <v>6</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="G8" s="2">
         <v>1</v>
@@ -7469,13 +7508,13 @@
         <v>40000004</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="E9" s="2">
         <v>6</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="G9" s="2">
         <v>1</v>
@@ -7496,13 +7535,13 @@
         <v>40000005</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="E10" s="2">
         <v>6</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="G10" s="2">
         <v>1</v>
@@ -7523,13 +7562,13 @@
         <v>40000006</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="E11" s="2">
         <v>6</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="G11" s="2">
         <v>1</v>

--- a/Excel/ItemConfig.xlsx
+++ b/Excel/ItemConfig.xlsx
@@ -649,6 +649,12 @@
     <t>宠物升级的材料</t>
   </si>
   <si>
+    <t>传世精华</t>
+  </si>
+  <si>
+    <t>分解传世装备获取，强化传世装备</t>
+  </si>
+  <si>
     <t>灵盾碎片</t>
   </si>
   <si>
@@ -749,12 +755,6 @@
   </si>
   <si>
     <t>分解红装获取，红装升阶材料，红装随机属性强化材料</t>
-  </si>
-  <si>
-    <t>传世精华</t>
-  </si>
-  <si>
-    <t>分解传世装备获取，升级传世装备</t>
   </si>
   <si>
     <t>传世挑战卷</t>
@@ -1328,12 +1328,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -3622,7 +3622,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:M115"/>
+  <dimension ref="C3:M116"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="3"/>
@@ -3872,55 +3872,54 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" s="6" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C10" s="7"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="3"/>
-      <c r="H10" s="3"/>
-      <c r="I10" s="3"/>
-      <c r="J10" s="3"/>
-      <c r="K10" s="3"/>
-      <c r="L10" s="3"/>
-      <c r="M10" s="3"/>
+    <row r="10" s="3" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C10" s="3">
+        <v>5005</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="E10" s="3">
+        <v>5</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="G10" s="3">
+        <v>1</v>
+      </c>
+      <c r="H10" s="3">
+        <v>99999999</v>
+      </c>
+      <c r="I10" s="3">
+        <v>0</v>
+      </c>
+      <c r="J10" s="3">
+        <v>5</v>
+      </c>
+      <c r="L10" s="3">
+        <v>0</v>
+      </c>
+      <c r="M10" s="3">
+        <v>0</v>
+      </c>
     </row>
     <row r="11" s="6" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C11" s="8">
-        <v>5011</v>
-      </c>
-      <c r="D11" s="9" t="s">
-        <v>141</v>
-      </c>
-      <c r="E11" s="10">
-        <v>5</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="G11" s="3">
-        <v>1</v>
-      </c>
-      <c r="H11" s="3">
-        <v>99999999</v>
-      </c>
-      <c r="I11" s="3">
-        <v>0</v>
-      </c>
-      <c r="J11" s="3">
-        <v>3</v>
-      </c>
+      <c r="C11" s="7"/>
+      <c r="D11" s="7"/>
+      <c r="E11" s="7"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="3"/>
+      <c r="H11" s="3"/>
+      <c r="I11" s="3"/>
+      <c r="J11" s="3"/>
       <c r="K11" s="3"/>
-      <c r="L11" s="3">
-        <v>0</v>
-      </c>
-      <c r="M11" s="3">
-        <v>0</v>
-      </c>
+      <c r="L11" s="3"/>
+      <c r="M11" s="3"/>
     </row>
     <row r="12" s="6" customFormat="1" customHeight="1" spans="3:13">
       <c r="C12" s="8">
-        <v>5012</v>
+        <v>5011</v>
       </c>
       <c r="D12" s="9" t="s">
         <v>143</v>
@@ -3953,7 +3952,7 @@
     </row>
     <row r="13" s="6" customFormat="1" customHeight="1" spans="3:13">
       <c r="C13" s="8">
-        <v>5013</v>
+        <v>5012</v>
       </c>
       <c r="D13" s="9" t="s">
         <v>145</v>
@@ -3986,7 +3985,7 @@
     </row>
     <row r="14" s="6" customFormat="1" customHeight="1" spans="3:13">
       <c r="C14" s="8">
-        <v>5014</v>
+        <v>5013</v>
       </c>
       <c r="D14" s="9" t="s">
         <v>147</v>
@@ -4018,53 +4017,54 @@
       </c>
     </row>
     <row r="15" s="6" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C15" s="7"/>
-      <c r="D15" s="7"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="7"/>
-      <c r="G15" s="7"/>
-      <c r="H15" s="7"/>
-      <c r="I15" s="7"/>
-      <c r="J15" s="7"/>
-      <c r="K15" s="7"/>
-      <c r="L15" s="7"/>
-      <c r="M15" s="7"/>
-    </row>
-    <row r="16" s="3" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C16" s="3">
-        <v>7001</v>
-      </c>
-      <c r="D16" s="3" t="s">
+      <c r="C15" s="8">
+        <v>5014</v>
+      </c>
+      <c r="D15" s="9" t="s">
         <v>149</v>
       </c>
-      <c r="E16" s="3">
-        <v>7</v>
-      </c>
-      <c r="F16" s="3" t="s">
+      <c r="E15" s="10">
+        <v>5</v>
+      </c>
+      <c r="F15" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="G16" s="3">
-        <v>1</v>
-      </c>
-      <c r="H16" s="3">
-        <v>9999999</v>
-      </c>
-      <c r="I16" s="3">
-        <v>0</v>
-      </c>
-      <c r="J16" s="3">
-        <v>6</v>
-      </c>
-      <c r="L16" s="3">
-        <v>0</v>
-      </c>
-      <c r="M16" s="3">
-        <v>0</v>
-      </c>
+      <c r="G15" s="3">
+        <v>1</v>
+      </c>
+      <c r="H15" s="3">
+        <v>99999999</v>
+      </c>
+      <c r="I15" s="3">
+        <v>0</v>
+      </c>
+      <c r="J15" s="3">
+        <v>3</v>
+      </c>
+      <c r="K15" s="3"/>
+      <c r="L15" s="3">
+        <v>0</v>
+      </c>
+      <c r="M15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" s="6" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C16" s="7"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="7"/>
+      <c r="F16" s="7"/>
+      <c r="G16" s="7"/>
+      <c r="H16" s="7"/>
+      <c r="I16" s="7"/>
+      <c r="J16" s="7"/>
+      <c r="K16" s="7"/>
+      <c r="L16" s="7"/>
+      <c r="M16" s="7"/>
     </row>
     <row r="17" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C17" s="3">
-        <v>7002</v>
+        <v>7001</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>151</v>
@@ -4085,65 +4085,65 @@
         <v>0</v>
       </c>
       <c r="J17" s="3">
+        <v>6</v>
+      </c>
+      <c r="L17" s="3">
+        <v>0</v>
+      </c>
+      <c r="M17" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" s="3" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C18" s="3">
+        <v>7002</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="E18" s="3">
         <v>7</v>
       </c>
-      <c r="K17" s="3">
-        <v>0</v>
-      </c>
-      <c r="L17" s="3">
-        <v>0</v>
-      </c>
-      <c r="M17" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C19" s="3"/>
-      <c r="D19" s="3"/>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
-      <c r="G19" s="3"/>
-      <c r="H19" s="3"/>
-      <c r="I19" s="3"/>
-      <c r="J19" s="3"/>
-      <c r="L19" s="3"/>
-      <c r="M19" s="3"/>
-    </row>
-    <row r="20" s="3" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C20" s="3">
-        <v>4001</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="E20" s="3">
-        <v>5</v>
-      </c>
-      <c r="F20" s="3" t="s">
+      <c r="F18" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="G20" s="3">
-        <v>1</v>
-      </c>
-      <c r="H20" s="3">
-        <v>99999999999</v>
-      </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
-      <c r="J20" s="3">
-        <v>5</v>
-      </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
+      <c r="G18" s="3">
+        <v>1</v>
+      </c>
+      <c r="H18" s="3">
+        <v>9999999</v>
+      </c>
+      <c r="I18" s="3">
+        <v>0</v>
+      </c>
+      <c r="J18" s="3">
+        <v>7</v>
+      </c>
+      <c r="K18" s="3">
+        <v>0</v>
+      </c>
+      <c r="L18" s="3">
+        <v>0</v>
+      </c>
+      <c r="M18" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C20" s="3"/>
+      <c r="D20" s="3"/>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
+      <c r="G20" s="3"/>
+      <c r="H20" s="3"/>
+      <c r="I20" s="3"/>
+      <c r="J20" s="3"/>
+      <c r="L20" s="3"/>
+      <c r="M20" s="3"/>
     </row>
     <row r="21" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C21" s="3">
-        <v>4002</v>
+        <v>4001</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>155</v>
@@ -4175,13 +4175,13 @@
     </row>
     <row r="22" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C22" s="3">
-        <v>4003</v>
+        <v>4002</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>157</v>
       </c>
       <c r="E22" s="3">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F22" s="3" t="s">
         <v>158</v>
@@ -4190,7 +4190,7 @@
         <v>1</v>
       </c>
       <c r="H22" s="3">
-        <v>9999999</v>
+        <v>99999999999</v>
       </c>
       <c r="I22" s="3">
         <v>0</v>
@@ -4207,13 +4207,13 @@
     </row>
     <row r="23" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C23" s="3">
-        <v>4004</v>
+        <v>4003</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>159</v>
       </c>
       <c r="E23" s="3">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F23" s="3" t="s">
         <v>160</v>
@@ -4239,7 +4239,7 @@
     </row>
     <row r="24" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C24" s="3">
-        <v>4005</v>
+        <v>4004</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>161</v>
@@ -4271,7 +4271,7 @@
     </row>
     <row r="25" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C25" s="3">
-        <v>4006</v>
+        <v>4005</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>163</v>
@@ -4286,16 +4286,13 @@
         <v>1</v>
       </c>
       <c r="H25" s="3">
-        <v>99999999</v>
+        <v>9999999</v>
       </c>
       <c r="I25" s="3">
         <v>0</v>
       </c>
       <c r="J25" s="3">
         <v>5</v>
-      </c>
-      <c r="K25" s="3">
-        <v>0</v>
       </c>
       <c r="L25" s="3">
         <v>0</v>
@@ -4306,7 +4303,7 @@
     </row>
     <row r="26" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C26" s="3">
-        <v>4007</v>
+        <v>4006</v>
       </c>
       <c r="D26" s="3" t="s">
         <v>165</v>
@@ -4321,13 +4318,16 @@
         <v>1</v>
       </c>
       <c r="H26" s="3">
-        <v>9999999999</v>
+        <v>99999999</v>
       </c>
       <c r="I26" s="3">
         <v>0</v>
       </c>
       <c r="J26" s="3">
         <v>5</v>
+      </c>
+      <c r="K26" s="3">
+        <v>0</v>
       </c>
       <c r="L26" s="3">
         <v>0</v>
@@ -4338,7 +4338,7 @@
     </row>
     <row r="27" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C27" s="3">
-        <v>4008</v>
+        <v>4007</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>167</v>
@@ -4353,7 +4353,7 @@
         <v>1</v>
       </c>
       <c r="H27" s="3">
-        <v>9999999</v>
+        <v>9999999999</v>
       </c>
       <c r="I27" s="3">
         <v>0</v>
@@ -4370,7 +4370,7 @@
     </row>
     <row r="28" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C28" s="3">
-        <v>4009</v>
+        <v>4008</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>169</v>
@@ -4402,7 +4402,7 @@
     </row>
     <row r="29" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C29" s="3">
-        <v>4010</v>
+        <v>4009</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>171</v>
@@ -4434,7 +4434,7 @@
     </row>
     <row r="30" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C30" s="3">
-        <v>4011</v>
+        <v>4010</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>173</v>
@@ -4455,7 +4455,7 @@
         <v>0</v>
       </c>
       <c r="J30" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L30" s="3">
         <v>0</v>
@@ -4466,7 +4466,7 @@
     </row>
     <row r="31" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C31" s="3">
-        <v>4012</v>
+        <v>4011</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>175</v>
@@ -4496,50 +4496,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" s="3" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C32" s="3">
-        <v>4013</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="E32" s="3">
-        <v>9</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="G32" s="3">
-        <v>1</v>
-      </c>
-      <c r="H32" s="3">
-        <v>9999999</v>
-      </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
-      <c r="J32" s="3">
-        <v>5</v>
-      </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
-    </row>
     <row r="33" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C33" s="3">
-        <v>4015</v>
+        <v>4013</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="E33" s="3">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="G33" s="3">
         <v>1</v>
@@ -4551,7 +4519,7 @@
         <v>0</v>
       </c>
       <c r="J33" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L33" s="3">
         <v>0</v>
@@ -4562,16 +4530,16 @@
     </row>
     <row r="34" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C34" s="3">
-        <v>4016</v>
+        <v>4015</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="E34" s="3">
         <v>5</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="G34" s="3">
         <v>1</v>
@@ -4594,16 +4562,16 @@
     </row>
     <row r="35" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C35" s="3">
-        <v>4017</v>
+        <v>4016</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="E35" s="3">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="G35" s="3">
         <v>1</v>
@@ -4615,7 +4583,7 @@
         <v>0</v>
       </c>
       <c r="J35" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L35" s="3">
         <v>0</v>
@@ -4626,16 +4594,16 @@
     </row>
     <row r="36" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C36" s="3">
-        <v>4018</v>
+        <v>4017</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="E36" s="3">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="G36" s="3">
         <v>1</v>
@@ -4647,7 +4615,7 @@
         <v>0</v>
       </c>
       <c r="J36" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L36" s="3">
         <v>0</v>
@@ -4658,16 +4626,16 @@
     </row>
     <row r="37" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C37" s="3">
-        <v>4019</v>
+        <v>4018</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="E37" s="3">
         <v>5</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="G37" s="3">
         <v>1</v>
@@ -4679,59 +4647,59 @@
         <v>0</v>
       </c>
       <c r="J37" s="3">
+        <v>6</v>
+      </c>
+      <c r="L37" s="3">
+        <v>0</v>
+      </c>
+      <c r="M37" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" s="3" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C38" s="3">
+        <v>4019</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="E38" s="3">
+        <v>5</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="G38" s="3">
+        <v>1</v>
+      </c>
+      <c r="H38" s="3">
+        <v>9999999</v>
+      </c>
+      <c r="I38" s="3">
+        <v>0</v>
+      </c>
+      <c r="J38" s="3">
         <v>7</v>
       </c>
-      <c r="L37" s="3">
-        <v>0</v>
-      </c>
-      <c r="M37" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" s="3" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C39" s="3">
-        <v>4021</v>
-      </c>
-      <c r="D39" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="E39" s="3">
-        <v>5</v>
-      </c>
-      <c r="F39" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="G39" s="3">
-        <v>1</v>
-      </c>
-      <c r="H39" s="3">
-        <v>9999999</v>
-      </c>
-      <c r="I39" s="3">
-        <v>0</v>
-      </c>
-      <c r="J39" s="3">
-        <v>6</v>
-      </c>
-      <c r="L39" s="3">
-        <v>0</v>
-      </c>
-      <c r="M39" s="3">
+      <c r="L38" s="3">
+        <v>0</v>
+      </c>
+      <c r="M38" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="40" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C40" s="3">
-        <v>4022</v>
+        <v>4021</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E40" s="3">
         <v>5</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="G40" s="3">
         <v>1</v>
@@ -4743,7 +4711,7 @@
         <v>0</v>
       </c>
       <c r="J40" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L40" s="3">
         <v>0</v>
@@ -4754,16 +4722,16 @@
     </row>
     <row r="41" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C41" s="3">
-        <v>4023</v>
+        <v>4022</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="E41" s="3">
         <v>5</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="G41" s="3">
         <v>1</v>
@@ -4786,16 +4754,16 @@
     </row>
     <row r="42" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C42" s="3">
-        <v>4024</v>
+        <v>4023</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="E42" s="3">
         <v>5</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="G42" s="3">
         <v>1</v>
@@ -4807,7 +4775,7 @@
         <v>0</v>
       </c>
       <c r="J42" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L42" s="3">
         <v>0</v>
@@ -4818,16 +4786,16 @@
     </row>
     <row r="43" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C43" s="3">
-        <v>4025</v>
+        <v>4024</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="E43" s="3">
         <v>5</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="G43" s="3">
         <v>1</v>
@@ -4839,7 +4807,7 @@
         <v>0</v>
       </c>
       <c r="J43" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L43" s="3">
         <v>0</v>
@@ -4850,16 +4818,16 @@
     </row>
     <row r="44" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C44" s="3">
-        <v>4026</v>
+        <v>4025</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="E44" s="3">
         <v>5</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="G44" s="3">
         <v>1</v>
@@ -4871,7 +4839,7 @@
         <v>0</v>
       </c>
       <c r="J44" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -4882,16 +4850,16 @@
     </row>
     <row r="45" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C45" s="3">
-        <v>4027</v>
+        <v>4026</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="E45" s="3">
         <v>5</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="G45" s="3">
         <v>1</v>
@@ -4903,7 +4871,7 @@
         <v>0</v>
       </c>
       <c r="J45" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L45" s="3">
         <v>0</v>
@@ -4914,16 +4882,16 @@
     </row>
     <row r="46" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C46" s="3">
-        <v>4028</v>
+        <v>4027</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E46" s="3">
         <v>5</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="G46" s="3">
         <v>1</v>
@@ -4946,16 +4914,16 @@
     </row>
     <row r="47" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C47" s="3">
-        <v>4029</v>
+        <v>4028</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E47" s="3">
         <v>5</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="G47" s="3">
         <v>1</v>
@@ -4978,16 +4946,16 @@
     </row>
     <row r="48" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C48" s="3">
-        <v>4030</v>
+        <v>4029</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="E48" s="3">
         <v>5</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="G48" s="3">
         <v>1</v>
@@ -5010,16 +4978,16 @@
     </row>
     <row r="49" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C49" s="3">
-        <v>4031</v>
+        <v>4030</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="E49" s="3">
         <v>5</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="G49" s="3">
         <v>1</v>
@@ -5042,16 +5010,16 @@
     </row>
     <row r="50" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C50" s="3">
-        <v>4032</v>
+        <v>4031</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="E50" s="3">
         <v>5</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="G50" s="3">
         <v>1</v>
@@ -5074,16 +5042,16 @@
     </row>
     <row r="51" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C51" s="3">
-        <v>4033</v>
+        <v>4032</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="E51" s="3">
         <v>5</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>182</v>
+        <v>212</v>
       </c>
       <c r="G51" s="3">
         <v>1</v>
@@ -5095,7 +5063,7 @@
         <v>0</v>
       </c>
       <c r="J51" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L51" s="3">
         <v>0</v>
@@ -5106,16 +5074,16 @@
     </row>
     <row r="52" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C52" s="3">
-        <v>4034</v>
+        <v>4033</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E52" s="3">
         <v>5</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>215</v>
+        <v>182</v>
       </c>
       <c r="G52" s="3">
         <v>1</v>
@@ -5127,7 +5095,7 @@
         <v>0</v>
       </c>
       <c r="J52" s="3">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L52" s="3">
         <v>0</v>
@@ -5138,16 +5106,16 @@
     </row>
     <row r="53" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C53" s="3">
-        <v>4035</v>
+        <v>4034</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="E53" s="3">
         <v>5</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="G53" s="3">
         <v>1</v>
@@ -5159,7 +5127,7 @@
         <v>0</v>
       </c>
       <c r="J53" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L53" s="3">
         <v>0</v>
@@ -5170,16 +5138,16 @@
     </row>
     <row r="54" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C54" s="3">
-        <v>4037</v>
+        <v>4035</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="E54" s="3">
         <v>5</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="G54" s="3">
         <v>1</v>
@@ -5191,7 +5159,7 @@
         <v>0</v>
       </c>
       <c r="J54" s="3">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L54" s="3">
         <v>0</v>
@@ -5202,16 +5170,16 @@
     </row>
     <row r="55" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C55" s="3">
-        <v>4038</v>
+        <v>4037</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="E55" s="3">
         <v>5</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="G55" s="3">
         <v>1</v>
@@ -5234,16 +5202,16 @@
     </row>
     <row r="56" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C56" s="3">
-        <v>4039</v>
+        <v>4038</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="E56" s="3">
         <v>5</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="G56" s="3">
         <v>1</v>
@@ -5255,7 +5223,7 @@
         <v>0</v>
       </c>
       <c r="J56" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L56" s="3">
         <v>0</v>
@@ -5266,16 +5234,16 @@
     </row>
     <row r="57" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C57" s="3">
-        <v>4040</v>
+        <v>4039</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="E57" s="3">
         <v>5</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>182</v>
+        <v>223</v>
       </c>
       <c r="G57" s="3">
         <v>1</v>
@@ -5287,7 +5255,7 @@
         <v>0</v>
       </c>
       <c r="J57" s="3">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L57" s="3">
         <v>0</v>
@@ -5298,16 +5266,16 @@
     </row>
     <row r="58" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C58" s="3">
-        <v>4041</v>
+        <v>4040</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E58" s="3">
         <v>5</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>226</v>
+        <v>182</v>
       </c>
       <c r="G58" s="3">
         <v>1</v>
@@ -5319,7 +5287,7 @@
         <v>0</v>
       </c>
       <c r="J58" s="3">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L58" s="3">
         <v>0</v>
@@ -5330,28 +5298,28 @@
     </row>
     <row r="59" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C59" s="3">
-        <v>4042</v>
+        <v>4041</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E59" s="3">
         <v>5</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="G59" s="3">
         <v>1</v>
       </c>
       <c r="H59" s="3">
-        <v>1999999999</v>
+        <v>9999999</v>
       </c>
       <c r="I59" s="3">
         <v>0</v>
       </c>
       <c r="J59" s="3">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="L59" s="3">
         <v>0</v>
@@ -5362,10 +5330,10 @@
     </row>
     <row r="60" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C60" s="3">
-        <v>4043</v>
+        <v>4042</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E60" s="3">
         <v>5</v>
@@ -5377,13 +5345,13 @@
         <v>1</v>
       </c>
       <c r="H60" s="3">
-        <v>9999999</v>
+        <v>1999999999</v>
       </c>
       <c r="I60" s="3">
         <v>0</v>
       </c>
       <c r="J60" s="3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L60" s="3">
         <v>0</v>
@@ -5394,16 +5362,16 @@
     </row>
     <row r="61" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C61" s="3">
-        <v>4044</v>
+        <v>4043</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E61" s="3">
         <v>5</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="G61" s="3">
         <v>1</v>
@@ -5415,71 +5383,71 @@
         <v>0</v>
       </c>
       <c r="J61" s="3">
+        <v>7</v>
+      </c>
+      <c r="L61" s="3">
+        <v>0</v>
+      </c>
+      <c r="M61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" s="3" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C62" s="3">
+        <v>4044</v>
+      </c>
+      <c r="D62" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="E62" s="3">
+        <v>5</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="G62" s="3">
+        <v>1</v>
+      </c>
+      <c r="H62" s="3">
+        <v>9999999</v>
+      </c>
+      <c r="I62" s="3">
+        <v>0</v>
+      </c>
+      <c r="J62" s="3">
         <v>9</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C62" s="3"/>
-      <c r="D62" s="3"/>
-      <c r="E62" s="3"/>
-      <c r="F62" s="3"/>
-      <c r="G62" s="3"/>
-      <c r="H62" s="3"/>
-      <c r="I62" s="3"/>
-      <c r="J62" s="3"/>
-      <c r="L62" s="3"/>
-      <c r="M62" s="3"/>
-    </row>
-    <row r="63" s="3" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C63" s="3">
-        <v>4101</v>
-      </c>
-      <c r="D63" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="E63" s="3">
-        <v>5</v>
-      </c>
-      <c r="F63" s="3" t="s">
-        <v>233</v>
-      </c>
-      <c r="G63" s="3">
-        <v>1</v>
-      </c>
-      <c r="H63" s="3">
-        <v>9999999</v>
-      </c>
-      <c r="I63" s="3">
-        <v>0</v>
-      </c>
-      <c r="J63" s="3">
-        <v>5</v>
-      </c>
-      <c r="L63" s="3">
-        <v>0</v>
-      </c>
-      <c r="M63" s="3">
-        <v>0</v>
-      </c>
+      <c r="L62" s="3">
+        <v>0</v>
+      </c>
+      <c r="M62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C63" s="3"/>
+      <c r="D63" s="3"/>
+      <c r="E63" s="3"/>
+      <c r="F63" s="3"/>
+      <c r="G63" s="3"/>
+      <c r="H63" s="3"/>
+      <c r="I63" s="3"/>
+      <c r="J63" s="3"/>
+      <c r="L63" s="3"/>
+      <c r="M63" s="3"/>
     </row>
     <row r="64" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C64" s="3">
-        <v>4111</v>
+        <v>4101</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E64" s="3">
         <v>5</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="G64" s="3">
         <v>1</v>
@@ -5502,16 +5470,16 @@
     </row>
     <row r="65" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C65" s="3">
-        <v>4112</v>
+        <v>4111</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="E65" s="3">
         <v>5</v>
       </c>
       <c r="F65" s="3" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="G65" s="3">
         <v>1</v>
@@ -5523,7 +5491,7 @@
         <v>0</v>
       </c>
       <c r="J65" s="3">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="L65" s="3">
         <v>0</v>
@@ -5534,16 +5502,16 @@
     </row>
     <row r="66" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C66" s="3">
-        <v>4113</v>
+        <v>4112</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="E66" s="3">
         <v>5</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="G66" s="3">
         <v>1</v>
@@ -5555,97 +5523,97 @@
         <v>0</v>
       </c>
       <c r="J66" s="3">
+        <v>8</v>
+      </c>
+      <c r="L66" s="3">
+        <v>0</v>
+      </c>
+      <c r="M66" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" s="3" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C67" s="3">
+        <v>4113</v>
+      </c>
+      <c r="D67" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="E67" s="3">
+        <v>5</v>
+      </c>
+      <c r="F67" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="G67" s="3">
+        <v>1</v>
+      </c>
+      <c r="H67" s="3">
+        <v>9999999</v>
+      </c>
+      <c r="I67" s="3">
+        <v>0</v>
+      </c>
+      <c r="J67" s="3">
         <v>7</v>
       </c>
-      <c r="L66" s="3">
-        <v>0</v>
-      </c>
-      <c r="M66" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C67" s="3"/>
-      <c r="D67" s="3"/>
-      <c r="E67" s="3"/>
-      <c r="F67" s="3"/>
-      <c r="G67" s="3"/>
-      <c r="H67" s="3"/>
-      <c r="I67" s="3"/>
-      <c r="J67" s="3"/>
-      <c r="L67" s="3"/>
-      <c r="M67" s="3"/>
-    </row>
-    <row r="68" s="3" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C68" s="3">
+      <c r="L67" s="3">
+        <v>0</v>
+      </c>
+      <c r="M67" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C68" s="3"/>
+      <c r="D68" s="3"/>
+      <c r="E68" s="3"/>
+      <c r="F68" s="3"/>
+      <c r="G68" s="3"/>
+      <c r="H68" s="3"/>
+      <c r="I68" s="3"/>
+      <c r="J68" s="3"/>
+      <c r="L68" s="3"/>
+      <c r="M68" s="3"/>
+    </row>
+    <row r="69" s="3" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C69" s="3">
         <v>4201</v>
       </c>
-      <c r="D68" s="3" t="s">
+      <c r="D69" s="3" t="s">
         <v>240</v>
       </c>
-      <c r="E68" s="3">
-        <v>5</v>
-      </c>
-      <c r="F68" s="3" t="s">
+      <c r="E69" s="3">
+        <v>5</v>
+      </c>
+      <c r="F69" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="G68" s="3">
-        <v>1</v>
-      </c>
-      <c r="H68" s="3">
+      <c r="G69" s="3">
+        <v>1</v>
+      </c>
+      <c r="H69" s="3">
         <v>99999999</v>
       </c>
-      <c r="I68" s="3">
-        <v>0</v>
-      </c>
-      <c r="J68" s="3">
-        <v>5</v>
-      </c>
-      <c r="L68" s="3">
+      <c r="I69" s="3">
+        <v>0</v>
+      </c>
+      <c r="J69" s="3">
+        <v>5</v>
+      </c>
+      <c r="L69" s="3">
         <v>4002</v>
       </c>
-      <c r="M68" s="3">
+      <c r="M69" s="3">
         <v>1000</v>
-      </c>
-    </row>
-    <row r="73" s="3" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C73" s="3">
-        <v>8001</v>
-      </c>
-      <c r="D73" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="E73" s="3">
-        <v>5</v>
-      </c>
-      <c r="F73" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="G73" s="3">
-        <v>1</v>
-      </c>
-      <c r="H73" s="3">
-        <v>9999999</v>
-      </c>
-      <c r="I73" s="3">
-        <v>0</v>
-      </c>
-      <c r="J73" s="3">
-        <v>6</v>
-      </c>
-      <c r="L73" s="3">
-        <v>0</v>
-      </c>
-      <c r="M73" s="3">
-        <v>0</v>
       </c>
     </row>
     <row r="74" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C74" s="3">
-        <v>8002</v>
+        <v>8001</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="E74" s="3">
         <v>5</v>
@@ -5674,10 +5642,10 @@
     </row>
     <row r="75" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C75" s="3">
-        <v>8003</v>
+        <v>8002</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="E75" s="3">
         <v>5</v>
@@ -5706,10 +5674,10 @@
     </row>
     <row r="76" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C76" s="3">
-        <v>8004</v>
+        <v>8003</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E76" s="3">
         <v>5</v>
@@ -5738,10 +5706,10 @@
     </row>
     <row r="77" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C77" s="3">
-        <v>8005</v>
+        <v>8004</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="E77" s="3">
         <v>5</v>
@@ -5770,10 +5738,10 @@
     </row>
     <row r="78" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C78" s="3">
-        <v>8006</v>
+        <v>8005</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E78" s="3">
         <v>5</v>
@@ -5802,10 +5770,10 @@
     </row>
     <row r="79" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C79" s="3">
-        <v>8007</v>
+        <v>8006</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E79" s="3">
         <v>5</v>
@@ -5834,10 +5802,10 @@
     </row>
     <row r="80" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C80" s="3">
-        <v>8008</v>
+        <v>8007</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E80" s="3">
         <v>5</v>
@@ -5866,10 +5834,10 @@
     </row>
     <row r="81" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C81" s="3">
-        <v>8009</v>
+        <v>8008</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="E81" s="3">
         <v>5</v>
@@ -5898,10 +5866,10 @@
     </row>
     <row r="82" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C82" s="3">
-        <v>8010</v>
+        <v>8009</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E82" s="3">
         <v>5</v>
@@ -5928,44 +5896,44 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" s="3" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C84" s="3">
-        <v>8101</v>
-      </c>
-      <c r="D84" s="9" t="s">
-        <v>253</v>
-      </c>
-      <c r="E84" s="3">
-        <v>5</v>
-      </c>
-      <c r="F84" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="G84" s="3">
-        <v>1</v>
-      </c>
-      <c r="H84" s="3">
+    <row r="83" s="3" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C83" s="3">
+        <v>8010</v>
+      </c>
+      <c r="D83" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="E83" s="3">
+        <v>5</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="G83" s="3">
+        <v>1</v>
+      </c>
+      <c r="H83" s="3">
         <v>9999999</v>
       </c>
-      <c r="I84" s="3">
-        <v>0</v>
-      </c>
-      <c r="J84" s="3">
-        <v>7</v>
-      </c>
-      <c r="L84" s="3">
-        <v>0</v>
-      </c>
-      <c r="M84" s="3">
+      <c r="I83" s="3">
+        <v>0</v>
+      </c>
+      <c r="J83" s="3">
+        <v>6</v>
+      </c>
+      <c r="L83" s="3">
+        <v>0</v>
+      </c>
+      <c r="M83" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="85" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C85" s="3">
-        <v>8102</v>
+        <v>8101</v>
       </c>
       <c r="D85" s="9" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="E85" s="3">
         <v>5</v>
@@ -5994,10 +5962,10 @@
     </row>
     <row r="86" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C86" s="3">
-        <v>8103</v>
+        <v>8102</v>
       </c>
       <c r="D86" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E86" s="3">
         <v>5</v>
@@ -6026,10 +5994,10 @@
     </row>
     <row r="87" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C87" s="3">
-        <v>8104</v>
+        <v>8103</v>
       </c>
       <c r="D87" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E87" s="3">
         <v>5</v>
@@ -6058,10 +6026,10 @@
     </row>
     <row r="88" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C88" s="3">
-        <v>8105</v>
+        <v>8104</v>
       </c>
       <c r="D88" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E88" s="3">
         <v>5</v>
@@ -6090,10 +6058,10 @@
     </row>
     <row r="89" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C89" s="3">
-        <v>8106</v>
+        <v>8105</v>
       </c>
       <c r="D89" s="9" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E89" s="3">
         <v>5</v>
@@ -6122,10 +6090,10 @@
     </row>
     <row r="90" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C90" s="3">
-        <v>8107</v>
+        <v>8106</v>
       </c>
       <c r="D90" s="9" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E90" s="3">
         <v>5</v>
@@ -6154,10 +6122,10 @@
     </row>
     <row r="91" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C91" s="3">
-        <v>8108</v>
+        <v>8107</v>
       </c>
       <c r="D91" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E91" s="3">
         <v>5</v>
@@ -6184,53 +6152,50 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" customHeight="1" spans="3:13">
-      <c r="C93" s="3">
-        <v>8201</v>
-      </c>
-      <c r="D93" s="9" t="s">
-        <v>262</v>
-      </c>
-      <c r="E93" s="3">
-        <v>16</v>
-      </c>
-      <c r="F93" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="G93" s="3">
-        <v>1</v>
-      </c>
-      <c r="H93" s="3">
-        <v>1</v>
-      </c>
-      <c r="I93" s="3">
-        <v>0</v>
-      </c>
-      <c r="J93" s="3">
-        <v>1</v>
-      </c>
-      <c r="K93" s="3">
-        <v>0</v>
-      </c>
-      <c r="L93" s="3">
-        <v>0</v>
-      </c>
-      <c r="M93" s="3">
+    <row r="92" s="3" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C92" s="3">
+        <v>8108</v>
+      </c>
+      <c r="D92" s="9" t="s">
+        <v>261</v>
+      </c>
+      <c r="E92" s="3">
+        <v>5</v>
+      </c>
+      <c r="F92" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="G92" s="3">
+        <v>1</v>
+      </c>
+      <c r="H92" s="3">
+        <v>9999999</v>
+      </c>
+      <c r="I92" s="3">
+        <v>0</v>
+      </c>
+      <c r="J92" s="3">
+        <v>7</v>
+      </c>
+      <c r="L92" s="3">
+        <v>0</v>
+      </c>
+      <c r="M92" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="94" customHeight="1" spans="3:13">
       <c r="C94" s="3">
-        <v>8202</v>
+        <v>8201</v>
       </c>
       <c r="D94" s="9" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="E94" s="3">
         <v>16</v>
       </c>
       <c r="F94" s="3" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="G94" s="3">
         <v>1</v>
@@ -6242,7 +6207,7 @@
         <v>0</v>
       </c>
       <c r="J94" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K94" s="3">
         <v>0</v>
@@ -6256,16 +6221,16 @@
     </row>
     <row r="95" customHeight="1" spans="3:13">
       <c r="C95" s="3">
-        <v>8203</v>
+        <v>8202</v>
       </c>
       <c r="D95" s="9" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="E95" s="3">
         <v>16</v>
       </c>
       <c r="F95" s="3" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="G95" s="3">
         <v>1</v>
@@ -6277,7 +6242,7 @@
         <v>0</v>
       </c>
       <c r="J95" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K95" s="3">
         <v>0</v>
@@ -6291,16 +6256,16 @@
     </row>
     <row r="96" customHeight="1" spans="3:13">
       <c r="C96" s="3">
-        <v>8204</v>
+        <v>8203</v>
       </c>
       <c r="D96" s="9" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="E96" s="3">
         <v>16</v>
       </c>
       <c r="F96" s="3" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="G96" s="3">
         <v>1</v>
@@ -6312,7 +6277,7 @@
         <v>0</v>
       </c>
       <c r="J96" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -6326,16 +6291,16 @@
     </row>
     <row r="97" customHeight="1" spans="3:13">
       <c r="C97" s="3">
-        <v>8205</v>
+        <v>8204</v>
       </c>
       <c r="D97" s="9" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="E97" s="3">
         <v>16</v>
       </c>
       <c r="F97" s="3" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="G97" s="3">
         <v>1</v>
@@ -6347,7 +6312,7 @@
         <v>0</v>
       </c>
       <c r="J97" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K97" s="3">
         <v>0</v>
@@ -6361,16 +6326,16 @@
     </row>
     <row r="98" customHeight="1" spans="3:13">
       <c r="C98" s="3">
-        <v>8206</v>
+        <v>8205</v>
       </c>
       <c r="D98" s="9" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E98" s="3">
         <v>16</v>
       </c>
       <c r="F98" s="3" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="G98" s="3">
         <v>1</v>
@@ -6382,7 +6347,7 @@
         <v>0</v>
       </c>
       <c r="J98" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K98" s="3">
         <v>0</v>
@@ -6396,41 +6361,73 @@
     </row>
     <row r="99" customHeight="1" spans="3:13">
       <c r="C99" s="3">
-        <v>8207</v>
+        <v>8206</v>
       </c>
       <c r="D99" s="9" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="E99" s="3">
         <v>16</v>
       </c>
       <c r="F99" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="G99" s="3">
+        <v>1</v>
+      </c>
+      <c r="H99" s="3">
+        <v>1</v>
+      </c>
+      <c r="I99" s="3">
+        <v>0</v>
+      </c>
+      <c r="J99" s="3">
+        <v>6</v>
+      </c>
+      <c r="K99" s="3">
+        <v>0</v>
+      </c>
+      <c r="L99" s="3">
+        <v>0</v>
+      </c>
+      <c r="M99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" customHeight="1" spans="3:13">
+      <c r="C100" s="3">
+        <v>8207</v>
+      </c>
+      <c r="D100" s="9" t="s">
+        <v>274</v>
+      </c>
+      <c r="E100" s="3">
+        <v>16</v>
+      </c>
+      <c r="F100" s="3" t="s">
         <v>275</v>
       </c>
-      <c r="G99" s="3">
-        <v>1</v>
-      </c>
-      <c r="H99" s="3">
-        <v>1</v>
-      </c>
-      <c r="I99" s="3">
-        <v>0</v>
-      </c>
-      <c r="J99" s="3">
+      <c r="G100" s="3">
+        <v>1</v>
+      </c>
+      <c r="H100" s="3">
+        <v>1</v>
+      </c>
+      <c r="I100" s="3">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3">
         <v>7</v>
       </c>
-      <c r="K99" s="3">
-        <v>0</v>
-      </c>
-      <c r="L99" s="3">
-        <v>0</v>
-      </c>
-      <c r="M99" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" customHeight="1" spans="3:13">
-      <c r="D101" s="9"/>
+      <c r="K100" s="3">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3">
+        <v>0</v>
+      </c>
     </row>
     <row r="102" customHeight="1" spans="3:13">
       <c r="D102" s="9"/>
@@ -6450,8 +6447,8 @@
     <row r="107" customHeight="1" spans="3:13">
       <c r="D107" s="9"/>
     </row>
-    <row r="109" customHeight="1" spans="3:13">
-      <c r="D109" s="9"/>
+    <row r="108" customHeight="1" spans="3:13">
+      <c r="D108" s="9"/>
     </row>
     <row r="110" customHeight="1" spans="3:13">
       <c r="D110" s="9"/>
@@ -6471,12 +6468,15 @@
     <row r="115" customHeight="1" spans="4:4">
       <c r="D115" s="9"/>
     </row>
+    <row r="116" customHeight="1" spans="4:4">
+      <c r="D116" s="9"/>
+    </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C10:D10 C15:D15 C11:C14 C3:D5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C11:D11 C16:D16 C12:C15 C3:D5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="L15:M15 L3:M5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="L16:M16 L3:M5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,L3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/ItemConfig.xlsx
+++ b/Excel/ItemConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="1"/>
+    <workbookView windowHeight="17680" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="技能" sheetId="1" r:id="rId1"/>
@@ -224,7 +224,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="543" uniqueCount="300">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="555" uniqueCount="309">
   <si>
     <t>_Id</t>
   </si>
@@ -1105,22 +1105,49 @@
     <t>大佬再临</t>
   </si>
   <si>
-    <t>鸡毛</t>
-  </si>
-  <si>
-    <t>珍宝材料</t>
-  </si>
-  <si>
-    <t>鸡蛋</t>
-  </si>
-  <si>
-    <t>鸡冠</t>
-  </si>
-  <si>
-    <t>鹿角</t>
-  </si>
-  <si>
-    <t>鹿茸</t>
+    <t>狼毛</t>
+  </si>
+  <si>
+    <t>落日平原珍宝材料</t>
+  </si>
+  <si>
+    <t>蛛丝</t>
+  </si>
+  <si>
+    <t>雄狮利爪</t>
+  </si>
+  <si>
+    <t>虫卵</t>
+  </si>
+  <si>
+    <t>幽暗沼泽珍宝材料</t>
+  </si>
+  <si>
+    <t>蛇皮</t>
+  </si>
+  <si>
+    <t>巨鳄之泪</t>
+  </si>
+  <si>
+    <t>乌鸦羽</t>
+  </si>
+  <si>
+    <t>碎石矿场珍宝材料</t>
+  </si>
+  <si>
+    <t>蝙蝠牙</t>
+  </si>
+  <si>
+    <t>尸王之心</t>
+  </si>
+  <si>
+    <t>树叶</t>
+  </si>
+  <si>
+    <t>枯骨荒漠珍宝材料</t>
+  </si>
+  <si>
+    <t>鱼鳞</t>
   </si>
   <si>
     <t>鹿血</t>
@@ -7295,7 +7322,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:M11"/>
+  <dimension ref="C1:M17"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="2"/>
@@ -7514,7 +7541,7 @@
         <v>6</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="G9" s="2">
         <v>1</v>
@@ -7535,13 +7562,13 @@
         <v>40000005</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="E10" s="2">
         <v>6</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="G10" s="2">
         <v>1</v>
@@ -7562,13 +7589,13 @@
         <v>40000006</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="E11" s="2">
         <v>6</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="G11" s="2">
         <v>1</v>
@@ -7585,6 +7612,162 @@
       <c r="K11" s="6"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
+    </row>
+    <row r="12" customHeight="1" spans="3:13">
+      <c r="C12" s="3">
+        <v>40000007</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="E12" s="2">
+        <v>6</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="G12" s="2">
+        <v>1</v>
+      </c>
+      <c r="H12" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I12" s="2">
+        <v>0</v>
+      </c>
+      <c r="J12" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" customHeight="1" spans="3:13">
+      <c r="C13" s="3">
+        <v>40000008</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="E13" s="2">
+        <v>6</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="G13" s="2">
+        <v>1</v>
+      </c>
+      <c r="H13" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I13" s="2">
+        <v>0</v>
+      </c>
+      <c r="J13" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" customHeight="1" spans="3:13">
+      <c r="C14" s="3">
+        <v>40000009</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="E14" s="2">
+        <v>6</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="G14" s="2">
+        <v>1</v>
+      </c>
+      <c r="H14" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I14" s="2">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15" customHeight="1" spans="3:13">
+      <c r="C15" s="3">
+        <v>40000010</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="E15" s="2">
+        <v>6</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="G15" s="2">
+        <v>1</v>
+      </c>
+      <c r="H15" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I15" s="2">
+        <v>0</v>
+      </c>
+      <c r="J15" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" customHeight="1" spans="3:13">
+      <c r="C16" s="3">
+        <v>40000011</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="E16" s="2">
+        <v>6</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="G16" s="2">
+        <v>1</v>
+      </c>
+      <c r="H16" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I16" s="2">
+        <v>0</v>
+      </c>
+      <c r="J16" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" customHeight="1" spans="3:10">
+      <c r="C17" s="3">
+        <v>40000012</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="E17" s="2">
+        <v>6</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="G17" s="2">
+        <v>1</v>
+      </c>
+      <c r="H17" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I17" s="2">
+        <v>0</v>
+      </c>
+      <c r="J17" s="3">
+        <v>6</v>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="2">

--- a/Excel/ItemConfig.xlsx
+++ b/Excel/ItemConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="4"/>
+    <workbookView windowHeight="17680" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="技能" sheetId="1" r:id="rId1"/>
@@ -3790,7 +3790,7 @@
         <v>0</v>
       </c>
       <c r="J6" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K6" s="3"/>
       <c r="L6" s="3">

--- a/Excel/ItemConfig.xlsx
+++ b/Excel/ItemConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="1"/>
+    <workbookView windowHeight="17680" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="技能" sheetId="1" r:id="rId1"/>

--- a/Excel/ItemConfig.xlsx
+++ b/Excel/ItemConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="4"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="技能" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
     <author>admin</author>
   </authors>
   <commentList>
-    <comment ref="E3" authorId="0">
+    <comment ref="F3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -73,7 +73,7 @@
     <author>admin</author>
   </authors>
   <commentList>
-    <comment ref="E3" authorId="0">
+    <comment ref="F3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -112,7 +112,7 @@
     <author>admin</author>
   </authors>
   <commentList>
-    <comment ref="E3" authorId="0">
+    <comment ref="F3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -151,7 +151,7 @@
     <author>admin</author>
   </authors>
   <commentList>
-    <comment ref="E3" authorId="0">
+    <comment ref="F3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -190,7 +190,7 @@
     <author>admin</author>
   </authors>
   <commentList>
-    <comment ref="E3" authorId="0">
+    <comment ref="F3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -224,7 +224,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="555" uniqueCount="309">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="606" uniqueCount="313">
   <si>
     <t>_Id</t>
   </si>
@@ -232,6 +232,9 @@
     <t>道具名字</t>
   </si>
   <si>
+    <t>LogoId</t>
+  </si>
+  <si>
     <t>道具类型</t>
   </si>
   <si>
@@ -301,6 +304,9 @@
     <t>基础心法</t>
   </si>
   <si>
+    <t>sb1</t>
+  </si>
+  <si>
     <t>学习或者升级战士技能基础剑术</t>
   </si>
   <si>
@@ -418,6 +424,9 @@
     <t>冥想心法</t>
   </si>
   <si>
+    <t>sb2</t>
+  </si>
+  <si>
     <t>学习或者升级法师技能火球术</t>
   </si>
   <si>
@@ -524,6 +533,9 @@
   </si>
   <si>
     <t>祈福心法</t>
+  </si>
+  <si>
+    <t>sb3</t>
   </si>
   <si>
     <t>学习或者升级道士技能疗伤术</t>
@@ -2162,27 +2174,34 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:M43"/>
+  <dimension ref="A1:N43"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="3"/>
     <col min="4" max="4" width="10.125" style="3" customWidth="1"/>
-    <col min="5" max="5" width="9.875" style="3" customWidth="1"/>
-    <col min="6" max="6" width="26.75" style="3" customWidth="1"/>
-    <col min="7" max="7" width="8" style="3" customWidth="1"/>
-    <col min="8" max="11" width="12.25" style="3" customWidth="1"/>
-    <col min="12" max="13" width="12.375" style="3" customWidth="1"/>
-    <col min="14" max="16384" width="9" style="3"/>
+    <col min="5" max="5" width="9.58333333333333" style="2" customWidth="1"/>
+    <col min="6" max="6" width="9.875" style="3" customWidth="1"/>
+    <col min="7" max="7" width="26.75" style="3" customWidth="1"/>
+    <col min="8" max="8" width="8" style="3" customWidth="1"/>
+    <col min="9" max="12" width="12.25" style="3" customWidth="1"/>
+    <col min="13" max="14" width="12.375" style="3" customWidth="1"/>
+    <col min="15" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="3" customHeight="1" spans="1:13">
+    <row r="1" customHeight="1" spans="1:14">
+      <c r="E1" s="1"/>
+    </row>
+    <row r="2" customHeight="1" spans="1:14">
+      <c r="E2" s="1"/>
+    </row>
+    <row r="3" customHeight="1" spans="1:14">
       <c r="C3" s="5" t="s">
         <v>0</v>
       </c>
       <c r="D3" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="4" t="s">
         <v>2</v>
       </c>
       <c r="F3" s="5" t="s">
@@ -2209,16 +2228,19 @@
       <c r="M3" s="5" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="4" customHeight="1" spans="1:13">
+      <c r="N3" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" customHeight="1" spans="1:14">
       <c r="C4" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E4" s="5" t="s">
         <v>13</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>2</v>
       </c>
       <c r="F4" s="5" t="s">
         <v>14</v>
@@ -2239,1404 +2261,1518 @@
         <v>19</v>
       </c>
       <c r="L4" s="5" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="M4" s="5" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="5" customHeight="1" spans="1:13">
+      <c r="N4" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" customHeight="1" spans="1:14">
       <c r="C5" s="5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>20</v>
+        <v>22</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>22</v>
       </c>
       <c r="F5" s="5" t="s">
         <v>21</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K5" s="5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L5" s="5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M5" s="5" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="6" customHeight="1" spans="1:13">
+        <v>21</v>
+      </c>
+      <c r="N5" s="5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" customHeight="1" spans="1:14">
       <c r="C6" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E6" s="3">
+        <v>25</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F6" s="3">
         <v>4</v>
       </c>
-      <c r="F6" s="3" t="s">
-        <v>25</v>
-      </c>
       <c r="G6" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I6" s="3">
+        <v>99999999</v>
+      </c>
+      <c r="J6" s="3">
+        <v>1</v>
+      </c>
+      <c r="K6" s="3">
+        <v>3</v>
+      </c>
+      <c r="L6" s="3">
+        <v>0</v>
+      </c>
+      <c r="M6" s="3">
+        <v>0</v>
+      </c>
+      <c r="N6" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" customHeight="1" spans="1:14">
+      <c r="C7" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="E7" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="H6" s="3">
+      <c r="F7" s="3">
+        <v>4</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I7" s="3">
         <v>99999999</v>
       </c>
-      <c r="I6" s="3">
-        <v>1</v>
-      </c>
-      <c r="J6" s="3">
+      <c r="J7" s="3">
+        <v>7</v>
+      </c>
+      <c r="K7" s="3">
         <v>3</v>
       </c>
-      <c r="K6" s="3">
-        <v>0</v>
-      </c>
-      <c r="L6" s="3">
-        <v>0</v>
-      </c>
-      <c r="M6" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" customHeight="1" spans="1:13">
-      <c r="C7" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D7" s="6" t="s">
+      <c r="L7" s="3">
+        <v>0</v>
+      </c>
+      <c r="M7" s="3">
+        <v>0</v>
+      </c>
+      <c r="N7" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" customHeight="1" spans="1:14">
+      <c r="C8" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F8" s="3">
+        <v>4</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="H8" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="E7" s="3">
+      <c r="I8" s="3">
+        <v>99999999</v>
+      </c>
+      <c r="J8" s="3">
+        <v>14</v>
+      </c>
+      <c r="K8" s="3">
+        <v>3</v>
+      </c>
+      <c r="L8" s="3">
+        <v>0</v>
+      </c>
+      <c r="M8" s="3">
+        <v>0</v>
+      </c>
+      <c r="N8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" customHeight="1" spans="1:14">
+      <c r="C9" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F9" s="3">
         <v>4</v>
       </c>
-      <c r="F7" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="G7" s="3" t="s">
+      <c r="G9" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="I9" s="3">
+        <v>99999999</v>
+      </c>
+      <c r="J9" s="3">
+        <v>21</v>
+      </c>
+      <c r="K9" s="3">
+        <v>3</v>
+      </c>
+      <c r="L9" s="3">
+        <v>0</v>
+      </c>
+      <c r="M9" s="3">
+        <v>0</v>
+      </c>
+      <c r="N9" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" customHeight="1" spans="1:14">
+      <c r="C10" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="E10" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="H7" s="3">
+      <c r="F10" s="3">
+        <v>4</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="I10" s="3">
         <v>99999999</v>
       </c>
-      <c r="I7" s="3">
+      <c r="J10" s="3">
+        <v>28</v>
+      </c>
+      <c r="K10" s="3">
+        <v>4</v>
+      </c>
+      <c r="L10" s="3">
+        <v>0</v>
+      </c>
+      <c r="M10" s="3">
+        <v>0</v>
+      </c>
+      <c r="N10" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" customHeight="1" spans="1:14">
+      <c r="C11" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F11" s="3">
+        <v>4</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="I11" s="3">
+        <v>99999999</v>
+      </c>
+      <c r="J11" s="3">
+        <v>35</v>
+      </c>
+      <c r="K11" s="3">
+        <v>4</v>
+      </c>
+      <c r="L11" s="3">
+        <v>0</v>
+      </c>
+      <c r="M11" s="3">
+        <v>0</v>
+      </c>
+      <c r="N11" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" customHeight="1" spans="1:14">
+      <c r="C12" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F12" s="3">
+        <v>4</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="I12" s="3">
+        <v>99999999</v>
+      </c>
+      <c r="J12" s="3">
+        <v>42</v>
+      </c>
+      <c r="K12" s="3">
+        <v>4</v>
+      </c>
+      <c r="L12" s="3">
+        <v>0</v>
+      </c>
+      <c r="M12" s="3">
+        <v>0</v>
+      </c>
+      <c r="N12" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" customHeight="1" spans="1:14">
+      <c r="A13" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F13" s="3">
+        <v>4</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="I13" s="3">
+        <v>99999999</v>
+      </c>
+      <c r="J13" s="3">
+        <v>49</v>
+      </c>
+      <c r="K13" s="3">
+        <v>5</v>
+      </c>
+      <c r="L13" s="3">
+        <v>0</v>
+      </c>
+      <c r="M13" s="3">
+        <v>0</v>
+      </c>
+      <c r="N13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" customHeight="1" spans="1:14">
+      <c r="A14" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C14" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F14" s="3">
+        <v>4</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="I14" s="3">
+        <v>99999999</v>
+      </c>
+      <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3">
+        <v>5</v>
+      </c>
+      <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" customHeight="1" spans="1:14">
+      <c r="A15" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C15" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F15" s="3">
+        <v>4</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="I15" s="3">
+        <v>99999999</v>
+      </c>
+      <c r="J15" s="3">
+        <v>0</v>
+      </c>
+      <c r="K15" s="3">
+        <v>6</v>
+      </c>
+      <c r="L15" s="3">
+        <v>0</v>
+      </c>
+      <c r="M15" s="3">
+        <v>0</v>
+      </c>
+      <c r="N15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" customHeight="1" spans="1:14">
+      <c r="A16" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C16" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F16" s="3">
+        <v>4</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="I16" s="3">
+        <v>99999999</v>
+      </c>
+      <c r="J16" s="3">
+        <v>0</v>
+      </c>
+      <c r="K16" s="3">
         <v>7</v>
       </c>
-      <c r="J7" s="3">
+      <c r="L16" s="3">
+        <v>0</v>
+      </c>
+      <c r="M16" s="3">
+        <v>0</v>
+      </c>
+      <c r="N16" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" customHeight="1" spans="1:14">
+      <c r="A17" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C17" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F17" s="3">
+        <v>4</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="I17" s="3">
+        <v>99999999</v>
+      </c>
+      <c r="J17" s="3">
+        <v>6</v>
+      </c>
+      <c r="K17" s="3">
+        <v>8</v>
+      </c>
+      <c r="L17" s="3">
+        <v>0</v>
+      </c>
+      <c r="M17" s="3">
+        <v>0</v>
+      </c>
+      <c r="N17" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" customHeight="1" spans="1:14">
+      <c r="C19" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="F19" s="3">
+        <v>4</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I19" s="3">
+        <v>99999999</v>
+      </c>
+      <c r="J19" s="3">
+        <v>1</v>
+      </c>
+      <c r="K19" s="3">
         <v>3</v>
       </c>
-      <c r="K7" s="3">
-        <v>0</v>
-      </c>
-      <c r="L7" s="3">
-        <v>0</v>
-      </c>
-      <c r="M7" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" customHeight="1" spans="1:13">
-      <c r="C8" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="E8" s="3">
+      <c r="L19" s="3">
+        <v>0</v>
+      </c>
+      <c r="M19" s="3">
+        <v>0</v>
+      </c>
+      <c r="N19" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" customHeight="1" spans="1:14">
+      <c r="C20" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="F20" s="3">
         <v>4</v>
       </c>
-      <c r="F8" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="H8" s="3">
+      <c r="G20" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I20" s="3">
         <v>99999999</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J20" s="3">
+        <v>7</v>
+      </c>
+      <c r="K20" s="3">
+        <v>3</v>
+      </c>
+      <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" customHeight="1" spans="1:14">
+      <c r="C21" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="F21" s="3">
+        <v>4</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I21" s="3">
+        <v>99999999</v>
+      </c>
+      <c r="J21" s="3">
         <v>14</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K21" s="3">
         <v>3</v>
       </c>
-      <c r="K8" s="3">
-        <v>0</v>
-      </c>
-      <c r="L8" s="3">
-        <v>0</v>
-      </c>
-      <c r="M8" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" customHeight="1" spans="1:13">
-      <c r="C9" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="E9" s="3">
+      <c r="L21" s="3">
+        <v>0</v>
+      </c>
+      <c r="M21" s="3">
+        <v>0</v>
+      </c>
+      <c r="N21" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" customHeight="1" spans="1:14">
+      <c r="C22" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="F22" s="3">
         <v>4</v>
       </c>
-      <c r="F9" s="3" t="s">
+      <c r="G22" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="I22" s="3">
+        <v>99999999</v>
+      </c>
+      <c r="J22" s="3">
+        <v>21</v>
+      </c>
+      <c r="K22" s="3">
+        <v>3</v>
+      </c>
+      <c r="L22" s="3">
+        <v>0</v>
+      </c>
+      <c r="M22" s="3">
+        <v>0</v>
+      </c>
+      <c r="N22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" customHeight="1" spans="1:14">
+      <c r="C23" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="F23" s="3">
+        <v>4</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="I23" s="3">
+        <v>99999999</v>
+      </c>
+      <c r="J23" s="3">
+        <v>28</v>
+      </c>
+      <c r="K23" s="3">
+        <v>4</v>
+      </c>
+      <c r="L23" s="3">
+        <v>0</v>
+      </c>
+      <c r="M23" s="3">
+        <v>0</v>
+      </c>
+      <c r="N23" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" customHeight="1" spans="1:14">
+      <c r="C24" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="F24" s="3">
+        <v>4</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="I24" s="3">
+        <v>99999999</v>
+      </c>
+      <c r="J24" s="3">
         <v>35</v>
       </c>
-      <c r="G9" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="H9" s="3">
+      <c r="K24" s="3">
+        <v>4</v>
+      </c>
+      <c r="L24" s="3">
+        <v>0</v>
+      </c>
+      <c r="M24" s="3">
+        <v>0</v>
+      </c>
+      <c r="N24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" customHeight="1" spans="1:14">
+      <c r="C25" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="F25" s="3">
+        <v>4</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="I25" s="3">
         <v>99999999</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J25" s="3">
+        <v>42</v>
+      </c>
+      <c r="K25" s="3">
+        <v>4</v>
+      </c>
+      <c r="L25" s="3">
+        <v>0</v>
+      </c>
+      <c r="M25" s="3">
+        <v>0</v>
+      </c>
+      <c r="N25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" customHeight="1" spans="1:14">
+      <c r="A26" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C26" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="F26" s="3">
+        <v>4</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="I26" s="3">
+        <v>99999999</v>
+      </c>
+      <c r="J26" s="3">
+        <v>49</v>
+      </c>
+      <c r="K26" s="3">
+        <v>5</v>
+      </c>
+      <c r="L26" s="3">
+        <v>0</v>
+      </c>
+      <c r="M26" s="3">
+        <v>0</v>
+      </c>
+      <c r="N26" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" customHeight="1" spans="1:14">
+      <c r="A27" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C27" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="F27" s="3">
+        <v>4</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="I27" s="3">
+        <v>99999999</v>
+      </c>
+      <c r="J27" s="3">
+        <v>0</v>
+      </c>
+      <c r="K27" s="3">
+        <v>5</v>
+      </c>
+      <c r="L27" s="3">
+        <v>0</v>
+      </c>
+      <c r="M27" s="3">
+        <v>0</v>
+      </c>
+      <c r="N27" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" customHeight="1" spans="1:14">
+      <c r="A28" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C28" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="F28" s="3">
+        <v>4</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="I28" s="3">
+        <v>99999999</v>
+      </c>
+      <c r="J28" s="3">
+        <v>0</v>
+      </c>
+      <c r="K28" s="3">
+        <v>6</v>
+      </c>
+      <c r="L28" s="3">
+        <v>0</v>
+      </c>
+      <c r="M28" s="3">
+        <v>0</v>
+      </c>
+      <c r="N28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" customHeight="1" spans="1:14">
+      <c r="A29" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C29" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="F29" s="3">
+        <v>4</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="I29" s="3">
+        <v>99999999</v>
+      </c>
+      <c r="J29" s="3">
+        <v>0</v>
+      </c>
+      <c r="K29" s="3">
+        <v>7</v>
+      </c>
+      <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3">
+        <v>0</v>
+      </c>
+      <c r="N29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" customHeight="1" spans="1:14">
+      <c r="A30" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C30" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="F30" s="3">
+        <v>4</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="H30" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="I30" s="3">
+        <v>99999999</v>
+      </c>
+      <c r="J30" s="3">
+        <v>6</v>
+      </c>
+      <c r="K30" s="3">
+        <v>8</v>
+      </c>
+      <c r="L30" s="3">
+        <v>0</v>
+      </c>
+      <c r="M30" s="3">
+        <v>0</v>
+      </c>
+      <c r="N30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" customHeight="1" spans="1:14">
+      <c r="C32" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="D32" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="F32" s="3">
+        <v>4</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I32" s="3">
+        <v>99999999</v>
+      </c>
+      <c r="J32" s="3">
+        <v>1</v>
+      </c>
+      <c r="K32" s="3">
+        <v>3</v>
+      </c>
+      <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" customHeight="1" spans="1:14">
+      <c r="C33" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="D33" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="F33" s="3">
+        <v>4</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I33" s="3">
+        <v>99999999</v>
+      </c>
+      <c r="J33" s="3">
+        <v>7</v>
+      </c>
+      <c r="K33" s="3">
+        <v>3</v>
+      </c>
+      <c r="L33" s="3">
+        <v>0</v>
+      </c>
+      <c r="M33" s="3">
+        <v>0</v>
+      </c>
+      <c r="N33" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" customHeight="1" spans="1:14">
+      <c r="C34" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D34" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="F34" s="3">
+        <v>4</v>
+      </c>
+      <c r="G34" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="H34" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I34" s="3">
+        <v>99999999</v>
+      </c>
+      <c r="J34" s="3">
+        <v>14</v>
+      </c>
+      <c r="K34" s="3">
+        <v>3</v>
+      </c>
+      <c r="L34" s="3">
+        <v>0</v>
+      </c>
+      <c r="M34" s="3">
+        <v>0</v>
+      </c>
+      <c r="N34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" customHeight="1" spans="1:14">
+      <c r="C35" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="D35" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="F35" s="3">
+        <v>4</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="I35" s="3">
+        <v>99999999</v>
+      </c>
+      <c r="J35" s="3">
         <v>21</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K35" s="3">
         <v>3</v>
       </c>
-      <c r="K9" s="3">
-        <v>0</v>
-      </c>
-      <c r="L9" s="3">
-        <v>0</v>
-      </c>
-      <c r="M9" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" customHeight="1" spans="1:13">
-      <c r="C10" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="D10" s="6" t="s">
+      <c r="L35" s="3">
+        <v>0</v>
+      </c>
+      <c r="M35" s="3">
+        <v>0</v>
+      </c>
+      <c r="N35" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" customHeight="1" spans="1:14">
+      <c r="C36" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="D36" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="F36" s="3">
+        <v>4</v>
+      </c>
+      <c r="G36" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="H36" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="E10" s="3">
+      <c r="I36" s="3">
+        <v>99999999</v>
+      </c>
+      <c r="J36" s="3">
+        <v>28</v>
+      </c>
+      <c r="K36" s="3">
         <v>4</v>
       </c>
-      <c r="F10" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="H10" s="3">
+      <c r="L36" s="3">
+        <v>0</v>
+      </c>
+      <c r="M36" s="3">
+        <v>0</v>
+      </c>
+      <c r="N36" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" customHeight="1" spans="1:14">
+      <c r="C37" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="D37" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="F37" s="3">
+        <v>4</v>
+      </c>
+      <c r="G37" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="H37" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="I37" s="3">
         <v>99999999</v>
       </c>
-      <c r="I10" s="3">
-        <v>28</v>
-      </c>
-      <c r="J10" s="3">
+      <c r="J37" s="3">
+        <v>35</v>
+      </c>
+      <c r="K37" s="3">
         <v>4</v>
       </c>
-      <c r="K10" s="3">
-        <v>0</v>
-      </c>
-      <c r="L10" s="3">
-        <v>0</v>
-      </c>
-      <c r="M10" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" customHeight="1" spans="1:13">
-      <c r="C11" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="E11" s="3">
+      <c r="L37" s="3">
+        <v>0</v>
+      </c>
+      <c r="M37" s="3">
+        <v>0</v>
+      </c>
+      <c r="N37" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" customHeight="1" spans="1:14">
+      <c r="C38" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="D38" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="F38" s="3">
         <v>4</v>
       </c>
-      <c r="F11" s="3" t="s">
+      <c r="G38" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="H38" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="I38" s="3">
+        <v>99999999</v>
+      </c>
+      <c r="J38" s="3">
         <v>42</v>
       </c>
-      <c r="G11" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="H11" s="3">
+      <c r="K38" s="3">
+        <v>4</v>
+      </c>
+      <c r="L38" s="3">
+        <v>0</v>
+      </c>
+      <c r="M38" s="3">
+        <v>0</v>
+      </c>
+      <c r="N38" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" customHeight="1" spans="1:14">
+      <c r="A39" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C39" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="D39" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="F39" s="3">
+        <v>4</v>
+      </c>
+      <c r="G39" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="H39" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="I39" s="3">
         <v>99999999</v>
       </c>
-      <c r="I11" s="3">
-        <v>35</v>
-      </c>
-      <c r="J11" s="3">
+      <c r="J39" s="3">
+        <v>49</v>
+      </c>
+      <c r="K39" s="3">
+        <v>5</v>
+      </c>
+      <c r="L39" s="3">
+        <v>0</v>
+      </c>
+      <c r="M39" s="3">
+        <v>0</v>
+      </c>
+      <c r="N39" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" customHeight="1" spans="1:14">
+      <c r="A40" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C40" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="D40" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="F40" s="3">
         <v>4</v>
       </c>
-      <c r="K11" s="3">
-        <v>0</v>
-      </c>
-      <c r="L11" s="3">
-        <v>0</v>
-      </c>
-      <c r="M11" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" customHeight="1" spans="1:13">
-      <c r="C12" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="E12" s="3">
+      <c r="G40" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="H40" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="I40" s="3">
+        <v>99999999</v>
+      </c>
+      <c r="J40" s="3">
+        <v>0</v>
+      </c>
+      <c r="K40" s="3">
+        <v>5</v>
+      </c>
+      <c r="L40" s="3">
+        <v>0</v>
+      </c>
+      <c r="M40" s="3">
+        <v>0</v>
+      </c>
+      <c r="N40" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" customHeight="1" spans="1:14">
+      <c r="A41" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C41" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="D41" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="F41" s="3">
         <v>4</v>
       </c>
-      <c r="F12" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="H12" s="3">
+      <c r="G41" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="H41" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="I41" s="3">
         <v>99999999</v>
       </c>
-      <c r="I12" s="3">
-        <v>42</v>
-      </c>
-      <c r="J12" s="3">
+      <c r="J41" s="3">
+        <v>0</v>
+      </c>
+      <c r="K41" s="3">
+        <v>6</v>
+      </c>
+      <c r="L41" s="3">
+        <v>0</v>
+      </c>
+      <c r="M41" s="3">
+        <v>0</v>
+      </c>
+      <c r="N41" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" customHeight="1" spans="1:14">
+      <c r="A42" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C42" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="D42" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="F42" s="3">
         <v>4</v>
       </c>
-      <c r="K12" s="3">
-        <v>0</v>
-      </c>
-      <c r="L12" s="3">
-        <v>0</v>
-      </c>
-      <c r="M12" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" customHeight="1" spans="1:13">
-      <c r="A13" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="C13" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="D13" s="6" t="s">
+      <c r="G42" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="H42" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="I42" s="3">
+        <v>99999999</v>
+      </c>
+      <c r="J42" s="3">
+        <v>0</v>
+      </c>
+      <c r="K42" s="3">
+        <v>7</v>
+      </c>
+      <c r="L42" s="3">
+        <v>0</v>
+      </c>
+      <c r="M42" s="3">
+        <v>0</v>
+      </c>
+      <c r="N42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" customHeight="1" spans="1:14">
+      <c r="A43" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="E13" s="3">
+      <c r="B43" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C43" s="11" t="s">
+        <v>135</v>
+      </c>
+      <c r="D43" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="F43" s="3">
         <v>4</v>
       </c>
-      <c r="F13" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="H13" s="3">
+      <c r="G43" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="I43" s="3">
         <v>99999999</v>
       </c>
-      <c r="I13" s="3">
-        <v>49</v>
-      </c>
-      <c r="J13" s="3">
-        <v>5</v>
-      </c>
-      <c r="K13" s="3">
-        <v>0</v>
-      </c>
-      <c r="L13" s="3">
-        <v>0</v>
-      </c>
-      <c r="M13" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" customHeight="1" spans="1:13">
-      <c r="A14" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="C14" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="D14" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="E14" s="3">
-        <v>4</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="H14" s="3">
-        <v>99999999</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>5</v>
-      </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" customHeight="1" spans="1:13">
-      <c r="A15" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="C15" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="D15" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="E15" s="3">
-        <v>4</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="H15" s="3">
-        <v>99999999</v>
-      </c>
-      <c r="I15" s="3">
-        <v>0</v>
-      </c>
-      <c r="J15" s="3">
+      <c r="J43" s="3">
         <v>6</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
-      <c r="M15" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" customHeight="1" spans="1:13">
-      <c r="A16" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="C16" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="D16" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="E16" s="3">
-        <v>4</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="H16" s="3">
-        <v>99999999</v>
-      </c>
-      <c r="I16" s="3">
-        <v>0</v>
-      </c>
-      <c r="J16" s="3">
-        <v>7</v>
-      </c>
-      <c r="K16" s="3">
-        <v>0</v>
-      </c>
-      <c r="L16" s="3">
-        <v>0</v>
-      </c>
-      <c r="M16" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" customHeight="1" spans="1:13">
-      <c r="A17" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="C17" s="11" t="s">
-        <v>59</v>
-      </c>
-      <c r="D17" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="E17" s="3">
-        <v>4</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="H17" s="3">
-        <v>99999999</v>
-      </c>
-      <c r="I17" s="3">
-        <v>6</v>
-      </c>
-      <c r="J17" s="3">
+      <c r="K43" s="3">
         <v>8</v>
       </c>
-      <c r="K17" s="3">
-        <v>0</v>
-      </c>
-      <c r="L17" s="3">
-        <v>0</v>
-      </c>
-      <c r="M17" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" customHeight="1" spans="1:13">
-      <c r="C19" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="D19" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="E19" s="3">
-        <v>4</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="H19" s="3">
-        <v>99999999</v>
-      </c>
-      <c r="I19" s="3">
-        <v>1</v>
-      </c>
-      <c r="J19" s="3">
-        <v>3</v>
-      </c>
-      <c r="K19" s="3">
-        <v>0</v>
-      </c>
-      <c r="L19" s="3">
-        <v>0</v>
-      </c>
-      <c r="M19" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" customHeight="1" spans="1:13">
-      <c r="C20" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="D20" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="E20" s="3">
-        <v>4</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="H20" s="3">
-        <v>99999999</v>
-      </c>
-      <c r="I20" s="3">
-        <v>7</v>
-      </c>
-      <c r="J20" s="3">
-        <v>3</v>
-      </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" customHeight="1" spans="1:13">
-      <c r="C21" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="D21" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="E21" s="3">
-        <v>4</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="H21" s="3">
-        <v>99999999</v>
-      </c>
-      <c r="I21" s="3">
-        <v>14</v>
-      </c>
-      <c r="J21" s="3">
-        <v>3</v>
-      </c>
-      <c r="K21" s="3">
-        <v>0</v>
-      </c>
-      <c r="L21" s="3">
-        <v>0</v>
-      </c>
-      <c r="M21" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" customHeight="1" spans="1:13">
-      <c r="C22" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="D22" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="E22" s="3">
-        <v>4</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="H22" s="3">
-        <v>99999999</v>
-      </c>
-      <c r="I22" s="3">
-        <v>21</v>
-      </c>
-      <c r="J22" s="3">
-        <v>3</v>
-      </c>
-      <c r="K22" s="3">
-        <v>0</v>
-      </c>
-      <c r="L22" s="3">
-        <v>0</v>
-      </c>
-      <c r="M22" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" customHeight="1" spans="1:13">
-      <c r="C23" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="D23" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="E23" s="3">
-        <v>4</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="H23" s="3">
-        <v>99999999</v>
-      </c>
-      <c r="I23" s="3">
-        <v>28</v>
-      </c>
-      <c r="J23" s="3">
-        <v>4</v>
-      </c>
-      <c r="K23" s="3">
-        <v>0</v>
-      </c>
-      <c r="L23" s="3">
-        <v>0</v>
-      </c>
-      <c r="M23" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" customHeight="1" spans="1:13">
-      <c r="C24" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="D24" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="E24" s="3">
-        <v>4</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="H24" s="3">
-        <v>99999999</v>
-      </c>
-      <c r="I24" s="3">
-        <v>35</v>
-      </c>
-      <c r="J24" s="3">
-        <v>4</v>
-      </c>
-      <c r="K24" s="3">
-        <v>0</v>
-      </c>
-      <c r="L24" s="3">
-        <v>0</v>
-      </c>
-      <c r="M24" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" customHeight="1" spans="1:13">
-      <c r="C25" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D25" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="E25" s="3">
-        <v>4</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="G25" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="H25" s="3">
-        <v>99999999</v>
-      </c>
-      <c r="I25" s="3">
-        <v>42</v>
-      </c>
-      <c r="J25" s="3">
-        <v>4</v>
-      </c>
-      <c r="K25" s="3">
-        <v>0</v>
-      </c>
-      <c r="L25" s="3">
-        <v>0</v>
-      </c>
-      <c r="M25" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" customHeight="1" spans="1:13">
-      <c r="A26" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="C26" s="11" t="s">
-        <v>83</v>
-      </c>
-      <c r="D26" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="E26" s="3">
-        <v>4</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="G26" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="H26" s="3">
-        <v>99999999</v>
-      </c>
-      <c r="I26" s="3">
-        <v>49</v>
-      </c>
-      <c r="J26" s="3">
-        <v>5</v>
-      </c>
-      <c r="K26" s="3">
-        <v>0</v>
-      </c>
-      <c r="L26" s="3">
-        <v>0</v>
-      </c>
-      <c r="M26" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" customHeight="1" spans="1:13">
-      <c r="A27" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="C27" s="11" t="s">
-        <v>86</v>
-      </c>
-      <c r="D27" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="E27" s="3">
-        <v>4</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="G27" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="H27" s="3">
-        <v>99999999</v>
-      </c>
-      <c r="I27" s="3">
-        <v>0</v>
-      </c>
-      <c r="J27" s="3">
-        <v>5</v>
-      </c>
-      <c r="K27" s="3">
-        <v>0</v>
-      </c>
-      <c r="L27" s="3">
-        <v>0</v>
-      </c>
-      <c r="M27" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" customHeight="1" spans="1:13">
-      <c r="A28" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="C28" s="11" t="s">
-        <v>89</v>
-      </c>
-      <c r="D28" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="E28" s="3">
-        <v>4</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="G28" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="H28" s="3">
-        <v>99999999</v>
-      </c>
-      <c r="I28" s="3">
-        <v>0</v>
-      </c>
-      <c r="J28" s="3">
-        <v>6</v>
-      </c>
-      <c r="K28" s="3">
-        <v>0</v>
-      </c>
-      <c r="L28" s="3">
-        <v>0</v>
-      </c>
-      <c r="M28" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" customHeight="1" spans="1:13">
-      <c r="A29" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="C29" s="11" t="s">
-        <v>92</v>
-      </c>
-      <c r="D29" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="E29" s="3">
-        <v>4</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="H29" s="3">
-        <v>99999999</v>
-      </c>
-      <c r="I29" s="3">
-        <v>0</v>
-      </c>
-      <c r="J29" s="3">
-        <v>7</v>
-      </c>
-      <c r="K29" s="3">
-        <v>0</v>
-      </c>
-      <c r="L29" s="3">
-        <v>0</v>
-      </c>
-      <c r="M29" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" customHeight="1" spans="1:13">
-      <c r="A30" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="C30" s="11" t="s">
-        <v>95</v>
-      </c>
-      <c r="D30" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="E30" s="3">
-        <v>4</v>
-      </c>
-      <c r="F30" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="G30" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="H30" s="3">
-        <v>99999999</v>
-      </c>
-      <c r="I30" s="3">
-        <v>6</v>
-      </c>
-      <c r="J30" s="3">
-        <v>8</v>
-      </c>
-      <c r="K30" s="3">
-        <v>0</v>
-      </c>
-      <c r="L30" s="3">
-        <v>0</v>
-      </c>
-      <c r="M30" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" customHeight="1" spans="1:13">
-      <c r="C32" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="D32" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="E32" s="3">
-        <v>4</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="G32" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="H32" s="3">
-        <v>99999999</v>
-      </c>
-      <c r="I32" s="3">
-        <v>1</v>
-      </c>
-      <c r="J32" s="3">
-        <v>3</v>
-      </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" customHeight="1" spans="1:13">
-      <c r="C33" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="D33" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="E33" s="3">
-        <v>4</v>
-      </c>
-      <c r="F33" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="G33" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="H33" s="3">
-        <v>99999999</v>
-      </c>
-      <c r="I33" s="3">
-        <v>7</v>
-      </c>
-      <c r="J33" s="3">
-        <v>3</v>
-      </c>
-      <c r="K33" s="3">
-        <v>0</v>
-      </c>
-      <c r="L33" s="3">
-        <v>0</v>
-      </c>
-      <c r="M33" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" customHeight="1" spans="1:13">
-      <c r="C34" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="D34" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="E34" s="3">
-        <v>4</v>
-      </c>
-      <c r="F34" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="G34" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="H34" s="3">
-        <v>99999999</v>
-      </c>
-      <c r="I34" s="3">
-        <v>14</v>
-      </c>
-      <c r="J34" s="3">
-        <v>3</v>
-      </c>
-      <c r="K34" s="3">
-        <v>0</v>
-      </c>
-      <c r="L34" s="3">
-        <v>0</v>
-      </c>
-      <c r="M34" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" customHeight="1" spans="1:13">
-      <c r="C35" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="D35" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="E35" s="3">
-        <v>4</v>
-      </c>
-      <c r="F35" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="G35" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="H35" s="3">
-        <v>99999999</v>
-      </c>
-      <c r="I35" s="3">
-        <v>21</v>
-      </c>
-      <c r="J35" s="3">
-        <v>3</v>
-      </c>
-      <c r="K35" s="3">
-        <v>0</v>
-      </c>
-      <c r="L35" s="3">
-        <v>0</v>
-      </c>
-      <c r="M35" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" customHeight="1" spans="1:13">
-      <c r="C36" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="D36" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="E36" s="3">
-        <v>4</v>
-      </c>
-      <c r="F36" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="G36" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="H36" s="3">
-        <v>99999999</v>
-      </c>
-      <c r="I36" s="3">
-        <v>28</v>
-      </c>
-      <c r="J36" s="3">
-        <v>4</v>
-      </c>
-      <c r="K36" s="3">
-        <v>0</v>
-      </c>
-      <c r="L36" s="3">
-        <v>0</v>
-      </c>
-      <c r="M36" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" customHeight="1" spans="1:13">
-      <c r="C37" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="D37" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="E37" s="3">
-        <v>4</v>
-      </c>
-      <c r="F37" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="G37" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="H37" s="3">
-        <v>99999999</v>
-      </c>
-      <c r="I37" s="3">
-        <v>35</v>
-      </c>
-      <c r="J37" s="3">
-        <v>4</v>
-      </c>
-      <c r="K37" s="3">
-        <v>0</v>
-      </c>
-      <c r="L37" s="3">
-        <v>0</v>
-      </c>
-      <c r="M37" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" customHeight="1" spans="1:13">
-      <c r="C38" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="D38" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="E38" s="3">
-        <v>4</v>
-      </c>
-      <c r="F38" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="G38" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="H38" s="3">
-        <v>99999999</v>
-      </c>
-      <c r="I38" s="3">
-        <v>42</v>
-      </c>
-      <c r="J38" s="3">
-        <v>4</v>
-      </c>
-      <c r="K38" s="3">
-        <v>0</v>
-      </c>
-      <c r="L38" s="3">
-        <v>0</v>
-      </c>
-      <c r="M38" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" customHeight="1" spans="1:13">
-      <c r="A39" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="C39" s="11" t="s">
-        <v>119</v>
-      </c>
-      <c r="D39" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="E39" s="3">
-        <v>4</v>
-      </c>
-      <c r="F39" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="G39" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="H39" s="3">
-        <v>99999999</v>
-      </c>
-      <c r="I39" s="3">
-        <v>49</v>
-      </c>
-      <c r="J39" s="3">
-        <v>5</v>
-      </c>
-      <c r="K39" s="3">
-        <v>0</v>
-      </c>
-      <c r="L39" s="3">
-        <v>0</v>
-      </c>
-      <c r="M39" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" customHeight="1" spans="1:13">
-      <c r="A40" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="C40" s="11" t="s">
-        <v>122</v>
-      </c>
-      <c r="D40" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="E40" s="3">
-        <v>4</v>
-      </c>
-      <c r="F40" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="G40" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="H40" s="3">
-        <v>99999999</v>
-      </c>
-      <c r="I40" s="3">
-        <v>0</v>
-      </c>
-      <c r="J40" s="3">
-        <v>5</v>
-      </c>
-      <c r="K40" s="3">
-        <v>0</v>
-      </c>
-      <c r="L40" s="3">
-        <v>0</v>
-      </c>
-      <c r="M40" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" customHeight="1" spans="1:13">
-      <c r="A41" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="C41" s="11" t="s">
-        <v>125</v>
-      </c>
-      <c r="D41" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="E41" s="3">
-        <v>4</v>
-      </c>
-      <c r="F41" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="G41" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="H41" s="3">
-        <v>99999999</v>
-      </c>
-      <c r="I41" s="3">
-        <v>0</v>
-      </c>
-      <c r="J41" s="3">
-        <v>6</v>
-      </c>
-      <c r="K41" s="3">
-        <v>0</v>
-      </c>
-      <c r="L41" s="3">
-        <v>0</v>
-      </c>
-      <c r="M41" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" customHeight="1" spans="1:13">
-      <c r="A42" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="C42" s="11" t="s">
-        <v>128</v>
-      </c>
-      <c r="D42" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="E42" s="3">
-        <v>4</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="G42" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="H42" s="3">
-        <v>99999999</v>
-      </c>
-      <c r="I42" s="3">
-        <v>0</v>
-      </c>
-      <c r="J42" s="3">
-        <v>7</v>
-      </c>
-      <c r="K42" s="3">
-        <v>0</v>
-      </c>
-      <c r="L42" s="3">
-        <v>0</v>
-      </c>
-      <c r="M42" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" customHeight="1" spans="1:13">
-      <c r="A43" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="C43" s="11" t="s">
-        <v>131</v>
-      </c>
-      <c r="D43" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="E43" s="3">
-        <v>4</v>
-      </c>
-      <c r="F43" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="G43" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="H43" s="3">
-        <v>99999999</v>
-      </c>
-      <c r="I43" s="3">
-        <v>6</v>
-      </c>
-      <c r="J43" s="3">
-        <v>8</v>
-      </c>
-      <c r="K43" s="3">
-        <v>0</v>
-      </c>
       <c r="L43" s="3">
         <v>0</v>
       </c>
       <c r="M43" s="3">
+        <v>0</v>
+      </c>
+      <c r="N43" s="3">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="L3:M5" errorStyle="warning">
-      <formula1>COUNTIF($A:$A,L3)&lt;2</formula1>
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="E3 E4 E5 C3:D5" errorStyle="warning">
+      <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:D5" errorStyle="warning">
-      <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="M3:N5" errorStyle="warning">
+      <formula1>COUNTIF($A:$A,M3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3649,27 +3785,34 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:M116"/>
+  <dimension ref="C1:N116"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="3"/>
     <col min="4" max="4" width="12.625" style="3" customWidth="1"/>
-    <col min="5" max="5" width="9.875" style="3" customWidth="1"/>
-    <col min="6" max="6" width="47.25" style="3" customWidth="1"/>
-    <col min="7" max="7" width="8" style="3" customWidth="1"/>
-    <col min="8" max="11" width="12.25" style="3" customWidth="1"/>
-    <col min="12" max="13" width="13.5083333333333" style="3" customWidth="1"/>
-    <col min="14" max="16384" width="9" style="3"/>
+    <col min="5" max="5" width="9.58333333333333" style="2" customWidth="1"/>
+    <col min="6" max="6" width="9.875" style="3" customWidth="1"/>
+    <col min="7" max="7" width="47.25" style="3" customWidth="1"/>
+    <col min="8" max="8" width="8" style="3" customWidth="1"/>
+    <col min="9" max="12" width="12.25" style="3" customWidth="1"/>
+    <col min="13" max="14" width="13.5083333333333" style="3" customWidth="1"/>
+    <col min="15" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="3" s="3" customFormat="1" customHeight="1" spans="3:13">
+    <row r="1" customHeight="1" spans="3:14">
+      <c r="E1" s="1"/>
+    </row>
+    <row r="2" customHeight="1" spans="3:14">
+      <c r="E2" s="1"/>
+    </row>
+    <row r="3" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C3" s="5" t="s">
         <v>0</v>
       </c>
       <c r="D3" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="4" t="s">
         <v>2</v>
       </c>
       <c r="F3" s="5" t="s">
@@ -3696,16 +3839,19 @@
       <c r="M3" s="5" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="4" s="3" customFormat="1" customHeight="1" spans="3:13">
+      <c r="N3" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C4" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E4" s="5" t="s">
         <v>13</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>2</v>
       </c>
       <c r="F4" s="5" t="s">
         <v>14</v>
@@ -3726,216 +3872,227 @@
         <v>19</v>
       </c>
       <c r="L4" s="5" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="M4" s="5" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="5" s="3" customFormat="1" customHeight="1" spans="3:13">
+      <c r="N4" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C5" s="5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>20</v>
+        <v>22</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>22</v>
       </c>
       <c r="F5" s="5" t="s">
         <v>21</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K5" s="5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L5" s="5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M5" s="5" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="6" s="3" customFormat="1" customHeight="1" spans="3:13">
+        <v>21</v>
+      </c>
+      <c r="N5" s="5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C6" s="3">
         <v>5001</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="E6" s="3">
-        <v>5</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="G6" s="3">
-        <v>1</v>
+        <v>138</v>
+      </c>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3">
+        <v>5</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>139</v>
       </c>
       <c r="H6" s="3">
+        <v>1</v>
+      </c>
+      <c r="I6" s="3">
         <v>99999999</v>
       </c>
-      <c r="I6" s="3">
-        <v>0</v>
-      </c>
       <c r="J6" s="3">
+        <v>0</v>
+      </c>
+      <c r="K6" s="3">
         <v>3</v>
       </c>
-      <c r="K6" s="3"/>
-      <c r="L6" s="3">
-        <v>0</v>
-      </c>
+      <c r="L6" s="3"/>
       <c r="M6" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" s="6" customFormat="1" customHeight="1" spans="3:13">
+      <c r="N6" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" s="6" customFormat="1" customHeight="1" spans="3:14">
       <c r="C7" s="3">
         <v>5002</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="E7" s="3">
-        <v>5</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="G7" s="3">
-        <v>1</v>
+        <v>140</v>
+      </c>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3">
+        <v>5</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>139</v>
       </c>
       <c r="H7" s="3">
+        <v>1</v>
+      </c>
+      <c r="I7" s="3">
         <v>99999999</v>
       </c>
-      <c r="I7" s="3">
-        <v>0</v>
-      </c>
       <c r="J7" s="3">
-        <v>5</v>
-      </c>
-      <c r="K7" s="3"/>
-      <c r="L7" s="3">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K7" s="3">
+        <v>5</v>
+      </c>
+      <c r="L7" s="3"/>
       <c r="M7" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" s="6" customFormat="1" customHeight="1" spans="3:13">
+      <c r="N7" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" s="6" customFormat="1" customHeight="1" spans="3:14">
       <c r="C8" s="3">
         <v>5003</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="E8" s="3">
-        <v>5</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="G8" s="3">
-        <v>1</v>
+        <v>141</v>
+      </c>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3">
+        <v>5</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>142</v>
       </c>
       <c r="H8" s="3">
+        <v>1</v>
+      </c>
+      <c r="I8" s="3">
         <v>99999999</v>
       </c>
-      <c r="I8" s="3">
-        <v>0</v>
-      </c>
       <c r="J8" s="3">
-        <v>5</v>
-      </c>
-      <c r="K8" s="3"/>
-      <c r="L8" s="3">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K8" s="3">
+        <v>5</v>
+      </c>
+      <c r="L8" s="3"/>
       <c r="M8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" s="6" customFormat="1" customHeight="1" spans="3:13">
+      <c r="N8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" s="6" customFormat="1" customHeight="1" spans="3:14">
       <c r="C9" s="3">
         <v>5004</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="E9" s="3">
-        <v>5</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="G9" s="3">
-        <v>1</v>
+        <v>143</v>
+      </c>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3">
+        <v>5</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>144</v>
       </c>
       <c r="H9" s="3">
+        <v>1</v>
+      </c>
+      <c r="I9" s="3">
         <v>99999999</v>
       </c>
-      <c r="I9" s="3">
-        <v>0</v>
-      </c>
       <c r="J9" s="3">
-        <v>5</v>
-      </c>
-      <c r="K9" s="3"/>
-      <c r="L9" s="3">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K9" s="3">
+        <v>5</v>
+      </c>
+      <c r="L9" s="3"/>
       <c r="M9" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" s="3" customFormat="1" customHeight="1" spans="3:13">
+      <c r="N9" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C10" s="3">
         <v>5005</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="E10" s="3">
-        <v>5</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="G10" s="3">
-        <v>1</v>
+        <v>145</v>
+      </c>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3">
+        <v>5</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>146</v>
       </c>
       <c r="H10" s="3">
+        <v>1</v>
+      </c>
+      <c r="I10" s="3">
         <v>99999999</v>
       </c>
-      <c r="I10" s="3">
-        <v>0</v>
-      </c>
       <c r="J10" s="3">
-        <v>5</v>
-      </c>
-      <c r="L10" s="3">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="K10" s="3">
+        <v>5</v>
       </c>
       <c r="M10" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" s="6" customFormat="1" customHeight="1" spans="3:13">
+      <c r="N10" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" s="6" customFormat="1" customHeight="1" spans="3:14">
       <c r="C11" s="7"/>
       <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="3"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="7"/>
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
       <c r="I11" s="3"/>
@@ -3943,143 +4100,148 @@
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
-    </row>
-    <row r="12" s="6" customFormat="1" customHeight="1" spans="3:13">
+      <c r="N11" s="3"/>
+    </row>
+    <row r="12" s="6" customFormat="1" customHeight="1" spans="3:14">
       <c r="C12" s="8">
         <v>5011</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="E12" s="10">
-        <v>5</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="G12" s="3">
-        <v>1</v>
+        <v>147</v>
+      </c>
+      <c r="E12" s="2"/>
+      <c r="F12" s="10">
+        <v>5</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>148</v>
       </c>
       <c r="H12" s="3">
+        <v>1</v>
+      </c>
+      <c r="I12" s="3">
         <v>99999999</v>
       </c>
-      <c r="I12" s="3">
-        <v>0</v>
-      </c>
       <c r="J12" s="3">
+        <v>0</v>
+      </c>
+      <c r="K12" s="3">
         <v>3</v>
       </c>
-      <c r="K12" s="3"/>
-      <c r="L12" s="3">
-        <v>0</v>
-      </c>
+      <c r="L12" s="3"/>
       <c r="M12" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" s="6" customFormat="1" customHeight="1" spans="3:13">
+      <c r="N12" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" s="6" customFormat="1" customHeight="1" spans="3:14">
       <c r="C13" s="8">
         <v>5012</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>145</v>
-      </c>
-      <c r="E13" s="10">
-        <v>5</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="G13" s="3">
-        <v>1</v>
+        <v>149</v>
+      </c>
+      <c r="E13" s="2"/>
+      <c r="F13" s="10">
+        <v>5</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>150</v>
       </c>
       <c r="H13" s="3">
+        <v>1</v>
+      </c>
+      <c r="I13" s="3">
         <v>99999999</v>
       </c>
-      <c r="I13" s="3">
-        <v>0</v>
-      </c>
       <c r="J13" s="3">
+        <v>0</v>
+      </c>
+      <c r="K13" s="3">
         <v>3</v>
       </c>
-      <c r="K13" s="3"/>
-      <c r="L13" s="3">
-        <v>0</v>
-      </c>
+      <c r="L13" s="3"/>
       <c r="M13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" s="6" customFormat="1" customHeight="1" spans="3:13">
+      <c r="N13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" s="6" customFormat="1" customHeight="1" spans="3:14">
       <c r="C14" s="8">
         <v>5013</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>147</v>
-      </c>
-      <c r="E14" s="10">
-        <v>5</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="G14" s="3">
-        <v>1</v>
+        <v>151</v>
+      </c>
+      <c r="E14" s="3"/>
+      <c r="F14" s="10">
+        <v>5</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>152</v>
       </c>
       <c r="H14" s="3">
+        <v>1</v>
+      </c>
+      <c r="I14" s="3">
         <v>99999999</v>
       </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
       <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3">
         <v>3</v>
       </c>
-      <c r="K14" s="3"/>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
+      <c r="L14" s="3"/>
       <c r="M14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" s="6" customFormat="1" customHeight="1" spans="3:13">
+      <c r="N14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" s="6" customFormat="1" customHeight="1" spans="3:14">
       <c r="C15" s="8">
         <v>5014</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="E15" s="10">
-        <v>5</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="G15" s="3">
-        <v>1</v>
+        <v>153</v>
+      </c>
+      <c r="E15" s="3"/>
+      <c r="F15" s="10">
+        <v>5</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>154</v>
       </c>
       <c r="H15" s="3">
+        <v>1</v>
+      </c>
+      <c r="I15" s="3">
         <v>99999999</v>
       </c>
-      <c r="I15" s="3">
-        <v>0</v>
-      </c>
       <c r="J15" s="3">
+        <v>0</v>
+      </c>
+      <c r="K15" s="3">
         <v>3</v>
       </c>
-      <c r="K15" s="3"/>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
+      <c r="L15" s="3"/>
       <c r="M15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" s="6" customFormat="1" customHeight="1" spans="3:13">
+      <c r="N15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" s="6" customFormat="1" customHeight="1" spans="3:14">
       <c r="C16" s="7"/>
       <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
+      <c r="E16" s="3"/>
       <c r="F16" s="7"/>
       <c r="G16" s="7"/>
       <c r="H16" s="7"/>
@@ -4088,273 +4250,280 @@
       <c r="K16" s="7"/>
       <c r="L16" s="7"/>
       <c r="M16" s="7"/>
-    </row>
-    <row r="17" s="3" customFormat="1" customHeight="1" spans="3:13">
+      <c r="N16" s="7"/>
+    </row>
+    <row r="17" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C17" s="3">
         <v>7001</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="E17" s="3">
+        <v>155</v>
+      </c>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3">
         <v>7</v>
       </c>
-      <c r="F17" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="G17" s="3">
-        <v>1</v>
+      <c r="G17" s="3" t="s">
+        <v>156</v>
       </c>
       <c r="H17" s="3">
+        <v>1</v>
+      </c>
+      <c r="I17" s="3">
         <v>9999999</v>
       </c>
-      <c r="I17" s="3">
-        <v>0</v>
-      </c>
       <c r="J17" s="3">
+        <v>0</v>
+      </c>
+      <c r="K17" s="3">
         <v>6</v>
       </c>
-      <c r="L17" s="3">
-        <v>0</v>
-      </c>
       <c r="M17" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" s="3" customFormat="1" customHeight="1" spans="3:13">
+      <c r="N17" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C18" s="3">
         <v>7002</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="E18" s="3">
+        <v>157</v>
+      </c>
+      <c r="E18" s="2"/>
+      <c r="F18" s="3">
         <v>7</v>
       </c>
-      <c r="F18" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="G18" s="3">
-        <v>1</v>
+      <c r="G18" s="3" t="s">
+        <v>158</v>
       </c>
       <c r="H18" s="3">
+        <v>1</v>
+      </c>
+      <c r="I18" s="3">
         <v>9999999</v>
       </c>
-      <c r="I18" s="3">
-        <v>0</v>
-      </c>
       <c r="J18" s="3">
+        <v>0</v>
+      </c>
+      <c r="K18" s="3">
         <v>7</v>
       </c>
-      <c r="K18" s="3">
-        <v>0</v>
-      </c>
       <c r="L18" s="3">
         <v>0</v>
       </c>
       <c r="M18" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="20" customFormat="1" customHeight="1" spans="3:13">
+      <c r="N18" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" customFormat="1" customHeight="1" spans="3:14">
       <c r="C20" s="3"/>
       <c r="D20" s="3"/>
-      <c r="E20" s="3"/>
+      <c r="E20" s="2"/>
       <c r="F20" s="3"/>
       <c r="G20" s="3"/>
       <c r="H20" s="3"/>
       <c r="I20" s="3"/>
       <c r="J20" s="3"/>
-      <c r="L20" s="3"/>
+      <c r="K20" s="3"/>
       <c r="M20" s="3"/>
-    </row>
-    <row r="21" s="3" customFormat="1" customHeight="1" spans="3:13">
+      <c r="N20" s="3"/>
+    </row>
+    <row r="21" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C21" s="3">
         <v>4001</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="E21" s="3">
-        <v>5</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="G21" s="3">
-        <v>1</v>
+        <v>159</v>
+      </c>
+      <c r="E21" s="2"/>
+      <c r="F21" s="3">
+        <v>5</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>160</v>
       </c>
       <c r="H21" s="3">
+        <v>1</v>
+      </c>
+      <c r="I21" s="3">
         <v>99999999999</v>
       </c>
-      <c r="I21" s="3">
-        <v>0</v>
-      </c>
       <c r="J21" s="3">
-        <v>5</v>
-      </c>
-      <c r="L21" s="3">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="K21" s="3">
+        <v>5</v>
       </c>
       <c r="M21" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" s="3" customFormat="1" customHeight="1" spans="3:13">
+      <c r="N21" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C22" s="3">
         <v>4002</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="E22" s="3">
-        <v>5</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="G22" s="3">
-        <v>1</v>
+        <v>161</v>
+      </c>
+      <c r="E22" s="2"/>
+      <c r="F22" s="3">
+        <v>5</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>162</v>
       </c>
       <c r="H22" s="3">
+        <v>1</v>
+      </c>
+      <c r="I22" s="3">
         <v>99999999999</v>
       </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
       <c r="J22" s="3">
-        <v>5</v>
-      </c>
-      <c r="L22" s="3">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="K22" s="3">
+        <v>5</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" s="3" customFormat="1" customHeight="1" spans="3:13">
+      <c r="N22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C23" s="3">
         <v>4003</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="E23" s="3">
+        <v>163</v>
+      </c>
+      <c r="E23" s="2"/>
+      <c r="F23" s="3">
         <v>9</v>
       </c>
-      <c r="F23" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="G23" s="3">
-        <v>1</v>
+      <c r="G23" s="3" t="s">
+        <v>164</v>
       </c>
       <c r="H23" s="3">
+        <v>1</v>
+      </c>
+      <c r="I23" s="3">
         <v>9999999</v>
       </c>
-      <c r="I23" s="3">
-        <v>0</v>
-      </c>
       <c r="J23" s="3">
-        <v>5</v>
-      </c>
-      <c r="L23" s="3">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="K23" s="3">
+        <v>5</v>
       </c>
       <c r="M23" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" s="3" customFormat="1" customHeight="1" spans="3:13">
+      <c r="N23" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C24" s="3">
         <v>4004</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="E24" s="3">
-        <v>5</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="G24" s="3">
-        <v>1</v>
+        <v>165</v>
+      </c>
+      <c r="E24" s="2"/>
+      <c r="F24" s="3">
+        <v>5</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>166</v>
       </c>
       <c r="H24" s="3">
+        <v>1</v>
+      </c>
+      <c r="I24" s="3">
         <v>9999999</v>
       </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
       <c r="J24" s="3">
-        <v>5</v>
-      </c>
-      <c r="L24" s="3">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="K24" s="3">
+        <v>5</v>
       </c>
       <c r="M24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" s="3" customFormat="1" customHeight="1" spans="3:13">
+      <c r="N24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C25" s="3">
         <v>4005</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="E25" s="3">
-        <v>5</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="G25" s="3">
-        <v>1</v>
+        <v>167</v>
+      </c>
+      <c r="E25" s="2"/>
+      <c r="F25" s="3">
+        <v>5</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>168</v>
       </c>
       <c r="H25" s="3">
+        <v>1</v>
+      </c>
+      <c r="I25" s="3">
         <v>9999999</v>
       </c>
-      <c r="I25" s="3">
-        <v>0</v>
-      </c>
       <c r="J25" s="3">
-        <v>5</v>
-      </c>
-      <c r="L25" s="3">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="K25" s="3">
+        <v>5</v>
       </c>
       <c r="M25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" s="3" customFormat="1" customHeight="1" spans="3:13">
+      <c r="N25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C26" s="3">
         <v>4006</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="E26" s="3">
-        <v>5</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="G26" s="3">
-        <v>1</v>
+        <v>169</v>
+      </c>
+      <c r="E26" s="2"/>
+      <c r="F26" s="3">
+        <v>5</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>170</v>
       </c>
       <c r="H26" s="3">
+        <v>1</v>
+      </c>
+      <c r="I26" s="3">
         <v>99999999</v>
       </c>
-      <c r="I26" s="3">
-        <v>0</v>
-      </c>
       <c r="J26" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K26" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L26" s="3">
         <v>0</v>
@@ -4362,1882 +4531,1942 @@
       <c r="M26" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" s="3" customFormat="1" customHeight="1" spans="3:13">
+      <c r="N26" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C27" s="3">
         <v>4007</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="E27" s="3">
-        <v>5</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="G27" s="3">
-        <v>1</v>
+        <v>171</v>
+      </c>
+      <c r="E27" s="2"/>
+      <c r="F27" s="3">
+        <v>5</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>172</v>
       </c>
       <c r="H27" s="3">
+        <v>1</v>
+      </c>
+      <c r="I27" s="3">
         <v>9999999999</v>
       </c>
-      <c r="I27" s="3">
-        <v>0</v>
-      </c>
       <c r="J27" s="3">
-        <v>5</v>
-      </c>
-      <c r="L27" s="3">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="K27" s="3">
+        <v>5</v>
       </c>
       <c r="M27" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" s="3" customFormat="1" customHeight="1" spans="3:13">
+      <c r="N27" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C28" s="3">
         <v>4008</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="E28" s="3">
-        <v>5</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="G28" s="3">
-        <v>1</v>
+        <v>173</v>
+      </c>
+      <c r="E28" s="2"/>
+      <c r="F28" s="3">
+        <v>5</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>174</v>
       </c>
       <c r="H28" s="3">
+        <v>1</v>
+      </c>
+      <c r="I28" s="3">
         <v>9999999</v>
       </c>
-      <c r="I28" s="3">
-        <v>0</v>
-      </c>
       <c r="J28" s="3">
-        <v>5</v>
-      </c>
-      <c r="L28" s="3">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="K28" s="3">
+        <v>5</v>
       </c>
       <c r="M28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" s="3" customFormat="1" customHeight="1" spans="3:13">
+      <c r="N28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C29" s="3">
         <v>4009</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="E29" s="3">
-        <v>5</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="G29" s="3">
-        <v>1</v>
+        <v>175</v>
+      </c>
+      <c r="E29" s="2"/>
+      <c r="F29" s="3">
+        <v>5</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>176</v>
       </c>
       <c r="H29" s="3">
+        <v>1</v>
+      </c>
+      <c r="I29" s="3">
         <v>9999999</v>
       </c>
-      <c r="I29" s="3">
-        <v>0</v>
-      </c>
       <c r="J29" s="3">
-        <v>5</v>
-      </c>
-      <c r="L29" s="3">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="K29" s="3">
+        <v>5</v>
       </c>
       <c r="M29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" s="3" customFormat="1" customHeight="1" spans="3:13">
+      <c r="N29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C30" s="3">
         <v>4010</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="E30" s="3">
-        <v>5</v>
-      </c>
-      <c r="F30" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="G30" s="3">
-        <v>1</v>
+        <v>177</v>
+      </c>
+      <c r="E30" s="2"/>
+      <c r="F30" s="3">
+        <v>5</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>178</v>
       </c>
       <c r="H30" s="3">
+        <v>1</v>
+      </c>
+      <c r="I30" s="3">
         <v>9999999</v>
       </c>
-      <c r="I30" s="3">
-        <v>0</v>
-      </c>
       <c r="J30" s="3">
-        <v>5</v>
-      </c>
-      <c r="L30" s="3">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="K30" s="3">
+        <v>5</v>
       </c>
       <c r="M30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" s="3" customFormat="1" customHeight="1" spans="3:13">
+      <c r="N30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C31" s="3">
         <v>4011</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="E31" s="3">
-        <v>5</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="G31" s="3">
-        <v>1</v>
+        <v>179</v>
+      </c>
+      <c r="E31" s="2"/>
+      <c r="F31" s="3">
+        <v>5</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>180</v>
       </c>
       <c r="H31" s="3">
+        <v>1</v>
+      </c>
+      <c r="I31" s="3">
         <v>9999999</v>
       </c>
-      <c r="I31" s="3">
-        <v>0</v>
-      </c>
       <c r="J31" s="3">
+        <v>0</v>
+      </c>
+      <c r="K31" s="3">
         <v>6</v>
       </c>
-      <c r="L31" s="3">
-        <v>0</v>
-      </c>
       <c r="M31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" s="3" customFormat="1" customHeight="1" spans="3:13">
+      <c r="N31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C33" s="3">
         <v>4013</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="E33" s="3">
+        <v>181</v>
+      </c>
+      <c r="E33" s="2"/>
+      <c r="F33" s="3">
         <v>9</v>
       </c>
-      <c r="F33" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="G33" s="3">
-        <v>1</v>
+      <c r="G33" s="3" t="s">
+        <v>182</v>
       </c>
       <c r="H33" s="3">
+        <v>1</v>
+      </c>
+      <c r="I33" s="3">
         <v>9999999</v>
       </c>
-      <c r="I33" s="3">
-        <v>0</v>
-      </c>
       <c r="J33" s="3">
-        <v>5</v>
-      </c>
-      <c r="L33" s="3">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="K33" s="3">
+        <v>5</v>
       </c>
       <c r="M33" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" s="3" customFormat="1" customHeight="1" spans="3:13">
+      <c r="N33" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C34" s="3">
         <v>4015</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="E34" s="3">
-        <v>5</v>
-      </c>
-      <c r="F34" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="G34" s="3">
-        <v>1</v>
+        <v>183</v>
+      </c>
+      <c r="E34" s="2"/>
+      <c r="F34" s="3">
+        <v>5</v>
+      </c>
+      <c r="G34" s="3" t="s">
+        <v>184</v>
       </c>
       <c r="H34" s="3">
+        <v>1</v>
+      </c>
+      <c r="I34" s="3">
         <v>9999999</v>
       </c>
-      <c r="I34" s="3">
-        <v>0</v>
-      </c>
       <c r="J34" s="3">
+        <v>0</v>
+      </c>
+      <c r="K34" s="3">
         <v>6</v>
       </c>
-      <c r="L34" s="3">
-        <v>0</v>
-      </c>
       <c r="M34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" s="3" customFormat="1" customHeight="1" spans="3:13">
+      <c r="N34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C35" s="3">
         <v>4016</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="E35" s="3">
-        <v>5</v>
-      </c>
-      <c r="F35" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="G35" s="3">
-        <v>1</v>
+        <v>185</v>
+      </c>
+      <c r="E35" s="2"/>
+      <c r="F35" s="3">
+        <v>5</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>186</v>
       </c>
       <c r="H35" s="3">
+        <v>1</v>
+      </c>
+      <c r="I35" s="3">
         <v>9999999</v>
       </c>
-      <c r="I35" s="3">
-        <v>0</v>
-      </c>
       <c r="J35" s="3">
+        <v>0</v>
+      </c>
+      <c r="K35" s="3">
         <v>6</v>
       </c>
-      <c r="L35" s="3">
-        <v>0</v>
-      </c>
       <c r="M35" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="36" s="3" customFormat="1" customHeight="1" spans="3:13">
+      <c r="N35" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C36" s="3">
         <v>4017</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="E36" s="3">
+        <v>187</v>
+      </c>
+      <c r="E36" s="2"/>
+      <c r="F36" s="3">
         <v>9</v>
       </c>
-      <c r="F36" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="G36" s="3">
-        <v>1</v>
+      <c r="G36" s="3" t="s">
+        <v>188</v>
       </c>
       <c r="H36" s="3">
+        <v>1</v>
+      </c>
+      <c r="I36" s="3">
         <v>9999999</v>
       </c>
-      <c r="I36" s="3">
-        <v>0</v>
-      </c>
       <c r="J36" s="3">
-        <v>5</v>
-      </c>
-      <c r="L36" s="3">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="K36" s="3">
+        <v>5</v>
       </c>
       <c r="M36" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" s="3" customFormat="1" customHeight="1" spans="3:13">
+      <c r="N36" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C37" s="3">
         <v>4018</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="E37" s="3">
-        <v>5</v>
-      </c>
-      <c r="F37" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="G37" s="3">
-        <v>1</v>
+        <v>189</v>
+      </c>
+      <c r="E37" s="2"/>
+      <c r="F37" s="3">
+        <v>5</v>
+      </c>
+      <c r="G37" s="3" t="s">
+        <v>190</v>
       </c>
       <c r="H37" s="3">
+        <v>1</v>
+      </c>
+      <c r="I37" s="3">
         <v>9999999</v>
       </c>
-      <c r="I37" s="3">
-        <v>0</v>
-      </c>
       <c r="J37" s="3">
+        <v>0</v>
+      </c>
+      <c r="K37" s="3">
         <v>6</v>
       </c>
-      <c r="L37" s="3">
-        <v>0</v>
-      </c>
       <c r="M37" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="38" s="3" customFormat="1" customHeight="1" spans="3:13">
+      <c r="N37" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C38" s="3">
         <v>4019</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="E38" s="3">
-        <v>5</v>
-      </c>
-      <c r="F38" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="G38" s="3">
-        <v>1</v>
+        <v>191</v>
+      </c>
+      <c r="E38" s="2"/>
+      <c r="F38" s="3">
+        <v>5</v>
+      </c>
+      <c r="G38" s="3" t="s">
+        <v>192</v>
       </c>
       <c r="H38" s="3">
+        <v>1</v>
+      </c>
+      <c r="I38" s="3">
         <v>9999999</v>
       </c>
-      <c r="I38" s="3">
-        <v>0</v>
-      </c>
       <c r="J38" s="3">
+        <v>0</v>
+      </c>
+      <c r="K38" s="3">
         <v>7</v>
       </c>
-      <c r="L38" s="3">
-        <v>0</v>
-      </c>
       <c r="M38" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="40" s="3" customFormat="1" customHeight="1" spans="3:13">
+      <c r="N38" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C40" s="3">
         <v>4021</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="E40" s="3">
-        <v>5</v>
-      </c>
-      <c r="F40" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="G40" s="3">
-        <v>1</v>
+        <v>193</v>
+      </c>
+      <c r="E40" s="2"/>
+      <c r="F40" s="3">
+        <v>5</v>
+      </c>
+      <c r="G40" s="3" t="s">
+        <v>194</v>
       </c>
       <c r="H40" s="3">
+        <v>1</v>
+      </c>
+      <c r="I40" s="3">
         <v>9999999</v>
       </c>
-      <c r="I40" s="3">
-        <v>0</v>
-      </c>
       <c r="J40" s="3">
+        <v>0</v>
+      </c>
+      <c r="K40" s="3">
         <v>6</v>
       </c>
-      <c r="L40" s="3">
-        <v>0</v>
-      </c>
       <c r="M40" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="41" s="3" customFormat="1" customHeight="1" spans="3:13">
+      <c r="N40" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C41" s="3">
         <v>4022</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="E41" s="3">
-        <v>5</v>
-      </c>
-      <c r="F41" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="G41" s="3">
-        <v>1</v>
+        <v>195</v>
+      </c>
+      <c r="E41" s="2"/>
+      <c r="F41" s="3">
+        <v>5</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>196</v>
       </c>
       <c r="H41" s="3">
+        <v>1</v>
+      </c>
+      <c r="I41" s="3">
         <v>9999999</v>
       </c>
-      <c r="I41" s="3">
-        <v>0</v>
-      </c>
       <c r="J41" s="3">
-        <v>5</v>
-      </c>
-      <c r="L41" s="3">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="K41" s="3">
+        <v>5</v>
       </c>
       <c r="M41" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" s="3" customFormat="1" customHeight="1" spans="3:13">
+      <c r="N41" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C42" s="3">
         <v>4023</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="E42" s="3">
-        <v>5</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="G42" s="3">
-        <v>1</v>
+        <v>197</v>
+      </c>
+      <c r="E42" s="2"/>
+      <c r="F42" s="3">
+        <v>5</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>198</v>
       </c>
       <c r="H42" s="3">
+        <v>1</v>
+      </c>
+      <c r="I42" s="3">
         <v>9999999</v>
       </c>
-      <c r="I42" s="3">
-        <v>0</v>
-      </c>
       <c r="J42" s="3">
-        <v>5</v>
-      </c>
-      <c r="L42" s="3">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="K42" s="3">
+        <v>5</v>
       </c>
       <c r="M42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" s="3" customFormat="1" customHeight="1" spans="3:13">
+      <c r="N42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C43" s="3">
         <v>4024</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="E43" s="3">
-        <v>5</v>
-      </c>
-      <c r="F43" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="G43" s="3">
-        <v>1</v>
+        <v>199</v>
+      </c>
+      <c r="E43" s="2"/>
+      <c r="F43" s="3">
+        <v>5</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>200</v>
       </c>
       <c r="H43" s="3">
+        <v>1</v>
+      </c>
+      <c r="I43" s="3">
         <v>9999999</v>
       </c>
-      <c r="I43" s="3">
-        <v>0</v>
-      </c>
       <c r="J43" s="3">
+        <v>0</v>
+      </c>
+      <c r="K43" s="3">
         <v>6</v>
       </c>
-      <c r="L43" s="3">
-        <v>0</v>
-      </c>
       <c r="M43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" s="3" customFormat="1" customHeight="1" spans="3:13">
+      <c r="N43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C44" s="3">
         <v>4025</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="E44" s="3">
-        <v>5</v>
-      </c>
-      <c r="F44" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="G44" s="3">
-        <v>1</v>
+        <v>201</v>
+      </c>
+      <c r="E44" s="2"/>
+      <c r="F44" s="3">
+        <v>5</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>202</v>
       </c>
       <c r="H44" s="3">
+        <v>1</v>
+      </c>
+      <c r="I44" s="3">
         <v>9999999</v>
       </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
       <c r="J44" s="3">
+        <v>0</v>
+      </c>
+      <c r="K44" s="3">
         <v>7</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
-      </c>
       <c r="M44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" s="3" customFormat="1" customHeight="1" spans="3:13">
+      <c r="N44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C45" s="3">
         <v>4026</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="E45" s="3">
-        <v>5</v>
-      </c>
-      <c r="F45" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="G45" s="3">
-        <v>1</v>
+        <v>203</v>
+      </c>
+      <c r="E45" s="2"/>
+      <c r="F45" s="3">
+        <v>5</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>204</v>
       </c>
       <c r="H45" s="3">
+        <v>1</v>
+      </c>
+      <c r="I45" s="3">
         <v>9999999</v>
       </c>
-      <c r="I45" s="3">
-        <v>0</v>
-      </c>
       <c r="J45" s="3">
+        <v>0</v>
+      </c>
+      <c r="K45" s="3">
         <v>8</v>
       </c>
-      <c r="L45" s="3">
-        <v>0</v>
-      </c>
       <c r="M45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" s="3" customFormat="1" customHeight="1" spans="3:13">
+      <c r="N45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C46" s="3">
         <v>4027</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="E46" s="3">
-        <v>5</v>
-      </c>
-      <c r="F46" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="G46" s="3">
-        <v>1</v>
+        <v>205</v>
+      </c>
+      <c r="E46" s="2"/>
+      <c r="F46" s="3">
+        <v>5</v>
+      </c>
+      <c r="G46" s="3" t="s">
+        <v>206</v>
       </c>
       <c r="H46" s="3">
+        <v>1</v>
+      </c>
+      <c r="I46" s="3">
         <v>9999999</v>
       </c>
-      <c r="I46" s="3">
-        <v>0</v>
-      </c>
       <c r="J46" s="3">
+        <v>0</v>
+      </c>
+      <c r="K46" s="3">
         <v>7</v>
       </c>
-      <c r="L46" s="3">
-        <v>0</v>
-      </c>
       <c r="M46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" s="3" customFormat="1" customHeight="1" spans="3:13">
+      <c r="N46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C47" s="3">
         <v>4028</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="E47" s="3">
-        <v>5</v>
-      </c>
-      <c r="F47" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="G47" s="3">
-        <v>1</v>
+        <v>207</v>
+      </c>
+      <c r="E47" s="2"/>
+      <c r="F47" s="3">
+        <v>5</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>208</v>
       </c>
       <c r="H47" s="3">
+        <v>1</v>
+      </c>
+      <c r="I47" s="3">
         <v>9999999</v>
       </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
       <c r="J47" s="3">
+        <v>0</v>
+      </c>
+      <c r="K47" s="3">
         <v>7</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
-      </c>
       <c r="M47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" s="3" customFormat="1" customHeight="1" spans="3:13">
+      <c r="N47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C48" s="3">
         <v>4029</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="E48" s="3">
-        <v>5</v>
-      </c>
-      <c r="F48" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="G48" s="3">
-        <v>1</v>
+        <v>209</v>
+      </c>
+      <c r="E48" s="2"/>
+      <c r="F48" s="3">
+        <v>5</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>210</v>
       </c>
       <c r="H48" s="3">
+        <v>1</v>
+      </c>
+      <c r="I48" s="3">
         <v>9999999</v>
       </c>
-      <c r="I48" s="3">
-        <v>0</v>
-      </c>
       <c r="J48" s="3">
+        <v>0</v>
+      </c>
+      <c r="K48" s="3">
         <v>7</v>
       </c>
-      <c r="L48" s="3">
-        <v>0</v>
-      </c>
       <c r="M48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" s="3" customFormat="1" customHeight="1" spans="3:13">
+      <c r="N48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C49" s="3">
         <v>4030</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="E49" s="3">
-        <v>5</v>
-      </c>
-      <c r="F49" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="G49" s="3">
-        <v>1</v>
+        <v>211</v>
+      </c>
+      <c r="E49" s="2"/>
+      <c r="F49" s="3">
+        <v>5</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>212</v>
       </c>
       <c r="H49" s="3">
+        <v>1</v>
+      </c>
+      <c r="I49" s="3">
         <v>9999999</v>
       </c>
-      <c r="I49" s="3">
-        <v>0</v>
-      </c>
       <c r="J49" s="3">
+        <v>0</v>
+      </c>
+      <c r="K49" s="3">
         <v>7</v>
       </c>
-      <c r="L49" s="3">
-        <v>0</v>
-      </c>
       <c r="M49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" s="3" customFormat="1" customHeight="1" spans="3:13">
+      <c r="N49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C50" s="3">
         <v>4031</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="E50" s="3">
-        <v>5</v>
-      </c>
-      <c r="F50" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="G50" s="3">
-        <v>1</v>
+        <v>213</v>
+      </c>
+      <c r="E50" s="2"/>
+      <c r="F50" s="3">
+        <v>5</v>
+      </c>
+      <c r="G50" s="3" t="s">
+        <v>214</v>
       </c>
       <c r="H50" s="3">
+        <v>1</v>
+      </c>
+      <c r="I50" s="3">
         <v>9999999</v>
       </c>
-      <c r="I50" s="3">
-        <v>0</v>
-      </c>
       <c r="J50" s="3">
+        <v>0</v>
+      </c>
+      <c r="K50" s="3">
         <v>7</v>
       </c>
-      <c r="L50" s="3">
-        <v>0</v>
-      </c>
       <c r="M50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" s="3" customFormat="1" customHeight="1" spans="3:13">
+      <c r="N50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C51" s="3">
         <v>4032</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="E51" s="3">
-        <v>5</v>
-      </c>
-      <c r="F51" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="G51" s="3">
-        <v>1</v>
+        <v>215</v>
+      </c>
+      <c r="E51" s="2"/>
+      <c r="F51" s="3">
+        <v>5</v>
+      </c>
+      <c r="G51" s="3" t="s">
+        <v>216</v>
       </c>
       <c r="H51" s="3">
+        <v>1</v>
+      </c>
+      <c r="I51" s="3">
         <v>9999999</v>
       </c>
-      <c r="I51" s="3">
-        <v>0</v>
-      </c>
       <c r="J51" s="3">
+        <v>0</v>
+      </c>
+      <c r="K51" s="3">
         <v>7</v>
       </c>
-      <c r="L51" s="3">
-        <v>0</v>
-      </c>
       <c r="M51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" s="3" customFormat="1" customHeight="1" spans="3:13">
+      <c r="N51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C52" s="3">
         <v>4033</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="E52" s="3">
-        <v>5</v>
-      </c>
-      <c r="F52" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="G52" s="3">
-        <v>1</v>
+        <v>217</v>
+      </c>
+      <c r="E52" s="2"/>
+      <c r="F52" s="3">
+        <v>5</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>186</v>
       </c>
       <c r="H52" s="3">
+        <v>1</v>
+      </c>
+      <c r="I52" s="3">
         <v>9999999</v>
       </c>
-      <c r="I52" s="3">
-        <v>0</v>
-      </c>
       <c r="J52" s="3">
+        <v>0</v>
+      </c>
+      <c r="K52" s="3">
         <v>6</v>
       </c>
-      <c r="L52" s="3">
-        <v>0</v>
-      </c>
       <c r="M52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" s="3" customFormat="1" customHeight="1" spans="3:13">
+      <c r="N52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C53" s="3">
         <v>4034</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="E53" s="3">
-        <v>5</v>
-      </c>
-      <c r="F53" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="G53" s="3">
-        <v>1</v>
+        <v>218</v>
+      </c>
+      <c r="E53" s="2"/>
+      <c r="F53" s="3">
+        <v>5</v>
+      </c>
+      <c r="G53" s="3" t="s">
+        <v>219</v>
       </c>
       <c r="H53" s="3">
+        <v>1</v>
+      </c>
+      <c r="I53" s="3">
         <v>9999999</v>
       </c>
-      <c r="I53" s="3">
-        <v>0</v>
-      </c>
       <c r="J53" s="3">
+        <v>0</v>
+      </c>
+      <c r="K53" s="3">
         <v>8</v>
       </c>
-      <c r="L53" s="3">
-        <v>0</v>
-      </c>
       <c r="M53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" s="3" customFormat="1" customHeight="1" spans="3:13">
+      <c r="N53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C54" s="3">
         <v>4035</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="E54" s="3">
-        <v>5</v>
-      </c>
-      <c r="F54" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="G54" s="3">
-        <v>1</v>
+        <v>220</v>
+      </c>
+      <c r="E54" s="2"/>
+      <c r="F54" s="3">
+        <v>5</v>
+      </c>
+      <c r="G54" s="3" t="s">
+        <v>221</v>
       </c>
       <c r="H54" s="3">
+        <v>1</v>
+      </c>
+      <c r="I54" s="3">
         <v>9999999</v>
       </c>
-      <c r="I54" s="3">
-        <v>0</v>
-      </c>
       <c r="J54" s="3">
+        <v>0</v>
+      </c>
+      <c r="K54" s="3">
         <v>7</v>
       </c>
-      <c r="L54" s="3">
-        <v>0</v>
-      </c>
       <c r="M54" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="55" s="3" customFormat="1" customHeight="1" spans="3:13">
+      <c r="N54" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C55" s="3">
         <v>4037</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="E55" s="3">
-        <v>5</v>
-      </c>
-      <c r="F55" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="G55" s="3">
-        <v>1</v>
+        <v>222</v>
+      </c>
+      <c r="E55" s="2"/>
+      <c r="F55" s="3">
+        <v>5</v>
+      </c>
+      <c r="G55" s="3" t="s">
+        <v>223</v>
       </c>
       <c r="H55" s="3">
+        <v>1</v>
+      </c>
+      <c r="I55" s="3">
         <v>9999999</v>
       </c>
-      <c r="I55" s="3">
-        <v>0</v>
-      </c>
       <c r="J55" s="3">
+        <v>0</v>
+      </c>
+      <c r="K55" s="3">
         <v>9</v>
       </c>
-      <c r="L55" s="3">
-        <v>0</v>
-      </c>
       <c r="M55" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="56" s="3" customFormat="1" customHeight="1" spans="3:13">
+      <c r="N55" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C56" s="3">
         <v>4038</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="E56" s="3">
-        <v>5</v>
-      </c>
-      <c r="F56" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="G56" s="3">
-        <v>1</v>
+        <v>224</v>
+      </c>
+      <c r="E56" s="2"/>
+      <c r="F56" s="3">
+        <v>5</v>
+      </c>
+      <c r="G56" s="3" t="s">
+        <v>225</v>
       </c>
       <c r="H56" s="3">
+        <v>1</v>
+      </c>
+      <c r="I56" s="3">
         <v>9999999</v>
       </c>
-      <c r="I56" s="3">
-        <v>0</v>
-      </c>
       <c r="J56" s="3">
+        <v>0</v>
+      </c>
+      <c r="K56" s="3">
         <v>9</v>
       </c>
-      <c r="L56" s="3">
-        <v>0</v>
-      </c>
       <c r="M56" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="57" s="3" customFormat="1" customHeight="1" spans="3:13">
+      <c r="N56" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C57" s="3">
         <v>4039</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="E57" s="3">
-        <v>5</v>
-      </c>
-      <c r="F57" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="G57" s="3">
-        <v>1</v>
+        <v>226</v>
+      </c>
+      <c r="E57" s="2"/>
+      <c r="F57" s="3">
+        <v>5</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>227</v>
       </c>
       <c r="H57" s="3">
+        <v>1</v>
+      </c>
+      <c r="I57" s="3">
         <v>9999999</v>
       </c>
-      <c r="I57" s="3">
-        <v>0</v>
-      </c>
       <c r="J57" s="3">
+        <v>0</v>
+      </c>
+      <c r="K57" s="3">
         <v>8</v>
       </c>
-      <c r="L57" s="3">
-        <v>0</v>
-      </c>
       <c r="M57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" s="3" customFormat="1" customHeight="1" spans="3:13">
+      <c r="N57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C58" s="3">
         <v>4040</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="E58" s="3">
-        <v>5</v>
-      </c>
-      <c r="F58" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="G58" s="3">
-        <v>1</v>
+        <v>228</v>
+      </c>
+      <c r="E58" s="2"/>
+      <c r="F58" s="3">
+        <v>5</v>
+      </c>
+      <c r="G58" s="3" t="s">
+        <v>186</v>
       </c>
       <c r="H58" s="3">
+        <v>1</v>
+      </c>
+      <c r="I58" s="3">
         <v>9999999</v>
       </c>
-      <c r="I58" s="3">
-        <v>0</v>
-      </c>
       <c r="J58" s="3">
+        <v>0</v>
+      </c>
+      <c r="K58" s="3">
         <v>6</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
       <c r="M58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" s="3" customFormat="1" customHeight="1" spans="3:13">
+      <c r="N58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C59" s="3">
         <v>4041</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="E59" s="3">
-        <v>5</v>
-      </c>
-      <c r="F59" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="G59" s="3">
-        <v>1</v>
+        <v>229</v>
+      </c>
+      <c r="E59" s="2"/>
+      <c r="F59" s="3">
+        <v>5</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>230</v>
       </c>
       <c r="H59" s="3">
+        <v>1</v>
+      </c>
+      <c r="I59" s="3">
         <v>9999999</v>
       </c>
-      <c r="I59" s="3">
-        <v>0</v>
-      </c>
       <c r="J59" s="3">
+        <v>0</v>
+      </c>
+      <c r="K59" s="3">
         <v>8</v>
       </c>
-      <c r="L59" s="3">
-        <v>0</v>
-      </c>
       <c r="M59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" s="3" customFormat="1" customHeight="1" spans="3:13">
+      <c r="N59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C60" s="3">
         <v>4042</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="E60" s="3">
-        <v>5</v>
-      </c>
-      <c r="F60" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="G60" s="3">
-        <v>1</v>
+        <v>231</v>
+      </c>
+      <c r="E60" s="2"/>
+      <c r="F60" s="3">
+        <v>5</v>
+      </c>
+      <c r="G60" s="3" t="s">
+        <v>232</v>
       </c>
       <c r="H60" s="3">
+        <v>1</v>
+      </c>
+      <c r="I60" s="3">
         <v>1999999999</v>
       </c>
-      <c r="I60" s="3">
-        <v>0</v>
-      </c>
       <c r="J60" s="3">
-        <v>5</v>
-      </c>
-      <c r="L60" s="3">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="K60" s="3">
+        <v>5</v>
       </c>
       <c r="M60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" s="3" customFormat="1" customHeight="1" spans="3:13">
+      <c r="N60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C61" s="3">
         <v>4043</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="E61" s="3">
-        <v>5</v>
-      </c>
-      <c r="F61" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="G61" s="3">
-        <v>1</v>
+        <v>233</v>
+      </c>
+      <c r="E61" s="2"/>
+      <c r="F61" s="3">
+        <v>5</v>
+      </c>
+      <c r="G61" s="3" t="s">
+        <v>232</v>
       </c>
       <c r="H61" s="3">
+        <v>1</v>
+      </c>
+      <c r="I61" s="3">
         <v>9999999</v>
       </c>
-      <c r="I61" s="3">
-        <v>0</v>
-      </c>
       <c r="J61" s="3">
+        <v>0</v>
+      </c>
+      <c r="K61" s="3">
         <v>7</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" s="3" customFormat="1" customHeight="1" spans="3:13">
+      <c r="N61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C62" s="3">
         <v>4044</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>230</v>
-      </c>
-      <c r="E62" s="3">
-        <v>5</v>
-      </c>
-      <c r="F62" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="G62" s="3">
-        <v>1</v>
+        <v>234</v>
+      </c>
+      <c r="E62" s="2"/>
+      <c r="F62" s="3">
+        <v>5</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>235</v>
       </c>
       <c r="H62" s="3">
+        <v>1</v>
+      </c>
+      <c r="I62" s="3">
         <v>9999999</v>
       </c>
-      <c r="I62" s="3">
-        <v>0</v>
-      </c>
       <c r="J62" s="3">
+        <v>0</v>
+      </c>
+      <c r="K62" s="3">
         <v>9</v>
       </c>
-      <c r="L62" s="3">
-        <v>0</v>
-      </c>
       <c r="M62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" customFormat="1" customHeight="1" spans="3:13">
+      <c r="N62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" customFormat="1" customHeight="1" spans="3:14">
       <c r="C63" s="3"/>
       <c r="D63" s="3"/>
-      <c r="E63" s="3"/>
+      <c r="E63" s="2"/>
       <c r="F63" s="3"/>
       <c r="G63" s="3"/>
       <c r="H63" s="3"/>
       <c r="I63" s="3"/>
       <c r="J63" s="3"/>
-      <c r="L63" s="3"/>
+      <c r="K63" s="3"/>
       <c r="M63" s="3"/>
-    </row>
-    <row r="64" s="3" customFormat="1" customHeight="1" spans="3:13">
+      <c r="N63" s="3"/>
+    </row>
+    <row r="64" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C64" s="3">
         <v>4101</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="E64" s="3">
-        <v>5</v>
-      </c>
-      <c r="F64" s="3" t="s">
-        <v>233</v>
-      </c>
-      <c r="G64" s="3">
-        <v>1</v>
+        <v>236</v>
+      </c>
+      <c r="E64" s="2"/>
+      <c r="F64" s="3">
+        <v>5</v>
+      </c>
+      <c r="G64" s="3" t="s">
+        <v>237</v>
       </c>
       <c r="H64" s="3">
+        <v>1</v>
+      </c>
+      <c r="I64" s="3">
         <v>9999999</v>
       </c>
-      <c r="I64" s="3">
-        <v>0</v>
-      </c>
       <c r="J64" s="3">
-        <v>5</v>
-      </c>
-      <c r="L64" s="3">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="K64" s="3">
+        <v>5</v>
       </c>
       <c r="M64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" s="3" customFormat="1" customHeight="1" spans="3:13">
+      <c r="N64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C65" s="3">
         <v>4111</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>234</v>
-      </c>
-      <c r="E65" s="3">
-        <v>5</v>
-      </c>
-      <c r="F65" s="3" t="s">
-        <v>235</v>
-      </c>
-      <c r="G65" s="3">
-        <v>1</v>
+        <v>238</v>
+      </c>
+      <c r="E65" s="2"/>
+      <c r="F65" s="3">
+        <v>5</v>
+      </c>
+      <c r="G65" s="3" t="s">
+        <v>239</v>
       </c>
       <c r="H65" s="3">
+        <v>1</v>
+      </c>
+      <c r="I65" s="3">
         <v>9999999</v>
       </c>
-      <c r="I65" s="3">
-        <v>0</v>
-      </c>
       <c r="J65" s="3">
-        <v>5</v>
-      </c>
-      <c r="L65" s="3">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="K65" s="3">
+        <v>5</v>
       </c>
       <c r="M65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" s="3" customFormat="1" customHeight="1" spans="3:13">
+      <c r="N65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C66" s="3">
         <v>4112</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>236</v>
-      </c>
-      <c r="E66" s="3">
-        <v>5</v>
-      </c>
-      <c r="F66" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="G66" s="3">
-        <v>1</v>
+        <v>240</v>
+      </c>
+      <c r="E66" s="2"/>
+      <c r="F66" s="3">
+        <v>5</v>
+      </c>
+      <c r="G66" s="3" t="s">
+        <v>241</v>
       </c>
       <c r="H66" s="3">
+        <v>1</v>
+      </c>
+      <c r="I66" s="3">
         <v>9999999</v>
       </c>
-      <c r="I66" s="3">
-        <v>0</v>
-      </c>
       <c r="J66" s="3">
+        <v>0</v>
+      </c>
+      <c r="K66" s="3">
         <v>8</v>
       </c>
-      <c r="L66" s="3">
-        <v>0</v>
-      </c>
       <c r="M66" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="67" s="3" customFormat="1" customHeight="1" spans="3:13">
+      <c r="N66" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C67" s="3">
         <v>4113</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="E67" s="3">
-        <v>5</v>
-      </c>
-      <c r="F67" s="3" t="s">
-        <v>239</v>
-      </c>
-      <c r="G67" s="3">
-        <v>1</v>
+        <v>242</v>
+      </c>
+      <c r="E67" s="2"/>
+      <c r="F67" s="3">
+        <v>5</v>
+      </c>
+      <c r="G67" s="3" t="s">
+        <v>243</v>
       </c>
       <c r="H67" s="3">
+        <v>1</v>
+      </c>
+      <c r="I67" s="3">
         <v>9999999</v>
       </c>
-      <c r="I67" s="3">
-        <v>0</v>
-      </c>
       <c r="J67" s="3">
+        <v>0</v>
+      </c>
+      <c r="K67" s="3">
         <v>7</v>
       </c>
-      <c r="L67" s="3">
-        <v>0</v>
-      </c>
       <c r="M67" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="68" customFormat="1" customHeight="1" spans="3:13">
+      <c r="N67" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" customFormat="1" customHeight="1" spans="3:14">
       <c r="C68" s="3"/>
       <c r="D68" s="3"/>
-      <c r="E68" s="3"/>
+      <c r="E68" s="2"/>
       <c r="F68" s="3"/>
       <c r="G68" s="3"/>
       <c r="H68" s="3"/>
       <c r="I68" s="3"/>
       <c r="J68" s="3"/>
-      <c r="L68" s="3"/>
+      <c r="K68" s="3"/>
       <c r="M68" s="3"/>
-    </row>
-    <row r="69" s="3" customFormat="1" customHeight="1" spans="3:13">
+      <c r="N68" s="3"/>
+    </row>
+    <row r="69" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C69" s="3">
         <v>4201</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="E69" s="3">
-        <v>5</v>
-      </c>
-      <c r="F69" s="3" t="s">
-        <v>241</v>
-      </c>
-      <c r="G69" s="3">
-        <v>1</v>
+        <v>244</v>
+      </c>
+      <c r="E69" s="2"/>
+      <c r="F69" s="3">
+        <v>5</v>
+      </c>
+      <c r="G69" s="3" t="s">
+        <v>245</v>
       </c>
       <c r="H69" s="3">
+        <v>1</v>
+      </c>
+      <c r="I69" s="3">
         <v>99999999</v>
       </c>
-      <c r="I69" s="3">
-        <v>0</v>
-      </c>
       <c r="J69" s="3">
-        <v>5</v>
-      </c>
-      <c r="L69" s="3">
+        <v>0</v>
+      </c>
+      <c r="K69" s="3">
+        <v>5</v>
+      </c>
+      <c r="M69" s="3">
         <v>4002</v>
       </c>
-      <c r="M69" s="3">
+      <c r="N69" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="74" s="3" customFormat="1" customHeight="1" spans="3:13">
+    <row r="74" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C74" s="3">
         <v>8001</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="E74" s="3">
-        <v>5</v>
-      </c>
-      <c r="F74" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="G74" s="3">
-        <v>1</v>
+        <v>246</v>
+      </c>
+      <c r="E74" s="2"/>
+      <c r="F74" s="3">
+        <v>5</v>
+      </c>
+      <c r="G74" s="3" t="s">
+        <v>247</v>
       </c>
       <c r="H74" s="3">
+        <v>1</v>
+      </c>
+      <c r="I74" s="3">
         <v>9999999</v>
       </c>
-      <c r="I74" s="3">
-        <v>0</v>
-      </c>
       <c r="J74" s="3">
+        <v>0</v>
+      </c>
+      <c r="K74" s="3">
         <v>6</v>
       </c>
-      <c r="L74" s="3">
-        <v>0</v>
-      </c>
       <c r="M74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" s="3" customFormat="1" customHeight="1" spans="3:13">
+      <c r="N74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C75" s="3">
         <v>8002</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>244</v>
-      </c>
-      <c r="E75" s="3">
-        <v>5</v>
-      </c>
-      <c r="F75" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="G75" s="3">
-        <v>1</v>
+        <v>248</v>
+      </c>
+      <c r="E75" s="2"/>
+      <c r="F75" s="3">
+        <v>5</v>
+      </c>
+      <c r="G75" s="3" t="s">
+        <v>247</v>
       </c>
       <c r="H75" s="3">
+        <v>1</v>
+      </c>
+      <c r="I75" s="3">
         <v>9999999</v>
       </c>
-      <c r="I75" s="3">
-        <v>0</v>
-      </c>
       <c r="J75" s="3">
+        <v>0</v>
+      </c>
+      <c r="K75" s="3">
         <v>6</v>
       </c>
-      <c r="L75" s="3">
-        <v>0</v>
-      </c>
       <c r="M75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" s="3" customFormat="1" customHeight="1" spans="3:13">
+      <c r="N75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C76" s="3">
         <v>8003</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="E76" s="3">
-        <v>5</v>
-      </c>
-      <c r="F76" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="G76" s="3">
-        <v>1</v>
+        <v>249</v>
+      </c>
+      <c r="E76" s="2"/>
+      <c r="F76" s="3">
+        <v>5</v>
+      </c>
+      <c r="G76" s="3" t="s">
+        <v>247</v>
       </c>
       <c r="H76" s="3">
+        <v>1</v>
+      </c>
+      <c r="I76" s="3">
         <v>9999999</v>
       </c>
-      <c r="I76" s="3">
-        <v>0</v>
-      </c>
       <c r="J76" s="3">
+        <v>0</v>
+      </c>
+      <c r="K76" s="3">
         <v>6</v>
       </c>
-      <c r="L76" s="3">
-        <v>0</v>
-      </c>
       <c r="M76" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="77" s="3" customFormat="1" customHeight="1" spans="3:13">
+      <c r="N76" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C77" s="3">
         <v>8004</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>246</v>
-      </c>
-      <c r="E77" s="3">
-        <v>5</v>
-      </c>
-      <c r="F77" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="G77" s="3">
-        <v>1</v>
+        <v>250</v>
+      </c>
+      <c r="E77" s="2"/>
+      <c r="F77" s="3">
+        <v>5</v>
+      </c>
+      <c r="G77" s="3" t="s">
+        <v>247</v>
       </c>
       <c r="H77" s="3">
+        <v>1</v>
+      </c>
+      <c r="I77" s="3">
         <v>9999999</v>
       </c>
-      <c r="I77" s="3">
-        <v>0</v>
-      </c>
       <c r="J77" s="3">
+        <v>0</v>
+      </c>
+      <c r="K77" s="3">
         <v>6</v>
       </c>
-      <c r="L77" s="3">
-        <v>0</v>
-      </c>
       <c r="M77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="78" s="3" customFormat="1" customHeight="1" spans="3:13">
+      <c r="N77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C78" s="3">
         <v>8005</v>
       </c>
       <c r="D78" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="E78" s="2"/>
+      <c r="F78" s="3">
+        <v>5</v>
+      </c>
+      <c r="G78" s="3" t="s">
         <v>247</v>
       </c>
-      <c r="E78" s="3">
-        <v>5</v>
-      </c>
-      <c r="F78" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="G78" s="3">
-        <v>1</v>
-      </c>
       <c r="H78" s="3">
+        <v>1</v>
+      </c>
+      <c r="I78" s="3">
         <v>9999999</v>
       </c>
-      <c r="I78" s="3">
-        <v>0</v>
-      </c>
       <c r="J78" s="3">
+        <v>0</v>
+      </c>
+      <c r="K78" s="3">
         <v>6</v>
       </c>
-      <c r="L78" s="3">
-        <v>0</v>
-      </c>
       <c r="M78" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" s="3" customFormat="1" customHeight="1" spans="3:13">
+      <c r="N78" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C79" s="3">
         <v>8006</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="E79" s="3">
-        <v>5</v>
-      </c>
-      <c r="F79" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="G79" s="3">
-        <v>1</v>
+        <v>252</v>
+      </c>
+      <c r="E79" s="2"/>
+      <c r="F79" s="3">
+        <v>5</v>
+      </c>
+      <c r="G79" s="3" t="s">
+        <v>247</v>
       </c>
       <c r="H79" s="3">
+        <v>1</v>
+      </c>
+      <c r="I79" s="3">
         <v>9999999</v>
       </c>
-      <c r="I79" s="3">
-        <v>0</v>
-      </c>
       <c r="J79" s="3">
+        <v>0</v>
+      </c>
+      <c r="K79" s="3">
         <v>6</v>
       </c>
-      <c r="L79" s="3">
-        <v>0</v>
-      </c>
       <c r="M79" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="80" s="3" customFormat="1" customHeight="1" spans="3:13">
+      <c r="N79" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C80" s="3">
         <v>8007</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="E80" s="3">
-        <v>5</v>
-      </c>
-      <c r="F80" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="G80" s="3">
-        <v>1</v>
+        <v>253</v>
+      </c>
+      <c r="E80" s="2"/>
+      <c r="F80" s="3">
+        <v>5</v>
+      </c>
+      <c r="G80" s="3" t="s">
+        <v>247</v>
       </c>
       <c r="H80" s="3">
+        <v>1</v>
+      </c>
+      <c r="I80" s="3">
         <v>9999999</v>
       </c>
-      <c r="I80" s="3">
-        <v>0</v>
-      </c>
       <c r="J80" s="3">
+        <v>0</v>
+      </c>
+      <c r="K80" s="3">
         <v>6</v>
       </c>
-      <c r="L80" s="3">
-        <v>0</v>
-      </c>
       <c r="M80" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="81" s="3" customFormat="1" customHeight="1" spans="3:13">
+      <c r="N80" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C81" s="3">
         <v>8008</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="E81" s="3">
-        <v>5</v>
-      </c>
-      <c r="F81" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="G81" s="3">
-        <v>1</v>
+        <v>254</v>
+      </c>
+      <c r="E81" s="2"/>
+      <c r="F81" s="3">
+        <v>5</v>
+      </c>
+      <c r="G81" s="3" t="s">
+        <v>247</v>
       </c>
       <c r="H81" s="3">
+        <v>1</v>
+      </c>
+      <c r="I81" s="3">
         <v>9999999</v>
       </c>
-      <c r="I81" s="3">
-        <v>0</v>
-      </c>
       <c r="J81" s="3">
+        <v>0</v>
+      </c>
+      <c r="K81" s="3">
         <v>6</v>
       </c>
-      <c r="L81" s="3">
-        <v>0</v>
-      </c>
       <c r="M81" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="82" s="3" customFormat="1" customHeight="1" spans="3:13">
+      <c r="N81" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C82" s="3">
         <v>8009</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>251</v>
-      </c>
-      <c r="E82" s="3">
-        <v>5</v>
-      </c>
-      <c r="F82" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="G82" s="3">
-        <v>1</v>
+        <v>255</v>
+      </c>
+      <c r="E82" s="2"/>
+      <c r="F82" s="3">
+        <v>5</v>
+      </c>
+      <c r="G82" s="3" t="s">
+        <v>247</v>
       </c>
       <c r="H82" s="3">
+        <v>1</v>
+      </c>
+      <c r="I82" s="3">
         <v>9999999</v>
       </c>
-      <c r="I82" s="3">
-        <v>0</v>
-      </c>
       <c r="J82" s="3">
+        <v>0</v>
+      </c>
+      <c r="K82" s="3">
         <v>6</v>
       </c>
-      <c r="L82" s="3">
-        <v>0</v>
-      </c>
       <c r="M82" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="83" s="3" customFormat="1" customHeight="1" spans="3:13">
+      <c r="N82" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C83" s="3">
         <v>8010</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="E83" s="3">
-        <v>5</v>
-      </c>
-      <c r="F83" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="G83" s="3">
-        <v>1</v>
+        <v>256</v>
+      </c>
+      <c r="E83" s="2"/>
+      <c r="F83" s="3">
+        <v>5</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>247</v>
       </c>
       <c r="H83" s="3">
+        <v>1</v>
+      </c>
+      <c r="I83" s="3">
         <v>9999999</v>
       </c>
-      <c r="I83" s="3">
-        <v>0</v>
-      </c>
       <c r="J83" s="3">
+        <v>0</v>
+      </c>
+      <c r="K83" s="3">
         <v>6</v>
       </c>
-      <c r="L83" s="3">
-        <v>0</v>
-      </c>
       <c r="M83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" s="3" customFormat="1" customHeight="1" spans="3:13">
+      <c r="N83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C85" s="3">
         <v>8101</v>
       </c>
       <c r="D85" s="9" t="s">
-        <v>253</v>
-      </c>
-      <c r="E85" s="3">
-        <v>5</v>
-      </c>
-      <c r="F85" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="G85" s="3">
-        <v>1</v>
+        <v>257</v>
+      </c>
+      <c r="E85" s="2"/>
+      <c r="F85" s="3">
+        <v>5</v>
+      </c>
+      <c r="G85" s="3" t="s">
+        <v>258</v>
       </c>
       <c r="H85" s="3">
+        <v>1</v>
+      </c>
+      <c r="I85" s="3">
         <v>9999999</v>
       </c>
-      <c r="I85" s="3">
-        <v>0</v>
-      </c>
       <c r="J85" s="3">
+        <v>0</v>
+      </c>
+      <c r="K85" s="3">
         <v>7</v>
       </c>
-      <c r="L85" s="3">
-        <v>0</v>
-      </c>
       <c r="M85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" s="3" customFormat="1" customHeight="1" spans="3:13">
+      <c r="N85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C86" s="3">
         <v>8102</v>
       </c>
       <c r="D86" s="9" t="s">
-        <v>255</v>
-      </c>
-      <c r="E86" s="3">
-        <v>5</v>
-      </c>
-      <c r="F86" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="G86" s="3">
-        <v>1</v>
+        <v>259</v>
+      </c>
+      <c r="E86" s="2"/>
+      <c r="F86" s="3">
+        <v>5</v>
+      </c>
+      <c r="G86" s="3" t="s">
+        <v>258</v>
       </c>
       <c r="H86" s="3">
+        <v>1</v>
+      </c>
+      <c r="I86" s="3">
         <v>9999999</v>
       </c>
-      <c r="I86" s="3">
-        <v>0</v>
-      </c>
       <c r="J86" s="3">
+        <v>0</v>
+      </c>
+      <c r="K86" s="3">
         <v>7</v>
       </c>
-      <c r="L86" s="3">
-        <v>0</v>
-      </c>
       <c r="M86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" s="3" customFormat="1" customHeight="1" spans="3:13">
+      <c r="N86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C87" s="3">
         <v>8103</v>
       </c>
       <c r="D87" s="9" t="s">
-        <v>256</v>
-      </c>
-      <c r="E87" s="3">
-        <v>5</v>
-      </c>
-      <c r="F87" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="G87" s="3">
-        <v>1</v>
+        <v>260</v>
+      </c>
+      <c r="E87" s="2"/>
+      <c r="F87" s="3">
+        <v>5</v>
+      </c>
+      <c r="G87" s="3" t="s">
+        <v>258</v>
       </c>
       <c r="H87" s="3">
+        <v>1</v>
+      </c>
+      <c r="I87" s="3">
         <v>9999999</v>
       </c>
-      <c r="I87" s="3">
-        <v>0</v>
-      </c>
       <c r="J87" s="3">
+        <v>0</v>
+      </c>
+      <c r="K87" s="3">
         <v>7</v>
       </c>
-      <c r="L87" s="3">
-        <v>0</v>
-      </c>
       <c r="M87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" s="3" customFormat="1" customHeight="1" spans="3:13">
+      <c r="N87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C88" s="3">
         <v>8104</v>
       </c>
       <c r="D88" s="9" t="s">
-        <v>257</v>
-      </c>
-      <c r="E88" s="3">
-        <v>5</v>
-      </c>
-      <c r="F88" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="G88" s="3">
-        <v>1</v>
+        <v>261</v>
+      </c>
+      <c r="E88" s="2"/>
+      <c r="F88" s="3">
+        <v>5</v>
+      </c>
+      <c r="G88" s="3" t="s">
+        <v>258</v>
       </c>
       <c r="H88" s="3">
+        <v>1</v>
+      </c>
+      <c r="I88" s="3">
         <v>9999999</v>
       </c>
-      <c r="I88" s="3">
-        <v>0</v>
-      </c>
       <c r="J88" s="3">
+        <v>0</v>
+      </c>
+      <c r="K88" s="3">
         <v>7</v>
       </c>
-      <c r="L88" s="3">
-        <v>0</v>
-      </c>
       <c r="M88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" s="3" customFormat="1" customHeight="1" spans="3:13">
+      <c r="N88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C89" s="3">
         <v>8105</v>
       </c>
       <c r="D89" s="9" t="s">
+        <v>262</v>
+      </c>
+      <c r="E89" s="2"/>
+      <c r="F89" s="3">
+        <v>5</v>
+      </c>
+      <c r="G89" s="3" t="s">
         <v>258</v>
       </c>
-      <c r="E89" s="3">
-        <v>5</v>
-      </c>
-      <c r="F89" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="G89" s="3">
-        <v>1</v>
-      </c>
       <c r="H89" s="3">
+        <v>1</v>
+      </c>
+      <c r="I89" s="3">
         <v>9999999</v>
       </c>
-      <c r="I89" s="3">
-        <v>0</v>
-      </c>
       <c r="J89" s="3">
+        <v>0</v>
+      </c>
+      <c r="K89" s="3">
         <v>7</v>
       </c>
-      <c r="L89" s="3">
-        <v>0</v>
-      </c>
       <c r="M89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" s="3" customFormat="1" customHeight="1" spans="3:13">
+      <c r="N89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C90" s="3">
         <v>8106</v>
       </c>
       <c r="D90" s="9" t="s">
-        <v>259</v>
-      </c>
-      <c r="E90" s="3">
-        <v>5</v>
-      </c>
-      <c r="F90" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="G90" s="3">
-        <v>1</v>
+        <v>263</v>
+      </c>
+      <c r="E90" s="2"/>
+      <c r="F90" s="3">
+        <v>5</v>
+      </c>
+      <c r="G90" s="3" t="s">
+        <v>258</v>
       </c>
       <c r="H90" s="3">
+        <v>1</v>
+      </c>
+      <c r="I90" s="3">
         <v>9999999</v>
       </c>
-      <c r="I90" s="3">
-        <v>0</v>
-      </c>
       <c r="J90" s="3">
+        <v>0</v>
+      </c>
+      <c r="K90" s="3">
         <v>7</v>
       </c>
-      <c r="L90" s="3">
-        <v>0</v>
-      </c>
       <c r="M90" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="91" s="3" customFormat="1" customHeight="1" spans="3:13">
+      <c r="N90" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C91" s="3">
         <v>8107</v>
       </c>
       <c r="D91" s="9" t="s">
-        <v>260</v>
-      </c>
-      <c r="E91" s="3">
-        <v>5</v>
-      </c>
-      <c r="F91" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="G91" s="3">
-        <v>1</v>
+        <v>264</v>
+      </c>
+      <c r="E91" s="2"/>
+      <c r="F91" s="3">
+        <v>5</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>258</v>
       </c>
       <c r="H91" s="3">
+        <v>1</v>
+      </c>
+      <c r="I91" s="3">
         <v>9999999</v>
       </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
       <c r="J91" s="3">
+        <v>0</v>
+      </c>
+      <c r="K91" s="3">
         <v>7</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
-      </c>
       <c r="M91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" s="3" customFormat="1" customHeight="1" spans="3:13">
+      <c r="N91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C92" s="3">
         <v>8108</v>
       </c>
       <c r="D92" s="9" t="s">
-        <v>261</v>
-      </c>
-      <c r="E92" s="3">
-        <v>5</v>
-      </c>
-      <c r="F92" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="G92" s="3">
-        <v>1</v>
+        <v>265</v>
+      </c>
+      <c r="E92" s="2"/>
+      <c r="F92" s="3">
+        <v>5</v>
+      </c>
+      <c r="G92" s="3" t="s">
+        <v>258</v>
       </c>
       <c r="H92" s="3">
+        <v>1</v>
+      </c>
+      <c r="I92" s="3">
         <v>9999999</v>
       </c>
-      <c r="I92" s="3">
-        <v>0</v>
-      </c>
       <c r="J92" s="3">
+        <v>0</v>
+      </c>
+      <c r="K92" s="3">
         <v>7</v>
       </c>
-      <c r="L92" s="3">
-        <v>0</v>
-      </c>
       <c r="M92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" customHeight="1" spans="3:13">
+      <c r="N92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" customHeight="1" spans="3:14">
       <c r="C94" s="3">
         <v>8201</v>
       </c>
       <c r="D94" s="9" t="s">
-        <v>262</v>
-      </c>
-      <c r="E94" s="3">
+        <v>266</v>
+      </c>
+      <c r="E94" s="2"/>
+      <c r="F94" s="3">
         <v>16</v>
       </c>
-      <c r="F94" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="G94" s="3">
-        <v>1</v>
+      <c r="G94" s="3" t="s">
+        <v>267</v>
       </c>
       <c r="H94" s="3">
         <v>1</v>
       </c>
       <c r="I94" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J94" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K94" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L94" s="3">
         <v>0</v>
@@ -6245,139 +6474,143 @@
       <c r="M94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" customHeight="1" spans="3:13">
+      <c r="N94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" customHeight="1" spans="3:14">
       <c r="C95" s="3">
         <v>8202</v>
       </c>
       <c r="D95" s="9" t="s">
-        <v>264</v>
-      </c>
-      <c r="E95" s="3">
+        <v>268</v>
+      </c>
+      <c r="E95" s="2"/>
+      <c r="F95" s="3">
         <v>16</v>
       </c>
-      <c r="F95" s="3" t="s">
-        <v>265</v>
-      </c>
-      <c r="G95" s="3">
-        <v>1</v>
+      <c r="G95" s="3" t="s">
+        <v>269</v>
       </c>
       <c r="H95" s="3">
         <v>1</v>
       </c>
       <c r="I95" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J95" s="3">
+        <v>0</v>
+      </c>
+      <c r="K95" s="3">
         <v>2</v>
       </c>
-      <c r="K95" s="3">
-        <v>0</v>
-      </c>
       <c r="L95" s="3">
         <v>0</v>
       </c>
       <c r="M95" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="96" customHeight="1" spans="3:13">
+      <c r="N95" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" customHeight="1" spans="3:14">
       <c r="C96" s="3">
         <v>8203</v>
       </c>
       <c r="D96" s="9" t="s">
-        <v>266</v>
-      </c>
-      <c r="E96" s="3">
+        <v>270</v>
+      </c>
+      <c r="E96" s="2"/>
+      <c r="F96" s="3">
         <v>16</v>
       </c>
-      <c r="F96" s="3" t="s">
-        <v>267</v>
-      </c>
-      <c r="G96" s="3">
-        <v>1</v>
+      <c r="G96" s="3" t="s">
+        <v>271</v>
       </c>
       <c r="H96" s="3">
         <v>1</v>
       </c>
       <c r="I96" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J96" s="3">
+        <v>0</v>
+      </c>
+      <c r="K96" s="3">
         <v>3</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
       <c r="L96" s="3">
         <v>0</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" customHeight="1" spans="3:13">
+      <c r="N96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" customHeight="1" spans="3:14">
       <c r="C97" s="3">
         <v>8204</v>
       </c>
       <c r="D97" s="9" t="s">
-        <v>268</v>
-      </c>
-      <c r="E97" s="3">
+        <v>272</v>
+      </c>
+      <c r="E97" s="2"/>
+      <c r="F97" s="3">
         <v>16</v>
       </c>
-      <c r="F97" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="G97" s="3">
-        <v>1</v>
+      <c r="G97" s="3" t="s">
+        <v>273</v>
       </c>
       <c r="H97" s="3">
         <v>1</v>
       </c>
       <c r="I97" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J97" s="3">
+        <v>0</v>
+      </c>
+      <c r="K97" s="3">
         <v>4</v>
       </c>
-      <c r="K97" s="3">
-        <v>0</v>
-      </c>
       <c r="L97" s="3">
         <v>0</v>
       </c>
       <c r="M97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" customHeight="1" spans="3:13">
+      <c r="N97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" customHeight="1" spans="3:14">
       <c r="C98" s="3">
         <v>8205</v>
       </c>
       <c r="D98" s="9" t="s">
-        <v>270</v>
-      </c>
-      <c r="E98" s="3">
+        <v>274</v>
+      </c>
+      <c r="E98" s="2"/>
+      <c r="F98" s="3">
         <v>16</v>
       </c>
-      <c r="F98" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="G98" s="3">
-        <v>1</v>
+      <c r="G98" s="3" t="s">
+        <v>275</v>
       </c>
       <c r="H98" s="3">
         <v>1</v>
       </c>
       <c r="I98" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J98" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K98" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L98" s="3">
         <v>0</v>
@@ -6385,105 +6618,110 @@
       <c r="M98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" customHeight="1" spans="3:13">
+      <c r="N98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" customHeight="1" spans="3:14">
       <c r="C99" s="3">
         <v>8206</v>
       </c>
       <c r="D99" s="9" t="s">
-        <v>272</v>
-      </c>
-      <c r="E99" s="3">
+        <v>276</v>
+      </c>
+      <c r="E99" s="2"/>
+      <c r="F99" s="3">
         <v>16</v>
       </c>
-      <c r="F99" s="3" t="s">
-        <v>273</v>
-      </c>
-      <c r="G99" s="3">
-        <v>1</v>
+      <c r="G99" s="3" t="s">
+        <v>277</v>
       </c>
       <c r="H99" s="3">
         <v>1</v>
       </c>
       <c r="I99" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J99" s="3">
+        <v>0</v>
+      </c>
+      <c r="K99" s="3">
         <v>6</v>
       </c>
-      <c r="K99" s="3">
-        <v>0</v>
-      </c>
       <c r="L99" s="3">
         <v>0</v>
       </c>
       <c r="M99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" customHeight="1" spans="3:13">
+      <c r="N99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" customHeight="1" spans="3:14">
       <c r="C100" s="3">
         <v>8207</v>
       </c>
       <c r="D100" s="9" t="s">
-        <v>274</v>
-      </c>
-      <c r="E100" s="3">
+        <v>278</v>
+      </c>
+      <c r="E100" s="2"/>
+      <c r="F100" s="3">
         <v>16</v>
       </c>
-      <c r="F100" s="3" t="s">
-        <v>275</v>
-      </c>
-      <c r="G100" s="3">
-        <v>1</v>
+      <c r="G100" s="3" t="s">
+        <v>279</v>
       </c>
       <c r="H100" s="3">
         <v>1</v>
       </c>
       <c r="I100" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3">
         <v>7</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
       <c r="L100" s="3">
         <v>0</v>
       </c>
       <c r="M100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" customHeight="1" spans="3:13">
+      <c r="N100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" customHeight="1" spans="3:14">
       <c r="D102" s="9"/>
     </row>
-    <row r="103" customHeight="1" spans="3:13">
+    <row r="103" customHeight="1" spans="3:14">
       <c r="D103" s="9"/>
     </row>
-    <row r="104" customHeight="1" spans="3:13">
+    <row r="104" customHeight="1" spans="3:14">
       <c r="D104" s="9"/>
     </row>
-    <row r="105" customHeight="1" spans="3:13">
+    <row r="105" customHeight="1" spans="3:14">
       <c r="D105" s="9"/>
     </row>
-    <row r="106" customHeight="1" spans="3:13">
+    <row r="106" customHeight="1" spans="3:14">
       <c r="D106" s="9"/>
     </row>
-    <row r="107" customHeight="1" spans="3:13">
+    <row r="107" customHeight="1" spans="3:14">
       <c r="D107" s="9"/>
     </row>
-    <row r="108" customHeight="1" spans="3:13">
+    <row r="108" customHeight="1" spans="3:14">
       <c r="D108" s="9"/>
     </row>
-    <row r="110" customHeight="1" spans="3:13">
+    <row r="110" customHeight="1" spans="3:14">
       <c r="D110" s="9"/>
     </row>
-    <row r="111" customHeight="1" spans="3:13">
+    <row r="111" customHeight="1" spans="3:14">
       <c r="D111" s="9"/>
     </row>
-    <row r="112" customHeight="1" spans="3:13">
+    <row r="112" customHeight="1" spans="3:14">
       <c r="D112" s="9"/>
     </row>
     <row r="113" customHeight="1" spans="4:4">
@@ -6500,11 +6738,11 @@
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C11:D11 C16:D16 C12:C15 C3:D5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="E3 E4 E5 C11:D11 C16:D16 C12:C15 C3:D5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="L16:M16 L3:M5" errorStyle="warning">
-      <formula1>COUNTIF($A:$A,L3)&lt;2</formula1>
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="M16:N16 M3:N5" errorStyle="warning">
+      <formula1>COUNTIF($A:$A,M3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6516,23 +6754,24 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:M17"/>
+  <dimension ref="C1:N17"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="4" max="4" width="9.625" customWidth="1"/>
-    <col min="6" max="6" width="15.375" customWidth="1"/>
-    <col min="12" max="13" width="13.5083333333333" style="3" customWidth="1"/>
+    <col min="5" max="5" width="9.58333333333333" style="2" customWidth="1"/>
+    <col min="7" max="7" width="15.375" customWidth="1"/>
+    <col min="13" max="14" width="13.5083333333333" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="3:13">
-      <c r="L1" s="3"/>
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="3:14">
       <c r="M1" s="3"/>
-    </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="3:13">
-      <c r="L2" s="3"/>
+      <c r="N1" s="3"/>
+    </row>
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="3:14">
       <c r="M2" s="3"/>
-    </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:13">
+      <c r="N2" s="3"/>
+    </row>
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:14">
       <c r="C3" s="4" t="s">
         <v>0</v>
       </c>
@@ -6560,22 +6799,25 @@
       <c r="K3" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="L3" s="5" t="s">
+      <c r="L3" s="4" t="s">
         <v>9</v>
       </c>
       <c r="M3" s="5" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:13">
+      <c r="N3" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:14">
       <c r="C4" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="F4" s="4" t="s">
         <v>14</v>
@@ -6595,373 +6837,391 @@
       <c r="K4" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="L4" s="5" t="s">
-        <v>9</v>
+      <c r="L4" s="4" t="s">
+        <v>20</v>
       </c>
       <c r="M4" s="5" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:13">
+      <c r="N4" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:14">
       <c r="C5" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>21</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="H5" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="I5" s="4" t="s">
-        <v>20</v>
+      <c r="H5" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>23</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="L5" s="5" t="s">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="L5" s="4" t="s">
+        <v>21</v>
       </c>
       <c r="M5" s="5" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="6" s="2" customFormat="1" customHeight="1" spans="3:13">
+        <v>21</v>
+      </c>
+      <c r="N5" s="5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" s="2" customFormat="1" customHeight="1" spans="3:14">
       <c r="C6" s="2">
         <v>9001</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>276</v>
-      </c>
-      <c r="E6" s="2">
+        <v>280</v>
+      </c>
+      <c r="E6" s="3"/>
+      <c r="F6" s="2">
         <v>6</v>
       </c>
-      <c r="F6" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="G6" s="2">
-        <v>1</v>
+      <c r="G6" s="2" t="s">
+        <v>281</v>
       </c>
       <c r="H6" s="2">
+        <v>1</v>
+      </c>
+      <c r="I6" s="2">
         <v>99999</v>
       </c>
-      <c r="I6" s="2">
-        <v>0</v>
-      </c>
       <c r="J6" s="2">
+        <v>0</v>
+      </c>
+      <c r="K6" s="2">
         <v>8</v>
       </c>
-      <c r="K6" s="2"/>
-      <c r="L6" s="3"/>
+      <c r="L6" s="2"/>
       <c r="M6" s="3"/>
-    </row>
-    <row r="7" s="2" customFormat="1" customHeight="1" spans="3:13">
+      <c r="N6" s="3"/>
+    </row>
+    <row r="7" s="2" customFormat="1" customHeight="1" spans="3:14">
       <c r="C7" s="2">
         <v>9002</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>278</v>
-      </c>
-      <c r="E7" s="2">
+        <v>282</v>
+      </c>
+      <c r="E7" s="3"/>
+      <c r="F7" s="2">
         <v>6</v>
       </c>
-      <c r="F7" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="G7" s="2">
-        <v>1</v>
+      <c r="G7" s="2" t="s">
+        <v>281</v>
       </c>
       <c r="H7" s="2">
+        <v>1</v>
+      </c>
+      <c r="I7" s="2">
         <v>99999</v>
       </c>
-      <c r="I7" s="2">
-        <v>0</v>
-      </c>
       <c r="J7" s="2">
+        <v>0</v>
+      </c>
+      <c r="K7" s="2">
         <v>8</v>
       </c>
-      <c r="K7" s="2"/>
-      <c r="L7" s="3"/>
+      <c r="L7" s="2"/>
       <c r="M7" s="3"/>
-    </row>
-    <row r="8" s="2" customFormat="1" customHeight="1" spans="3:13">
+      <c r="N7" s="3"/>
+    </row>
+    <row r="8" s="2" customFormat="1" customHeight="1" spans="3:14">
       <c r="C8" s="2">
         <v>9003</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="E8" s="2">
+        <v>283</v>
+      </c>
+      <c r="E8" s="3"/>
+      <c r="F8" s="2">
         <v>6</v>
       </c>
-      <c r="F8" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="G8" s="2">
-        <v>1</v>
+      <c r="G8" s="2" t="s">
+        <v>281</v>
       </c>
       <c r="H8" s="2">
+        <v>1</v>
+      </c>
+      <c r="I8" s="2">
         <v>99999</v>
       </c>
-      <c r="I8" s="2">
-        <v>0</v>
-      </c>
       <c r="J8" s="2">
+        <v>0</v>
+      </c>
+      <c r="K8" s="2">
         <v>8</v>
       </c>
-      <c r="K8" s="2"/>
-      <c r="L8" s="3"/>
+      <c r="L8" s="2"/>
       <c r="M8" s="3"/>
-    </row>
-    <row r="9" s="2" customFormat="1" customHeight="1" spans="3:13">
+      <c r="N8" s="3"/>
+    </row>
+    <row r="9" s="2" customFormat="1" customHeight="1" spans="3:14">
       <c r="C9" s="2">
         <v>9004</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>280</v>
-      </c>
-      <c r="E9" s="2">
+        <v>284</v>
+      </c>
+      <c r="E9" s="3"/>
+      <c r="F9" s="2">
         <v>6</v>
       </c>
-      <c r="F9" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="G9" s="2">
-        <v>1</v>
+      <c r="G9" s="2" t="s">
+        <v>281</v>
       </c>
       <c r="H9" s="2">
+        <v>1</v>
+      </c>
+      <c r="I9" s="2">
         <v>99999</v>
       </c>
-      <c r="I9" s="2">
-        <v>0</v>
-      </c>
       <c r="J9" s="2">
+        <v>0</v>
+      </c>
+      <c r="K9" s="2">
         <v>8</v>
       </c>
-      <c r="K9" s="2"/>
-      <c r="L9" s="3"/>
+      <c r="L9" s="2"/>
       <c r="M9" s="3"/>
-    </row>
-    <row r="10" s="2" customFormat="1" customHeight="1" spans="3:13">
+      <c r="N9" s="3"/>
+    </row>
+    <row r="10" s="2" customFormat="1" customHeight="1" spans="3:14">
       <c r="C10" s="2">
         <v>9005</v>
       </c>
       <c r="D10" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="E10" s="3"/>
+      <c r="F10" s="2">
+        <v>6</v>
+      </c>
+      <c r="G10" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="E10" s="2">
-        <v>6</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="G10" s="2">
-        <v>1</v>
-      </c>
       <c r="H10" s="2">
+        <v>1</v>
+      </c>
+      <c r="I10" s="2">
         <v>99999</v>
       </c>
-      <c r="I10" s="2">
-        <v>0</v>
-      </c>
       <c r="J10" s="2">
+        <v>0</v>
+      </c>
+      <c r="K10" s="2">
         <v>8</v>
       </c>
-      <c r="K10" s="2"/>
-      <c r="L10" s="3"/>
+      <c r="L10" s="2"/>
       <c r="M10" s="3"/>
-    </row>
-    <row r="11" s="2" customFormat="1" customHeight="1" spans="3:13">
+      <c r="N10" s="3"/>
+    </row>
+    <row r="11" s="2" customFormat="1" customHeight="1" spans="3:14">
       <c r="C11" s="2">
         <v>9006</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>282</v>
-      </c>
-      <c r="E11" s="2">
+        <v>286</v>
+      </c>
+      <c r="E11" s="3"/>
+      <c r="F11" s="2">
         <v>6</v>
       </c>
-      <c r="F11" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="G11" s="2">
-        <v>1</v>
+      <c r="G11" s="2" t="s">
+        <v>281</v>
       </c>
       <c r="H11" s="2">
+        <v>1</v>
+      </c>
+      <c r="I11" s="2">
         <v>99999</v>
       </c>
-      <c r="I11" s="2">
-        <v>0</v>
-      </c>
       <c r="J11" s="2">
+        <v>0</v>
+      </c>
+      <c r="K11" s="2">
         <v>6</v>
       </c>
-      <c r="L11" s="3"/>
       <c r="M11" s="3"/>
-    </row>
-    <row r="12" s="2" customFormat="1" customHeight="1" spans="3:13">
+      <c r="N11" s="3"/>
+    </row>
+    <row r="12" s="2" customFormat="1" customHeight="1" spans="3:14">
       <c r="C12" s="2">
         <v>9007</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>283</v>
-      </c>
-      <c r="E12" s="2">
+        <v>287</v>
+      </c>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2">
         <v>6</v>
       </c>
-      <c r="F12" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="G12" s="2">
-        <v>1</v>
+      <c r="G12" s="2" t="s">
+        <v>281</v>
       </c>
       <c r="H12" s="2">
+        <v>1</v>
+      </c>
+      <c r="I12" s="2">
         <v>99999</v>
       </c>
-      <c r="I12" s="2">
-        <v>0</v>
-      </c>
       <c r="J12" s="2">
+        <v>0</v>
+      </c>
+      <c r="K12" s="2">
         <v>6</v>
       </c>
-      <c r="L12" s="3"/>
       <c r="M12" s="3"/>
-    </row>
-    <row r="13" s="2" customFormat="1" customHeight="1" spans="3:13">
+      <c r="N12" s="3"/>
+    </row>
+    <row r="13" s="2" customFormat="1" customHeight="1" spans="3:14">
       <c r="C13" s="2">
         <v>9008</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>284</v>
-      </c>
-      <c r="E13" s="2">
+        <v>288</v>
+      </c>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2">
         <v>6</v>
       </c>
-      <c r="F13" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="G13" s="2">
-        <v>1</v>
+      <c r="G13" s="2" t="s">
+        <v>281</v>
       </c>
       <c r="H13" s="2">
+        <v>1</v>
+      </c>
+      <c r="I13" s="2">
         <v>99999</v>
       </c>
-      <c r="I13" s="2">
-        <v>0</v>
-      </c>
       <c r="J13" s="2">
+        <v>0</v>
+      </c>
+      <c r="K13" s="2">
         <v>6</v>
       </c>
-      <c r="L13" s="3"/>
       <c r="M13" s="3"/>
-    </row>
-    <row r="14" s="2" customFormat="1" customHeight="1" spans="3:13">
+      <c r="N13" s="3"/>
+    </row>
+    <row r="14" s="2" customFormat="1" customHeight="1" spans="3:14">
       <c r="C14" s="2">
         <v>9009</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>285</v>
-      </c>
-      <c r="E14" s="2">
+        <v>289</v>
+      </c>
+      <c r="E14" s="3"/>
+      <c r="F14" s="2">
         <v>6</v>
       </c>
-      <c r="F14" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="G14" s="2">
-        <v>1</v>
+      <c r="G14" s="2" t="s">
+        <v>281</v>
       </c>
       <c r="H14" s="2">
+        <v>1</v>
+      </c>
+      <c r="I14" s="2">
         <v>99999</v>
       </c>
-      <c r="I14" s="2">
-        <v>0</v>
-      </c>
       <c r="J14" s="2">
+        <v>0</v>
+      </c>
+      <c r="K14" s="2">
         <v>6</v>
       </c>
-      <c r="L14" s="3"/>
       <c r="M14" s="3"/>
-    </row>
-    <row r="15" s="2" customFormat="1" customHeight="1" spans="3:13">
+      <c r="N14" s="3"/>
+    </row>
+    <row r="15" s="2" customFormat="1" customHeight="1" spans="3:14">
       <c r="C15" s="2">
         <v>9010</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="E15" s="2">
+        <v>290</v>
+      </c>
+      <c r="E15" s="3"/>
+      <c r="F15" s="2">
         <v>6</v>
       </c>
-      <c r="F15" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="G15" s="2">
-        <v>1</v>
+      <c r="G15" s="2" t="s">
+        <v>281</v>
       </c>
       <c r="H15" s="2">
+        <v>1</v>
+      </c>
+      <c r="I15" s="2">
         <v>99999</v>
       </c>
-      <c r="I15" s="2">
-        <v>0</v>
-      </c>
       <c r="J15" s="2">
+        <v>0</v>
+      </c>
+      <c r="K15" s="2">
         <v>7</v>
       </c>
-      <c r="L15" s="3"/>
       <c r="M15" s="3"/>
-    </row>
-    <row r="16" s="2" customFormat="1" customHeight="1" spans="3:13">
+      <c r="N15" s="3"/>
+    </row>
+    <row r="16" s="2" customFormat="1" customHeight="1" spans="3:14">
       <c r="C16" s="2">
         <v>9011</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>287</v>
-      </c>
-      <c r="E16" s="2">
+        <v>291</v>
+      </c>
+      <c r="E16" s="3"/>
+      <c r="F16" s="2">
         <v>6</v>
       </c>
-      <c r="F16" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="G16" s="2">
-        <v>1</v>
+      <c r="G16" s="2" t="s">
+        <v>281</v>
       </c>
       <c r="H16" s="2">
+        <v>1</v>
+      </c>
+      <c r="I16" s="2">
         <v>99999</v>
       </c>
-      <c r="I16" s="2">
-        <v>0</v>
-      </c>
       <c r="J16" s="2">
+        <v>0</v>
+      </c>
+      <c r="K16" s="2">
         <v>7</v>
       </c>
-      <c r="L16" s="3"/>
       <c r="M16" s="3"/>
-    </row>
-    <row r="17" s="2" customFormat="1" customHeight="1" spans="4:13">
+      <c r="N16" s="3"/>
+    </row>
+    <row r="17" s="2" customFormat="1" customHeight="1" spans="4:14">
       <c r="D17" s="3"/>
-      <c r="L17" s="3"/>
+      <c r="E17" s="3"/>
       <c r="M17" s="3"/>
+      <c r="N17" s="3"/>
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="L3:M5" errorStyle="warning">
-      <formula1>COUNTIF($A:$A,L3)&lt;2</formula1>
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="E3 E4 E5 C3:D5" errorStyle="warning">
+      <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:D5" errorStyle="warning">
-      <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="M3:N5" errorStyle="warning">
+      <formula1>COUNTIF($A:$A,M3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6973,23 +7233,24 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:M17"/>
+  <dimension ref="C1:N17"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="4" max="4" width="9.625" customWidth="1"/>
-    <col min="6" max="6" width="15.375" customWidth="1"/>
-    <col min="12" max="13" width="13.5083333333333" style="3" customWidth="1"/>
+    <col min="5" max="5" width="9.58333333333333" style="2" customWidth="1"/>
+    <col min="7" max="7" width="15.375" customWidth="1"/>
+    <col min="13" max="14" width="13.5083333333333" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="3:13">
-      <c r="L1" s="3"/>
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="3:14">
       <c r="M1" s="3"/>
-    </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="3:13">
-      <c r="L2" s="3"/>
+      <c r="N1" s="3"/>
+    </row>
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="3:14">
       <c r="M2" s="3"/>
-    </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:13">
+      <c r="N2" s="3"/>
+    </row>
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:14">
       <c r="C3" s="4" t="s">
         <v>0</v>
       </c>
@@ -7017,22 +7278,25 @@
       <c r="K3" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="L3" s="5" t="s">
+      <c r="L3" s="4" t="s">
         <v>9</v>
       </c>
       <c r="M3" s="5" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:13">
+      <c r="N3" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:14">
       <c r="C4" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="F4" s="4" t="s">
         <v>14</v>
@@ -7052,199 +7316,211 @@
       <c r="K4" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="L4" s="5" t="s">
-        <v>9</v>
+      <c r="L4" s="4" t="s">
+        <v>20</v>
       </c>
       <c r="M4" s="5" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:13">
+      <c r="N4" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:14">
       <c r="C5" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>21</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="H5" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="I5" s="4" t="s">
-        <v>20</v>
+      <c r="H5" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>23</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="L5" s="5" t="s">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="L5" s="4" t="s">
+        <v>21</v>
       </c>
       <c r="M5" s="5" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="6" s="2" customFormat="1" customHeight="1" spans="3:13">
+        <v>21</v>
+      </c>
+      <c r="N5" s="5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" s="2" customFormat="1" customHeight="1" spans="3:14">
       <c r="C6" s="2">
         <v>10001</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>288</v>
-      </c>
-      <c r="E6" s="2">
-        <v>5</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="G6" s="2">
-        <v>1</v>
+        <v>292</v>
+      </c>
+      <c r="E6" s="3"/>
+      <c r="F6" s="2">
+        <v>5</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>293</v>
       </c>
       <c r="H6" s="2">
+        <v>1</v>
+      </c>
+      <c r="I6" s="2">
         <v>99999</v>
       </c>
-      <c r="I6" s="2">
-        <v>0</v>
-      </c>
       <c r="J6" s="2">
+        <v>0</v>
+      </c>
+      <c r="K6" s="2">
         <v>4</v>
       </c>
-      <c r="L6" s="3">
+      <c r="M6" s="3">
         <v>5003</v>
       </c>
-      <c r="M6" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" s="2" customFormat="1" customHeight="1" spans="3:13">
+      <c r="N6" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" s="2" customFormat="1" customHeight="1" spans="3:14">
       <c r="C7" s="2">
         <v>10002</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>290</v>
-      </c>
-      <c r="E7" s="2">
-        <v>5</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="G7" s="2">
-        <v>1</v>
+        <v>294</v>
+      </c>
+      <c r="E7" s="3"/>
+      <c r="F7" s="2">
+        <v>5</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>293</v>
       </c>
       <c r="H7" s="2">
+        <v>1</v>
+      </c>
+      <c r="I7" s="2">
         <v>99999</v>
       </c>
-      <c r="I7" s="2">
-        <v>0</v>
-      </c>
       <c r="J7" s="2">
+        <v>0</v>
+      </c>
+      <c r="K7" s="2">
         <v>4</v>
       </c>
-      <c r="L7" s="3">
+      <c r="M7" s="3">
         <v>5003</v>
       </c>
-      <c r="M7" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" s="2" customFormat="1" customHeight="1" spans="3:13">
+      <c r="N7" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" s="2" customFormat="1" customHeight="1" spans="3:14">
       <c r="C8" s="2">
         <v>10003</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>291</v>
-      </c>
-      <c r="E8" s="2">
-        <v>5</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="G8" s="2">
-        <v>1</v>
+        <v>295</v>
+      </c>
+      <c r="E8" s="3"/>
+      <c r="F8" s="2">
+        <v>5</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>293</v>
       </c>
       <c r="H8" s="2">
+        <v>1</v>
+      </c>
+      <c r="I8" s="2">
         <v>99999</v>
       </c>
-      <c r="I8" s="2">
-        <v>0</v>
-      </c>
       <c r="J8" s="2">
+        <v>0</v>
+      </c>
+      <c r="K8" s="2">
         <v>4</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>5003</v>
       </c>
-      <c r="M8" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" s="2" customFormat="1" customHeight="1" spans="3:13">
+      <c r="N8" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" s="2" customFormat="1" customHeight="1" spans="3:14">
       <c r="C9" s="2">
         <v>10004</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>292</v>
-      </c>
-      <c r="E9" s="2">
-        <v>5</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="G9" s="2">
-        <v>1</v>
+        <v>296</v>
+      </c>
+      <c r="E9" s="3"/>
+      <c r="F9" s="2">
+        <v>5</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>293</v>
       </c>
       <c r="H9" s="2">
+        <v>1</v>
+      </c>
+      <c r="I9" s="2">
         <v>99999</v>
       </c>
-      <c r="I9" s="2">
-        <v>0</v>
-      </c>
       <c r="J9" s="2">
-        <v>5</v>
-      </c>
-      <c r="L9" s="3">
+        <v>0</v>
+      </c>
+      <c r="K9" s="2">
+        <v>5</v>
+      </c>
+      <c r="M9" s="3">
         <v>5003</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>10</v>
       </c>
     </row>
-    <row r="10" s="2" customFormat="1" customHeight="1" spans="3:13">
+    <row r="10" s="2" customFormat="1" customHeight="1" spans="3:14">
       <c r="D10" s="3"/>
-      <c r="E10" s="2"/>
+      <c r="E10" s="3"/>
       <c r="F10" s="2"/>
       <c r="G10" s="2"/>
       <c r="H10" s="2"/>
       <c r="I10" s="2"/>
       <c r="J10" s="2"/>
-      <c r="L10" s="3"/>
+      <c r="K10" s="2"/>
       <c r="M10" s="3"/>
-    </row>
-    <row r="11" s="2" customFormat="1" customHeight="1" spans="3:13">
+      <c r="N10" s="3"/>
+    </row>
+    <row r="11" s="2" customFormat="1" customHeight="1" spans="3:14">
       <c r="D11" s="3"/>
-      <c r="E11" s="2"/>
+      <c r="E11" s="3"/>
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
       <c r="H11" s="2"/>
       <c r="I11" s="2"/>
       <c r="J11" s="2"/>
-      <c r="L11" s="3"/>
+      <c r="K11" s="2"/>
       <c r="M11" s="3"/>
-    </row>
-    <row r="12" s="2" customFormat="1" customHeight="1" spans="3:13">
+      <c r="N11" s="3"/>
+    </row>
+    <row r="12" s="2" customFormat="1" customHeight="1" spans="3:14">
       <c r="D12" s="3"/>
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
@@ -7252,10 +7528,11 @@
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
       <c r="J12" s="2"/>
-      <c r="L12" s="3"/>
+      <c r="K12" s="2"/>
       <c r="M12" s="3"/>
-    </row>
-    <row r="13" s="2" customFormat="1" customHeight="1" spans="3:13">
+      <c r="N12" s="3"/>
+    </row>
+    <row r="13" s="2" customFormat="1" customHeight="1" spans="3:14">
       <c r="D13" s="3"/>
       <c r="E13" s="2"/>
       <c r="F13" s="2"/>
@@ -7263,54 +7540,59 @@
       <c r="H13" s="2"/>
       <c r="I13" s="2"/>
       <c r="J13" s="2"/>
-      <c r="L13" s="3"/>
+      <c r="K13" s="2"/>
       <c r="M13" s="3"/>
-    </row>
-    <row r="14" s="2" customFormat="1" customHeight="1" spans="3:13">
+      <c r="N13" s="3"/>
+    </row>
+    <row r="14" s="2" customFormat="1" customHeight="1" spans="3:14">
       <c r="D14" s="3"/>
-      <c r="E14" s="2"/>
+      <c r="E14" s="3"/>
       <c r="F14" s="2"/>
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
       <c r="I14" s="2"/>
       <c r="J14" s="2"/>
-      <c r="L14" s="3"/>
+      <c r="K14" s="2"/>
       <c r="M14" s="3"/>
-    </row>
-    <row r="15" s="2" customFormat="1" customHeight="1" spans="3:13">
+      <c r="N14" s="3"/>
+    </row>
+    <row r="15" s="2" customFormat="1" customHeight="1" spans="3:14">
       <c r="D15" s="3"/>
-      <c r="E15" s="2"/>
+      <c r="E15" s="3"/>
       <c r="F15" s="2"/>
       <c r="G15" s="2"/>
       <c r="H15" s="2"/>
       <c r="I15" s="2"/>
       <c r="J15" s="2"/>
-      <c r="L15" s="3"/>
+      <c r="K15" s="2"/>
       <c r="M15" s="3"/>
-    </row>
-    <row r="16" s="2" customFormat="1" customHeight="1" spans="3:13">
+      <c r="N15" s="3"/>
+    </row>
+    <row r="16" s="2" customFormat="1" customHeight="1" spans="3:14">
       <c r="D16" s="3"/>
-      <c r="E16" s="2"/>
+      <c r="E16" s="3"/>
       <c r="F16" s="2"/>
       <c r="G16" s="2"/>
       <c r="H16" s="2"/>
       <c r="I16" s="2"/>
       <c r="J16" s="2"/>
-      <c r="L16" s="3"/>
+      <c r="K16" s="2"/>
       <c r="M16" s="3"/>
-    </row>
-    <row r="17" s="2" customFormat="1" customHeight="1" spans="4:13">
+      <c r="N16" s="3"/>
+    </row>
+    <row r="17" s="2" customFormat="1" customHeight="1" spans="4:14">
       <c r="D17" s="3"/>
-      <c r="L17" s="3"/>
+      <c r="E17" s="3"/>
       <c r="M17" s="3"/>
+      <c r="N17" s="3"/>
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="L3:M5" errorStyle="warning">
-      <formula1>COUNTIF($A:$A,L3)&lt;2</formula1>
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="E3 E4 E5 C3:D5" errorStyle="warning">
+      <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:D5" errorStyle="warning">
-      <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="M3:N5" errorStyle="warning">
+      <formula1>COUNTIF($A:$A,M3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7322,29 +7604,29 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:M17"/>
+  <dimension ref="C1:N17"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="2"/>
-    <col min="4" max="4" width="9.625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="9" style="2"/>
-    <col min="6" max="6" width="20.875" style="2" customWidth="1"/>
-    <col min="7" max="8" width="9" style="2"/>
-    <col min="9" max="9" width="12.6666666666667" style="2" customWidth="1"/>
-    <col min="10" max="11" width="9" style="2"/>
-    <col min="12" max="13" width="13.5083333333333" style="3" customWidth="1"/>
-    <col min="14" max="16384" width="9" style="2"/>
+    <col min="4" max="5" width="9.58333333333333" style="2" customWidth="1"/>
+    <col min="6" max="6" width="9" style="2"/>
+    <col min="7" max="7" width="20.875" style="2" customWidth="1"/>
+    <col min="8" max="9" width="9" style="2"/>
+    <col min="10" max="10" width="12.6666666666667" style="2" customWidth="1"/>
+    <col min="11" max="12" width="9" style="2"/>
+    <col min="13" max="14" width="13.5083333333333" style="3" customWidth="1"/>
+    <col min="15" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="3:13">
-      <c r="L1" s="3"/>
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="3:14">
       <c r="M1" s="3"/>
-    </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="3:13">
-      <c r="L2" s="3"/>
+      <c r="N1" s="3"/>
+    </row>
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="3:14">
       <c r="M2" s="3"/>
-    </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:13">
+      <c r="N2" s="3"/>
+    </row>
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:14">
       <c r="C3" s="4" t="s">
         <v>0</v>
       </c>
@@ -7372,22 +7654,25 @@
       <c r="K3" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="L3" s="5" t="s">
+      <c r="L3" s="4" t="s">
         <v>9</v>
       </c>
       <c r="M3" s="5" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:13">
+      <c r="N3" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:14">
       <c r="C4" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="F4" s="4" t="s">
         <v>14</v>
@@ -7407,375 +7692,391 @@
       <c r="K4" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="L4" s="5" t="s">
-        <v>9</v>
+      <c r="L4" s="4" t="s">
+        <v>20</v>
       </c>
       <c r="M4" s="5" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:13">
+      <c r="N4" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:14">
       <c r="C5" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>21</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="H5" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="I5" s="4" t="s">
-        <v>20</v>
+      <c r="H5" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>23</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="L5" s="5" t="s">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="L5" s="4" t="s">
+        <v>21</v>
       </c>
       <c r="M5" s="5" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="6" customHeight="1" spans="3:13">
+        <v>21</v>
+      </c>
+      <c r="N5" s="5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" customHeight="1" spans="3:14">
       <c r="C6" s="3">
         <v>40000001</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>293</v>
-      </c>
-      <c r="E6" s="2">
+        <v>297</v>
+      </c>
+      <c r="E6" s="3"/>
+      <c r="F6" s="2">
         <v>6</v>
       </c>
-      <c r="F6" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="G6" s="2">
-        <v>1</v>
+      <c r="G6" s="2" t="s">
+        <v>298</v>
       </c>
       <c r="H6" s="2">
+        <v>1</v>
+      </c>
+      <c r="I6" s="2">
         <v>99999</v>
       </c>
-      <c r="I6" s="2">
-        <v>0</v>
-      </c>
-      <c r="J6" s="3">
+      <c r="J6" s="2">
+        <v>0</v>
+      </c>
+      <c r="K6" s="3">
         <v>4</v>
       </c>
-      <c r="K6" s="3"/>
-    </row>
-    <row r="7" customHeight="1" spans="3:13">
+      <c r="L6" s="3"/>
+    </row>
+    <row r="7" customHeight="1" spans="3:14">
       <c r="C7" s="3">
         <v>40000002</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="E7" s="2">
+        <v>299</v>
+      </c>
+      <c r="E7" s="3"/>
+      <c r="F7" s="2">
         <v>6</v>
       </c>
-      <c r="F7" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="G7" s="2">
-        <v>1</v>
+      <c r="G7" s="2" t="s">
+        <v>298</v>
       </c>
       <c r="H7" s="2">
+        <v>1</v>
+      </c>
+      <c r="I7" s="2">
         <v>99999</v>
       </c>
-      <c r="I7" s="2">
-        <v>0</v>
-      </c>
-      <c r="J7" s="3">
-        <v>5</v>
-      </c>
-      <c r="K7" s="3"/>
-    </row>
-    <row r="8" customHeight="1" spans="3:13">
+      <c r="J7" s="2">
+        <v>0</v>
+      </c>
+      <c r="K7" s="3">
+        <v>5</v>
+      </c>
+      <c r="L7" s="3"/>
+    </row>
+    <row r="8" customHeight="1" spans="3:14">
       <c r="C8" s="3">
         <v>40000003</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>296</v>
-      </c>
-      <c r="E8" s="2">
+        <v>300</v>
+      </c>
+      <c r="E8" s="3"/>
+      <c r="F8" s="2">
         <v>6</v>
       </c>
-      <c r="F8" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="G8" s="2">
-        <v>1</v>
+      <c r="G8" s="2" t="s">
+        <v>298</v>
       </c>
       <c r="H8" s="2">
+        <v>1</v>
+      </c>
+      <c r="I8" s="2">
         <v>99999</v>
       </c>
-      <c r="I8" s="2">
-        <v>0</v>
-      </c>
-      <c r="J8" s="3">
+      <c r="J8" s="2">
+        <v>0</v>
+      </c>
+      <c r="K8" s="3">
         <v>6</v>
       </c>
-      <c r="K8" s="3"/>
-    </row>
-    <row r="9" customHeight="1" spans="3:13">
+      <c r="L8" s="3"/>
+    </row>
+    <row r="9" customHeight="1" spans="3:14">
       <c r="C9" s="3">
         <v>40000004</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>297</v>
-      </c>
-      <c r="E9" s="2">
+        <v>301</v>
+      </c>
+      <c r="E9" s="3"/>
+      <c r="F9" s="2">
         <v>6</v>
       </c>
-      <c r="F9" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="G9" s="2">
-        <v>1</v>
+      <c r="G9" s="2" t="s">
+        <v>302</v>
       </c>
       <c r="H9" s="2">
+        <v>1</v>
+      </c>
+      <c r="I9" s="2">
         <v>99999</v>
       </c>
-      <c r="I9" s="2">
-        <v>0</v>
-      </c>
-      <c r="J9" s="3">
+      <c r="J9" s="2">
+        <v>0</v>
+      </c>
+      <c r="K9" s="3">
         <v>4</v>
       </c>
-      <c r="K9" s="3"/>
-    </row>
-    <row r="10" customHeight="1" spans="3:13">
+      <c r="L9" s="3"/>
+    </row>
+    <row r="10" customHeight="1" spans="3:14">
       <c r="C10" s="3">
         <v>40000005</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>299</v>
-      </c>
-      <c r="E10" s="2">
+        <v>303</v>
+      </c>
+      <c r="E10" s="3"/>
+      <c r="F10" s="2">
         <v>6</v>
       </c>
-      <c r="F10" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="G10" s="2">
-        <v>1</v>
+      <c r="G10" s="2" t="s">
+        <v>302</v>
       </c>
       <c r="H10" s="2">
+        <v>1</v>
+      </c>
+      <c r="I10" s="2">
         <v>99999</v>
       </c>
-      <c r="I10" s="2">
-        <v>0</v>
-      </c>
-      <c r="J10" s="3">
-        <v>5</v>
-      </c>
-      <c r="K10" s="6"/>
-    </row>
-    <row r="11" s="2" customFormat="1" customHeight="1" spans="3:13">
+      <c r="J10" s="2">
+        <v>0</v>
+      </c>
+      <c r="K10" s="3">
+        <v>5</v>
+      </c>
+      <c r="L10" s="6"/>
+    </row>
+    <row r="11" s="2" customFormat="1" customHeight="1" spans="3:14">
       <c r="C11" s="3">
         <v>40000006</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>300</v>
-      </c>
-      <c r="E11" s="2">
+        <v>304</v>
+      </c>
+      <c r="E11" s="3"/>
+      <c r="F11" s="2">
         <v>6</v>
       </c>
-      <c r="F11" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="G11" s="2">
-        <v>1</v>
+      <c r="G11" s="2" t="s">
+        <v>302</v>
       </c>
       <c r="H11" s="2">
+        <v>1</v>
+      </c>
+      <c r="I11" s="2">
         <v>99999</v>
       </c>
-      <c r="I11" s="2">
-        <v>0</v>
-      </c>
-      <c r="J11" s="3">
+      <c r="J11" s="2">
+        <v>0</v>
+      </c>
+      <c r="K11" s="3">
         <v>6</v>
       </c>
-      <c r="K11" s="6"/>
-      <c r="L11" s="3"/>
+      <c r="L11" s="6"/>
       <c r="M11" s="3"/>
-    </row>
-    <row r="12" customHeight="1" spans="3:13">
+      <c r="N11" s="3"/>
+    </row>
+    <row r="12" customHeight="1" spans="3:14">
       <c r="C12" s="3">
         <v>40000007</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>301</v>
-      </c>
-      <c r="E12" s="2">
+        <v>305</v>
+      </c>
+      <c r="F12" s="2">
         <v>6</v>
       </c>
-      <c r="F12" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="G12" s="2">
-        <v>1</v>
+      <c r="G12" s="2" t="s">
+        <v>306</v>
       </c>
       <c r="H12" s="2">
+        <v>1</v>
+      </c>
+      <c r="I12" s="2">
         <v>99999</v>
       </c>
-      <c r="I12" s="2">
-        <v>0</v>
-      </c>
-      <c r="J12" s="3">
+      <c r="J12" s="2">
+        <v>0</v>
+      </c>
+      <c r="K12" s="3">
         <v>4</v>
       </c>
     </row>
-    <row r="13" customHeight="1" spans="3:13">
+    <row r="13" customHeight="1" spans="3:14">
       <c r="C13" s="3">
         <v>40000008</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>303</v>
-      </c>
-      <c r="E13" s="2">
+        <v>307</v>
+      </c>
+      <c r="F13" s="2">
         <v>6</v>
       </c>
-      <c r="F13" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="G13" s="2">
-        <v>1</v>
+      <c r="G13" s="2" t="s">
+        <v>306</v>
       </c>
       <c r="H13" s="2">
+        <v>1</v>
+      </c>
+      <c r="I13" s="2">
         <v>99999</v>
       </c>
-      <c r="I13" s="2">
-        <v>0</v>
-      </c>
-      <c r="J13" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" customHeight="1" spans="3:13">
+      <c r="J13" s="2">
+        <v>0</v>
+      </c>
+      <c r="K13" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" customHeight="1" spans="3:14">
       <c r="C14" s="3">
         <v>40000009</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>304</v>
-      </c>
-      <c r="E14" s="2">
+        <v>308</v>
+      </c>
+      <c r="E14" s="3"/>
+      <c r="F14" s="2">
         <v>6</v>
       </c>
-      <c r="F14" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="G14" s="2">
-        <v>1</v>
+      <c r="G14" s="2" t="s">
+        <v>306</v>
       </c>
       <c r="H14" s="2">
+        <v>1</v>
+      </c>
+      <c r="I14" s="2">
         <v>99999</v>
       </c>
-      <c r="I14" s="2">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
+      <c r="J14" s="2">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3">
         <v>6</v>
       </c>
     </row>
-    <row r="15" customHeight="1" spans="3:13">
+    <row r="15" customHeight="1" spans="3:14">
       <c r="C15" s="3">
         <v>40000010</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>305</v>
-      </c>
-      <c r="E15" s="2">
+        <v>309</v>
+      </c>
+      <c r="E15" s="3"/>
+      <c r="F15" s="2">
         <v>6</v>
       </c>
-      <c r="F15" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="G15" s="2">
-        <v>1</v>
+      <c r="G15" s="2" t="s">
+        <v>310</v>
       </c>
       <c r="H15" s="2">
+        <v>1</v>
+      </c>
+      <c r="I15" s="2">
         <v>99999</v>
       </c>
-      <c r="I15" s="2">
-        <v>0</v>
-      </c>
-      <c r="J15" s="3">
+      <c r="J15" s="2">
+        <v>0</v>
+      </c>
+      <c r="K15" s="3">
         <v>4</v>
       </c>
     </row>
-    <row r="16" customHeight="1" spans="3:13">
+    <row r="16" customHeight="1" spans="3:14">
       <c r="C16" s="3">
         <v>40000011</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>307</v>
-      </c>
-      <c r="E16" s="2">
+        <v>311</v>
+      </c>
+      <c r="E16" s="3"/>
+      <c r="F16" s="2">
         <v>6</v>
       </c>
-      <c r="F16" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="G16" s="2">
-        <v>1</v>
+      <c r="G16" s="2" t="s">
+        <v>310</v>
       </c>
       <c r="H16" s="2">
+        <v>1</v>
+      </c>
+      <c r="I16" s="2">
         <v>99999</v>
       </c>
-      <c r="I16" s="2">
-        <v>0</v>
-      </c>
-      <c r="J16" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" customHeight="1" spans="3:10">
+      <c r="J16" s="2">
+        <v>0</v>
+      </c>
+      <c r="K16" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" customHeight="1" spans="3:11">
       <c r="C17" s="3">
         <v>40000012</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>308</v>
-      </c>
-      <c r="E17" s="2">
+        <v>312</v>
+      </c>
+      <c r="E17" s="3"/>
+      <c r="F17" s="2">
         <v>6</v>
       </c>
-      <c r="F17" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="G17" s="2">
-        <v>1</v>
+      <c r="G17" s="2" t="s">
+        <v>310</v>
       </c>
       <c r="H17" s="2">
+        <v>1</v>
+      </c>
+      <c r="I17" s="2">
         <v>99999</v>
       </c>
-      <c r="I17" s="2">
-        <v>0</v>
-      </c>
-      <c r="J17" s="3">
+      <c r="J17" s="2">
+        <v>0</v>
+      </c>
+      <c r="K17" s="3">
         <v>6</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="L3:M5" errorStyle="warning">
-      <formula1>COUNTIF($A:$A,L3)&lt;2</formula1>
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="E3 E4 E5 C3:D5" errorStyle="warning">
+      <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:D5" errorStyle="warning">
-      <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="M3:N5" errorStyle="warning">
+      <formula1>COUNTIF($A:$A,M3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Excel/ItemConfig.xlsx
+++ b/Excel/ItemConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView windowHeight="17680" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="技能" sheetId="1" r:id="rId1"/>
@@ -3768,7 +3768,7 @@
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="E3 E4 E5 C3:D5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:E5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
     <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="M3:N5" errorStyle="warning">
@@ -6449,7 +6449,6 @@
       <c r="D94" s="9" t="s">
         <v>266</v>
       </c>
-      <c r="E94" s="2"/>
       <c r="F94" s="3">
         <v>16</v>
       </c>
@@ -6485,7 +6484,6 @@
       <c r="D95" s="9" t="s">
         <v>268</v>
       </c>
-      <c r="E95" s="2"/>
       <c r="F95" s="3">
         <v>16</v>
       </c>
@@ -6521,7 +6519,6 @@
       <c r="D96" s="9" t="s">
         <v>270</v>
       </c>
-      <c r="E96" s="2"/>
       <c r="F96" s="3">
         <v>16</v>
       </c>
@@ -6557,7 +6554,6 @@
       <c r="D97" s="9" t="s">
         <v>272</v>
       </c>
-      <c r="E97" s="2"/>
       <c r="F97" s="3">
         <v>16</v>
       </c>
@@ -6593,7 +6589,6 @@
       <c r="D98" s="9" t="s">
         <v>274</v>
       </c>
-      <c r="E98" s="2"/>
       <c r="F98" s="3">
         <v>16</v>
       </c>
@@ -6629,7 +6624,6 @@
       <c r="D99" s="9" t="s">
         <v>276</v>
       </c>
-      <c r="E99" s="2"/>
       <c r="F99" s="3">
         <v>16</v>
       </c>
@@ -6665,7 +6659,6 @@
       <c r="D100" s="9" t="s">
         <v>278</v>
       </c>
-      <c r="E100" s="2"/>
       <c r="F100" s="3">
         <v>16</v>
       </c>
@@ -6738,7 +6731,7 @@
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="E3 E4 E5 C11:D11 C16:D16 C12:C15 C3:D5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C11:D11 C16:D16 C12:C15 C3:E5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
     <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="M16:N16 M3:N5" errorStyle="warning">
@@ -7217,7 +7210,7 @@
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="E3 E4 E5 C3:D5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:E5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
     <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="M3:N5" errorStyle="warning">
@@ -7588,7 +7581,7 @@
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="E3 E4 E5 C3:D5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:E5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
     <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="M3:N5" errorStyle="warning">
@@ -8072,7 +8065,7 @@
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="E3 E4 E5 C3:D5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:E5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
     <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="M3:N5" errorStyle="warning">

--- a/Excel/ItemConfig.xlsx
+++ b/Excel/ItemConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="4"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="技能" sheetId="1" r:id="rId1"/>
@@ -325,7 +325,7 @@
     <t>1003</t>
   </si>
   <si>
-    <t>四方剑阵</t>
+    <t>月华剑阵</t>
   </si>
   <si>
     <t>学习或者升级战士技能旋风斩</t>
@@ -334,7 +334,7 @@
     <t>1004</t>
   </si>
   <si>
-    <t>重击剑术</t>
+    <t>蛮牛冲撞</t>
   </si>
   <si>
     <t>学习或者升级战士技能腾空斩</t>
@@ -346,7 +346,7 @@
     <t>1005</t>
   </si>
   <si>
-    <t>武神盾</t>
+    <t>龙魂护体</t>
   </si>
   <si>
     <t>学习或者升级战士技能武神盾</t>
@@ -433,7 +433,7 @@
     <t>2002</t>
   </si>
   <si>
-    <t>神雷术</t>
+    <t>紫电神雷</t>
   </si>
   <si>
     <t>学习或者升级法师技能落雷术</t>
@@ -442,7 +442,7 @@
     <t>2003</t>
   </si>
   <si>
-    <t>火海术</t>
+    <t>火狱阵法</t>
   </si>
   <si>
     <t>学习或者升级法师技能火焰墙</t>
@@ -451,7 +451,7 @@
     <t>2004</t>
   </si>
   <si>
-    <t>烈焰术</t>
+    <t>烈焰焚天</t>
   </si>
   <si>
     <t>学习或者升级法师技能烈焰环</t>
@@ -460,7 +460,7 @@
     <t>2005</t>
   </si>
   <si>
-    <t>念力盾</t>
+    <t>炎凰法盾</t>
   </si>
   <si>
     <t>学习或者升级法师技能法力盾</t>
@@ -469,7 +469,7 @@
     <t>2006</t>
   </si>
   <si>
-    <t>冰心诀</t>
+    <t>万法归宗</t>
   </si>
   <si>
     <t>学习或者升级法师技能法术精通</t>
@@ -478,7 +478,7 @@
     <t>2007</t>
   </si>
   <si>
-    <t>冰封术</t>
+    <t>极寒冰暴</t>
   </si>
   <si>
     <t>学习或者升级法师技能冰爆术</t>
@@ -532,7 +532,7 @@
     <t>3001</t>
   </si>
   <si>
-    <t>祈福心法</t>
+    <t>清心咒</t>
   </si>
   <si>
     <t>sb3</t>
@@ -544,7 +544,7 @@
     <t>3002</t>
   </si>
   <si>
-    <t>灭魔符</t>
+    <t>破魔符咒</t>
   </si>
   <si>
     <t>学习或者升级道士技能驱魔符</t>
@@ -562,7 +562,7 @@
     <t>3004</t>
   </si>
   <si>
-    <t>疗伤术</t>
+    <t>圣疗术</t>
   </si>
   <si>
     <t>学习或者升级道士技能召唤小兵</t>
@@ -571,7 +571,7 @@
     <t>3005</t>
   </si>
   <si>
-    <t>护魂盾</t>
+    <t>太虚麟盾</t>
   </si>
   <si>
     <t>学习或者升级道士技能道力盾</t>
@@ -580,7 +580,7 @@
     <t>3006</t>
   </si>
   <si>
-    <t>圣心诀</t>
+    <t>道法自然</t>
   </si>
   <si>
     <t>学习或者升级道士技能道力精通</t>
@@ -589,7 +589,7 @@
     <t>3007</t>
   </si>
   <si>
-    <t>唤神咒</t>
+    <t>召唤英灵</t>
   </si>
   <si>
     <t>学习或者升级道士技能召唤魔兽</t>

--- a/Excel/ItemConfig.xlsx
+++ b/Excel/ItemConfig.xlsx
@@ -304,7 +304,7 @@
     <t>基础心法</t>
   </si>
   <si>
-    <t>sb1</t>
+    <t>ItemLogo/sb1</t>
   </si>
   <si>
     <t>学习或者升级战士技能基础剑术</t>
@@ -424,7 +424,7 @@
     <t>冥想心法</t>
   </si>
   <si>
-    <t>sb2</t>
+    <t>ItemLogo/sb2</t>
   </si>
   <si>
     <t>学习或者升级法师技能火球术</t>
@@ -535,7 +535,7 @@
     <t>清心咒</t>
   </si>
   <si>
-    <t>sb3</t>
+    <t>ItemLogo/sb3</t>
   </si>
   <si>
     <t>学习或者升级道士技能疗伤术</t>
@@ -2174,12 +2174,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N43"/>
+  <dimension ref="A3:N43"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="3"/>
     <col min="4" max="4" width="10.125" style="3" customWidth="1"/>
-    <col min="5" max="5" width="9.58333333333333" style="2" customWidth="1"/>
+    <col min="5" max="5" width="12.3333333333333" style="3" customWidth="1"/>
     <col min="6" max="6" width="9.875" style="3" customWidth="1"/>
     <col min="7" max="7" width="26.75" style="3" customWidth="1"/>
     <col min="8" max="8" width="8" style="3" customWidth="1"/>
@@ -2188,12 +2188,6 @@
     <col min="15" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" customHeight="1" spans="1:14">
-      <c r="E1" s="1"/>
-    </row>
-    <row r="2" customHeight="1" spans="1:14">
-      <c r="E2" s="1"/>
-    </row>
     <row r="3" customHeight="1" spans="1:14">
       <c r="C3" s="5" t="s">
         <v>0</v>
@@ -2201,7 +2195,7 @@
       <c r="D3" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="5" t="s">
         <v>2</v>
       </c>
       <c r="F3" s="5" t="s">
@@ -2239,7 +2233,7 @@
       <c r="D4" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="5" t="s">
         <v>2</v>
       </c>
       <c r="F4" s="5" t="s">
@@ -2277,7 +2271,7 @@
       <c r="D5" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="5" t="s">
         <v>22</v>
       </c>
       <c r="F5" s="5" t="s">
@@ -2801,7 +2795,7 @@
       <c r="D19" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="E19" s="2" t="s">
+      <c r="E19" s="3" t="s">
         <v>66</v>
       </c>
       <c r="F19" s="3">
@@ -2839,7 +2833,7 @@
       <c r="D20" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="E20" s="2" t="s">
+      <c r="E20" s="3" t="s">
         <v>66</v>
       </c>
       <c r="F20" s="3">
@@ -2877,7 +2871,7 @@
       <c r="D21" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="E21" s="2" t="s">
+      <c r="E21" s="3" t="s">
         <v>66</v>
       </c>
       <c r="F21" s="3">
@@ -2915,7 +2909,7 @@
       <c r="D22" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="E22" s="2" t="s">
+      <c r="E22" s="3" t="s">
         <v>66</v>
       </c>
       <c r="F22" s="3">
@@ -2953,7 +2947,7 @@
       <c r="D23" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="E23" s="2" t="s">
+      <c r="E23" s="3" t="s">
         <v>66</v>
       </c>
       <c r="F23" s="3">
@@ -2991,7 +2985,7 @@
       <c r="D24" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="E24" s="2" t="s">
+      <c r="E24" s="3" t="s">
         <v>66</v>
       </c>
       <c r="F24" s="3">
@@ -3029,7 +3023,7 @@
       <c r="D25" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="E25" s="2" t="s">
+      <c r="E25" s="3" t="s">
         <v>66</v>
       </c>
       <c r="F25" s="3">
@@ -3073,7 +3067,7 @@
       <c r="D26" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="E26" s="2" t="s">
+      <c r="E26" s="3" t="s">
         <v>66</v>
       </c>
       <c r="F26" s="3">
@@ -3117,7 +3111,7 @@
       <c r="D27" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="E27" s="2" t="s">
+      <c r="E27" s="3" t="s">
         <v>66</v>
       </c>
       <c r="F27" s="3">
@@ -3161,7 +3155,7 @@
       <c r="D28" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="E28" s="2" t="s">
+      <c r="E28" s="3" t="s">
         <v>66</v>
       </c>
       <c r="F28" s="3">
@@ -3205,7 +3199,7 @@
       <c r="D29" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="E29" s="2" t="s">
+      <c r="E29" s="3" t="s">
         <v>66</v>
       </c>
       <c r="F29" s="3">
@@ -3249,7 +3243,7 @@
       <c r="D30" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="E30" s="2" t="s">
+      <c r="E30" s="3" t="s">
         <v>66</v>
       </c>
       <c r="F30" s="3">
@@ -3287,7 +3281,7 @@
       <c r="D32" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="E32" s="2" t="s">
+      <c r="E32" s="3" t="s">
         <v>103</v>
       </c>
       <c r="F32" s="3">
@@ -3325,7 +3319,7 @@
       <c r="D33" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="E33" s="2" t="s">
+      <c r="E33" s="3" t="s">
         <v>103</v>
       </c>
       <c r="F33" s="3">
@@ -3363,7 +3357,7 @@
       <c r="D34" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="E34" s="2" t="s">
+      <c r="E34" s="3" t="s">
         <v>103</v>
       </c>
       <c r="F34" s="3">
@@ -3401,7 +3395,7 @@
       <c r="D35" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="E35" s="2" t="s">
+      <c r="E35" s="3" t="s">
         <v>103</v>
       </c>
       <c r="F35" s="3">
@@ -3439,7 +3433,7 @@
       <c r="D36" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="E36" s="2" t="s">
+      <c r="E36" s="3" t="s">
         <v>103</v>
       </c>
       <c r="F36" s="3">
@@ -3477,7 +3471,7 @@
       <c r="D37" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="E37" s="2" t="s">
+      <c r="E37" s="3" t="s">
         <v>103</v>
       </c>
       <c r="F37" s="3">
@@ -3515,7 +3509,7 @@
       <c r="D38" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="E38" s="2" t="s">
+      <c r="E38" s="3" t="s">
         <v>103</v>
       </c>
       <c r="F38" s="3">
@@ -3559,7 +3553,7 @@
       <c r="D39" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="E39" s="2" t="s">
+      <c r="E39" s="3" t="s">
         <v>103</v>
       </c>
       <c r="F39" s="3">
@@ -3603,7 +3597,7 @@
       <c r="D40" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="E40" s="2" t="s">
+      <c r="E40" s="3" t="s">
         <v>103</v>
       </c>
       <c r="F40" s="3">
@@ -3647,7 +3641,7 @@
       <c r="D41" s="6" t="s">
         <v>130</v>
       </c>
-      <c r="E41" s="2" t="s">
+      <c r="E41" s="3" t="s">
         <v>103</v>
       </c>
       <c r="F41" s="3">
@@ -3691,7 +3685,7 @@
       <c r="D42" s="6" t="s">
         <v>133</v>
       </c>
-      <c r="E42" s="2" t="s">
+      <c r="E42" s="3" t="s">
         <v>103</v>
       </c>
       <c r="F42" s="3">
@@ -3735,7 +3729,7 @@
       <c r="D43" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="E43" s="2" t="s">
+      <c r="E43" s="3" t="s">
         <v>103</v>
       </c>
       <c r="F43" s="3">

--- a/Excel/ItemConfig.xlsx
+++ b/Excel/ItemConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView windowHeight="17680" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="技能" sheetId="1" r:id="rId1"/>

--- a/Excel/ItemConfig.xlsx
+++ b/Excel/ItemConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="1"/>
+    <workbookView windowHeight="17680" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="技能" sheetId="1" r:id="rId1"/>
@@ -224,7 +224,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="606" uniqueCount="313">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="618" uniqueCount="321">
   <si>
     <t>_Id</t>
   </si>
@@ -1163,6 +1163,30 @@
   </si>
   <si>
     <t>鹿血</t>
+  </si>
+  <si>
+    <t>骨弓</t>
+  </si>
+  <si>
+    <t>迷雾森林珍宝材料</t>
+  </si>
+  <si>
+    <t>骨杖</t>
+  </si>
+  <si>
+    <t>骨龙核心</t>
+  </si>
+  <si>
+    <t>獠牙</t>
+  </si>
+  <si>
+    <t>熔火地穴珍宝材料</t>
+  </si>
+  <si>
+    <t>图腾</t>
+  </si>
+  <si>
+    <t>酋长重锤</t>
   </si>
 </sst>
 </file>
@@ -7591,7 +7615,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:N17"/>
+  <dimension ref="A1:N23"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="2"/>
@@ -8030,7 +8054,8 @@
         <v>5</v>
       </c>
     </row>
-    <row r="17" customHeight="1" spans="3:11">
+    <row r="17" customHeight="1" spans="1:11">
+      <c r="A17" s="3"/>
       <c r="C17" s="3">
         <v>40000012</v>
       </c>
@@ -8054,6 +8079,167 @@
         <v>0</v>
       </c>
       <c r="K17" s="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18" customHeight="1" spans="1:11">
+      <c r="C18" s="3">
+        <v>40000013</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="E18" s="3"/>
+      <c r="F18" s="2">
+        <v>6</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="H18" s="2">
+        <v>1</v>
+      </c>
+      <c r="I18" s="2">
+        <v>99999</v>
+      </c>
+      <c r="J18" s="2">
+        <v>0</v>
+      </c>
+      <c r="K18" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" customHeight="1" spans="1:11">
+      <c r="C19" s="3">
+        <v>40000014</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="F19" s="2">
+        <v>6</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="H19" s="2">
+        <v>1</v>
+      </c>
+      <c r="I19" s="2">
+        <v>99999</v>
+      </c>
+      <c r="J19" s="2">
+        <v>0</v>
+      </c>
+      <c r="K19" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" customHeight="1" spans="1:11">
+      <c r="C20" s="3">
+        <v>40000015</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="E20" s="3"/>
+      <c r="F20" s="2">
+        <v>6</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="H20" s="2">
+        <v>1</v>
+      </c>
+      <c r="I20" s="2">
+        <v>99999</v>
+      </c>
+      <c r="J20" s="2">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="21" customHeight="1" spans="1:11">
+      <c r="C21" s="3">
+        <v>40000016</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="E21" s="3"/>
+      <c r="F21" s="2">
+        <v>6</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="H21" s="2">
+        <v>1</v>
+      </c>
+      <c r="I21" s="2">
+        <v>99999</v>
+      </c>
+      <c r="J21" s="2">
+        <v>0</v>
+      </c>
+      <c r="K21" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" customHeight="1" spans="1:11">
+      <c r="C22" s="3">
+        <v>40000017</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="E22" s="3"/>
+      <c r="F22" s="2">
+        <v>6</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="H22" s="2">
+        <v>1</v>
+      </c>
+      <c r="I22" s="2">
+        <v>99999</v>
+      </c>
+      <c r="J22" s="2">
+        <v>0</v>
+      </c>
+      <c r="K22" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" customHeight="1" spans="1:11">
+      <c r="C23" s="3">
+        <v>40000018</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="E23" s="3"/>
+      <c r="F23" s="2">
+        <v>6</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="H23" s="2">
+        <v>1</v>
+      </c>
+      <c r="I23" s="2">
+        <v>99999</v>
+      </c>
+      <c r="J23" s="2">
+        <v>0</v>
+      </c>
+      <c r="K23" s="3">
         <v>6</v>
       </c>
     </row>

--- a/Excel/ItemConfig.xlsx
+++ b/Excel/ItemConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="4"/>
+    <workbookView windowHeight="17680" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="技能" sheetId="1" r:id="rId1"/>
@@ -224,7 +224,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="618" uniqueCount="321">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="620" uniqueCount="322">
   <si>
     <t>_Id</t>
   </si>
@@ -667,6 +667,12 @@
     <t>分解传世装备获取，强化传世装备</t>
   </si>
   <si>
+    <t>传奇精华</t>
+  </si>
+  <si>
+    <t>分解传奇装备获取，传承传奇装备</t>
+  </si>
+  <si>
     <t>灵盾碎片</t>
   </si>
   <si>
@@ -884,9 +890,6 @@
   </si>
   <si>
     <t>激活上阵时装</t>
-  </si>
-  <si>
-    <t>传奇精华</t>
   </si>
   <si>
     <t>升阶传奇专属的材料</t>
@@ -3803,7 +3806,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:N116"/>
+  <dimension ref="C1:N117"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="3"/>
@@ -4106,57 +4109,57 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" s="6" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C11" s="7"/>
-      <c r="D11" s="7"/>
+    <row r="11" s="3" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C11" s="3">
+        <v>5006</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>147</v>
+      </c>
       <c r="E11" s="3"/>
-      <c r="F11" s="7"/>
-      <c r="G11" s="3"/>
-      <c r="H11" s="3"/>
-      <c r="I11" s="3"/>
-      <c r="J11" s="3"/>
-      <c r="K11" s="3"/>
+      <c r="F11" s="3">
+        <v>5</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="H11" s="3">
+        <v>1</v>
+      </c>
+      <c r="I11" s="3">
+        <v>99999999</v>
+      </c>
+      <c r="J11" s="3">
+        <v>0</v>
+      </c>
+      <c r="K11" s="3">
+        <v>7</v>
+      </c>
       <c r="L11" s="3"/>
-      <c r="M11" s="3"/>
-      <c r="N11" s="3"/>
+      <c r="M11" s="3">
+        <v>0</v>
+      </c>
+      <c r="N11" s="3">
+        <v>0</v>
+      </c>
     </row>
     <row r="12" s="6" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C12" s="8">
-        <v>5011</v>
-      </c>
-      <c r="D12" s="9" t="s">
-        <v>147</v>
-      </c>
-      <c r="E12" s="2"/>
-      <c r="F12" s="10">
-        <v>5</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="H12" s="3">
-        <v>1</v>
-      </c>
-      <c r="I12" s="3">
-        <v>99999999</v>
-      </c>
-      <c r="J12" s="3">
-        <v>0</v>
-      </c>
-      <c r="K12" s="3">
-        <v>3</v>
-      </c>
+      <c r="C12" s="7"/>
+      <c r="D12" s="7"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="7"/>
+      <c r="G12" s="3"/>
+      <c r="H12" s="3"/>
+      <c r="I12" s="3"/>
+      <c r="J12" s="3"/>
+      <c r="K12" s="3"/>
       <c r="L12" s="3"/>
-      <c r="M12" s="3">
-        <v>0</v>
-      </c>
-      <c r="N12" s="3">
-        <v>0</v>
-      </c>
+      <c r="M12" s="3"/>
+      <c r="N12" s="3"/>
     </row>
     <row r="13" s="6" customFormat="1" customHeight="1" spans="3:14">
       <c r="C13" s="8">
-        <v>5012</v>
+        <v>5011</v>
       </c>
       <c r="D13" s="9" t="s">
         <v>149</v>
@@ -4190,12 +4193,12 @@
     </row>
     <row r="14" s="6" customFormat="1" customHeight="1" spans="3:14">
       <c r="C14" s="8">
-        <v>5013</v>
+        <v>5012</v>
       </c>
       <c r="D14" s="9" t="s">
         <v>151</v>
       </c>
-      <c r="E14" s="3"/>
+      <c r="E14" s="2"/>
       <c r="F14" s="10">
         <v>5</v>
       </c>
@@ -4224,7 +4227,7 @@
     </row>
     <row r="15" s="6" customFormat="1" customHeight="1" spans="3:14">
       <c r="C15" s="8">
-        <v>5014</v>
+        <v>5013</v>
       </c>
       <c r="D15" s="9" t="s">
         <v>153</v>
@@ -4257,60 +4260,61 @@
       </c>
     </row>
     <row r="16" s="6" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
+      <c r="C16" s="8">
+        <v>5014</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>155</v>
+      </c>
       <c r="E16" s="3"/>
-      <c r="F16" s="7"/>
-      <c r="G16" s="7"/>
-      <c r="H16" s="7"/>
-      <c r="I16" s="7"/>
-      <c r="J16" s="7"/>
-      <c r="K16" s="7"/>
-      <c r="L16" s="7"/>
-      <c r="M16" s="7"/>
-      <c r="N16" s="7"/>
-    </row>
-    <row r="17" s="3" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C17" s="3">
-        <v>7001</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>155</v>
-      </c>
+      <c r="F16" s="10">
+        <v>5</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="H16" s="3">
+        <v>1</v>
+      </c>
+      <c r="I16" s="3">
+        <v>99999999</v>
+      </c>
+      <c r="J16" s="3">
+        <v>0</v>
+      </c>
+      <c r="K16" s="3">
+        <v>3</v>
+      </c>
+      <c r="L16" s="3"/>
+      <c r="M16" s="3">
+        <v>0</v>
+      </c>
+      <c r="N16" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" s="6" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C17" s="7"/>
+      <c r="D17" s="7"/>
       <c r="E17" s="3"/>
-      <c r="F17" s="3">
-        <v>7</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="H17" s="3">
-        <v>1</v>
-      </c>
-      <c r="I17" s="3">
-        <v>9999999</v>
-      </c>
-      <c r="J17" s="3">
-        <v>0</v>
-      </c>
-      <c r="K17" s="3">
-        <v>6</v>
-      </c>
-      <c r="M17" s="3">
-        <v>0</v>
-      </c>
-      <c r="N17" s="3">
-        <v>0</v>
-      </c>
+      <c r="F17" s="7"/>
+      <c r="G17" s="7"/>
+      <c r="H17" s="7"/>
+      <c r="I17" s="7"/>
+      <c r="J17" s="7"/>
+      <c r="K17" s="7"/>
+      <c r="L17" s="7"/>
+      <c r="M17" s="7"/>
+      <c r="N17" s="7"/>
     </row>
     <row r="18" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C18" s="3">
-        <v>7002</v>
+        <v>7001</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="E18" s="2"/>
+      <c r="E18" s="3"/>
       <c r="F18" s="3">
         <v>7</v>
       </c>
@@ -4327,67 +4331,67 @@
         <v>0</v>
       </c>
       <c r="K18" s="3">
+        <v>6</v>
+      </c>
+      <c r="M18" s="3">
+        <v>0</v>
+      </c>
+      <c r="N18" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" s="3" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C19" s="3">
+        <v>7002</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="E19" s="2"/>
+      <c r="F19" s="3">
         <v>7</v>
       </c>
-      <c r="L18" s="3">
-        <v>0</v>
-      </c>
-      <c r="M18" s="3">
-        <v>0</v>
-      </c>
-      <c r="N18" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C20" s="3"/>
-      <c r="D20" s="3"/>
-      <c r="E20" s="2"/>
-      <c r="F20" s="3"/>
-      <c r="G20" s="3"/>
-      <c r="H20" s="3"/>
-      <c r="I20" s="3"/>
-      <c r="J20" s="3"/>
-      <c r="K20" s="3"/>
-      <c r="M20" s="3"/>
-      <c r="N20" s="3"/>
-    </row>
-    <row r="21" s="3" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C21" s="3">
-        <v>4001</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>159</v>
-      </c>
+      <c r="G19" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="H19" s="3">
+        <v>1</v>
+      </c>
+      <c r="I19" s="3">
+        <v>9999999</v>
+      </c>
+      <c r="J19" s="3">
+        <v>0</v>
+      </c>
+      <c r="K19" s="3">
+        <v>7</v>
+      </c>
+      <c r="L19" s="3">
+        <v>0</v>
+      </c>
+      <c r="M19" s="3">
+        <v>0</v>
+      </c>
+      <c r="N19" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C21" s="3"/>
+      <c r="D21" s="3"/>
       <c r="E21" s="2"/>
-      <c r="F21" s="3">
-        <v>5</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="H21" s="3">
-        <v>1</v>
-      </c>
-      <c r="I21" s="3">
-        <v>99999999999</v>
-      </c>
-      <c r="J21" s="3">
-        <v>0</v>
-      </c>
-      <c r="K21" s="3">
-        <v>5</v>
-      </c>
-      <c r="M21" s="3">
-        <v>0</v>
-      </c>
-      <c r="N21" s="3">
-        <v>0</v>
-      </c>
+      <c r="F21" s="3"/>
+      <c r="G21" s="3"/>
+      <c r="H21" s="3"/>
+      <c r="I21" s="3"/>
+      <c r="J21" s="3"/>
+      <c r="K21" s="3"/>
+      <c r="M21" s="3"/>
+      <c r="N21" s="3"/>
     </row>
     <row r="22" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C22" s="3">
-        <v>4002</v>
+        <v>4001</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>161</v>
@@ -4420,14 +4424,14 @@
     </row>
     <row r="23" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C23" s="3">
-        <v>4003</v>
+        <v>4002</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>163</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" s="3">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>164</v>
@@ -4436,7 +4440,7 @@
         <v>1</v>
       </c>
       <c r="I23" s="3">
-        <v>9999999</v>
+        <v>99999999999</v>
       </c>
       <c r="J23" s="3">
         <v>0</v>
@@ -4453,14 +4457,14 @@
     </row>
     <row r="24" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C24" s="3">
-        <v>4004</v>
+        <v>4003</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>165</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" s="3">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>166</v>
@@ -4486,7 +4490,7 @@
     </row>
     <row r="25" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C25" s="3">
-        <v>4005</v>
+        <v>4004</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>167</v>
@@ -4519,7 +4523,7 @@
     </row>
     <row r="26" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C26" s="3">
-        <v>4006</v>
+        <v>4005</v>
       </c>
       <c r="D26" s="3" t="s">
         <v>169</v>
@@ -4535,16 +4539,13 @@
         <v>1</v>
       </c>
       <c r="I26" s="3">
-        <v>99999999</v>
+        <v>9999999</v>
       </c>
       <c r="J26" s="3">
         <v>0</v>
       </c>
       <c r="K26" s="3">
         <v>5</v>
-      </c>
-      <c r="L26" s="3">
-        <v>0</v>
       </c>
       <c r="M26" s="3">
         <v>0</v>
@@ -4555,7 +4556,7 @@
     </row>
     <row r="27" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C27" s="3">
-        <v>4007</v>
+        <v>4006</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>171</v>
@@ -4571,13 +4572,16 @@
         <v>1</v>
       </c>
       <c r="I27" s="3">
-        <v>9999999999</v>
+        <v>99999999</v>
       </c>
       <c r="J27" s="3">
         <v>0</v>
       </c>
       <c r="K27" s="3">
         <v>5</v>
+      </c>
+      <c r="L27" s="3">
+        <v>0</v>
       </c>
       <c r="M27" s="3">
         <v>0</v>
@@ -4588,7 +4592,7 @@
     </row>
     <row r="28" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C28" s="3">
-        <v>4008</v>
+        <v>4007</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>173</v>
@@ -4604,7 +4608,7 @@
         <v>1</v>
       </c>
       <c r="I28" s="3">
-        <v>9999999</v>
+        <v>9999999999</v>
       </c>
       <c r="J28" s="3">
         <v>0</v>
@@ -4621,7 +4625,7 @@
     </row>
     <row r="29" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C29" s="3">
-        <v>4009</v>
+        <v>4008</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>175</v>
@@ -4654,7 +4658,7 @@
     </row>
     <row r="30" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C30" s="3">
-        <v>4010</v>
+        <v>4009</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>177</v>
@@ -4687,7 +4691,7 @@
     </row>
     <row r="31" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C31" s="3">
-        <v>4011</v>
+        <v>4010</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>179</v>
@@ -4709,58 +4713,58 @@
         <v>0</v>
       </c>
       <c r="K31" s="3">
+        <v>5</v>
+      </c>
+      <c r="M31" s="3">
+        <v>0</v>
+      </c>
+      <c r="N31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" s="3" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C32" s="3">
+        <v>4011</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="E32" s="2"/>
+      <c r="F32" s="3">
+        <v>5</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="H32" s="3">
+        <v>1</v>
+      </c>
+      <c r="I32" s="3">
+        <v>9999999</v>
+      </c>
+      <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
         <v>6</v>
       </c>
-      <c r="M31" s="3">
-        <v>0</v>
-      </c>
-      <c r="N31" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" s="3" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C33" s="3">
-        <v>4013</v>
-      </c>
-      <c r="D33" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="E33" s="2"/>
-      <c r="F33" s="3">
-        <v>9</v>
-      </c>
-      <c r="G33" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="H33" s="3">
-        <v>1</v>
-      </c>
-      <c r="I33" s="3">
-        <v>9999999</v>
-      </c>
-      <c r="J33" s="3">
-        <v>0</v>
-      </c>
-      <c r="K33" s="3">
-        <v>5</v>
-      </c>
-      <c r="M33" s="3">
-        <v>0</v>
-      </c>
-      <c r="N33" s="3">
+      <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="34" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C34" s="3">
-        <v>4015</v>
+        <v>4013</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>183</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" s="3">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G34" s="3" t="s">
         <v>184</v>
@@ -4775,7 +4779,7 @@
         <v>0</v>
       </c>
       <c r="K34" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M34" s="3">
         <v>0</v>
@@ -4786,7 +4790,7 @@
     </row>
     <row r="35" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C35" s="3">
-        <v>4016</v>
+        <v>4015</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>185</v>
@@ -4819,14 +4823,14 @@
     </row>
     <row r="36" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C36" s="3">
-        <v>4017</v>
+        <v>4016</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>187</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" s="3">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G36" s="3" t="s">
         <v>188</v>
@@ -4841,7 +4845,7 @@
         <v>0</v>
       </c>
       <c r="K36" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M36" s="3">
         <v>0</v>
@@ -4852,14 +4856,14 @@
     </row>
     <row r="37" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C37" s="3">
-        <v>4018</v>
+        <v>4017</v>
       </c>
       <c r="D37" s="3" t="s">
         <v>189</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" s="3">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G37" s="3" t="s">
         <v>190</v>
@@ -4874,7 +4878,7 @@
         <v>0</v>
       </c>
       <c r="K37" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M37" s="3">
         <v>0</v>
@@ -4885,7 +4889,7 @@
     </row>
     <row r="38" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C38" s="3">
-        <v>4019</v>
+        <v>4018</v>
       </c>
       <c r="D38" s="3" t="s">
         <v>191</v>
@@ -4907,51 +4911,51 @@
         <v>0</v>
       </c>
       <c r="K38" s="3">
+        <v>6</v>
+      </c>
+      <c r="M38" s="3">
+        <v>0</v>
+      </c>
+      <c r="N38" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" s="3" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C39" s="3">
+        <v>4019</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="E39" s="2"/>
+      <c r="F39" s="3">
+        <v>5</v>
+      </c>
+      <c r="G39" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="H39" s="3">
+        <v>1</v>
+      </c>
+      <c r="I39" s="3">
+        <v>9999999</v>
+      </c>
+      <c r="J39" s="3">
+        <v>0</v>
+      </c>
+      <c r="K39" s="3">
         <v>7</v>
       </c>
-      <c r="M38" s="3">
-        <v>0</v>
-      </c>
-      <c r="N38" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" s="3" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C40" s="3">
-        <v>4021</v>
-      </c>
-      <c r="D40" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="E40" s="2"/>
-      <c r="F40" s="3">
-        <v>5</v>
-      </c>
-      <c r="G40" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="H40" s="3">
-        <v>1</v>
-      </c>
-      <c r="I40" s="3">
-        <v>9999999</v>
-      </c>
-      <c r="J40" s="3">
-        <v>0</v>
-      </c>
-      <c r="K40" s="3">
-        <v>6</v>
-      </c>
-      <c r="M40" s="3">
-        <v>0</v>
-      </c>
-      <c r="N40" s="3">
+      <c r="M39" s="3">
+        <v>0</v>
+      </c>
+      <c r="N39" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="41" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C41" s="3">
-        <v>4022</v>
+        <v>4021</v>
       </c>
       <c r="D41" s="3" t="s">
         <v>195</v>
@@ -4973,7 +4977,7 @@
         <v>0</v>
       </c>
       <c r="K41" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M41" s="3">
         <v>0</v>
@@ -4984,7 +4988,7 @@
     </row>
     <row r="42" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C42" s="3">
-        <v>4023</v>
+        <v>4022</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>197</v>
@@ -5017,7 +5021,7 @@
     </row>
     <row r="43" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C43" s="3">
-        <v>4024</v>
+        <v>4023</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>199</v>
@@ -5039,7 +5043,7 @@
         <v>0</v>
       </c>
       <c r="K43" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M43" s="3">
         <v>0</v>
@@ -5050,7 +5054,7 @@
     </row>
     <row r="44" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C44" s="3">
-        <v>4025</v>
+        <v>4024</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>201</v>
@@ -5072,7 +5076,7 @@
         <v>0</v>
       </c>
       <c r="K44" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -5083,7 +5087,7 @@
     </row>
     <row r="45" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C45" s="3">
-        <v>4026</v>
+        <v>4025</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>203</v>
@@ -5105,7 +5109,7 @@
         <v>0</v>
       </c>
       <c r="K45" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M45" s="3">
         <v>0</v>
@@ -5116,7 +5120,7 @@
     </row>
     <row r="46" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C46" s="3">
-        <v>4027</v>
+        <v>4026</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>205</v>
@@ -5138,7 +5142,7 @@
         <v>0</v>
       </c>
       <c r="K46" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M46" s="3">
         <v>0</v>
@@ -5149,7 +5153,7 @@
     </row>
     <row r="47" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C47" s="3">
-        <v>4028</v>
+        <v>4027</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>207</v>
@@ -5182,7 +5186,7 @@
     </row>
     <row r="48" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C48" s="3">
-        <v>4029</v>
+        <v>4028</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>209</v>
@@ -5215,7 +5219,7 @@
     </row>
     <row r="49" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C49" s="3">
-        <v>4030</v>
+        <v>4029</v>
       </c>
       <c r="D49" s="3" t="s">
         <v>211</v>
@@ -5248,7 +5252,7 @@
     </row>
     <row r="50" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C50" s="3">
-        <v>4031</v>
+        <v>4030</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>213</v>
@@ -5281,7 +5285,7 @@
     </row>
     <row r="51" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C51" s="3">
-        <v>4032</v>
+        <v>4031</v>
       </c>
       <c r="D51" s="3" t="s">
         <v>215</v>
@@ -5314,7 +5318,7 @@
     </row>
     <row r="52" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C52" s="3">
-        <v>4033</v>
+        <v>4032</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>217</v>
@@ -5324,7 +5328,7 @@
         <v>5</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>186</v>
+        <v>218</v>
       </c>
       <c r="H52" s="3">
         <v>1</v>
@@ -5336,7 +5340,7 @@
         <v>0</v>
       </c>
       <c r="K52" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M52" s="3">
         <v>0</v>
@@ -5347,17 +5351,17 @@
     </row>
     <row r="53" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C53" s="3">
-        <v>4034</v>
+        <v>4033</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" s="3">
         <v>5</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>219</v>
+        <v>188</v>
       </c>
       <c r="H53" s="3">
         <v>1</v>
@@ -5369,7 +5373,7 @@
         <v>0</v>
       </c>
       <c r="K53" s="3">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M53" s="3">
         <v>0</v>
@@ -5380,7 +5384,7 @@
     </row>
     <row r="54" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C54" s="3">
-        <v>4035</v>
+        <v>4034</v>
       </c>
       <c r="D54" s="3" t="s">
         <v>220</v>
@@ -5402,7 +5406,7 @@
         <v>0</v>
       </c>
       <c r="K54" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M54" s="3">
         <v>0</v>
@@ -5413,17 +5417,17 @@
     </row>
     <row r="55" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C55" s="3">
-        <v>4037</v>
+        <v>4035</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>222</v>
+        <v>147</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" s="3">
         <v>5</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="H55" s="3">
         <v>1</v>
@@ -5435,7 +5439,7 @@
         <v>0</v>
       </c>
       <c r="K55" s="3">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="M55" s="3">
         <v>0</v>
@@ -5446,17 +5450,17 @@
     </row>
     <row r="56" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C56" s="3">
-        <v>4038</v>
+        <v>4037</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" s="3">
         <v>5</v>
       </c>
       <c r="G56" s="3" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H56" s="3">
         <v>1</v>
@@ -5479,17 +5483,17 @@
     </row>
     <row r="57" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C57" s="3">
-        <v>4039</v>
+        <v>4038</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" s="3">
         <v>5</v>
       </c>
       <c r="G57" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H57" s="3">
         <v>1</v>
@@ -5501,7 +5505,7 @@
         <v>0</v>
       </c>
       <c r="K57" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M57" s="3">
         <v>0</v>
@@ -5512,17 +5516,17 @@
     </row>
     <row r="58" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C58" s="3">
-        <v>4040</v>
+        <v>4039</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" s="3">
         <v>5</v>
       </c>
       <c r="G58" s="3" t="s">
-        <v>186</v>
+        <v>228</v>
       </c>
       <c r="H58" s="3">
         <v>1</v>
@@ -5534,7 +5538,7 @@
         <v>0</v>
       </c>
       <c r="K58" s="3">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M58" s="3">
         <v>0</v>
@@ -5545,7 +5549,7 @@
     </row>
     <row r="59" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C59" s="3">
-        <v>4041</v>
+        <v>4040</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>229</v>
@@ -5555,7 +5559,7 @@
         <v>5</v>
       </c>
       <c r="G59" s="3" t="s">
-        <v>230</v>
+        <v>188</v>
       </c>
       <c r="H59" s="3">
         <v>1</v>
@@ -5567,7 +5571,7 @@
         <v>0</v>
       </c>
       <c r="K59" s="3">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M59" s="3">
         <v>0</v>
@@ -5578,29 +5582,29 @@
     </row>
     <row r="60" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C60" s="3">
-        <v>4042</v>
+        <v>4041</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" s="3">
         <v>5</v>
       </c>
       <c r="G60" s="3" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="H60" s="3">
         <v>1</v>
       </c>
       <c r="I60" s="3">
-        <v>1999999999</v>
+        <v>9999999</v>
       </c>
       <c r="J60" s="3">
         <v>0</v>
       </c>
       <c r="K60" s="3">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="M60" s="3">
         <v>0</v>
@@ -5611,29 +5615,29 @@
     </row>
     <row r="61" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C61" s="3">
-        <v>4043</v>
+        <v>4042</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" s="3">
         <v>5</v>
       </c>
       <c r="G61" s="3" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H61" s="3">
         <v>1</v>
       </c>
       <c r="I61" s="3">
-        <v>9999999</v>
+        <v>1999999999</v>
       </c>
       <c r="J61" s="3">
         <v>0</v>
       </c>
       <c r="K61" s="3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M61" s="3">
         <v>0</v>
@@ -5644,7 +5648,7 @@
     </row>
     <row r="62" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C62" s="3">
-        <v>4044</v>
+        <v>4043</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>234</v>
@@ -5654,7 +5658,7 @@
         <v>5</v>
       </c>
       <c r="G62" s="3" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="H62" s="3">
         <v>1</v>
@@ -5666,74 +5670,74 @@
         <v>0</v>
       </c>
       <c r="K62" s="3">
+        <v>7</v>
+      </c>
+      <c r="M62" s="3">
+        <v>0</v>
+      </c>
+      <c r="N62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" s="3" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C63" s="3">
+        <v>4044</v>
+      </c>
+      <c r="D63" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="E63" s="2"/>
+      <c r="F63" s="3">
+        <v>5</v>
+      </c>
+      <c r="G63" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="H63" s="3">
+        <v>1</v>
+      </c>
+      <c r="I63" s="3">
+        <v>9999999</v>
+      </c>
+      <c r="J63" s="3">
+        <v>0</v>
+      </c>
+      <c r="K63" s="3">
         <v>9</v>
       </c>
-      <c r="M62" s="3">
-        <v>0</v>
-      </c>
-      <c r="N62" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C63" s="3"/>
-      <c r="D63" s="3"/>
-      <c r="E63" s="2"/>
-      <c r="F63" s="3"/>
-      <c r="G63" s="3"/>
-      <c r="H63" s="3"/>
-      <c r="I63" s="3"/>
-      <c r="J63" s="3"/>
-      <c r="K63" s="3"/>
-      <c r="M63" s="3"/>
-      <c r="N63" s="3"/>
-    </row>
-    <row r="64" s="3" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C64" s="3">
-        <v>4101</v>
-      </c>
-      <c r="D64" s="3" t="s">
-        <v>236</v>
-      </c>
+      <c r="M63" s="3">
+        <v>0</v>
+      </c>
+      <c r="N63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C64" s="3"/>
+      <c r="D64" s="3"/>
       <c r="E64" s="2"/>
-      <c r="F64" s="3">
-        <v>5</v>
-      </c>
-      <c r="G64" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="H64" s="3">
-        <v>1</v>
-      </c>
-      <c r="I64" s="3">
-        <v>9999999</v>
-      </c>
-      <c r="J64" s="3">
-        <v>0</v>
-      </c>
-      <c r="K64" s="3">
-        <v>5</v>
-      </c>
-      <c r="M64" s="3">
-        <v>0</v>
-      </c>
-      <c r="N64" s="3">
-        <v>0</v>
-      </c>
+      <c r="F64" s="3"/>
+      <c r="G64" s="3"/>
+      <c r="H64" s="3"/>
+      <c r="I64" s="3"/>
+      <c r="J64" s="3"/>
+      <c r="K64" s="3"/>
+      <c r="M64" s="3"/>
+      <c r="N64" s="3"/>
     </row>
     <row r="65" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C65" s="3">
-        <v>4111</v>
+        <v>4101</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" s="3">
         <v>5</v>
       </c>
       <c r="G65" s="3" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="H65" s="3">
         <v>1</v>
@@ -5756,17 +5760,17 @@
     </row>
     <row r="66" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C66" s="3">
-        <v>4112</v>
+        <v>4111</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" s="3">
         <v>5</v>
       </c>
       <c r="G66" s="3" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H66" s="3">
         <v>1</v>
@@ -5778,7 +5782,7 @@
         <v>0</v>
       </c>
       <c r="K66" s="3">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="M66" s="3">
         <v>0</v>
@@ -5789,17 +5793,17 @@
     </row>
     <row r="67" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C67" s="3">
-        <v>4113</v>
+        <v>4112</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" s="3">
         <v>5</v>
       </c>
       <c r="G67" s="3" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="H67" s="3">
         <v>1</v>
@@ -5811,107 +5815,107 @@
         <v>0</v>
       </c>
       <c r="K67" s="3">
+        <v>8</v>
+      </c>
+      <c r="M67" s="3">
+        <v>0</v>
+      </c>
+      <c r="N67" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" s="3" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C68" s="3">
+        <v>4113</v>
+      </c>
+      <c r="D68" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="E68" s="2"/>
+      <c r="F68" s="3">
+        <v>5</v>
+      </c>
+      <c r="G68" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="H68" s="3">
+        <v>1</v>
+      </c>
+      <c r="I68" s="3">
+        <v>9999999</v>
+      </c>
+      <c r="J68" s="3">
+        <v>0</v>
+      </c>
+      <c r="K68" s="3">
         <v>7</v>
       </c>
-      <c r="M67" s="3">
-        <v>0</v>
-      </c>
-      <c r="N67" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C68" s="3"/>
-      <c r="D68" s="3"/>
-      <c r="E68" s="2"/>
-      <c r="F68" s="3"/>
-      <c r="G68" s="3"/>
-      <c r="H68" s="3"/>
-      <c r="I68" s="3"/>
-      <c r="J68" s="3"/>
-      <c r="K68" s="3"/>
-      <c r="M68" s="3"/>
-      <c r="N68" s="3"/>
-    </row>
-    <row r="69" s="3" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C69" s="3">
+      <c r="M68" s="3">
+        <v>0</v>
+      </c>
+      <c r="N68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C69" s="3"/>
+      <c r="D69" s="3"/>
+      <c r="E69" s="2"/>
+      <c r="F69" s="3"/>
+      <c r="G69" s="3"/>
+      <c r="H69" s="3"/>
+      <c r="I69" s="3"/>
+      <c r="J69" s="3"/>
+      <c r="K69" s="3"/>
+      <c r="M69" s="3"/>
+      <c r="N69" s="3"/>
+    </row>
+    <row r="70" s="3" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C70" s="3">
         <v>4201</v>
       </c>
-      <c r="D69" s="3" t="s">
-        <v>244</v>
-      </c>
-      <c r="E69" s="2"/>
-      <c r="F69" s="3">
-        <v>5</v>
-      </c>
-      <c r="G69" s="3" t="s">
+      <c r="D70" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="H69" s="3">
-        <v>1</v>
-      </c>
-      <c r="I69" s="3">
+      <c r="E70" s="2"/>
+      <c r="F70" s="3">
+        <v>5</v>
+      </c>
+      <c r="G70" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="H70" s="3">
+        <v>1</v>
+      </c>
+      <c r="I70" s="3">
         <v>99999999</v>
       </c>
-      <c r="J69" s="3">
-        <v>0</v>
-      </c>
-      <c r="K69" s="3">
-        <v>5</v>
-      </c>
-      <c r="M69" s="3">
+      <c r="J70" s="3">
+        <v>0</v>
+      </c>
+      <c r="K70" s="3">
+        <v>5</v>
+      </c>
+      <c r="M70" s="3">
         <v>4002</v>
       </c>
-      <c r="N69" s="3">
+      <c r="N70" s="3">
         <v>1000</v>
-      </c>
-    </row>
-    <row r="74" s="3" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C74" s="3">
-        <v>8001</v>
-      </c>
-      <c r="D74" s="3" t="s">
-        <v>246</v>
-      </c>
-      <c r="E74" s="2"/>
-      <c r="F74" s="3">
-        <v>5</v>
-      </c>
-      <c r="G74" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="H74" s="3">
-        <v>1</v>
-      </c>
-      <c r="I74" s="3">
-        <v>9999999</v>
-      </c>
-      <c r="J74" s="3">
-        <v>0</v>
-      </c>
-      <c r="K74" s="3">
-        <v>6</v>
-      </c>
-      <c r="M74" s="3">
-        <v>0</v>
-      </c>
-      <c r="N74" s="3">
-        <v>0</v>
       </c>
     </row>
     <row r="75" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C75" s="3">
-        <v>8002</v>
+        <v>8001</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" s="3">
         <v>5</v>
       </c>
       <c r="G75" s="3" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H75" s="3">
         <v>1</v>
@@ -5934,7 +5938,7 @@
     </row>
     <row r="76" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C76" s="3">
-        <v>8003</v>
+        <v>8002</v>
       </c>
       <c r="D76" s="3" t="s">
         <v>249</v>
@@ -5944,7 +5948,7 @@
         <v>5</v>
       </c>
       <c r="G76" s="3" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H76" s="3">
         <v>1</v>
@@ -5967,7 +5971,7 @@
     </row>
     <row r="77" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C77" s="3">
-        <v>8004</v>
+        <v>8003</v>
       </c>
       <c r="D77" s="3" t="s">
         <v>250</v>
@@ -5977,7 +5981,7 @@
         <v>5</v>
       </c>
       <c r="G77" s="3" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H77" s="3">
         <v>1</v>
@@ -6000,7 +6004,7 @@
     </row>
     <row r="78" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C78" s="3">
-        <v>8005</v>
+        <v>8004</v>
       </c>
       <c r="D78" s="3" t="s">
         <v>251</v>
@@ -6010,7 +6014,7 @@
         <v>5</v>
       </c>
       <c r="G78" s="3" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H78" s="3">
         <v>1</v>
@@ -6033,7 +6037,7 @@
     </row>
     <row r="79" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C79" s="3">
-        <v>8006</v>
+        <v>8005</v>
       </c>
       <c r="D79" s="3" t="s">
         <v>252</v>
@@ -6043,7 +6047,7 @@
         <v>5</v>
       </c>
       <c r="G79" s="3" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H79" s="3">
         <v>1</v>
@@ -6066,7 +6070,7 @@
     </row>
     <row r="80" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C80" s="3">
-        <v>8007</v>
+        <v>8006</v>
       </c>
       <c r="D80" s="3" t="s">
         <v>253</v>
@@ -6076,7 +6080,7 @@
         <v>5</v>
       </c>
       <c r="G80" s="3" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H80" s="3">
         <v>1</v>
@@ -6099,7 +6103,7 @@
     </row>
     <row r="81" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C81" s="3">
-        <v>8008</v>
+        <v>8007</v>
       </c>
       <c r="D81" s="3" t="s">
         <v>254</v>
@@ -6109,7 +6113,7 @@
         <v>5</v>
       </c>
       <c r="G81" s="3" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H81" s="3">
         <v>1</v>
@@ -6132,7 +6136,7 @@
     </row>
     <row r="82" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C82" s="3">
-        <v>8009</v>
+        <v>8008</v>
       </c>
       <c r="D82" s="3" t="s">
         <v>255</v>
@@ -6142,7 +6146,7 @@
         <v>5</v>
       </c>
       <c r="G82" s="3" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H82" s="3">
         <v>1</v>
@@ -6165,7 +6169,7 @@
     </row>
     <row r="83" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C83" s="3">
-        <v>8010</v>
+        <v>8009</v>
       </c>
       <c r="D83" s="3" t="s">
         <v>256</v>
@@ -6175,7 +6179,7 @@
         <v>5</v>
       </c>
       <c r="G83" s="3" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H83" s="3">
         <v>1</v>
@@ -6196,52 +6200,52 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" s="3" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C85" s="3">
-        <v>8101</v>
-      </c>
-      <c r="D85" s="9" t="s">
+    <row r="84" s="3" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C84" s="3">
+        <v>8010</v>
+      </c>
+      <c r="D84" s="3" t="s">
         <v>257</v>
       </c>
-      <c r="E85" s="2"/>
-      <c r="F85" s="3">
-        <v>5</v>
-      </c>
-      <c r="G85" s="3" t="s">
-        <v>258</v>
-      </c>
-      <c r="H85" s="3">
-        <v>1</v>
-      </c>
-      <c r="I85" s="3">
+      <c r="E84" s="2"/>
+      <c r="F84" s="3">
+        <v>5</v>
+      </c>
+      <c r="G84" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="H84" s="3">
+        <v>1</v>
+      </c>
+      <c r="I84" s="3">
         <v>9999999</v>
       </c>
-      <c r="J85" s="3">
-        <v>0</v>
-      </c>
-      <c r="K85" s="3">
-        <v>7</v>
-      </c>
-      <c r="M85" s="3">
-        <v>0</v>
-      </c>
-      <c r="N85" s="3">
+      <c r="J84" s="3">
+        <v>0</v>
+      </c>
+      <c r="K84" s="3">
+        <v>6</v>
+      </c>
+      <c r="M84" s="3">
+        <v>0</v>
+      </c>
+      <c r="N84" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="86" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C86" s="3">
-        <v>8102</v>
+        <v>8101</v>
       </c>
       <c r="D86" s="9" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" s="3">
         <v>5</v>
       </c>
       <c r="G86" s="3" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H86" s="3">
         <v>1</v>
@@ -6264,7 +6268,7 @@
     </row>
     <row r="87" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C87" s="3">
-        <v>8103</v>
+        <v>8102</v>
       </c>
       <c r="D87" s="9" t="s">
         <v>260</v>
@@ -6274,7 +6278,7 @@
         <v>5</v>
       </c>
       <c r="G87" s="3" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H87" s="3">
         <v>1</v>
@@ -6297,7 +6301,7 @@
     </row>
     <row r="88" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C88" s="3">
-        <v>8104</v>
+        <v>8103</v>
       </c>
       <c r="D88" s="9" t="s">
         <v>261</v>
@@ -6307,7 +6311,7 @@
         <v>5</v>
       </c>
       <c r="G88" s="3" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H88" s="3">
         <v>1</v>
@@ -6330,7 +6334,7 @@
     </row>
     <row r="89" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C89" s="3">
-        <v>8105</v>
+        <v>8104</v>
       </c>
       <c r="D89" s="9" t="s">
         <v>262</v>
@@ -6340,7 +6344,7 @@
         <v>5</v>
       </c>
       <c r="G89" s="3" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H89" s="3">
         <v>1</v>
@@ -6363,7 +6367,7 @@
     </row>
     <row r="90" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C90" s="3">
-        <v>8106</v>
+        <v>8105</v>
       </c>
       <c r="D90" s="9" t="s">
         <v>263</v>
@@ -6373,7 +6377,7 @@
         <v>5</v>
       </c>
       <c r="G90" s="3" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H90" s="3">
         <v>1</v>
@@ -6396,7 +6400,7 @@
     </row>
     <row r="91" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C91" s="3">
-        <v>8107</v>
+        <v>8106</v>
       </c>
       <c r="D91" s="9" t="s">
         <v>264</v>
@@ -6406,7 +6410,7 @@
         <v>5</v>
       </c>
       <c r="G91" s="3" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H91" s="3">
         <v>1</v>
@@ -6429,7 +6433,7 @@
     </row>
     <row r="92" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C92" s="3">
-        <v>8108</v>
+        <v>8107</v>
       </c>
       <c r="D92" s="9" t="s">
         <v>265</v>
@@ -6439,7 +6443,7 @@
         <v>5</v>
       </c>
       <c r="G92" s="3" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H92" s="3">
         <v>1</v>
@@ -6460,53 +6464,51 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" customHeight="1" spans="3:14">
-      <c r="C94" s="3">
-        <v>8201</v>
-      </c>
-      <c r="D94" s="9" t="s">
+    <row r="93" s="3" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C93" s="3">
+        <v>8108</v>
+      </c>
+      <c r="D93" s="9" t="s">
         <v>266</v>
       </c>
-      <c r="F94" s="3">
-        <v>16</v>
-      </c>
-      <c r="G94" s="3" t="s">
-        <v>267</v>
-      </c>
-      <c r="H94" s="3">
-        <v>1</v>
-      </c>
-      <c r="I94" s="3">
-        <v>1</v>
-      </c>
-      <c r="J94" s="3">
-        <v>0</v>
-      </c>
-      <c r="K94" s="3">
-        <v>1</v>
-      </c>
-      <c r="L94" s="3">
-        <v>0</v>
-      </c>
-      <c r="M94" s="3">
-        <v>0</v>
-      </c>
-      <c r="N94" s="3">
+      <c r="E93" s="2"/>
+      <c r="F93" s="3">
+        <v>5</v>
+      </c>
+      <c r="G93" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="H93" s="3">
+        <v>1</v>
+      </c>
+      <c r="I93" s="3">
+        <v>9999999</v>
+      </c>
+      <c r="J93" s="3">
+        <v>0</v>
+      </c>
+      <c r="K93" s="3">
+        <v>7</v>
+      </c>
+      <c r="M93" s="3">
+        <v>0</v>
+      </c>
+      <c r="N93" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="95" customHeight="1" spans="3:14">
       <c r="C95" s="3">
-        <v>8202</v>
+        <v>8201</v>
       </c>
       <c r="D95" s="9" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="F95" s="3">
         <v>16</v>
       </c>
       <c r="G95" s="3" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H95" s="3">
         <v>1</v>
@@ -6518,7 +6520,7 @@
         <v>0</v>
       </c>
       <c r="K95" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L95" s="3">
         <v>0</v>
@@ -6532,16 +6534,16 @@
     </row>
     <row r="96" customHeight="1" spans="3:14">
       <c r="C96" s="3">
-        <v>8203</v>
+        <v>8202</v>
       </c>
       <c r="D96" s="9" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="F96" s="3">
         <v>16</v>
       </c>
       <c r="G96" s="3" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H96" s="3">
         <v>1</v>
@@ -6553,7 +6555,7 @@
         <v>0</v>
       </c>
       <c r="K96" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -6567,16 +6569,16 @@
     </row>
     <row r="97" customHeight="1" spans="3:14">
       <c r="C97" s="3">
-        <v>8204</v>
+        <v>8203</v>
       </c>
       <c r="D97" s="9" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="F97" s="3">
         <v>16</v>
       </c>
       <c r="G97" s="3" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H97" s="3">
         <v>1</v>
@@ -6588,7 +6590,7 @@
         <v>0</v>
       </c>
       <c r="K97" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L97" s="3">
         <v>0</v>
@@ -6602,16 +6604,16 @@
     </row>
     <row r="98" customHeight="1" spans="3:14">
       <c r="C98" s="3">
-        <v>8205</v>
+        <v>8204</v>
       </c>
       <c r="D98" s="9" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="F98" s="3">
         <v>16</v>
       </c>
       <c r="G98" s="3" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H98" s="3">
         <v>1</v>
@@ -6623,7 +6625,7 @@
         <v>0</v>
       </c>
       <c r="K98" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L98" s="3">
         <v>0</v>
@@ -6637,16 +6639,16 @@
     </row>
     <row r="99" customHeight="1" spans="3:14">
       <c r="C99" s="3">
-        <v>8206</v>
+        <v>8205</v>
       </c>
       <c r="D99" s="9" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F99" s="3">
         <v>16</v>
       </c>
       <c r="G99" s="3" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H99" s="3">
         <v>1</v>
@@ -6658,7 +6660,7 @@
         <v>0</v>
       </c>
       <c r="K99" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L99" s="3">
         <v>0</v>
@@ -6672,41 +6674,73 @@
     </row>
     <row r="100" customHeight="1" spans="3:14">
       <c r="C100" s="3">
-        <v>8207</v>
+        <v>8206</v>
       </c>
       <c r="D100" s="9" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="F100" s="3">
         <v>16</v>
       </c>
       <c r="G100" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="H100" s="3">
+        <v>1</v>
+      </c>
+      <c r="I100" s="3">
+        <v>1</v>
+      </c>
+      <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3">
+        <v>6</v>
+      </c>
+      <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" customHeight="1" spans="3:14">
+      <c r="C101" s="3">
+        <v>8207</v>
+      </c>
+      <c r="D101" s="9" t="s">
         <v>279</v>
       </c>
-      <c r="H100" s="3">
-        <v>1</v>
-      </c>
-      <c r="I100" s="3">
-        <v>1</v>
-      </c>
-      <c r="J100" s="3">
-        <v>0</v>
-      </c>
-      <c r="K100" s="3">
+      <c r="F101" s="3">
+        <v>16</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="H101" s="3">
+        <v>1</v>
+      </c>
+      <c r="I101" s="3">
+        <v>1</v>
+      </c>
+      <c r="J101" s="3">
+        <v>0</v>
+      </c>
+      <c r="K101" s="3">
         <v>7</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
-      </c>
-      <c r="M100" s="3">
-        <v>0</v>
-      </c>
-      <c r="N100" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" customHeight="1" spans="3:14">
-      <c r="D102" s="9"/>
+      <c r="L101" s="3">
+        <v>0</v>
+      </c>
+      <c r="M101" s="3">
+        <v>0</v>
+      </c>
+      <c r="N101" s="3">
+        <v>0</v>
+      </c>
     </row>
     <row r="103" customHeight="1" spans="3:14">
       <c r="D103" s="9"/>
@@ -6726,8 +6760,8 @@
     <row r="108" customHeight="1" spans="3:14">
       <c r="D108" s="9"/>
     </row>
-    <row r="110" customHeight="1" spans="3:14">
-      <c r="D110" s="9"/>
+    <row r="109" customHeight="1" spans="3:14">
+      <c r="D109" s="9"/>
     </row>
     <row r="111" customHeight="1" spans="3:14">
       <c r="D111" s="9"/>
@@ -6747,12 +6781,15 @@
     <row r="116" customHeight="1" spans="4:4">
       <c r="D116" s="9"/>
     </row>
+    <row r="117" customHeight="1" spans="4:4">
+      <c r="D117" s="9"/>
+    </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C11:D11 C16:D16 C12:C15 C3:E5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C12:D12 C17:D17 C13:C16 C3:E5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="M16:N16 M3:N5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="M17:N17 M3:N5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,M3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>
@@ -6901,14 +6938,14 @@
         <v>9001</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="E6" s="3"/>
       <c r="F6" s="2">
         <v>6</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="H6" s="2">
         <v>1</v>
@@ -6931,14 +6968,14 @@
         <v>9002</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="E7" s="3"/>
       <c r="F7" s="2">
         <v>6</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="H7" s="2">
         <v>1</v>
@@ -6961,14 +6998,14 @@
         <v>9003</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="E8" s="3"/>
       <c r="F8" s="2">
         <v>6</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="H8" s="2">
         <v>1</v>
@@ -6991,14 +7028,14 @@
         <v>9004</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="E9" s="3"/>
       <c r="F9" s="2">
         <v>6</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="H9" s="2">
         <v>1</v>
@@ -7021,14 +7058,14 @@
         <v>9005</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="E10" s="3"/>
       <c r="F10" s="2">
         <v>6</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="H10" s="2">
         <v>1</v>
@@ -7051,14 +7088,14 @@
         <v>9006</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="E11" s="3"/>
       <c r="F11" s="2">
         <v>6</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="H11" s="2">
         <v>1</v>
@@ -7080,14 +7117,14 @@
         <v>9007</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" s="2">
         <v>6</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="H12" s="2">
         <v>1</v>
@@ -7109,14 +7146,14 @@
         <v>9008</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" s="2">
         <v>6</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="H13" s="2">
         <v>1</v>
@@ -7138,14 +7175,14 @@
         <v>9009</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="E14" s="3"/>
       <c r="F14" s="2">
         <v>6</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="H14" s="2">
         <v>1</v>
@@ -7167,14 +7204,14 @@
         <v>9010</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="E15" s="3"/>
       <c r="F15" s="2">
         <v>6</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="H15" s="2">
         <v>1</v>
@@ -7196,14 +7233,14 @@
         <v>9011</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="E16" s="3"/>
       <c r="F16" s="2">
         <v>6</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="H16" s="2">
         <v>1</v>
@@ -7380,14 +7417,14 @@
         <v>10001</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E6" s="3"/>
       <c r="F6" s="2">
         <v>5</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H6" s="2">
         <v>1</v>
@@ -7413,14 +7450,14 @@
         <v>10002</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="E7" s="3"/>
       <c r="F7" s="2">
         <v>5</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H7" s="2">
         <v>1</v>
@@ -7446,14 +7483,14 @@
         <v>10003</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="E8" s="3"/>
       <c r="F8" s="2">
         <v>5</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H8" s="2">
         <v>1</v>
@@ -7479,14 +7516,14 @@
         <v>10004</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="E9" s="3"/>
       <c r="F9" s="2">
         <v>5</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H9" s="2">
         <v>1</v>
@@ -7756,14 +7793,14 @@
         <v>40000001</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="E6" s="3"/>
       <c r="F6" s="2">
         <v>6</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H6" s="2">
         <v>1</v>
@@ -7784,14 +7821,14 @@
         <v>40000002</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="E7" s="3"/>
       <c r="F7" s="2">
         <v>6</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H7" s="2">
         <v>1</v>
@@ -7812,14 +7849,14 @@
         <v>40000003</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E8" s="3"/>
       <c r="F8" s="2">
         <v>6</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H8" s="2">
         <v>1</v>
@@ -7840,14 +7877,14 @@
         <v>40000004</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="E9" s="3"/>
       <c r="F9" s="2">
         <v>6</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H9" s="2">
         <v>1</v>
@@ -7868,14 +7905,14 @@
         <v>40000005</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E10" s="3"/>
       <c r="F10" s="2">
         <v>6</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H10" s="2">
         <v>1</v>
@@ -7896,14 +7933,14 @@
         <v>40000006</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E11" s="3"/>
       <c r="F11" s="2">
         <v>6</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H11" s="2">
         <v>1</v>
@@ -7926,13 +7963,13 @@
         <v>40000007</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="F12" s="2">
         <v>6</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H12" s="2">
         <v>1</v>
@@ -7952,13 +7989,13 @@
         <v>40000008</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F13" s="2">
         <v>6</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H13" s="2">
         <v>1</v>
@@ -7978,14 +8015,14 @@
         <v>40000009</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="E14" s="3"/>
       <c r="F14" s="2">
         <v>6</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H14" s="2">
         <v>1</v>
@@ -8005,14 +8042,14 @@
         <v>40000010</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="E15" s="3"/>
       <c r="F15" s="2">
         <v>6</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="H15" s="2">
         <v>1</v>
@@ -8032,14 +8069,14 @@
         <v>40000011</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="E16" s="3"/>
       <c r="F16" s="2">
         <v>6</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="H16" s="2">
         <v>1</v>
@@ -8060,14 +8097,14 @@
         <v>40000012</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="E17" s="3"/>
       <c r="F17" s="2">
         <v>6</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="H17" s="2">
         <v>1</v>
@@ -8087,14 +8124,14 @@
         <v>40000013</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="E18" s="3"/>
       <c r="F18" s="2">
         <v>6</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H18" s="2">
         <v>1</v>
@@ -8114,13 +8151,13 @@
         <v>40000014</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="F19" s="2">
         <v>6</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H19" s="2">
         <v>1</v>
@@ -8140,14 +8177,14 @@
         <v>40000015</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="E20" s="3"/>
       <c r="F20" s="2">
         <v>6</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H20" s="2">
         <v>1</v>
@@ -8167,14 +8204,14 @@
         <v>40000016</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="E21" s="3"/>
       <c r="F21" s="2">
         <v>6</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H21" s="2">
         <v>1</v>
@@ -8194,14 +8231,14 @@
         <v>40000017</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="E22" s="3"/>
       <c r="F22" s="2">
         <v>6</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H22" s="2">
         <v>1</v>
@@ -8221,14 +8258,14 @@
         <v>40000018</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="E23" s="3"/>
       <c r="F23" s="2">
         <v>6</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H23" s="2">
         <v>1</v>

--- a/Excel/ItemConfig.xlsx
+++ b/Excel/ItemConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="1"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="技能" sheetId="1" r:id="rId1"/>
@@ -307,7 +307,7 @@
     <t>ItemLogo/sb1</t>
   </si>
   <si>
-    <t>学习或者升级战士技能基础剑术</t>
+    <t>学习或者升级战士技能基础心法</t>
   </si>
   <si>
     <t>10000</t>
@@ -319,7 +319,7 @@
     <t>流光剑诀</t>
   </si>
   <si>
-    <t>学习或者升级战士技能流光剑法</t>
+    <t>学习或者升级战士技能流光剑诀</t>
   </si>
   <si>
     <t>1003</t>
@@ -328,7 +328,7 @@
     <t>月华剑阵</t>
   </si>
   <si>
-    <t>学习或者升级战士技能旋风斩</t>
+    <t>学习或者升级战士技能月华剑阵</t>
   </si>
   <si>
     <t>1004</t>
@@ -337,7 +337,7 @@
     <t>蛮牛冲撞</t>
   </si>
   <si>
-    <t>学习或者升级战士技能腾空斩</t>
+    <t>学习或者升级战士技能蛮牛冲撞</t>
   </si>
   <si>
     <t>100000</t>
@@ -349,7 +349,7 @@
     <t>龙魂护体</t>
   </si>
   <si>
-    <t>学习或者升级战士技能武神盾</t>
+    <t>学习或者升级战士技能龙魂护体</t>
   </si>
   <si>
     <t>1006</t>
@@ -358,7 +358,7 @@
     <t>无求易决</t>
   </si>
   <si>
-    <t>学习或者升级战士技能武力精通</t>
+    <t>学习或者升级战士技能无求易决</t>
   </si>
   <si>
     <t>1007</t>
@@ -367,7 +367,7 @@
     <t>火麟剑诀</t>
   </si>
   <si>
-    <t>学习或者升级战士技能烈焰斩</t>
+    <t>学习或者升级战士技能火麟剑诀</t>
   </si>
   <si>
     <t>#</t>
@@ -427,7 +427,7 @@
     <t>ItemLogo/sb2</t>
   </si>
   <si>
-    <t>学习或者升级法师技能火球术</t>
+    <t>学习或者升级法师技能冥想心法</t>
   </si>
   <si>
     <t>2002</t>
@@ -436,7 +436,7 @@
     <t>紫电神雷</t>
   </si>
   <si>
-    <t>学习或者升级法师技能落雷术</t>
+    <t>学习或者升级法师技能紫电神雷</t>
   </si>
   <si>
     <t>2003</t>
@@ -445,7 +445,7 @@
     <t>火狱阵法</t>
   </si>
   <si>
-    <t>学习或者升级法师技能火焰墙</t>
+    <t>学习或者升级法师技能火狱阵法</t>
   </si>
   <si>
     <t>2004</t>
@@ -454,7 +454,7 @@
     <t>烈焰焚天</t>
   </si>
   <si>
-    <t>学习或者升级法师技能烈焰环</t>
+    <t>学习或者升级法师技能烈焰焚天</t>
   </si>
   <si>
     <t>2005</t>
@@ -463,7 +463,7 @@
     <t>炎凰法盾</t>
   </si>
   <si>
-    <t>学习或者升级法师技能法力盾</t>
+    <t>学习或者升级法师技能炎凰法盾</t>
   </si>
   <si>
     <t>2006</t>
@@ -472,7 +472,7 @@
     <t>万法归宗</t>
   </si>
   <si>
-    <t>学习或者升级法师技能法术精通</t>
+    <t>学习或者升级法师技能万法归宗</t>
   </si>
   <si>
     <t>2007</t>
@@ -481,7 +481,7 @@
     <t>极寒冰暴</t>
   </si>
   <si>
-    <t>学习或者升级法师技能冰爆术</t>
+    <t>学习或者升级法师技能极寒冰暴</t>
   </si>
   <si>
     <t>2008</t>
@@ -538,7 +538,7 @@
     <t>ItemLogo/sb3</t>
   </si>
   <si>
-    <t>学习或者升级道士技能疗伤术</t>
+    <t>学习或者升级道士技能清心咒</t>
   </si>
   <si>
     <t>3002</t>
@@ -547,7 +547,7 @@
     <t>破魔符咒</t>
   </si>
   <si>
-    <t>学习或者升级道士技能驱魔符</t>
+    <t>学习或者升级道士技能破魔符咒</t>
   </si>
   <si>
     <t>3003</t>
@@ -565,7 +565,7 @@
     <t>圣疗术</t>
   </si>
   <si>
-    <t>学习或者升级道士技能召唤小兵</t>
+    <t>学习或者升级道士技能圣疗术</t>
   </si>
   <si>
     <t>3005</t>
@@ -574,7 +574,7 @@
     <t>太虚麟盾</t>
   </si>
   <si>
-    <t>学习或者升级道士技能道力盾</t>
+    <t>学习或者升级道士技能太虚麟盾</t>
   </si>
   <si>
     <t>3006</t>
@@ -583,7 +583,7 @@
     <t>道法自然</t>
   </si>
   <si>
-    <t>学习或者升级道士技能道力精通</t>
+    <t>学习或者升级道士技能道法自然</t>
   </si>
   <si>
     <t>3007</t>
@@ -592,7 +592,7 @@
     <t>召唤英灵</t>
   </si>
   <si>
-    <t>学习或者升级道士技能召唤魔兽</t>
+    <t>学习或者升级道士技能召唤英灵</t>
   </si>
   <si>
     <t>3008</t>
@@ -2208,7 +2208,7 @@
     <col min="4" max="4" width="10.125" style="3" customWidth="1"/>
     <col min="5" max="5" width="12.3333333333333" style="3" customWidth="1"/>
     <col min="6" max="6" width="9.875" style="3" customWidth="1"/>
-    <col min="7" max="7" width="26.75" style="3" customWidth="1"/>
+    <col min="7" max="7" width="30.8333333333333" style="3" customWidth="1"/>
     <col min="8" max="8" width="8" style="3" customWidth="1"/>
     <col min="9" max="12" width="12.25" style="3" customWidth="1"/>
     <col min="13" max="14" width="12.375" style="3" customWidth="1"/>

--- a/Excel/ItemConfig.xlsx
+++ b/Excel/ItemConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView windowHeight="17680" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="技能" sheetId="1" r:id="rId1"/>
@@ -224,7 +224,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="620" uniqueCount="322">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="632" uniqueCount="334">
   <si>
     <t>_Id</t>
   </si>
@@ -1123,49 +1123,85 @@
     <t>狼毛</t>
   </si>
   <si>
+    <t>ItemLogo/Exclusive_Metal/em1</t>
+  </si>
+  <si>
     <t>落日平原珍宝材料</t>
   </si>
   <si>
     <t>蛛丝</t>
   </si>
   <si>
+    <t>ItemLogo/Exclusive_Metal/em2</t>
+  </si>
+  <si>
     <t>雄狮利爪</t>
   </si>
   <si>
+    <t>ItemLogo/Exclusive_Metal/em3</t>
+  </si>
+  <si>
     <t>虫卵</t>
   </si>
   <si>
+    <t>ItemLogo/Exclusive_Metal/em4</t>
+  </si>
+  <si>
     <t>幽暗沼泽珍宝材料</t>
   </si>
   <si>
     <t>蛇皮</t>
   </si>
   <si>
+    <t>ItemLogo/Exclusive_Metal/em5</t>
+  </si>
+  <si>
     <t>巨鳄之泪</t>
   </si>
   <si>
+    <t>ItemLogo/Exclusive_Metal/em6</t>
+  </si>
+  <si>
     <t>乌鸦羽</t>
   </si>
   <si>
+    <t>ItemLogo/Exclusive_Metal/em7</t>
+  </si>
+  <si>
     <t>碎石矿场珍宝材料</t>
   </si>
   <si>
     <t>蝙蝠牙</t>
   </si>
   <si>
+    <t>ItemLogo/Exclusive_Metal/em8</t>
+  </si>
+  <si>
     <t>尸王之心</t>
   </si>
   <si>
+    <t>ItemLogo/Exclusive_Metal/em9</t>
+  </si>
+  <si>
     <t>树叶</t>
   </si>
   <si>
+    <t>ItemLogo/Exclusive_Metal/em10</t>
+  </si>
+  <si>
     <t>枯骨荒漠珍宝材料</t>
   </si>
   <si>
     <t>鱼鳞</t>
   </si>
   <si>
+    <t>ItemLogo/Exclusive_Metal/em11</t>
+  </si>
+  <si>
     <t>鹿血</t>
+  </si>
+  <si>
+    <t>ItemLogo/Exclusive_Metal/em12</t>
   </si>
   <si>
     <t>骨弓</t>
@@ -7656,7 +7692,8 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="2"/>
-    <col min="4" max="5" width="9.58333333333333" style="2" customWidth="1"/>
+    <col min="4" max="4" width="9.58333333333333" style="2" customWidth="1"/>
+    <col min="5" max="5" width="24.9166666666667" style="2" customWidth="1"/>
     <col min="6" max="6" width="9" style="2"/>
     <col min="7" max="7" width="20.875" style="2" customWidth="1"/>
     <col min="8" max="9" width="9" style="2"/>
@@ -7795,12 +7832,14 @@
       <c r="D6" s="3" t="s">
         <v>298</v>
       </c>
-      <c r="E6" s="3"/>
+      <c r="E6" s="3" t="s">
+        <v>299</v>
+      </c>
       <c r="F6" s="2">
         <v>6</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H6" s="2">
         <v>1</v>
@@ -7821,14 +7860,16 @@
         <v>40000002</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>300</v>
-      </c>
-      <c r="E7" s="3"/>
+        <v>301</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>302</v>
+      </c>
       <c r="F7" s="2">
         <v>6</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H7" s="2">
         <v>1</v>
@@ -7849,14 +7890,16 @@
         <v>40000003</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>301</v>
-      </c>
-      <c r="E8" s="3"/>
+        <v>303</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>304</v>
+      </c>
       <c r="F8" s="2">
         <v>6</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H8" s="2">
         <v>1</v>
@@ -7877,14 +7920,16 @@
         <v>40000004</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>302</v>
-      </c>
-      <c r="E9" s="3"/>
+        <v>305</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>306</v>
+      </c>
       <c r="F9" s="2">
         <v>6</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="H9" s="2">
         <v>1</v>
@@ -7905,14 +7950,16 @@
         <v>40000005</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>304</v>
-      </c>
-      <c r="E10" s="3"/>
+        <v>308</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>309</v>
+      </c>
       <c r="F10" s="2">
         <v>6</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="H10" s="2">
         <v>1</v>
@@ -7933,14 +7980,16 @@
         <v>40000006</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>305</v>
-      </c>
-      <c r="E11" s="3"/>
+        <v>310</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>311</v>
+      </c>
       <c r="F11" s="2">
         <v>6</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="H11" s="2">
         <v>1</v>
@@ -7963,13 +8012,16 @@
         <v>40000007</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>306</v>
+        <v>312</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>313</v>
       </c>
       <c r="F12" s="2">
         <v>6</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>307</v>
+        <v>314</v>
       </c>
       <c r="H12" s="2">
         <v>1</v>
@@ -7989,13 +8041,16 @@
         <v>40000008</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>308</v>
+        <v>315</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>316</v>
       </c>
       <c r="F13" s="2">
         <v>6</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>307</v>
+        <v>314</v>
       </c>
       <c r="H13" s="2">
         <v>1</v>
@@ -8015,14 +8070,16 @@
         <v>40000009</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>309</v>
-      </c>
-      <c r="E14" s="3"/>
+        <v>317</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>318</v>
+      </c>
       <c r="F14" s="2">
         <v>6</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>307</v>
+        <v>314</v>
       </c>
       <c r="H14" s="2">
         <v>1</v>
@@ -8042,14 +8099,16 @@
         <v>40000010</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>310</v>
-      </c>
-      <c r="E15" s="3"/>
+        <v>319</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>320</v>
+      </c>
       <c r="F15" s="2">
         <v>6</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="H15" s="2">
         <v>1</v>
@@ -8069,14 +8128,16 @@
         <v>40000011</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>312</v>
-      </c>
-      <c r="E16" s="3"/>
+        <v>322</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>323</v>
+      </c>
       <c r="F16" s="2">
         <v>6</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="H16" s="2">
         <v>1</v>
@@ -8097,14 +8158,16 @@
         <v>40000012</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>313</v>
-      </c>
-      <c r="E17" s="3"/>
+        <v>324</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>325</v>
+      </c>
       <c r="F17" s="2">
         <v>6</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="H17" s="2">
         <v>1</v>
@@ -8124,14 +8187,14 @@
         <v>40000013</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>314</v>
+        <v>326</v>
       </c>
       <c r="E18" s="3"/>
       <c r="F18" s="2">
         <v>6</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>315</v>
+        <v>327</v>
       </c>
       <c r="H18" s="2">
         <v>1</v>
@@ -8151,13 +8214,14 @@
         <v>40000014</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>316</v>
-      </c>
+        <v>328</v>
+      </c>
+      <c r="E19" s="3"/>
       <c r="F19" s="2">
         <v>6</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>315</v>
+        <v>327</v>
       </c>
       <c r="H19" s="2">
         <v>1</v>
@@ -8177,14 +8241,14 @@
         <v>40000015</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>317</v>
+        <v>329</v>
       </c>
       <c r="E20" s="3"/>
       <c r="F20" s="2">
         <v>6</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>315</v>
+        <v>327</v>
       </c>
       <c r="H20" s="2">
         <v>1</v>
@@ -8204,14 +8268,14 @@
         <v>40000016</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>318</v>
+        <v>330</v>
       </c>
       <c r="E21" s="3"/>
       <c r="F21" s="2">
         <v>6</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>319</v>
+        <v>331</v>
       </c>
       <c r="H21" s="2">
         <v>1</v>
@@ -8231,14 +8295,14 @@
         <v>40000017</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>320</v>
+        <v>332</v>
       </c>
       <c r="E22" s="3"/>
       <c r="F22" s="2">
         <v>6</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>319</v>
+        <v>331</v>
       </c>
       <c r="H22" s="2">
         <v>1</v>
@@ -8258,14 +8322,14 @@
         <v>40000018</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>321</v>
+        <v>333</v>
       </c>
       <c r="E23" s="3"/>
       <c r="F23" s="2">
         <v>6</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>319</v>
+        <v>331</v>
       </c>
       <c r="H23" s="2">
         <v>1</v>

--- a/Excel/ItemConfig.xlsx
+++ b/Excel/ItemConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="4"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="技能" sheetId="1" r:id="rId1"/>
@@ -673,6 +673,12 @@
     <t>分解传奇装备获取，传承传奇装备</t>
   </si>
   <si>
+    <t>书页</t>
+  </si>
+  <si>
+    <t>升级技能，获得10点技能经验</t>
+  </si>
+  <si>
     <t>灵盾碎片</t>
   </si>
   <si>
@@ -737,12 +743,6 @@
   </si>
   <si>
     <t>兑换专属自选包</t>
-  </si>
-  <si>
-    <t>书页</t>
-  </si>
-  <si>
-    <t>每20个升级一级任意技能</t>
   </si>
   <si>
     <t>四格碎片</t>
@@ -2397,10 +2397,10 @@
         <v>0</v>
       </c>
       <c r="M6" s="3">
-        <v>0</v>
+        <v>5007</v>
       </c>
       <c r="N6" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="1:14">
@@ -2435,10 +2435,10 @@
         <v>0</v>
       </c>
       <c r="M7" s="3">
-        <v>0</v>
+        <v>5007</v>
       </c>
       <c r="N7" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="1:14">
@@ -2473,10 +2473,10 @@
         <v>0</v>
       </c>
       <c r="M8" s="3">
-        <v>0</v>
+        <v>5007</v>
       </c>
       <c r="N8" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="1:14">
@@ -2511,10 +2511,10 @@
         <v>0</v>
       </c>
       <c r="M9" s="3">
-        <v>0</v>
+        <v>5007</v>
       </c>
       <c r="N9" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10" customHeight="1" spans="1:14">
@@ -2549,10 +2549,10 @@
         <v>0</v>
       </c>
       <c r="M10" s="3">
-        <v>0</v>
+        <v>5007</v>
       </c>
       <c r="N10" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="1:14">
@@ -2587,10 +2587,10 @@
         <v>0</v>
       </c>
       <c r="M11" s="3">
-        <v>0</v>
+        <v>5007</v>
       </c>
       <c r="N11" s="3">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12" customHeight="1" spans="1:14">
@@ -2625,10 +2625,10 @@
         <v>0</v>
       </c>
       <c r="M12" s="3">
-        <v>0</v>
+        <v>5007</v>
       </c>
       <c r="N12" s="3">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13" customHeight="1" spans="1:14">
@@ -2669,10 +2669,10 @@
         <v>0</v>
       </c>
       <c r="M13" s="3">
-        <v>0</v>
+        <v>5007</v>
       </c>
       <c r="N13" s="3">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="1:14">
@@ -2713,10 +2713,10 @@
         <v>0</v>
       </c>
       <c r="M14" s="3">
-        <v>0</v>
+        <v>5007</v>
       </c>
       <c r="N14" s="3">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="1:14">
@@ -2757,10 +2757,10 @@
         <v>0</v>
       </c>
       <c r="M15" s="3">
-        <v>0</v>
+        <v>5007</v>
       </c>
       <c r="N15" s="3">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16" customHeight="1" spans="1:14">
@@ -2801,10 +2801,10 @@
         <v>0</v>
       </c>
       <c r="M16" s="3">
-        <v>0</v>
+        <v>5007</v>
       </c>
       <c r="N16" s="3">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="1:14">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="M17" s="3">
-        <v>0</v>
+        <v>5007</v>
       </c>
       <c r="N17" s="3">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="1:14">
@@ -2883,10 +2883,10 @@
         <v>0</v>
       </c>
       <c r="M19" s="3">
-        <v>0</v>
+        <v>5007</v>
       </c>
       <c r="N19" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="1:14">
@@ -2921,10 +2921,10 @@
         <v>0</v>
       </c>
       <c r="M20" s="3">
-        <v>0</v>
+        <v>5007</v>
       </c>
       <c r="N20" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="1:14">
@@ -2959,10 +2959,10 @@
         <v>0</v>
       </c>
       <c r="M21" s="3">
-        <v>0</v>
+        <v>5007</v>
       </c>
       <c r="N21" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="1:14">
@@ -2997,10 +2997,10 @@
         <v>0</v>
       </c>
       <c r="M22" s="3">
-        <v>0</v>
+        <v>5007</v>
       </c>
       <c r="N22" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="1:14">
@@ -3035,10 +3035,10 @@
         <v>0</v>
       </c>
       <c r="M23" s="3">
-        <v>0</v>
+        <v>5007</v>
       </c>
       <c r="N23" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24" customHeight="1" spans="1:14">
@@ -3073,10 +3073,10 @@
         <v>0</v>
       </c>
       <c r="M24" s="3">
-        <v>0</v>
+        <v>5007</v>
       </c>
       <c r="N24" s="3">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25" customHeight="1" spans="1:14">
@@ -3111,10 +3111,10 @@
         <v>0</v>
       </c>
       <c r="M25" s="3">
-        <v>0</v>
+        <v>5007</v>
       </c>
       <c r="N25" s="3">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="26" customHeight="1" spans="1:14">
@@ -3155,10 +3155,10 @@
         <v>0</v>
       </c>
       <c r="M26" s="3">
-        <v>0</v>
+        <v>5007</v>
       </c>
       <c r="N26" s="3">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="27" customHeight="1" spans="1:14">
@@ -3199,10 +3199,10 @@
         <v>0</v>
       </c>
       <c r="M27" s="3">
-        <v>0</v>
+        <v>5007</v>
       </c>
       <c r="N27" s="3">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="28" customHeight="1" spans="1:14">
@@ -3243,10 +3243,10 @@
         <v>0</v>
       </c>
       <c r="M28" s="3">
-        <v>0</v>
+        <v>5007</v>
       </c>
       <c r="N28" s="3">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="29" customHeight="1" spans="1:14">
@@ -3287,10 +3287,10 @@
         <v>0</v>
       </c>
       <c r="M29" s="3">
-        <v>0</v>
+        <v>5007</v>
       </c>
       <c r="N29" s="3">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="30" customHeight="1" spans="1:14">
@@ -3331,10 +3331,10 @@
         <v>0</v>
       </c>
       <c r="M30" s="3">
-        <v>0</v>
+        <v>5007</v>
       </c>
       <c r="N30" s="3">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="32" customHeight="1" spans="1:14">
@@ -3369,10 +3369,10 @@
         <v>0</v>
       </c>
       <c r="M32" s="3">
-        <v>0</v>
+        <v>5007</v>
       </c>
       <c r="N32" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33" customHeight="1" spans="1:14">
@@ -3407,10 +3407,10 @@
         <v>0</v>
       </c>
       <c r="M33" s="3">
-        <v>0</v>
+        <v>5007</v>
       </c>
       <c r="N33" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34" customHeight="1" spans="1:14">
@@ -3445,10 +3445,10 @@
         <v>0</v>
       </c>
       <c r="M34" s="3">
-        <v>0</v>
+        <v>5007</v>
       </c>
       <c r="N34" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="35" customHeight="1" spans="1:14">
@@ -3483,10 +3483,10 @@
         <v>0</v>
       </c>
       <c r="M35" s="3">
-        <v>0</v>
+        <v>5007</v>
       </c>
       <c r="N35" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="36" customHeight="1" spans="1:14">
@@ -3521,10 +3521,10 @@
         <v>0</v>
       </c>
       <c r="M36" s="3">
-        <v>0</v>
+        <v>5007</v>
       </c>
       <c r="N36" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="37" customHeight="1" spans="1:14">
@@ -3559,10 +3559,10 @@
         <v>0</v>
       </c>
       <c r="M37" s="3">
-        <v>0</v>
+        <v>5007</v>
       </c>
       <c r="N37" s="3">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="38" customHeight="1" spans="1:14">
@@ -3597,10 +3597,10 @@
         <v>0</v>
       </c>
       <c r="M38" s="3">
-        <v>0</v>
+        <v>5007</v>
       </c>
       <c r="N38" s="3">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="39" customHeight="1" spans="1:14">
@@ -3641,10 +3641,10 @@
         <v>0</v>
       </c>
       <c r="M39" s="3">
-        <v>0</v>
+        <v>5007</v>
       </c>
       <c r="N39" s="3">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="40" customHeight="1" spans="1:14">
@@ -3685,10 +3685,10 @@
         <v>0</v>
       </c>
       <c r="M40" s="3">
-        <v>0</v>
+        <v>5007</v>
       </c>
       <c r="N40" s="3">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="41" customHeight="1" spans="1:14">
@@ -3729,10 +3729,10 @@
         <v>0</v>
       </c>
       <c r="M41" s="3">
-        <v>0</v>
+        <v>5007</v>
       </c>
       <c r="N41" s="3">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="42" customHeight="1" spans="1:14">
@@ -3773,10 +3773,10 @@
         <v>0</v>
       </c>
       <c r="M42" s="3">
-        <v>0</v>
+        <v>5007</v>
       </c>
       <c r="N42" s="3">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="43" customHeight="1" spans="1:14">
@@ -3817,10 +3817,10 @@
         <v>0</v>
       </c>
       <c r="M43" s="3">
-        <v>0</v>
+        <v>5007</v>
       </c>
       <c r="N43" s="3">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -3842,7 +3842,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:N117"/>
+  <dimension ref="C1:N118"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="3"/>
@@ -4179,57 +4179,59 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" s="6" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C12" s="7"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="7"/>
-      <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
-      <c r="I12" s="3"/>
-      <c r="J12" s="3"/>
-      <c r="K12" s="3"/>
-      <c r="L12" s="3"/>
-      <c r="M12" s="3"/>
-      <c r="N12" s="3"/>
+    <row r="12" s="3" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C12" s="3">
+        <v>5007</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="E12" s="2"/>
+      <c r="F12" s="3">
+        <v>5</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="H12" s="3">
+        <v>1</v>
+      </c>
+      <c r="I12" s="3">
+        <v>99999999</v>
+      </c>
+      <c r="J12" s="3">
+        <v>0</v>
+      </c>
+      <c r="K12" s="3">
+        <v>5</v>
+      </c>
+      <c r="L12" s="3">
+        <v>10</v>
+      </c>
+      <c r="M12" s="3">
+        <v>0</v>
+      </c>
+      <c r="N12" s="3">
+        <v>0</v>
+      </c>
     </row>
     <row r="13" s="6" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C13" s="8">
-        <v>5011</v>
-      </c>
-      <c r="D13" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="E13" s="2"/>
-      <c r="F13" s="10">
-        <v>5</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="H13" s="3">
-        <v>1</v>
-      </c>
-      <c r="I13" s="3">
-        <v>99999999</v>
-      </c>
-      <c r="J13" s="3">
-        <v>0</v>
-      </c>
-      <c r="K13" s="3">
-        <v>3</v>
-      </c>
+      <c r="C13" s="7"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="7"/>
+      <c r="G13" s="3"/>
+      <c r="H13" s="3"/>
+      <c r="I13" s="3"/>
+      <c r="J13" s="3"/>
+      <c r="K13" s="3"/>
       <c r="L13" s="3"/>
-      <c r="M13" s="3">
-        <v>0</v>
-      </c>
-      <c r="N13" s="3">
-        <v>0</v>
-      </c>
+      <c r="M13" s="3"/>
+      <c r="N13" s="3"/>
     </row>
     <row r="14" s="6" customFormat="1" customHeight="1" spans="3:14">
       <c r="C14" s="8">
-        <v>5012</v>
+        <v>5011</v>
       </c>
       <c r="D14" s="9" t="s">
         <v>151</v>
@@ -4263,12 +4265,12 @@
     </row>
     <row r="15" s="6" customFormat="1" customHeight="1" spans="3:14">
       <c r="C15" s="8">
-        <v>5013</v>
+        <v>5012</v>
       </c>
       <c r="D15" s="9" t="s">
         <v>153</v>
       </c>
-      <c r="E15" s="3"/>
+      <c r="E15" s="2"/>
       <c r="F15" s="10">
         <v>5</v>
       </c>
@@ -4297,7 +4299,7 @@
     </row>
     <row r="16" s="6" customFormat="1" customHeight="1" spans="3:14">
       <c r="C16" s="8">
-        <v>5014</v>
+        <v>5013</v>
       </c>
       <c r="D16" s="9" t="s">
         <v>155</v>
@@ -4330,60 +4332,61 @@
       </c>
     </row>
     <row r="17" s="6" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
+      <c r="C17" s="8">
+        <v>5014</v>
+      </c>
+      <c r="D17" s="9" t="s">
+        <v>157</v>
+      </c>
       <c r="E17" s="3"/>
-      <c r="F17" s="7"/>
-      <c r="G17" s="7"/>
-      <c r="H17" s="7"/>
-      <c r="I17" s="7"/>
-      <c r="J17" s="7"/>
-      <c r="K17" s="7"/>
-      <c r="L17" s="7"/>
-      <c r="M17" s="7"/>
-      <c r="N17" s="7"/>
-    </row>
-    <row r="18" s="3" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C18" s="3">
-        <v>7001</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>157</v>
-      </c>
+      <c r="F17" s="10">
+        <v>5</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="H17" s="3">
+        <v>1</v>
+      </c>
+      <c r="I17" s="3">
+        <v>99999999</v>
+      </c>
+      <c r="J17" s="3">
+        <v>0</v>
+      </c>
+      <c r="K17" s="3">
+        <v>3</v>
+      </c>
+      <c r="L17" s="3"/>
+      <c r="M17" s="3">
+        <v>0</v>
+      </c>
+      <c r="N17" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" s="6" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C18" s="7"/>
+      <c r="D18" s="7"/>
       <c r="E18" s="3"/>
-      <c r="F18" s="3">
-        <v>7</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="H18" s="3">
-        <v>1</v>
-      </c>
-      <c r="I18" s="3">
-        <v>9999999</v>
-      </c>
-      <c r="J18" s="3">
-        <v>0</v>
-      </c>
-      <c r="K18" s="3">
-        <v>6</v>
-      </c>
-      <c r="M18" s="3">
-        <v>0</v>
-      </c>
-      <c r="N18" s="3">
-        <v>0</v>
-      </c>
+      <c r="F18" s="7"/>
+      <c r="G18" s="7"/>
+      <c r="H18" s="7"/>
+      <c r="I18" s="7"/>
+      <c r="J18" s="7"/>
+      <c r="K18" s="7"/>
+      <c r="L18" s="7"/>
+      <c r="M18" s="7"/>
+      <c r="N18" s="7"/>
     </row>
     <row r="19" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C19" s="3">
-        <v>7002</v>
+        <v>7001</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="E19" s="2"/>
+      <c r="E19" s="3"/>
       <c r="F19" s="3">
         <v>7</v>
       </c>
@@ -4400,67 +4403,67 @@
         <v>0</v>
       </c>
       <c r="K19" s="3">
+        <v>6</v>
+      </c>
+      <c r="M19" s="3">
+        <v>0</v>
+      </c>
+      <c r="N19" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" s="3" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C20" s="3">
+        <v>7002</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="E20" s="2"/>
+      <c r="F20" s="3">
         <v>7</v>
       </c>
-      <c r="L19" s="3">
-        <v>0</v>
-      </c>
-      <c r="M19" s="3">
-        <v>0</v>
-      </c>
-      <c r="N19" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C21" s="3"/>
-      <c r="D21" s="3"/>
-      <c r="E21" s="2"/>
-      <c r="F21" s="3"/>
-      <c r="G21" s="3"/>
-      <c r="H21" s="3"/>
-      <c r="I21" s="3"/>
-      <c r="J21" s="3"/>
-      <c r="K21" s="3"/>
-      <c r="M21" s="3"/>
-      <c r="N21" s="3"/>
-    </row>
-    <row r="22" s="3" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C22" s="3">
-        <v>4001</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>161</v>
-      </c>
+      <c r="G20" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="H20" s="3">
+        <v>1</v>
+      </c>
+      <c r="I20" s="3">
+        <v>9999999</v>
+      </c>
+      <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
+        <v>7</v>
+      </c>
+      <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C22" s="3"/>
+      <c r="D22" s="3"/>
       <c r="E22" s="2"/>
-      <c r="F22" s="3">
-        <v>5</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="H22" s="3">
-        <v>1</v>
-      </c>
-      <c r="I22" s="3">
-        <v>99999999999</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
-      </c>
-      <c r="K22" s="3">
-        <v>5</v>
-      </c>
-      <c r="M22" s="3">
-        <v>0</v>
-      </c>
-      <c r="N22" s="3">
-        <v>0</v>
-      </c>
+      <c r="F22" s="3"/>
+      <c r="G22" s="3"/>
+      <c r="H22" s="3"/>
+      <c r="I22" s="3"/>
+      <c r="J22" s="3"/>
+      <c r="K22" s="3"/>
+      <c r="M22" s="3"/>
+      <c r="N22" s="3"/>
     </row>
     <row r="23" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C23" s="3">
-        <v>4002</v>
+        <v>4001</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>163</v>
@@ -4493,14 +4496,14 @@
     </row>
     <row r="24" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C24" s="3">
-        <v>4003</v>
+        <v>4002</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>165</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" s="3">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>166</v>
@@ -4509,7 +4512,7 @@
         <v>1</v>
       </c>
       <c r="I24" s="3">
-        <v>9999999</v>
+        <v>99999999999</v>
       </c>
       <c r="J24" s="3">
         <v>0</v>
@@ -4526,14 +4529,14 @@
     </row>
     <row r="25" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C25" s="3">
-        <v>4004</v>
+        <v>4003</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>167</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" s="3">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>168</v>
@@ -4559,7 +4562,7 @@
     </row>
     <row r="26" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C26" s="3">
-        <v>4005</v>
+        <v>4004</v>
       </c>
       <c r="D26" s="3" t="s">
         <v>169</v>
@@ -4592,7 +4595,7 @@
     </row>
     <row r="27" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C27" s="3">
-        <v>4006</v>
+        <v>4005</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>171</v>
@@ -4608,7 +4611,7 @@
         <v>1</v>
       </c>
       <c r="I27" s="3">
-        <v>99999999</v>
+        <v>9999999</v>
       </c>
       <c r="J27" s="3">
         <v>0</v>
@@ -4616,68 +4619,32 @@
       <c r="K27" s="3">
         <v>5</v>
       </c>
-      <c r="L27" s="3">
-        <v>0</v>
-      </c>
       <c r="M27" s="3">
         <v>0</v>
       </c>
       <c r="N27" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" s="3" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C28" s="3">
-        <v>4007</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="E28" s="2"/>
-      <c r="F28" s="3">
-        <v>5</v>
-      </c>
-      <c r="G28" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="H28" s="3">
-        <v>1</v>
-      </c>
-      <c r="I28" s="3">
-        <v>9999999999</v>
-      </c>
-      <c r="J28" s="3">
-        <v>0</v>
-      </c>
-      <c r="K28" s="3">
-        <v>5</v>
-      </c>
-      <c r="M28" s="3">
-        <v>0</v>
-      </c>
-      <c r="N28" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="29" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C29" s="3">
-        <v>4008</v>
+        <v>4007</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" s="3">
         <v>5</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="H29" s="3">
         <v>1</v>
       </c>
       <c r="I29" s="3">
-        <v>9999999</v>
+        <v>9999999999</v>
       </c>
       <c r="J29" s="3">
         <v>0</v>
@@ -4694,17 +4661,17 @@
     </row>
     <row r="30" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C30" s="3">
-        <v>4009</v>
+        <v>4008</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" s="3">
         <v>5</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H30" s="3">
         <v>1</v>
@@ -4727,17 +4694,17 @@
     </row>
     <row r="31" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C31" s="3">
-        <v>4010</v>
+        <v>4009</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" s="3">
         <v>5</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H31" s="3">
         <v>1</v>
@@ -4760,17 +4727,17 @@
     </row>
     <row r="32" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C32" s="3">
-        <v>4011</v>
+        <v>4010</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" s="3">
         <v>5</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H32" s="3">
         <v>1</v>
@@ -4782,61 +4749,61 @@
         <v>0</v>
       </c>
       <c r="K32" s="3">
+        <v>5</v>
+      </c>
+      <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" s="3" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C33" s="3">
+        <v>4011</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="E33" s="2"/>
+      <c r="F33" s="3">
+        <v>5</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="H33" s="3">
+        <v>1</v>
+      </c>
+      <c r="I33" s="3">
+        <v>9999999</v>
+      </c>
+      <c r="J33" s="3">
+        <v>0</v>
+      </c>
+      <c r="K33" s="3">
         <v>6</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" s="3" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C34" s="3">
-        <v>4013</v>
-      </c>
-      <c r="D34" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="E34" s="2"/>
-      <c r="F34" s="3">
-        <v>9</v>
-      </c>
-      <c r="G34" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="H34" s="3">
-        <v>1</v>
-      </c>
-      <c r="I34" s="3">
-        <v>9999999</v>
-      </c>
-      <c r="J34" s="3">
-        <v>0</v>
-      </c>
-      <c r="K34" s="3">
-        <v>5</v>
-      </c>
-      <c r="M34" s="3">
-        <v>0</v>
-      </c>
-      <c r="N34" s="3">
+      <c r="M33" s="3">
+        <v>0</v>
+      </c>
+      <c r="N33" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="35" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C35" s="3">
-        <v>4015</v>
+        <v>4013</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" s="3">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H35" s="3">
         <v>1</v>
@@ -4848,7 +4815,7 @@
         <v>0</v>
       </c>
       <c r="K35" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M35" s="3">
         <v>0</v>
@@ -4859,17 +4826,17 @@
     </row>
     <row r="36" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C36" s="3">
-        <v>4016</v>
+        <v>4015</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" s="3">
         <v>5</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="H36" s="3">
         <v>1</v>
@@ -4892,17 +4859,17 @@
     </row>
     <row r="37" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C37" s="3">
-        <v>4017</v>
+        <v>4016</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" s="3">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="H37" s="3">
         <v>1</v>
@@ -4914,7 +4881,7 @@
         <v>0</v>
       </c>
       <c r="K37" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M37" s="3">
         <v>0</v>
@@ -4925,17 +4892,17 @@
     </row>
     <row r="38" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C38" s="3">
-        <v>4018</v>
+        <v>4017</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" s="3">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="H38" s="3">
         <v>1</v>
@@ -4947,7 +4914,7 @@
         <v>0</v>
       </c>
       <c r="K38" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M38" s="3">
         <v>0</v>
@@ -4958,17 +4925,17 @@
     </row>
     <row r="39" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C39" s="3">
-        <v>4019</v>
+        <v>4018</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" s="3">
         <v>5</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="H39" s="3">
         <v>1</v>
@@ -4980,61 +4947,61 @@
         <v>0</v>
       </c>
       <c r="K39" s="3">
+        <v>6</v>
+      </c>
+      <c r="M39" s="3">
+        <v>0</v>
+      </c>
+      <c r="N39" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" s="3" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C40" s="3">
+        <v>4019</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="E40" s="2"/>
+      <c r="F40" s="3">
+        <v>5</v>
+      </c>
+      <c r="G40" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="H40" s="3">
+        <v>1</v>
+      </c>
+      <c r="I40" s="3">
+        <v>9999999</v>
+      </c>
+      <c r="J40" s="3">
+        <v>0</v>
+      </c>
+      <c r="K40" s="3">
         <v>7</v>
       </c>
-      <c r="M39" s="3">
-        <v>0</v>
-      </c>
-      <c r="N39" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" s="3" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C41" s="3">
-        <v>4021</v>
-      </c>
-      <c r="D41" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="E41" s="2"/>
-      <c r="F41" s="3">
-        <v>5</v>
-      </c>
-      <c r="G41" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="H41" s="3">
-        <v>1</v>
-      </c>
-      <c r="I41" s="3">
-        <v>9999999</v>
-      </c>
-      <c r="J41" s="3">
-        <v>0</v>
-      </c>
-      <c r="K41" s="3">
-        <v>6</v>
-      </c>
-      <c r="M41" s="3">
-        <v>0</v>
-      </c>
-      <c r="N41" s="3">
+      <c r="M40" s="3">
+        <v>0</v>
+      </c>
+      <c r="N40" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="42" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C42" s="3">
-        <v>4022</v>
+        <v>4021</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" s="3">
         <v>5</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="H42" s="3">
         <v>1</v>
@@ -5046,7 +5013,7 @@
         <v>0</v>
       </c>
       <c r="K42" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M42" s="3">
         <v>0</v>
@@ -5057,17 +5024,17 @@
     </row>
     <row r="43" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C43" s="3">
-        <v>4023</v>
+        <v>4022</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" s="3">
         <v>5</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="H43" s="3">
         <v>1</v>
@@ -5090,17 +5057,17 @@
     </row>
     <row r="44" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C44" s="3">
-        <v>4024</v>
+        <v>4023</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" s="3">
         <v>5</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="H44" s="3">
         <v>1</v>
@@ -5112,7 +5079,7 @@
         <v>0</v>
       </c>
       <c r="K44" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -5123,17 +5090,17 @@
     </row>
     <row r="45" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C45" s="3">
-        <v>4025</v>
+        <v>4024</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" s="3">
         <v>5</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="H45" s="3">
         <v>1</v>
@@ -5145,7 +5112,7 @@
         <v>0</v>
       </c>
       <c r="K45" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M45" s="3">
         <v>0</v>
@@ -5156,17 +5123,17 @@
     </row>
     <row r="46" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C46" s="3">
-        <v>4026</v>
+        <v>4025</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" s="3">
         <v>5</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="H46" s="3">
         <v>1</v>
@@ -5178,7 +5145,7 @@
         <v>0</v>
       </c>
       <c r="K46" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M46" s="3">
         <v>0</v>
@@ -5189,17 +5156,17 @@
     </row>
     <row r="47" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C47" s="3">
-        <v>4027</v>
+        <v>4026</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" s="3">
         <v>5</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="H47" s="3">
         <v>1</v>
@@ -5211,7 +5178,7 @@
         <v>0</v>
       </c>
       <c r="K47" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -5222,17 +5189,17 @@
     </row>
     <row r="48" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C48" s="3">
-        <v>4028</v>
+        <v>4027</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" s="3">
         <v>5</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="H48" s="3">
         <v>1</v>
@@ -5255,17 +5222,17 @@
     </row>
     <row r="49" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C49" s="3">
-        <v>4029</v>
+        <v>4028</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" s="3">
         <v>5</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="H49" s="3">
         <v>1</v>
@@ -5288,17 +5255,17 @@
     </row>
     <row r="50" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C50" s="3">
-        <v>4030</v>
+        <v>4029</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" s="3">
         <v>5</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="H50" s="3">
         <v>1</v>
@@ -5321,17 +5288,17 @@
     </row>
     <row r="51" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C51" s="3">
-        <v>4031</v>
+        <v>4030</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" s="3">
         <v>5</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="H51" s="3">
         <v>1</v>
@@ -5354,17 +5321,17 @@
     </row>
     <row r="52" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C52" s="3">
-        <v>4032</v>
+        <v>4031</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" s="3">
         <v>5</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="H52" s="3">
         <v>1</v>
@@ -5387,17 +5354,17 @@
     </row>
     <row r="53" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C53" s="3">
-        <v>4033</v>
+        <v>4032</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" s="3">
         <v>5</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>188</v>
+        <v>218</v>
       </c>
       <c r="H53" s="3">
         <v>1</v>
@@ -5409,7 +5376,7 @@
         <v>0</v>
       </c>
       <c r="K53" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M53" s="3">
         <v>0</v>
@@ -5420,17 +5387,17 @@
     </row>
     <row r="54" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C54" s="3">
-        <v>4034</v>
+        <v>4033</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" s="3">
         <v>5</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>221</v>
+        <v>188</v>
       </c>
       <c r="H54" s="3">
         <v>1</v>
@@ -5442,7 +5409,7 @@
         <v>0</v>
       </c>
       <c r="K54" s="3">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M54" s="3">
         <v>0</v>
@@ -5453,17 +5420,17 @@
     </row>
     <row r="55" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C55" s="3">
-        <v>4035</v>
+        <v>4034</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>147</v>
+        <v>220</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" s="3">
         <v>5</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H55" s="3">
         <v>1</v>
@@ -5475,7 +5442,7 @@
         <v>0</v>
       </c>
       <c r="K55" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M55" s="3">
         <v>0</v>
@@ -5486,17 +5453,17 @@
     </row>
     <row r="56" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C56" s="3">
-        <v>4037</v>
+        <v>4035</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>223</v>
+        <v>147</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" s="3">
         <v>5</v>
       </c>
       <c r="G56" s="3" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="H56" s="3">
         <v>1</v>
@@ -5508,7 +5475,7 @@
         <v>0</v>
       </c>
       <c r="K56" s="3">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="M56" s="3">
         <v>0</v>
@@ -5519,17 +5486,17 @@
     </row>
     <row r="57" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C57" s="3">
-        <v>4038</v>
+        <v>4037</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" s="3">
         <v>5</v>
       </c>
       <c r="G57" s="3" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="H57" s="3">
         <v>1</v>
@@ -5552,17 +5519,17 @@
     </row>
     <row r="58" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C58" s="3">
-        <v>4039</v>
+        <v>4038</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" s="3">
         <v>5</v>
       </c>
       <c r="G58" s="3" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="H58" s="3">
         <v>1</v>
@@ -5574,7 +5541,7 @@
         <v>0</v>
       </c>
       <c r="K58" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M58" s="3">
         <v>0</v>
@@ -5585,17 +5552,17 @@
     </row>
     <row r="59" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C59" s="3">
-        <v>4040</v>
+        <v>4039</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" s="3">
         <v>5</v>
       </c>
       <c r="G59" s="3" t="s">
-        <v>188</v>
+        <v>228</v>
       </c>
       <c r="H59" s="3">
         <v>1</v>
@@ -5607,7 +5574,7 @@
         <v>0</v>
       </c>
       <c r="K59" s="3">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M59" s="3">
         <v>0</v>
@@ -5618,17 +5585,17 @@
     </row>
     <row r="60" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C60" s="3">
-        <v>4041</v>
+        <v>4040</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" s="3">
         <v>5</v>
       </c>
       <c r="G60" s="3" t="s">
-        <v>231</v>
+        <v>188</v>
       </c>
       <c r="H60" s="3">
         <v>1</v>
@@ -5640,7 +5607,7 @@
         <v>0</v>
       </c>
       <c r="K60" s="3">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M60" s="3">
         <v>0</v>
@@ -5651,29 +5618,29 @@
     </row>
     <row r="61" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C61" s="3">
-        <v>4042</v>
+        <v>4041</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" s="3">
         <v>5</v>
       </c>
       <c r="G61" s="3" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="H61" s="3">
         <v>1</v>
       </c>
       <c r="I61" s="3">
-        <v>1999999999</v>
+        <v>9999999</v>
       </c>
       <c r="J61" s="3">
         <v>0</v>
       </c>
       <c r="K61" s="3">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="M61" s="3">
         <v>0</v>
@@ -5684,10 +5651,10 @@
     </row>
     <row r="62" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C62" s="3">
-        <v>4043</v>
+        <v>4042</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" s="3">
@@ -5700,13 +5667,13 @@
         <v>1</v>
       </c>
       <c r="I62" s="3">
-        <v>9999999</v>
+        <v>1999999999</v>
       </c>
       <c r="J62" s="3">
         <v>0</v>
       </c>
       <c r="K62" s="3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M62" s="3">
         <v>0</v>
@@ -5717,17 +5684,17 @@
     </row>
     <row r="63" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C63" s="3">
-        <v>4044</v>
+        <v>4043</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" s="3">
         <v>5</v>
       </c>
       <c r="G63" s="3" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="H63" s="3">
         <v>1</v>
@@ -5739,74 +5706,74 @@
         <v>0</v>
       </c>
       <c r="K63" s="3">
+        <v>7</v>
+      </c>
+      <c r="M63" s="3">
+        <v>0</v>
+      </c>
+      <c r="N63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" s="3" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C64" s="3">
+        <v>4044</v>
+      </c>
+      <c r="D64" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="E64" s="2"/>
+      <c r="F64" s="3">
+        <v>5</v>
+      </c>
+      <c r="G64" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="H64" s="3">
+        <v>1</v>
+      </c>
+      <c r="I64" s="3">
+        <v>9999999</v>
+      </c>
+      <c r="J64" s="3">
+        <v>0</v>
+      </c>
+      <c r="K64" s="3">
         <v>9</v>
       </c>
-      <c r="M63" s="3">
-        <v>0</v>
-      </c>
-      <c r="N63" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C64" s="3"/>
-      <c r="D64" s="3"/>
-      <c r="E64" s="2"/>
-      <c r="F64" s="3"/>
-      <c r="G64" s="3"/>
-      <c r="H64" s="3"/>
-      <c r="I64" s="3"/>
-      <c r="J64" s="3"/>
-      <c r="K64" s="3"/>
-      <c r="M64" s="3"/>
-      <c r="N64" s="3"/>
-    </row>
-    <row r="65" s="3" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C65" s="3">
-        <v>4101</v>
-      </c>
-      <c r="D65" s="3" t="s">
-        <v>237</v>
-      </c>
+      <c r="M64" s="3">
+        <v>0</v>
+      </c>
+      <c r="N64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C65" s="3"/>
+      <c r="D65" s="3"/>
       <c r="E65" s="2"/>
-      <c r="F65" s="3">
-        <v>5</v>
-      </c>
-      <c r="G65" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="H65" s="3">
-        <v>1</v>
-      </c>
-      <c r="I65" s="3">
-        <v>9999999</v>
-      </c>
-      <c r="J65" s="3">
-        <v>0</v>
-      </c>
-      <c r="K65" s="3">
-        <v>5</v>
-      </c>
-      <c r="M65" s="3">
-        <v>0</v>
-      </c>
-      <c r="N65" s="3">
-        <v>0</v>
-      </c>
+      <c r="F65" s="3"/>
+      <c r="G65" s="3"/>
+      <c r="H65" s="3"/>
+      <c r="I65" s="3"/>
+      <c r="J65" s="3"/>
+      <c r="K65" s="3"/>
+      <c r="M65" s="3"/>
+      <c r="N65" s="3"/>
     </row>
     <row r="66" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C66" s="3">
-        <v>4111</v>
+        <v>4101</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" s="3">
         <v>5</v>
       </c>
       <c r="G66" s="3" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="H66" s="3">
         <v>1</v>
@@ -5829,17 +5796,17 @@
     </row>
     <row r="67" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C67" s="3">
-        <v>4112</v>
+        <v>4111</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" s="3">
         <v>5</v>
       </c>
       <c r="G67" s="3" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="H67" s="3">
         <v>1</v>
@@ -5851,7 +5818,7 @@
         <v>0</v>
       </c>
       <c r="K67" s="3">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="M67" s="3">
         <v>0</v>
@@ -5862,17 +5829,17 @@
     </row>
     <row r="68" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C68" s="3">
-        <v>4113</v>
+        <v>4112</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" s="3">
         <v>5</v>
       </c>
       <c r="G68" s="3" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="H68" s="3">
         <v>1</v>
@@ -5884,100 +5851,100 @@
         <v>0</v>
       </c>
       <c r="K68" s="3">
+        <v>8</v>
+      </c>
+      <c r="M68" s="3">
+        <v>0</v>
+      </c>
+      <c r="N68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" s="3" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C69" s="3">
+        <v>4113</v>
+      </c>
+      <c r="D69" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="E69" s="2"/>
+      <c r="F69" s="3">
+        <v>5</v>
+      </c>
+      <c r="G69" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="H69" s="3">
+        <v>1</v>
+      </c>
+      <c r="I69" s="3">
+        <v>9999999</v>
+      </c>
+      <c r="J69" s="3">
+        <v>0</v>
+      </c>
+      <c r="K69" s="3">
         <v>7</v>
       </c>
-      <c r="M68" s="3">
-        <v>0</v>
-      </c>
-      <c r="N68" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C69" s="3"/>
-      <c r="D69" s="3"/>
-      <c r="E69" s="2"/>
-      <c r="F69" s="3"/>
-      <c r="G69" s="3"/>
-      <c r="H69" s="3"/>
-      <c r="I69" s="3"/>
-      <c r="J69" s="3"/>
-      <c r="K69" s="3"/>
-      <c r="M69" s="3"/>
-      <c r="N69" s="3"/>
-    </row>
-    <row r="70" s="3" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C70" s="3">
+      <c r="M69" s="3">
+        <v>0</v>
+      </c>
+      <c r="N69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C70" s="3"/>
+      <c r="D70" s="3"/>
+      <c r="E70" s="2"/>
+      <c r="F70" s="3"/>
+      <c r="G70" s="3"/>
+      <c r="H70" s="3"/>
+      <c r="I70" s="3"/>
+      <c r="J70" s="3"/>
+      <c r="K70" s="3"/>
+      <c r="M70" s="3"/>
+      <c r="N70" s="3"/>
+    </row>
+    <row r="71" s="3" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C71" s="3">
         <v>4201</v>
       </c>
-      <c r="D70" s="3" t="s">
+      <c r="D71" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="E70" s="2"/>
-      <c r="F70" s="3">
-        <v>5</v>
-      </c>
-      <c r="G70" s="3" t="s">
+      <c r="E71" s="2"/>
+      <c r="F71" s="3">
+        <v>5</v>
+      </c>
+      <c r="G71" s="3" t="s">
         <v>246</v>
       </c>
-      <c r="H70" s="3">
-        <v>1</v>
-      </c>
-      <c r="I70" s="3">
+      <c r="H71" s="3">
+        <v>1</v>
+      </c>
+      <c r="I71" s="3">
         <v>99999999</v>
       </c>
-      <c r="J70" s="3">
-        <v>0</v>
-      </c>
-      <c r="K70" s="3">
-        <v>5</v>
-      </c>
-      <c r="M70" s="3">
+      <c r="J71" s="3">
+        <v>0</v>
+      </c>
+      <c r="K71" s="3">
+        <v>5</v>
+      </c>
+      <c r="M71" s="3">
         <v>4002</v>
       </c>
-      <c r="N70" s="3">
+      <c r="N71" s="3">
         <v>1000</v>
-      </c>
-    </row>
-    <row r="75" s="3" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C75" s="3">
-        <v>8001</v>
-      </c>
-      <c r="D75" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="E75" s="2"/>
-      <c r="F75" s="3">
-        <v>5</v>
-      </c>
-      <c r="G75" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="H75" s="3">
-        <v>1</v>
-      </c>
-      <c r="I75" s="3">
-        <v>9999999</v>
-      </c>
-      <c r="J75" s="3">
-        <v>0</v>
-      </c>
-      <c r="K75" s="3">
-        <v>6</v>
-      </c>
-      <c r="M75" s="3">
-        <v>0</v>
-      </c>
-      <c r="N75" s="3">
-        <v>0</v>
       </c>
     </row>
     <row r="76" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C76" s="3">
-        <v>8002</v>
+        <v>8001</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" s="3">
@@ -6007,10 +5974,10 @@
     </row>
     <row r="77" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C77" s="3">
-        <v>8003</v>
+        <v>8002</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" s="3">
@@ -6040,10 +6007,10 @@
     </row>
     <row r="78" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C78" s="3">
-        <v>8004</v>
+        <v>8003</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" s="3">
@@ -6073,10 +6040,10 @@
     </row>
     <row r="79" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C79" s="3">
-        <v>8005</v>
+        <v>8004</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" s="3">
@@ -6106,10 +6073,10 @@
     </row>
     <row r="80" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C80" s="3">
-        <v>8006</v>
+        <v>8005</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" s="3">
@@ -6139,10 +6106,10 @@
     </row>
     <row r="81" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C81" s="3">
-        <v>8007</v>
+        <v>8006</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" s="3">
@@ -6172,10 +6139,10 @@
     </row>
     <row r="82" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C82" s="3">
-        <v>8008</v>
+        <v>8007</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" s="3">
@@ -6205,10 +6172,10 @@
     </row>
     <row r="83" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C83" s="3">
-        <v>8009</v>
+        <v>8008</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" s="3">
@@ -6238,10 +6205,10 @@
     </row>
     <row r="84" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C84" s="3">
-        <v>8010</v>
+        <v>8009</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" s="3">
@@ -6269,45 +6236,45 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" s="3" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C86" s="3">
-        <v>8101</v>
-      </c>
-      <c r="D86" s="9" t="s">
-        <v>258</v>
-      </c>
-      <c r="E86" s="2"/>
-      <c r="F86" s="3">
-        <v>5</v>
-      </c>
-      <c r="G86" s="3" t="s">
-        <v>259</v>
-      </c>
-      <c r="H86" s="3">
-        <v>1</v>
-      </c>
-      <c r="I86" s="3">
+    <row r="85" s="3" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C85" s="3">
+        <v>8010</v>
+      </c>
+      <c r="D85" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="E85" s="2"/>
+      <c r="F85" s="3">
+        <v>5</v>
+      </c>
+      <c r="G85" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="H85" s="3">
+        <v>1</v>
+      </c>
+      <c r="I85" s="3">
         <v>9999999</v>
       </c>
-      <c r="J86" s="3">
-        <v>0</v>
-      </c>
-      <c r="K86" s="3">
-        <v>7</v>
-      </c>
-      <c r="M86" s="3">
-        <v>0</v>
-      </c>
-      <c r="N86" s="3">
+      <c r="J85" s="3">
+        <v>0</v>
+      </c>
+      <c r="K85" s="3">
+        <v>6</v>
+      </c>
+      <c r="M85" s="3">
+        <v>0</v>
+      </c>
+      <c r="N85" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="87" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C87" s="3">
-        <v>8102</v>
+        <v>8101</v>
       </c>
       <c r="D87" s="9" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" s="3">
@@ -6337,10 +6304,10 @@
     </row>
     <row r="88" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C88" s="3">
-        <v>8103</v>
+        <v>8102</v>
       </c>
       <c r="D88" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E88" s="2"/>
       <c r="F88" s="3">
@@ -6370,10 +6337,10 @@
     </row>
     <row r="89" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C89" s="3">
-        <v>8104</v>
+        <v>8103</v>
       </c>
       <c r="D89" s="9" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" s="3">
@@ -6403,10 +6370,10 @@
     </row>
     <row r="90" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C90" s="3">
-        <v>8105</v>
+        <v>8104</v>
       </c>
       <c r="D90" s="9" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E90" s="2"/>
       <c r="F90" s="3">
@@ -6436,10 +6403,10 @@
     </row>
     <row r="91" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C91" s="3">
-        <v>8106</v>
+        <v>8105</v>
       </c>
       <c r="D91" s="9" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E91" s="2"/>
       <c r="F91" s="3">
@@ -6469,10 +6436,10 @@
     </row>
     <row r="92" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C92" s="3">
-        <v>8107</v>
+        <v>8106</v>
       </c>
       <c r="D92" s="9" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E92" s="2"/>
       <c r="F92" s="3">
@@ -6502,10 +6469,10 @@
     </row>
     <row r="93" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C93" s="3">
-        <v>8108</v>
+        <v>8107</v>
       </c>
       <c r="D93" s="9" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="E93" s="2"/>
       <c r="F93" s="3">
@@ -6533,53 +6500,51 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" customHeight="1" spans="3:14">
-      <c r="C95" s="3">
-        <v>8201</v>
-      </c>
-      <c r="D95" s="9" t="s">
-        <v>267</v>
-      </c>
-      <c r="F95" s="3">
-        <v>16</v>
-      </c>
-      <c r="G95" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="H95" s="3">
-        <v>1</v>
-      </c>
-      <c r="I95" s="3">
-        <v>1</v>
-      </c>
-      <c r="J95" s="3">
-        <v>0</v>
-      </c>
-      <c r="K95" s="3">
-        <v>1</v>
-      </c>
-      <c r="L95" s="3">
-        <v>0</v>
-      </c>
-      <c r="M95" s="3">
-        <v>0</v>
-      </c>
-      <c r="N95" s="3">
+    <row r="94" s="3" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C94" s="3">
+        <v>8108</v>
+      </c>
+      <c r="D94" s="9" t="s">
+        <v>266</v>
+      </c>
+      <c r="E94" s="2"/>
+      <c r="F94" s="3">
+        <v>5</v>
+      </c>
+      <c r="G94" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="H94" s="3">
+        <v>1</v>
+      </c>
+      <c r="I94" s="3">
+        <v>9999999</v>
+      </c>
+      <c r="J94" s="3">
+        <v>0</v>
+      </c>
+      <c r="K94" s="3">
+        <v>7</v>
+      </c>
+      <c r="M94" s="3">
+        <v>0</v>
+      </c>
+      <c r="N94" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="96" customHeight="1" spans="3:14">
       <c r="C96" s="3">
-        <v>8202</v>
+        <v>8201</v>
       </c>
       <c r="D96" s="9" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="F96" s="3">
         <v>16</v>
       </c>
       <c r="G96" s="3" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="H96" s="3">
         <v>1</v>
@@ -6591,7 +6556,7 @@
         <v>0</v>
       </c>
       <c r="K96" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -6605,16 +6570,16 @@
     </row>
     <row r="97" customHeight="1" spans="3:14">
       <c r="C97" s="3">
-        <v>8203</v>
+        <v>8202</v>
       </c>
       <c r="D97" s="9" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="F97" s="3">
         <v>16</v>
       </c>
       <c r="G97" s="3" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="H97" s="3">
         <v>1</v>
@@ -6626,7 +6591,7 @@
         <v>0</v>
       </c>
       <c r="K97" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L97" s="3">
         <v>0</v>
@@ -6640,16 +6605,16 @@
     </row>
     <row r="98" customHeight="1" spans="3:14">
       <c r="C98" s="3">
-        <v>8204</v>
+        <v>8203</v>
       </c>
       <c r="D98" s="9" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="F98" s="3">
         <v>16</v>
       </c>
       <c r="G98" s="3" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="H98" s="3">
         <v>1</v>
@@ -6661,7 +6626,7 @@
         <v>0</v>
       </c>
       <c r="K98" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L98" s="3">
         <v>0</v>
@@ -6675,16 +6640,16 @@
     </row>
     <row r="99" customHeight="1" spans="3:14">
       <c r="C99" s="3">
-        <v>8205</v>
+        <v>8204</v>
       </c>
       <c r="D99" s="9" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="F99" s="3">
         <v>16</v>
       </c>
       <c r="G99" s="3" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="H99" s="3">
         <v>1</v>
@@ -6696,7 +6661,7 @@
         <v>0</v>
       </c>
       <c r="K99" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L99" s="3">
         <v>0</v>
@@ -6710,16 +6675,16 @@
     </row>
     <row r="100" customHeight="1" spans="3:14">
       <c r="C100" s="3">
-        <v>8206</v>
+        <v>8205</v>
       </c>
       <c r="D100" s="9" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="F100" s="3">
         <v>16</v>
       </c>
       <c r="G100" s="3" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H100" s="3">
         <v>1</v>
@@ -6731,7 +6696,7 @@
         <v>0</v>
       </c>
       <c r="K100" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L100" s="3">
         <v>0</v>
@@ -6745,41 +6710,73 @@
     </row>
     <row r="101" customHeight="1" spans="3:14">
       <c r="C101" s="3">
-        <v>8207</v>
+        <v>8206</v>
       </c>
       <c r="D101" s="9" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="F101" s="3">
         <v>16</v>
       </c>
       <c r="G101" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="H101" s="3">
+        <v>1</v>
+      </c>
+      <c r="I101" s="3">
+        <v>1</v>
+      </c>
+      <c r="J101" s="3">
+        <v>0</v>
+      </c>
+      <c r="K101" s="3">
+        <v>6</v>
+      </c>
+      <c r="L101" s="3">
+        <v>0</v>
+      </c>
+      <c r="M101" s="3">
+        <v>0</v>
+      </c>
+      <c r="N101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" customHeight="1" spans="3:14">
+      <c r="C102" s="3">
+        <v>8207</v>
+      </c>
+      <c r="D102" s="9" t="s">
+        <v>279</v>
+      </c>
+      <c r="F102" s="3">
+        <v>16</v>
+      </c>
+      <c r="G102" s="3" t="s">
         <v>280</v>
       </c>
-      <c r="H101" s="3">
-        <v>1</v>
-      </c>
-      <c r="I101" s="3">
-        <v>1</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
-      </c>
-      <c r="K101" s="3">
+      <c r="H102" s="3">
+        <v>1</v>
+      </c>
+      <c r="I102" s="3">
+        <v>1</v>
+      </c>
+      <c r="J102" s="3">
+        <v>0</v>
+      </c>
+      <c r="K102" s="3">
         <v>7</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
-      </c>
-      <c r="M101" s="3">
-        <v>0</v>
-      </c>
-      <c r="N101" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="103" customHeight="1" spans="3:14">
-      <c r="D103" s="9"/>
+      <c r="L102" s="3">
+        <v>0</v>
+      </c>
+      <c r="M102" s="3">
+        <v>0</v>
+      </c>
+      <c r="N102" s="3">
+        <v>0</v>
+      </c>
     </row>
     <row r="104" customHeight="1" spans="3:14">
       <c r="D104" s="9"/>
@@ -6799,8 +6796,8 @@
     <row r="109" customHeight="1" spans="3:14">
       <c r="D109" s="9"/>
     </row>
-    <row r="111" customHeight="1" spans="3:14">
-      <c r="D111" s="9"/>
+    <row r="110" customHeight="1" spans="3:14">
+      <c r="D110" s="9"/>
     </row>
     <row r="112" customHeight="1" spans="3:14">
       <c r="D112" s="9"/>
@@ -6820,12 +6817,15 @@
     <row r="117" customHeight="1" spans="4:4">
       <c r="D117" s="9"/>
     </row>
+    <row r="118" customHeight="1" spans="4:4">
+      <c r="D118" s="9"/>
+    </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C12:D12 C17:D17 C13:C16 C3:E5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C13:D13 C18:D18 C14:C17 C3:E5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="M17:N17 M3:N5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="M18:N18 M3:N5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,M3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/ItemConfig.xlsx
+++ b/Excel/ItemConfig.xlsx
@@ -325,7 +325,7 @@
     <t>1003</t>
   </si>
   <si>
-    <t>月华剑阵</t>
+    <t>月华剑网</t>
   </si>
   <si>
     <t>学习或者升级战士技能月华剑阵</t>

--- a/Excel/ItemConfig.xlsx
+++ b/Excel/ItemConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView windowHeight="17680" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="技能" sheetId="1" r:id="rId1"/>
@@ -1114,10 +1114,10 @@
     <t>QQ玩家</t>
   </si>
   <si>
-    <t>老玩家</t>
-  </si>
-  <si>
-    <t>大佬再临</t>
+    <t>无尽玩家</t>
+  </si>
+  <si>
+    <t>天下无敌</t>
   </si>
   <si>
     <t>狼毛</t>

--- a/Excel/ItemConfig.xlsx
+++ b/Excel/ItemConfig.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\legend2\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowHeight="17680" activeTab="3"/>
   </bookViews>

--- a/Excel/ItemConfig.xlsx
+++ b/Excel/ItemConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="3"/>
+    <workbookView windowHeight="17680" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="技能" sheetId="1" r:id="rId1"/>
@@ -229,7 +229,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="632" uniqueCount="334">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="642" uniqueCount="344">
   <si>
     <t>_Id</t>
   </si>
@@ -706,6 +706,36 @@
   </si>
   <si>
     <t>灵珠进阶材料</t>
+  </si>
+  <si>
+    <t>一阶神兵符</t>
+  </si>
+  <si>
+    <t>神兵进阶到1阶的材料</t>
+  </si>
+  <si>
+    <t>二阶神兵符</t>
+  </si>
+  <si>
+    <t>神兵进阶到2阶的材料</t>
+  </si>
+  <si>
+    <t>三阶神兵符</t>
+  </si>
+  <si>
+    <t>神兵进阶到3阶的材料</t>
+  </si>
+  <si>
+    <t>四阶神兵符</t>
+  </si>
+  <si>
+    <t>神兵进阶到4阶的材料</t>
+  </si>
+  <si>
+    <t>五阶神兵符</t>
+  </si>
+  <si>
+    <t>神兵进阶到5阶的材料</t>
   </si>
   <si>
     <t>等级丹</t>
@@ -1900,7 +1930,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1921,6 +1951,9 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
   </cellXfs>
@@ -2643,7 +2676,7 @@
       <c r="B13" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C13" s="11" t="s">
+      <c r="C13" s="12" t="s">
         <v>49</v>
       </c>
       <c r="D13" s="6" t="s">
@@ -2687,7 +2720,7 @@
       <c r="B14" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C14" s="11" t="s">
+      <c r="C14" s="12" t="s">
         <v>52</v>
       </c>
       <c r="D14" s="6" t="s">
@@ -2731,7 +2764,7 @@
       <c r="B15" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C15" s="11" t="s">
+      <c r="C15" s="12" t="s">
         <v>55</v>
       </c>
       <c r="D15" s="6" t="s">
@@ -2775,7 +2808,7 @@
       <c r="B16" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C16" s="11" t="s">
+      <c r="C16" s="12" t="s">
         <v>58</v>
       </c>
       <c r="D16" s="6" t="s">
@@ -2819,7 +2852,7 @@
       <c r="B17" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C17" s="11" t="s">
+      <c r="C17" s="12" t="s">
         <v>61</v>
       </c>
       <c r="D17" s="6" t="s">
@@ -3129,7 +3162,7 @@
       <c r="B26" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C26" s="11" t="s">
+      <c r="C26" s="12" t="s">
         <v>86</v>
       </c>
       <c r="D26" s="6" t="s">
@@ -3173,7 +3206,7 @@
       <c r="B27" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C27" s="11" t="s">
+      <c r="C27" s="12" t="s">
         <v>89</v>
       </c>
       <c r="D27" s="6" t="s">
@@ -3217,7 +3250,7 @@
       <c r="B28" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C28" s="11" t="s">
+      <c r="C28" s="12" t="s">
         <v>92</v>
       </c>
       <c r="D28" s="6" t="s">
@@ -3261,7 +3294,7 @@
       <c r="B29" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C29" s="11" t="s">
+      <c r="C29" s="12" t="s">
         <v>95</v>
       </c>
       <c r="D29" s="6" t="s">
@@ -3305,7 +3338,7 @@
       <c r="B30" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C30" s="11" t="s">
+      <c r="C30" s="12" t="s">
         <v>98</v>
       </c>
       <c r="D30" s="6" t="s">
@@ -3615,7 +3648,7 @@
       <c r="B39" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C39" s="11" t="s">
+      <c r="C39" s="12" t="s">
         <v>123</v>
       </c>
       <c r="D39" s="6" t="s">
@@ -3659,7 +3692,7 @@
       <c r="B40" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C40" s="11" t="s">
+      <c r="C40" s="12" t="s">
         <v>126</v>
       </c>
       <c r="D40" s="6" t="s">
@@ -3703,7 +3736,7 @@
       <c r="B41" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C41" s="11" t="s">
+      <c r="C41" s="12" t="s">
         <v>129</v>
       </c>
       <c r="D41" s="6" t="s">
@@ -3747,7 +3780,7 @@
       <c r="B42" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C42" s="11" t="s">
+      <c r="C42" s="12" t="s">
         <v>132</v>
       </c>
       <c r="D42" s="6" t="s">
@@ -3791,7 +3824,7 @@
       <c r="B43" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C43" s="11" t="s">
+      <c r="C43" s="12" t="s">
         <v>135</v>
       </c>
       <c r="D43" s="6" t="s">
@@ -3847,7 +3880,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:N118"/>
+  <dimension ref="C1:N122"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="3"/>
@@ -4371,45 +4404,66 @@
       </c>
     </row>
     <row r="18" s="6" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
+      <c r="C18" s="8">
+        <v>5015</v>
+      </c>
+      <c r="D18" s="11" t="s">
+        <v>159</v>
+      </c>
       <c r="E18" s="3"/>
-      <c r="F18" s="7"/>
-      <c r="G18" s="7"/>
-      <c r="H18" s="7"/>
-      <c r="I18" s="7"/>
-      <c r="J18" s="7"/>
-      <c r="K18" s="7"/>
-      <c r="L18" s="7"/>
-      <c r="M18" s="7"/>
-      <c r="N18" s="7"/>
-    </row>
-    <row r="19" s="3" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C19" s="3">
-        <v>7001</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>159</v>
+      <c r="F18" s="10">
+        <v>5</v>
+      </c>
+      <c r="G18" s="11" t="s">
+        <v>160</v>
+      </c>
+      <c r="H18" s="3">
+        <v>1</v>
+      </c>
+      <c r="I18" s="3">
+        <v>99999999</v>
+      </c>
+      <c r="J18" s="3">
+        <v>0</v>
+      </c>
+      <c r="K18" s="8">
+        <v>3</v>
+      </c>
+      <c r="L18" s="8"/>
+      <c r="M18" s="3">
+        <v>0</v>
+      </c>
+      <c r="N18" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" s="6" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C19" s="8">
+        <v>5016</v>
+      </c>
+      <c r="D19" s="11" t="s">
+        <v>161</v>
       </c>
       <c r="E19" s="3"/>
-      <c r="F19" s="3">
-        <v>7</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>160</v>
+      <c r="F19" s="10">
+        <v>5</v>
+      </c>
+      <c r="G19" s="11" t="s">
+        <v>162</v>
       </c>
       <c r="H19" s="3">
         <v>1</v>
       </c>
       <c r="I19" s="3">
-        <v>9999999</v>
+        <v>99999999</v>
       </c>
       <c r="J19" s="3">
         <v>0</v>
       </c>
-      <c r="K19" s="3">
-        <v>6</v>
-      </c>
+      <c r="K19" s="8">
+        <v>3</v>
+      </c>
+      <c r="L19" s="8"/>
       <c r="M19" s="3">
         <v>0</v>
       </c>
@@ -4417,35 +4471,33 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" s="3" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C20" s="3">
-        <v>7002</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="E20" s="2"/>
-      <c r="F20" s="3">
-        <v>7</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>162</v>
+    <row r="20" s="6" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C20" s="8">
+        <v>5017</v>
+      </c>
+      <c r="D20" s="11" t="s">
+        <v>163</v>
+      </c>
+      <c r="E20" s="3"/>
+      <c r="F20" s="10">
+        <v>5</v>
+      </c>
+      <c r="G20" s="11" t="s">
+        <v>164</v>
       </c>
       <c r="H20" s="3">
         <v>1</v>
       </c>
       <c r="I20" s="3">
-        <v>9999999</v>
+        <v>99999999</v>
       </c>
       <c r="J20" s="3">
         <v>0</v>
       </c>
-      <c r="K20" s="3">
-        <v>7</v>
-      </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
+      <c r="K20" s="8">
+        <v>4</v>
+      </c>
+      <c r="L20" s="8"/>
       <c r="M20" s="3">
         <v>0</v>
       </c>
@@ -4453,44 +4505,99 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C22" s="3"/>
-      <c r="D22" s="3"/>
-      <c r="E22" s="2"/>
-      <c r="F22" s="3"/>
-      <c r="G22" s="3"/>
-      <c r="H22" s="3"/>
-      <c r="I22" s="3"/>
-      <c r="J22" s="3"/>
-      <c r="K22" s="3"/>
-      <c r="M22" s="3"/>
-      <c r="N22" s="3"/>
+    <row r="21" s="6" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C21" s="8">
+        <v>5018</v>
+      </c>
+      <c r="D21" s="11" t="s">
+        <v>165</v>
+      </c>
+      <c r="E21" s="3"/>
+      <c r="F21" s="10">
+        <v>5</v>
+      </c>
+      <c r="G21" s="11" t="s">
+        <v>166</v>
+      </c>
+      <c r="H21" s="3">
+        <v>1</v>
+      </c>
+      <c r="I21" s="3">
+        <v>99999999</v>
+      </c>
+      <c r="J21" s="3">
+        <v>0</v>
+      </c>
+      <c r="K21" s="8">
+        <v>4</v>
+      </c>
+      <c r="L21" s="8"/>
+      <c r="M21" s="3">
+        <v>0</v>
+      </c>
+      <c r="N21" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" s="6" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C22" s="8">
+        <v>5019</v>
+      </c>
+      <c r="D22" s="11" t="s">
+        <v>167</v>
+      </c>
+      <c r="E22" s="3"/>
+      <c r="F22" s="10">
+        <v>5</v>
+      </c>
+      <c r="G22" s="11" t="s">
+        <v>168</v>
+      </c>
+      <c r="H22" s="3">
+        <v>1</v>
+      </c>
+      <c r="I22" s="3">
+        <v>99999999</v>
+      </c>
+      <c r="J22" s="3">
+        <v>0</v>
+      </c>
+      <c r="K22" s="8">
+        <v>5</v>
+      </c>
+      <c r="L22" s="8"/>
+      <c r="M22" s="3">
+        <v>0</v>
+      </c>
+      <c r="N22" s="3">
+        <v>0</v>
+      </c>
     </row>
     <row r="23" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C23" s="3">
-        <v>4001</v>
+        <v>7001</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="E23" s="2"/>
+        <v>169</v>
+      </c>
+      <c r="E23" s="3"/>
       <c r="F23" s="3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="H23" s="3">
         <v>1</v>
       </c>
       <c r="I23" s="3">
-        <v>99999999999</v>
+        <v>9999999</v>
       </c>
       <c r="J23" s="3">
         <v>0</v>
       </c>
       <c r="K23" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M23" s="3">
         <v>0</v>
@@ -4501,30 +4608,31 @@
     </row>
     <row r="24" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C24" s="3">
-        <v>4002</v>
+        <v>7002</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" s="3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="H24" s="3">
         <v>1</v>
       </c>
       <c r="I24" s="3">
-        <v>99999999999</v>
+        <v>9999999</v>
       </c>
       <c r="J24" s="3">
         <v>0</v>
       </c>
       <c r="K24" s="3">
-        <v>5</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="L24" s="3"/>
       <c r="M24" s="3">
         <v>0</v>
       </c>
@@ -4532,91 +4640,38 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" s="3" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C25" s="3">
-        <v>4003</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="E25" s="2"/>
-      <c r="F25" s="3">
-        <v>9</v>
-      </c>
-      <c r="G25" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="H25" s="3">
-        <v>1</v>
-      </c>
-      <c r="I25" s="3">
-        <v>9999999</v>
-      </c>
-      <c r="J25" s="3">
-        <v>0</v>
-      </c>
-      <c r="K25" s="3">
-        <v>5</v>
-      </c>
-      <c r="M25" s="3">
-        <v>0</v>
-      </c>
-      <c r="N25" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" s="3" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C26" s="3">
-        <v>4004</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>169</v>
-      </c>
+    <row r="26" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C26" s="3"/>
+      <c r="D26" s="3"/>
       <c r="E26" s="2"/>
-      <c r="F26" s="3">
-        <v>5</v>
-      </c>
-      <c r="G26" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="H26" s="3">
-        <v>1</v>
-      </c>
-      <c r="I26" s="3">
-        <v>9999999</v>
-      </c>
-      <c r="J26" s="3">
-        <v>0</v>
-      </c>
-      <c r="K26" s="3">
-        <v>5</v>
-      </c>
-      <c r="M26" s="3">
-        <v>0</v>
-      </c>
-      <c r="N26" s="3">
-        <v>0</v>
-      </c>
+      <c r="F26" s="3"/>
+      <c r="G26" s="3"/>
+      <c r="H26" s="3"/>
+      <c r="I26" s="3"/>
+      <c r="J26" s="3"/>
+      <c r="K26" s="3"/>
+      <c r="M26" s="3"/>
+      <c r="N26" s="3"/>
     </row>
     <row r="27" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C27" s="3">
-        <v>4005</v>
+        <v>4001</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" s="3">
         <v>5</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="H27" s="3">
         <v>1</v>
       </c>
       <c r="I27" s="3">
-        <v>9999999</v>
+        <v>99999999999</v>
       </c>
       <c r="J27" s="3">
         <v>0</v>
@@ -4628,28 +4683,61 @@
         <v>0</v>
       </c>
       <c r="N27" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" s="3" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C28" s="3">
+        <v>4002</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="E28" s="2"/>
+      <c r="F28" s="3">
+        <v>5</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H28" s="3">
+        <v>1</v>
+      </c>
+      <c r="I28" s="3">
+        <v>99999999999</v>
+      </c>
+      <c r="J28" s="3">
+        <v>0</v>
+      </c>
+      <c r="K28" s="3">
+        <v>5</v>
+      </c>
+      <c r="M28" s="3">
+        <v>0</v>
+      </c>
+      <c r="N28" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="29" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C29" s="3">
-        <v>4007</v>
+        <v>4003</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" s="3">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="H29" s="3">
         <v>1</v>
       </c>
       <c r="I29" s="3">
-        <v>9999999999</v>
+        <v>9999999</v>
       </c>
       <c r="J29" s="3">
         <v>0</v>
@@ -4666,17 +4754,17 @@
     </row>
     <row r="30" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C30" s="3">
-        <v>4008</v>
+        <v>4004</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" s="3">
         <v>5</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="H30" s="3">
         <v>1</v>
@@ -4699,17 +4787,17 @@
     </row>
     <row r="31" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C31" s="3">
-        <v>4009</v>
+        <v>4005</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" s="3">
         <v>5</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="H31" s="3">
         <v>1</v>
@@ -4730,85 +4818,85 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" s="3" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C32" s="3">
-        <v>4010</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="E32" s="2"/>
-      <c r="F32" s="3">
-        <v>5</v>
-      </c>
-      <c r="G32" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="H32" s="3">
-        <v>1</v>
-      </c>
-      <c r="I32" s="3">
-        <v>9999999</v>
-      </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
-      <c r="K32" s="3">
-        <v>5</v>
-      </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
-    </row>
     <row r="33" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C33" s="3">
-        <v>4011</v>
+        <v>4007</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" s="3">
         <v>5</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="H33" s="3">
         <v>1</v>
       </c>
       <c r="I33" s="3">
+        <v>9999999999</v>
+      </c>
+      <c r="J33" s="3">
+        <v>0</v>
+      </c>
+      <c r="K33" s="3">
+        <v>5</v>
+      </c>
+      <c r="M33" s="3">
+        <v>0</v>
+      </c>
+      <c r="N33" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" s="3" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C34" s="3">
+        <v>4008</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="E34" s="2"/>
+      <c r="F34" s="3">
+        <v>5</v>
+      </c>
+      <c r="G34" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="H34" s="3">
+        <v>1</v>
+      </c>
+      <c r="I34" s="3">
         <v>9999999</v>
       </c>
-      <c r="J33" s="3">
-        <v>0</v>
-      </c>
-      <c r="K33" s="3">
-        <v>6</v>
-      </c>
-      <c r="M33" s="3">
-        <v>0</v>
-      </c>
-      <c r="N33" s="3">
+      <c r="J34" s="3">
+        <v>0</v>
+      </c>
+      <c r="K34" s="3">
+        <v>5</v>
+      </c>
+      <c r="M34" s="3">
+        <v>0</v>
+      </c>
+      <c r="N34" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="35" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C35" s="3">
-        <v>4013</v>
+        <v>4009</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" s="3">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="H35" s="3">
         <v>1</v>
@@ -4831,17 +4919,17 @@
     </row>
     <row r="36" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C36" s="3">
-        <v>4015</v>
+        <v>4010</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" s="3">
         <v>5</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="H36" s="3">
         <v>1</v>
@@ -4853,7 +4941,7 @@
         <v>0</v>
       </c>
       <c r="K36" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M36" s="3">
         <v>0</v>
@@ -4864,17 +4952,17 @@
     </row>
     <row r="37" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C37" s="3">
-        <v>4016</v>
+        <v>4011</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" s="3">
         <v>5</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="H37" s="3">
         <v>1</v>
@@ -4895,52 +4983,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" s="3" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C38" s="3">
-        <v>4017</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="E38" s="2"/>
-      <c r="F38" s="3">
-        <v>9</v>
-      </c>
-      <c r="G38" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="H38" s="3">
-        <v>1</v>
-      </c>
-      <c r="I38" s="3">
-        <v>9999999</v>
-      </c>
-      <c r="J38" s="3">
-        <v>0</v>
-      </c>
-      <c r="K38" s="3">
-        <v>5</v>
-      </c>
-      <c r="M38" s="3">
-        <v>0</v>
-      </c>
-      <c r="N38" s="3">
-        <v>0</v>
-      </c>
-    </row>
     <row r="39" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C39" s="3">
-        <v>4018</v>
+        <v>4013</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" s="3">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H39" s="3">
         <v>1</v>
@@ -4952,7 +5007,7 @@
         <v>0</v>
       </c>
       <c r="K39" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M39" s="3">
         <v>0</v>
@@ -4963,17 +5018,17 @@
     </row>
     <row r="40" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C40" s="3">
-        <v>4019</v>
+        <v>4015</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" s="3">
         <v>5</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="H40" s="3">
         <v>1</v>
@@ -4985,28 +5040,61 @@
         <v>0</v>
       </c>
       <c r="K40" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M40" s="3">
         <v>0</v>
       </c>
       <c r="N40" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" s="3" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C41" s="3">
+        <v>4016</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="E41" s="2"/>
+      <c r="F41" s="3">
+        <v>5</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="H41" s="3">
+        <v>1</v>
+      </c>
+      <c r="I41" s="3">
+        <v>9999999</v>
+      </c>
+      <c r="J41" s="3">
+        <v>0</v>
+      </c>
+      <c r="K41" s="3">
+        <v>6</v>
+      </c>
+      <c r="M41" s="3">
+        <v>0</v>
+      </c>
+      <c r="N41" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="42" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C42" s="3">
-        <v>4021</v>
+        <v>4017</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" s="3">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="H42" s="3">
         <v>1</v>
@@ -5018,7 +5106,7 @@
         <v>0</v>
       </c>
       <c r="K42" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M42" s="3">
         <v>0</v>
@@ -5029,17 +5117,17 @@
     </row>
     <row r="43" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C43" s="3">
-        <v>4022</v>
+        <v>4018</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" s="3">
         <v>5</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="H43" s="3">
         <v>1</v>
@@ -5051,7 +5139,7 @@
         <v>0</v>
       </c>
       <c r="K43" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M43" s="3">
         <v>0</v>
@@ -5062,17 +5150,17 @@
     </row>
     <row r="44" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C44" s="3">
-        <v>4023</v>
+        <v>4019</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" s="3">
         <v>5</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="H44" s="3">
         <v>1</v>
@@ -5084,61 +5172,28 @@
         <v>0</v>
       </c>
       <c r="K44" s="3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
       </c>
       <c r="N44" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" s="3" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C45" s="3">
-        <v>4024</v>
-      </c>
-      <c r="D45" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="E45" s="2"/>
-      <c r="F45" s="3">
-        <v>5</v>
-      </c>
-      <c r="G45" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="H45" s="3">
-        <v>1</v>
-      </c>
-      <c r="I45" s="3">
-        <v>9999999</v>
-      </c>
-      <c r="J45" s="3">
-        <v>0</v>
-      </c>
-      <c r="K45" s="3">
-        <v>6</v>
-      </c>
-      <c r="M45" s="3">
-        <v>0</v>
-      </c>
-      <c r="N45" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="46" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C46" s="3">
-        <v>4025</v>
+        <v>4021</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" s="3">
         <v>5</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="H46" s="3">
         <v>1</v>
@@ -5150,7 +5205,7 @@
         <v>0</v>
       </c>
       <c r="K46" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M46" s="3">
         <v>0</v>
@@ -5161,17 +5216,17 @@
     </row>
     <row r="47" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C47" s="3">
-        <v>4026</v>
+        <v>4022</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" s="3">
         <v>5</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="H47" s="3">
         <v>1</v>
@@ -5183,7 +5238,7 @@
         <v>0</v>
       </c>
       <c r="K47" s="3">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -5194,17 +5249,17 @@
     </row>
     <row r="48" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C48" s="3">
-        <v>4027</v>
+        <v>4023</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" s="3">
         <v>5</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="H48" s="3">
         <v>1</v>
@@ -5216,7 +5271,7 @@
         <v>0</v>
       </c>
       <c r="K48" s="3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M48" s="3">
         <v>0</v>
@@ -5227,17 +5282,17 @@
     </row>
     <row r="49" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C49" s="3">
-        <v>4028</v>
+        <v>4024</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" s="3">
         <v>5</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="H49" s="3">
         <v>1</v>
@@ -5249,7 +5304,7 @@
         <v>0</v>
       </c>
       <c r="K49" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M49" s="3">
         <v>0</v>
@@ -5260,17 +5315,17 @@
     </row>
     <row r="50" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C50" s="3">
-        <v>4029</v>
+        <v>4025</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" s="3">
         <v>5</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="H50" s="3">
         <v>1</v>
@@ -5293,17 +5348,17 @@
     </row>
     <row r="51" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C51" s="3">
-        <v>4030</v>
+        <v>4026</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" s="3">
         <v>5</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="H51" s="3">
         <v>1</v>
@@ -5315,7 +5370,7 @@
         <v>0</v>
       </c>
       <c r="K51" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M51" s="3">
         <v>0</v>
@@ -5326,17 +5381,17 @@
     </row>
     <row r="52" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C52" s="3">
-        <v>4031</v>
+        <v>4027</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" s="3">
         <v>5</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="H52" s="3">
         <v>1</v>
@@ -5359,17 +5414,17 @@
     </row>
     <row r="53" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C53" s="3">
-        <v>4032</v>
+        <v>4028</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" s="3">
         <v>5</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="H53" s="3">
         <v>1</v>
@@ -5392,17 +5447,17 @@
     </row>
     <row r="54" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C54" s="3">
-        <v>4033</v>
+        <v>4029</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" s="3">
         <v>5</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>188</v>
+        <v>222</v>
       </c>
       <c r="H54" s="3">
         <v>1</v>
@@ -5414,7 +5469,7 @@
         <v>0</v>
       </c>
       <c r="K54" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M54" s="3">
         <v>0</v>
@@ -5425,17 +5480,17 @@
     </row>
     <row r="55" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C55" s="3">
-        <v>4034</v>
+        <v>4030</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" s="3">
         <v>5</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="H55" s="3">
         <v>1</v>
@@ -5447,7 +5502,7 @@
         <v>0</v>
       </c>
       <c r="K55" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M55" s="3">
         <v>0</v>
@@ -5458,17 +5513,17 @@
     </row>
     <row r="56" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C56" s="3">
-        <v>4035</v>
+        <v>4031</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>147</v>
+        <v>225</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" s="3">
         <v>5</v>
       </c>
       <c r="G56" s="3" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="H56" s="3">
         <v>1</v>
@@ -5491,17 +5546,17 @@
     </row>
     <row r="57" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C57" s="3">
-        <v>4037</v>
+        <v>4032</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" s="3">
         <v>5</v>
       </c>
       <c r="G57" s="3" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="H57" s="3">
         <v>1</v>
@@ -5513,7 +5568,7 @@
         <v>0</v>
       </c>
       <c r="K57" s="3">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="M57" s="3">
         <v>0</v>
@@ -5524,17 +5579,17 @@
     </row>
     <row r="58" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C58" s="3">
-        <v>4038</v>
+        <v>4033</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" s="3">
         <v>5</v>
       </c>
       <c r="G58" s="3" t="s">
-        <v>226</v>
+        <v>198</v>
       </c>
       <c r="H58" s="3">
         <v>1</v>
@@ -5546,7 +5601,7 @@
         <v>0</v>
       </c>
       <c r="K58" s="3">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="M58" s="3">
         <v>0</v>
@@ -5557,17 +5612,17 @@
     </row>
     <row r="59" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C59" s="3">
-        <v>4039</v>
+        <v>4034</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" s="3">
         <v>5</v>
       </c>
       <c r="G59" s="3" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="H59" s="3">
         <v>1</v>
@@ -5590,17 +5645,17 @@
     </row>
     <row r="60" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C60" s="3">
-        <v>4040</v>
+        <v>4035</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>229</v>
+        <v>147</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" s="3">
         <v>5</v>
       </c>
       <c r="G60" s="3" t="s">
-        <v>188</v>
+        <v>232</v>
       </c>
       <c r="H60" s="3">
         <v>1</v>
@@ -5612,7 +5667,7 @@
         <v>0</v>
       </c>
       <c r="K60" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M60" s="3">
         <v>0</v>
@@ -5623,17 +5678,17 @@
     </row>
     <row r="61" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C61" s="3">
-        <v>4041</v>
+        <v>4037</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" s="3">
         <v>5</v>
       </c>
       <c r="G61" s="3" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="H61" s="3">
         <v>1</v>
@@ -5645,7 +5700,7 @@
         <v>0</v>
       </c>
       <c r="K61" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M61" s="3">
         <v>0</v>
@@ -5656,29 +5711,29 @@
     </row>
     <row r="62" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C62" s="3">
-        <v>4042</v>
+        <v>4038</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" s="3">
         <v>5</v>
       </c>
       <c r="G62" s="3" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="H62" s="3">
         <v>1</v>
       </c>
       <c r="I62" s="3">
-        <v>1999999999</v>
+        <v>9999999</v>
       </c>
       <c r="J62" s="3">
         <v>0</v>
       </c>
       <c r="K62" s="3">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="M62" s="3">
         <v>0</v>
@@ -5689,17 +5744,17 @@
     </row>
     <row r="63" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C63" s="3">
-        <v>4043</v>
+        <v>4039</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" s="3">
         <v>5</v>
       </c>
       <c r="G63" s="3" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="H63" s="3">
         <v>1</v>
@@ -5711,7 +5766,7 @@
         <v>0</v>
       </c>
       <c r="K63" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M63" s="3">
         <v>0</v>
@@ -5722,17 +5777,17 @@
     </row>
     <row r="64" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C64" s="3">
-        <v>4044</v>
+        <v>4040</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" s="3">
         <v>5</v>
       </c>
       <c r="G64" s="3" t="s">
-        <v>236</v>
+        <v>198</v>
       </c>
       <c r="H64" s="3">
         <v>1</v>
@@ -5744,7 +5799,7 @@
         <v>0</v>
       </c>
       <c r="K64" s="3">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="M64" s="3">
         <v>0</v>
@@ -5753,38 +5808,58 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C65" s="3"/>
-      <c r="D65" s="3"/>
+    <row r="65" s="3" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C65" s="3">
+        <v>4041</v>
+      </c>
+      <c r="D65" s="3" t="s">
+        <v>240</v>
+      </c>
       <c r="E65" s="2"/>
-      <c r="F65" s="3"/>
-      <c r="G65" s="3"/>
-      <c r="H65" s="3"/>
-      <c r="I65" s="3"/>
-      <c r="J65" s="3"/>
-      <c r="K65" s="3"/>
-      <c r="M65" s="3"/>
-      <c r="N65" s="3"/>
+      <c r="F65" s="3">
+        <v>5</v>
+      </c>
+      <c r="G65" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="H65" s="3">
+        <v>1</v>
+      </c>
+      <c r="I65" s="3">
+        <v>9999999</v>
+      </c>
+      <c r="J65" s="3">
+        <v>0</v>
+      </c>
+      <c r="K65" s="3">
+        <v>8</v>
+      </c>
+      <c r="M65" s="3">
+        <v>0</v>
+      </c>
+      <c r="N65" s="3">
+        <v>0</v>
+      </c>
     </row>
     <row r="66" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C66" s="3">
-        <v>4101</v>
+        <v>4042</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" s="3">
         <v>5</v>
       </c>
       <c r="G66" s="3" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="H66" s="3">
         <v>1</v>
       </c>
       <c r="I66" s="3">
-        <v>9999999</v>
+        <v>1999999999</v>
       </c>
       <c r="J66" s="3">
         <v>0</v>
@@ -5801,17 +5876,17 @@
     </row>
     <row r="67" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C67" s="3">
-        <v>4111</v>
+        <v>4043</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" s="3">
         <v>5</v>
       </c>
       <c r="G67" s="3" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="H67" s="3">
         <v>1</v>
@@ -5823,7 +5898,7 @@
         <v>0</v>
       </c>
       <c r="K67" s="3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M67" s="3">
         <v>0</v>
@@ -5834,17 +5909,17 @@
     </row>
     <row r="68" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C68" s="3">
-        <v>4112</v>
+        <v>4044</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" s="3">
         <v>5</v>
       </c>
       <c r="G68" s="3" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="H68" s="3">
         <v>1</v>
@@ -5856,7 +5931,7 @@
         <v>0</v>
       </c>
       <c r="K68" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M68" s="3">
         <v>0</v>
@@ -5865,230 +5940,210 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" s="3" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C69" s="3">
-        <v>4113</v>
-      </c>
-      <c r="D69" s="3" t="s">
-        <v>243</v>
-      </c>
+    <row r="69" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C69" s="3"/>
+      <c r="D69" s="3"/>
       <c r="E69" s="2"/>
-      <c r="F69" s="3">
-        <v>5</v>
-      </c>
-      <c r="G69" s="3" t="s">
-        <v>244</v>
-      </c>
-      <c r="H69" s="3">
-        <v>1</v>
-      </c>
-      <c r="I69" s="3">
+      <c r="F69" s="3"/>
+      <c r="G69" s="3"/>
+      <c r="H69" s="3"/>
+      <c r="I69" s="3"/>
+      <c r="J69" s="3"/>
+      <c r="K69" s="3"/>
+      <c r="M69" s="3"/>
+      <c r="N69" s="3"/>
+    </row>
+    <row r="70" s="3" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C70" s="3">
+        <v>4101</v>
+      </c>
+      <c r="D70" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="E70" s="2"/>
+      <c r="F70" s="3">
+        <v>5</v>
+      </c>
+      <c r="G70" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="H70" s="3">
+        <v>1</v>
+      </c>
+      <c r="I70" s="3">
         <v>9999999</v>
       </c>
-      <c r="J69" s="3">
-        <v>0</v>
-      </c>
-      <c r="K69" s="3">
-        <v>7</v>
-      </c>
-      <c r="M69" s="3">
-        <v>0</v>
-      </c>
-      <c r="N69" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C70" s="3"/>
-      <c r="D70" s="3"/>
-      <c r="E70" s="2"/>
-      <c r="F70" s="3"/>
-      <c r="G70" s="3"/>
-      <c r="H70" s="3"/>
-      <c r="I70" s="3"/>
-      <c r="J70" s="3"/>
-      <c r="K70" s="3"/>
-      <c r="M70" s="3"/>
-      <c r="N70" s="3"/>
+      <c r="J70" s="3">
+        <v>0</v>
+      </c>
+      <c r="K70" s="3">
+        <v>5</v>
+      </c>
+      <c r="M70" s="3">
+        <v>0</v>
+      </c>
+      <c r="N70" s="3">
+        <v>0</v>
+      </c>
     </row>
     <row r="71" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C71" s="3">
-        <v>4201</v>
+        <v>4111</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" s="3">
         <v>5</v>
       </c>
       <c r="G71" s="3" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="H71" s="3">
         <v>1</v>
       </c>
       <c r="I71" s="3">
+        <v>9999999</v>
+      </c>
+      <c r="J71" s="3">
+        <v>0</v>
+      </c>
+      <c r="K71" s="3">
+        <v>5</v>
+      </c>
+      <c r="M71" s="3">
+        <v>0</v>
+      </c>
+      <c r="N71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" s="3" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C72" s="3">
+        <v>4112</v>
+      </c>
+      <c r="D72" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="E72" s="2"/>
+      <c r="F72" s="3">
+        <v>5</v>
+      </c>
+      <c r="G72" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="H72" s="3">
+        <v>1</v>
+      </c>
+      <c r="I72" s="3">
+        <v>9999999</v>
+      </c>
+      <c r="J72" s="3">
+        <v>0</v>
+      </c>
+      <c r="K72" s="3">
+        <v>8</v>
+      </c>
+      <c r="M72" s="3">
+        <v>0</v>
+      </c>
+      <c r="N72" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" s="3" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C73" s="3">
+        <v>4113</v>
+      </c>
+      <c r="D73" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="E73" s="2"/>
+      <c r="F73" s="3">
+        <v>5</v>
+      </c>
+      <c r="G73" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="H73" s="3">
+        <v>1</v>
+      </c>
+      <c r="I73" s="3">
+        <v>9999999</v>
+      </c>
+      <c r="J73" s="3">
+        <v>0</v>
+      </c>
+      <c r="K73" s="3">
+        <v>7</v>
+      </c>
+      <c r="M73" s="3">
+        <v>0</v>
+      </c>
+      <c r="N73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C74" s="3"/>
+      <c r="D74" s="3"/>
+      <c r="E74" s="2"/>
+      <c r="F74" s="3"/>
+      <c r="G74" s="3"/>
+      <c r="H74" s="3"/>
+      <c r="I74" s="3"/>
+      <c r="J74" s="3"/>
+      <c r="K74" s="3"/>
+      <c r="M74" s="3"/>
+      <c r="N74" s="3"/>
+    </row>
+    <row r="75" s="3" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C75" s="3">
+        <v>4201</v>
+      </c>
+      <c r="D75" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="E75" s="2"/>
+      <c r="F75" s="3">
+        <v>5</v>
+      </c>
+      <c r="G75" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H75" s="3">
+        <v>1</v>
+      </c>
+      <c r="I75" s="3">
         <v>99999999</v>
       </c>
-      <c r="J71" s="3">
-        <v>0</v>
-      </c>
-      <c r="K71" s="3">
-        <v>5</v>
-      </c>
-      <c r="M71" s="3">
+      <c r="J75" s="3">
+        <v>0</v>
+      </c>
+      <c r="K75" s="3">
+        <v>5</v>
+      </c>
+      <c r="M75" s="3">
         <v>4002</v>
       </c>
-      <c r="N71" s="3">
+      <c r="N75" s="3">
         <v>1000</v>
-      </c>
-    </row>
-    <row r="76" s="3" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C76" s="3">
-        <v>8001</v>
-      </c>
-      <c r="D76" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="E76" s="2"/>
-      <c r="F76" s="3">
-        <v>5</v>
-      </c>
-      <c r="G76" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="H76" s="3">
-        <v>1</v>
-      </c>
-      <c r="I76" s="3">
-        <v>9999999</v>
-      </c>
-      <c r="J76" s="3">
-        <v>0</v>
-      </c>
-      <c r="K76" s="3">
-        <v>6</v>
-      </c>
-      <c r="M76" s="3">
-        <v>0</v>
-      </c>
-      <c r="N76" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" s="3" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C77" s="3">
-        <v>8002</v>
-      </c>
-      <c r="D77" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="E77" s="2"/>
-      <c r="F77" s="3">
-        <v>5</v>
-      </c>
-      <c r="G77" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="H77" s="3">
-        <v>1</v>
-      </c>
-      <c r="I77" s="3">
-        <v>9999999</v>
-      </c>
-      <c r="J77" s="3">
-        <v>0</v>
-      </c>
-      <c r="K77" s="3">
-        <v>6</v>
-      </c>
-      <c r="M77" s="3">
-        <v>0</v>
-      </c>
-      <c r="N77" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="78" s="3" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C78" s="3">
-        <v>8003</v>
-      </c>
-      <c r="D78" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="E78" s="2"/>
-      <c r="F78" s="3">
-        <v>5</v>
-      </c>
-      <c r="G78" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="H78" s="3">
-        <v>1</v>
-      </c>
-      <c r="I78" s="3">
-        <v>9999999</v>
-      </c>
-      <c r="J78" s="3">
-        <v>0</v>
-      </c>
-      <c r="K78" s="3">
-        <v>6</v>
-      </c>
-      <c r="M78" s="3">
-        <v>0</v>
-      </c>
-      <c r="N78" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="79" s="3" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C79" s="3">
-        <v>8004</v>
-      </c>
-      <c r="D79" s="3" t="s">
-        <v>251</v>
-      </c>
-      <c r="E79" s="2"/>
-      <c r="F79" s="3">
-        <v>5</v>
-      </c>
-      <c r="G79" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="H79" s="3">
-        <v>1</v>
-      </c>
-      <c r="I79" s="3">
-        <v>9999999</v>
-      </c>
-      <c r="J79" s="3">
-        <v>0</v>
-      </c>
-      <c r="K79" s="3">
-        <v>6</v>
-      </c>
-      <c r="M79" s="3">
-        <v>0</v>
-      </c>
-      <c r="N79" s="3">
-        <v>0</v>
       </c>
     </row>
     <row r="80" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C80" s="3">
-        <v>8005</v>
+        <v>8001</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" s="3">
         <v>5</v>
       </c>
       <c r="G80" s="3" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
       <c r="H80" s="3">
         <v>1</v>
@@ -6111,17 +6166,17 @@
     </row>
     <row r="81" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C81" s="3">
-        <v>8006</v>
+        <v>8002</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" s="3">
         <v>5</v>
       </c>
       <c r="G81" s="3" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
       <c r="H81" s="3">
         <v>1</v>
@@ -6144,17 +6199,17 @@
     </row>
     <row r="82" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C82" s="3">
-        <v>8007</v>
+        <v>8003</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" s="3">
         <v>5</v>
       </c>
       <c r="G82" s="3" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
       <c r="H82" s="3">
         <v>1</v>
@@ -6177,17 +6232,17 @@
     </row>
     <row r="83" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C83" s="3">
-        <v>8008</v>
+        <v>8004</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" s="3">
         <v>5</v>
       </c>
       <c r="G83" s="3" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
       <c r="H83" s="3">
         <v>1</v>
@@ -6210,17 +6265,17 @@
     </row>
     <row r="84" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C84" s="3">
-        <v>8009</v>
+        <v>8005</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" s="3">
         <v>5</v>
       </c>
       <c r="G84" s="3" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
       <c r="H84" s="3">
         <v>1</v>
@@ -6243,17 +6298,17 @@
     </row>
     <row r="85" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C85" s="3">
-        <v>8010</v>
+        <v>8006</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" s="3">
         <v>5</v>
       </c>
       <c r="G85" s="3" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
       <c r="H85" s="3">
         <v>1</v>
@@ -6274,19 +6329,52 @@
         <v>0</v>
       </c>
     </row>
+    <row r="86" s="3" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C86" s="3">
+        <v>8007</v>
+      </c>
+      <c r="D86" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="E86" s="2"/>
+      <c r="F86" s="3">
+        <v>5</v>
+      </c>
+      <c r="G86" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="H86" s="3">
+        <v>1</v>
+      </c>
+      <c r="I86" s="3">
+        <v>9999999</v>
+      </c>
+      <c r="J86" s="3">
+        <v>0</v>
+      </c>
+      <c r="K86" s="3">
+        <v>6</v>
+      </c>
+      <c r="M86" s="3">
+        <v>0</v>
+      </c>
+      <c r="N86" s="3">
+        <v>0</v>
+      </c>
+    </row>
     <row r="87" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C87" s="3">
-        <v>8101</v>
-      </c>
-      <c r="D87" s="9" t="s">
-        <v>258</v>
+        <v>8008</v>
+      </c>
+      <c r="D87" s="3" t="s">
+        <v>265</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" s="3">
         <v>5</v>
       </c>
       <c r="G87" s="3" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H87" s="3">
         <v>1</v>
@@ -6298,7 +6386,7 @@
         <v>0</v>
       </c>
       <c r="K87" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M87" s="3">
         <v>0</v>
@@ -6309,17 +6397,17 @@
     </row>
     <row r="88" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C88" s="3">
-        <v>8102</v>
-      </c>
-      <c r="D88" s="9" t="s">
-        <v>260</v>
+        <v>8009</v>
+      </c>
+      <c r="D88" s="3" t="s">
+        <v>266</v>
       </c>
       <c r="E88" s="2"/>
       <c r="F88" s="3">
         <v>5</v>
       </c>
       <c r="G88" s="3" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H88" s="3">
         <v>1</v>
@@ -6331,7 +6419,7 @@
         <v>0</v>
       </c>
       <c r="K88" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M88" s="3">
         <v>0</v>
@@ -6342,17 +6430,17 @@
     </row>
     <row r="89" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C89" s="3">
-        <v>8103</v>
-      </c>
-      <c r="D89" s="9" t="s">
-        <v>261</v>
+        <v>8010</v>
+      </c>
+      <c r="D89" s="3" t="s">
+        <v>267</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" s="3">
         <v>5</v>
       </c>
       <c r="G89" s="3" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H89" s="3">
         <v>1</v>
@@ -6364,61 +6452,28 @@
         <v>0</v>
       </c>
       <c r="K89" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M89" s="3">
         <v>0</v>
       </c>
       <c r="N89" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" s="3" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C90" s="3">
-        <v>8104</v>
-      </c>
-      <c r="D90" s="9" t="s">
-        <v>262</v>
-      </c>
-      <c r="E90" s="2"/>
-      <c r="F90" s="3">
-        <v>5</v>
-      </c>
-      <c r="G90" s="3" t="s">
-        <v>259</v>
-      </c>
-      <c r="H90" s="3">
-        <v>1</v>
-      </c>
-      <c r="I90" s="3">
-        <v>9999999</v>
-      </c>
-      <c r="J90" s="3">
-        <v>0</v>
-      </c>
-      <c r="K90" s="3">
-        <v>7</v>
-      </c>
-      <c r="M90" s="3">
-        <v>0</v>
-      </c>
-      <c r="N90" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="91" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C91" s="3">
-        <v>8105</v>
+        <v>8101</v>
       </c>
       <c r="D91" s="9" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="E91" s="2"/>
       <c r="F91" s="3">
         <v>5</v>
       </c>
       <c r="G91" s="3" t="s">
-        <v>259</v>
+        <v>269</v>
       </c>
       <c r="H91" s="3">
         <v>1</v>
@@ -6441,17 +6496,17 @@
     </row>
     <row r="92" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C92" s="3">
-        <v>8106</v>
+        <v>8102</v>
       </c>
       <c r="D92" s="9" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="E92" s="2"/>
       <c r="F92" s="3">
         <v>5</v>
       </c>
       <c r="G92" s="3" t="s">
-        <v>259</v>
+        <v>269</v>
       </c>
       <c r="H92" s="3">
         <v>1</v>
@@ -6474,17 +6529,17 @@
     </row>
     <row r="93" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C93" s="3">
-        <v>8107</v>
+        <v>8103</v>
       </c>
       <c r="D93" s="9" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="E93" s="2"/>
       <c r="F93" s="3">
         <v>5</v>
       </c>
       <c r="G93" s="3" t="s">
-        <v>259</v>
+        <v>269</v>
       </c>
       <c r="H93" s="3">
         <v>1</v>
@@ -6507,17 +6562,17 @@
     </row>
     <row r="94" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C94" s="3">
-        <v>8108</v>
+        <v>8104</v>
       </c>
       <c r="D94" s="9" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="E94" s="2"/>
       <c r="F94" s="3">
         <v>5</v>
       </c>
       <c r="G94" s="3" t="s">
-        <v>259</v>
+        <v>269</v>
       </c>
       <c r="H94" s="3">
         <v>1</v>
@@ -6538,33 +6593,64 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" customHeight="1" spans="3:14">
+    <row r="95" s="3" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C95" s="3">
+        <v>8105</v>
+      </c>
+      <c r="D95" s="9" t="s">
+        <v>273</v>
+      </c>
+      <c r="E95" s="2"/>
+      <c r="F95" s="3">
+        <v>5</v>
+      </c>
+      <c r="G95" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="H95" s="3">
+        <v>1</v>
+      </c>
+      <c r="I95" s="3">
+        <v>9999999</v>
+      </c>
+      <c r="J95" s="3">
+        <v>0</v>
+      </c>
+      <c r="K95" s="3">
+        <v>7</v>
+      </c>
+      <c r="M95" s="3">
+        <v>0</v>
+      </c>
+      <c r="N95" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C96" s="3">
-        <v>8201</v>
+        <v>8106</v>
       </c>
       <c r="D96" s="9" t="s">
-        <v>267</v>
-      </c>
+        <v>274</v>
+      </c>
+      <c r="E96" s="2"/>
       <c r="F96" s="3">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="G96" s="3" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H96" s="3">
         <v>1</v>
       </c>
       <c r="I96" s="3">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="J96" s="3">
         <v>0</v>
       </c>
       <c r="K96" s="3">
-        <v>1</v>
-      </c>
-      <c r="L96" s="3">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -6573,33 +6659,31 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" customHeight="1" spans="3:14">
+    <row r="97" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C97" s="3">
-        <v>8202</v>
+        <v>8107</v>
       </c>
       <c r="D97" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="E97" s="2"/>
+      <c r="F97" s="3">
+        <v>5</v>
+      </c>
+      <c r="G97" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="F97" s="3">
-        <v>16</v>
-      </c>
-      <c r="G97" s="3" t="s">
-        <v>270</v>
-      </c>
       <c r="H97" s="3">
         <v>1</v>
       </c>
       <c r="I97" s="3">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="J97" s="3">
         <v>0</v>
       </c>
       <c r="K97" s="3">
-        <v>2</v>
-      </c>
-      <c r="L97" s="3">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M97" s="3">
         <v>0</v>
@@ -6608,88 +6692,51 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" customHeight="1" spans="3:14">
+    <row r="98" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C98" s="3">
-        <v>8203</v>
+        <v>8108</v>
       </c>
       <c r="D98" s="9" t="s">
-        <v>271</v>
-      </c>
+        <v>276</v>
+      </c>
+      <c r="E98" s="2"/>
       <c r="F98" s="3">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="G98" s="3" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="H98" s="3">
         <v>1</v>
       </c>
       <c r="I98" s="3">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="J98" s="3">
         <v>0</v>
       </c>
       <c r="K98" s="3">
-        <v>3</v>
-      </c>
-      <c r="L98" s="3">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M98" s="3">
         <v>0</v>
       </c>
       <c r="N98" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="99" customHeight="1" spans="3:14">
-      <c r="C99" s="3">
-        <v>8204</v>
-      </c>
-      <c r="D99" s="9" t="s">
-        <v>273</v>
-      </c>
-      <c r="F99" s="3">
-        <v>16</v>
-      </c>
-      <c r="G99" s="3" t="s">
-        <v>274</v>
-      </c>
-      <c r="H99" s="3">
-        <v>1</v>
-      </c>
-      <c r="I99" s="3">
-        <v>1</v>
-      </c>
-      <c r="J99" s="3">
-        <v>0</v>
-      </c>
-      <c r="K99" s="3">
-        <v>4</v>
-      </c>
-      <c r="L99" s="3">
-        <v>0</v>
-      </c>
-      <c r="M99" s="3">
-        <v>0</v>
-      </c>
-      <c r="N99" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="100" customHeight="1" spans="3:14">
       <c r="C100" s="3">
-        <v>8205</v>
+        <v>8201</v>
       </c>
       <c r="D100" s="9" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="F100" s="3">
         <v>16</v>
       </c>
       <c r="G100" s="3" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="H100" s="3">
         <v>1</v>
@@ -6701,7 +6748,7 @@
         <v>0</v>
       </c>
       <c r="K100" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L100" s="3">
         <v>0</v>
@@ -6715,16 +6762,16 @@
     </row>
     <row r="101" customHeight="1" spans="3:14">
       <c r="C101" s="3">
-        <v>8206</v>
+        <v>8202</v>
       </c>
       <c r="D101" s="9" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="F101" s="3">
         <v>16</v>
       </c>
       <c r="G101" s="3" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="H101" s="3">
         <v>1</v>
@@ -6736,7 +6783,7 @@
         <v>0</v>
       </c>
       <c r="K101" s="3">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -6750,16 +6797,16 @@
     </row>
     <row r="102" customHeight="1" spans="3:14">
       <c r="C102" s="3">
-        <v>8207</v>
+        <v>8203</v>
       </c>
       <c r="D102" s="9" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F102" s="3">
         <v>16</v>
       </c>
       <c r="G102" s="3" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="H102" s="3">
         <v>1</v>
@@ -6771,29 +6818,157 @@
         <v>0</v>
       </c>
       <c r="K102" s="3">
+        <v>3</v>
+      </c>
+      <c r="L102" s="3">
+        <v>0</v>
+      </c>
+      <c r="M102" s="3">
+        <v>0</v>
+      </c>
+      <c r="N102" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" customHeight="1" spans="3:14">
+      <c r="C103" s="3">
+        <v>8204</v>
+      </c>
+      <c r="D103" s="9" t="s">
+        <v>283</v>
+      </c>
+      <c r="F103" s="3">
+        <v>16</v>
+      </c>
+      <c r="G103" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="H103" s="3">
+        <v>1</v>
+      </c>
+      <c r="I103" s="3">
+        <v>1</v>
+      </c>
+      <c r="J103" s="3">
+        <v>0</v>
+      </c>
+      <c r="K103" s="3">
+        <v>4</v>
+      </c>
+      <c r="L103" s="3">
+        <v>0</v>
+      </c>
+      <c r="M103" s="3">
+        <v>0</v>
+      </c>
+      <c r="N103" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" customHeight="1" spans="3:14">
+      <c r="C104" s="3">
+        <v>8205</v>
+      </c>
+      <c r="D104" s="9" t="s">
+        <v>285</v>
+      </c>
+      <c r="F104" s="3">
+        <v>16</v>
+      </c>
+      <c r="G104" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="H104" s="3">
+        <v>1</v>
+      </c>
+      <c r="I104" s="3">
+        <v>1</v>
+      </c>
+      <c r="J104" s="3">
+        <v>0</v>
+      </c>
+      <c r="K104" s="3">
+        <v>5</v>
+      </c>
+      <c r="L104" s="3">
+        <v>0</v>
+      </c>
+      <c r="M104" s="3">
+        <v>0</v>
+      </c>
+      <c r="N104" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" customHeight="1" spans="3:14">
+      <c r="C105" s="3">
+        <v>8206</v>
+      </c>
+      <c r="D105" s="9" t="s">
+        <v>287</v>
+      </c>
+      <c r="F105" s="3">
+        <v>16</v>
+      </c>
+      <c r="G105" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="H105" s="3">
+        <v>1</v>
+      </c>
+      <c r="I105" s="3">
+        <v>1</v>
+      </c>
+      <c r="J105" s="3">
+        <v>0</v>
+      </c>
+      <c r="K105" s="3">
+        <v>6</v>
+      </c>
+      <c r="L105" s="3">
+        <v>0</v>
+      </c>
+      <c r="M105" s="3">
+        <v>0</v>
+      </c>
+      <c r="N105" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" customHeight="1" spans="3:14">
+      <c r="C106" s="3">
+        <v>8207</v>
+      </c>
+      <c r="D106" s="9" t="s">
+        <v>289</v>
+      </c>
+      <c r="F106" s="3">
+        <v>16</v>
+      </c>
+      <c r="G106" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="H106" s="3">
+        <v>1</v>
+      </c>
+      <c r="I106" s="3">
+        <v>1</v>
+      </c>
+      <c r="J106" s="3">
+        <v>0</v>
+      </c>
+      <c r="K106" s="3">
         <v>7</v>
       </c>
-      <c r="L102" s="3">
-        <v>0</v>
-      </c>
-      <c r="M102" s="3">
-        <v>0</v>
-      </c>
-      <c r="N102" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="104" customHeight="1" spans="3:14">
-      <c r="D104" s="9"/>
-    </row>
-    <row r="105" customHeight="1" spans="3:14">
-      <c r="D105" s="9"/>
-    </row>
-    <row r="106" customHeight="1" spans="3:14">
-      <c r="D106" s="9"/>
-    </row>
-    <row r="107" customHeight="1" spans="3:14">
-      <c r="D107" s="9"/>
+      <c r="L106" s="3">
+        <v>0</v>
+      </c>
+      <c r="M106" s="3">
+        <v>0</v>
+      </c>
+      <c r="N106" s="3">
+        <v>0</v>
+      </c>
     </row>
     <row r="108" customHeight="1" spans="3:14">
       <c r="D108" s="9"/>
@@ -6804,6 +6979,9 @@
     <row r="110" customHeight="1" spans="3:14">
       <c r="D110" s="9"/>
     </row>
+    <row r="111" customHeight="1" spans="3:14">
+      <c r="D111" s="9"/>
+    </row>
     <row r="112" customHeight="1" spans="3:14">
       <c r="D112" s="9"/>
     </row>
@@ -6813,9 +6991,6 @@
     <row r="114" customHeight="1" spans="4:4">
       <c r="D114" s="9"/>
     </row>
-    <row r="115" customHeight="1" spans="4:4">
-      <c r="D115" s="9"/>
-    </row>
     <row r="116" customHeight="1" spans="4:4">
       <c r="D116" s="9"/>
     </row>
@@ -6825,12 +7000,24 @@
     <row r="118" customHeight="1" spans="4:4">
       <c r="D118" s="9"/>
     </row>
+    <row r="119" customHeight="1" spans="4:4">
+      <c r="D119" s="9"/>
+    </row>
+    <row r="120" customHeight="1" spans="4:4">
+      <c r="D120" s="9"/>
+    </row>
+    <row r="121" customHeight="1" spans="4:4">
+      <c r="D121" s="9"/>
+    </row>
+    <row r="122" customHeight="1" spans="4:4">
+      <c r="D122" s="9"/>
+    </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C13:D13 C18:D18 C14:C17 C3:E5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C13:D13 C14:C17 C3:E5 C18:D22" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="M18:N18 M3:N5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="M3:N5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,M3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>
@@ -6979,14 +7166,14 @@
         <v>9001</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>281</v>
+        <v>291</v>
       </c>
       <c r="E6" s="3"/>
       <c r="F6" s="2">
         <v>6</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>282</v>
+        <v>292</v>
       </c>
       <c r="H6" s="2">
         <v>1</v>
@@ -7009,14 +7196,14 @@
         <v>9002</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>283</v>
+        <v>293</v>
       </c>
       <c r="E7" s="3"/>
       <c r="F7" s="2">
         <v>6</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>282</v>
+        <v>292</v>
       </c>
       <c r="H7" s="2">
         <v>1</v>
@@ -7039,14 +7226,14 @@
         <v>9003</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>284</v>
+        <v>294</v>
       </c>
       <c r="E8" s="3"/>
       <c r="F8" s="2">
         <v>6</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>282</v>
+        <v>292</v>
       </c>
       <c r="H8" s="2">
         <v>1</v>
@@ -7069,14 +7256,14 @@
         <v>9004</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>285</v>
+        <v>295</v>
       </c>
       <c r="E9" s="3"/>
       <c r="F9" s="2">
         <v>6</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>282</v>
+        <v>292</v>
       </c>
       <c r="H9" s="2">
         <v>1</v>
@@ -7099,14 +7286,14 @@
         <v>9005</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>286</v>
+        <v>296</v>
       </c>
       <c r="E10" s="3"/>
       <c r="F10" s="2">
         <v>6</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>282</v>
+        <v>292</v>
       </c>
       <c r="H10" s="2">
         <v>1</v>
@@ -7129,14 +7316,14 @@
         <v>9006</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>287</v>
+        <v>297</v>
       </c>
       <c r="E11" s="3"/>
       <c r="F11" s="2">
         <v>6</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>282</v>
+        <v>292</v>
       </c>
       <c r="H11" s="2">
         <v>1</v>
@@ -7158,14 +7345,14 @@
         <v>9007</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>288</v>
+        <v>298</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" s="2">
         <v>6</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>282</v>
+        <v>292</v>
       </c>
       <c r="H12" s="2">
         <v>1</v>
@@ -7187,14 +7374,14 @@
         <v>9008</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>289</v>
+        <v>299</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" s="2">
         <v>6</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>282</v>
+        <v>292</v>
       </c>
       <c r="H13" s="2">
         <v>1</v>
@@ -7216,14 +7403,14 @@
         <v>9009</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>290</v>
+        <v>300</v>
       </c>
       <c r="E14" s="3"/>
       <c r="F14" s="2">
         <v>6</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>282</v>
+        <v>292</v>
       </c>
       <c r="H14" s="2">
         <v>1</v>
@@ -7245,14 +7432,14 @@
         <v>9010</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>291</v>
+        <v>301</v>
       </c>
       <c r="E15" s="3"/>
       <c r="F15" s="2">
         <v>6</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>282</v>
+        <v>292</v>
       </c>
       <c r="H15" s="2">
         <v>1</v>
@@ -7274,14 +7461,14 @@
         <v>9011</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>292</v>
+        <v>302</v>
       </c>
       <c r="E16" s="3"/>
       <c r="F16" s="2">
         <v>6</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>282</v>
+        <v>292</v>
       </c>
       <c r="H16" s="2">
         <v>1</v>
@@ -7458,14 +7645,14 @@
         <v>10001</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>293</v>
+        <v>303</v>
       </c>
       <c r="E6" s="3"/>
       <c r="F6" s="2">
         <v>5</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>294</v>
+        <v>304</v>
       </c>
       <c r="H6" s="2">
         <v>1</v>
@@ -7479,26 +7666,22 @@
       <c r="K6" s="2">
         <v>4</v>
       </c>
-      <c r="M6" s="3">
-        <v>5003</v>
-      </c>
-      <c r="N6" s="3">
-        <v>1</v>
-      </c>
+      <c r="M6" s="3"/>
+      <c r="N6" s="3"/>
     </row>
     <row r="7" s="2" customFormat="1" customHeight="1" spans="3:14">
       <c r="C7" s="2">
         <v>10002</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="E7" s="3"/>
       <c r="F7" s="2">
         <v>5</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>294</v>
+        <v>304</v>
       </c>
       <c r="H7" s="2">
         <v>1</v>
@@ -7512,26 +7695,22 @@
       <c r="K7" s="2">
         <v>4</v>
       </c>
-      <c r="M7" s="3">
-        <v>5003</v>
-      </c>
-      <c r="N7" s="3">
-        <v>1</v>
-      </c>
+      <c r="M7" s="3"/>
+      <c r="N7" s="3"/>
     </row>
     <row r="8" s="2" customFormat="1" customHeight="1" spans="3:14">
       <c r="C8" s="2">
         <v>10003</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>296</v>
+        <v>306</v>
       </c>
       <c r="E8" s="3"/>
       <c r="F8" s="2">
         <v>5</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>294</v>
+        <v>304</v>
       </c>
       <c r="H8" s="2">
         <v>1</v>
@@ -7545,26 +7724,22 @@
       <c r="K8" s="2">
         <v>4</v>
       </c>
-      <c r="M8" s="3">
-        <v>5003</v>
-      </c>
-      <c r="N8" s="3">
-        <v>1</v>
-      </c>
+      <c r="M8" s="3"/>
+      <c r="N8" s="3"/>
     </row>
     <row r="9" s="2" customFormat="1" customHeight="1" spans="3:14">
       <c r="C9" s="2">
         <v>10004</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="E9" s="3"/>
       <c r="F9" s="2">
         <v>5</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>294</v>
+        <v>304</v>
       </c>
       <c r="H9" s="2">
         <v>1</v>
@@ -7582,7 +7757,7 @@
         <v>5003</v>
       </c>
       <c r="N9" s="3">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" s="2" customFormat="1" customHeight="1" spans="3:14">
@@ -7835,16 +8010,16 @@
         <v>40000001</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>298</v>
+        <v>308</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>299</v>
+        <v>309</v>
       </c>
       <c r="F6" s="2">
         <v>6</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>300</v>
+        <v>310</v>
       </c>
       <c r="H6" s="2">
         <v>1</v>
@@ -7865,16 +8040,16 @@
         <v>40000002</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>301</v>
+        <v>311</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>302</v>
+        <v>312</v>
       </c>
       <c r="F7" s="2">
         <v>6</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>300</v>
+        <v>310</v>
       </c>
       <c r="H7" s="2">
         <v>1</v>
@@ -7895,16 +8070,16 @@
         <v>40000003</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>303</v>
+        <v>313</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>304</v>
+        <v>314</v>
       </c>
       <c r="F8" s="2">
         <v>6</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>300</v>
+        <v>310</v>
       </c>
       <c r="H8" s="2">
         <v>1</v>
@@ -7925,16 +8100,16 @@
         <v>40000004</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>305</v>
+        <v>315</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>306</v>
+        <v>316</v>
       </c>
       <c r="F9" s="2">
         <v>6</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>307</v>
+        <v>317</v>
       </c>
       <c r="H9" s="2">
         <v>1</v>
@@ -7955,16 +8130,16 @@
         <v>40000005</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>308</v>
+        <v>318</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>309</v>
+        <v>319</v>
       </c>
       <c r="F10" s="2">
         <v>6</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>307</v>
+        <v>317</v>
       </c>
       <c r="H10" s="2">
         <v>1</v>
@@ -7985,16 +8160,16 @@
         <v>40000006</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>310</v>
+        <v>320</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="F11" s="2">
         <v>6</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>307</v>
+        <v>317</v>
       </c>
       <c r="H11" s="2">
         <v>1</v>
@@ -8017,16 +8192,16 @@
         <v>40000007</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>312</v>
+        <v>322</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>313</v>
+        <v>323</v>
       </c>
       <c r="F12" s="2">
         <v>6</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>314</v>
+        <v>324</v>
       </c>
       <c r="H12" s="2">
         <v>1</v>
@@ -8046,16 +8221,16 @@
         <v>40000008</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>315</v>
+        <v>325</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>316</v>
+        <v>326</v>
       </c>
       <c r="F13" s="2">
         <v>6</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>314</v>
+        <v>324</v>
       </c>
       <c r="H13" s="2">
         <v>1</v>
@@ -8075,16 +8250,16 @@
         <v>40000009</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>317</v>
+        <v>327</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>318</v>
+        <v>328</v>
       </c>
       <c r="F14" s="2">
         <v>6</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>314</v>
+        <v>324</v>
       </c>
       <c r="H14" s="2">
         <v>1</v>
@@ -8104,16 +8279,16 @@
         <v>40000010</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>319</v>
+        <v>329</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>320</v>
+        <v>330</v>
       </c>
       <c r="F15" s="2">
         <v>6</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>321</v>
+        <v>331</v>
       </c>
       <c r="H15" s="2">
         <v>1</v>
@@ -8133,16 +8308,16 @@
         <v>40000011</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>322</v>
+        <v>332</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>323</v>
+        <v>333</v>
       </c>
       <c r="F16" s="2">
         <v>6</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>321</v>
+        <v>331</v>
       </c>
       <c r="H16" s="2">
         <v>1</v>
@@ -8163,16 +8338,16 @@
         <v>40000012</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>324</v>
+        <v>334</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>325</v>
+        <v>335</v>
       </c>
       <c r="F17" s="2">
         <v>6</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>321</v>
+        <v>331</v>
       </c>
       <c r="H17" s="2">
         <v>1</v>
@@ -8192,14 +8367,14 @@
         <v>40000013</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>326</v>
+        <v>336</v>
       </c>
       <c r="E18" s="3"/>
       <c r="F18" s="2">
         <v>6</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>327</v>
+        <v>337</v>
       </c>
       <c r="H18" s="2">
         <v>1</v>
@@ -8219,14 +8394,14 @@
         <v>40000014</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>328</v>
+        <v>338</v>
       </c>
       <c r="E19" s="3"/>
       <c r="F19" s="2">
         <v>6</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>327</v>
+        <v>337</v>
       </c>
       <c r="H19" s="2">
         <v>1</v>
@@ -8246,14 +8421,14 @@
         <v>40000015</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>329</v>
+        <v>339</v>
       </c>
       <c r="E20" s="3"/>
       <c r="F20" s="2">
         <v>6</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>327</v>
+        <v>337</v>
       </c>
       <c r="H20" s="2">
         <v>1</v>
@@ -8273,14 +8448,14 @@
         <v>40000016</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>330</v>
+        <v>340</v>
       </c>
       <c r="E21" s="3"/>
       <c r="F21" s="2">
         <v>6</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="H21" s="2">
         <v>1</v>
@@ -8300,14 +8475,14 @@
         <v>40000017</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>332</v>
+        <v>342</v>
       </c>
       <c r="E22" s="3"/>
       <c r="F22" s="2">
         <v>6</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="H22" s="2">
         <v>1</v>
@@ -8327,14 +8502,14 @@
         <v>40000018</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>333</v>
+        <v>343</v>
       </c>
       <c r="E23" s="3"/>
       <c r="F23" s="2">
         <v>6</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="H23" s="2">
         <v>1</v>

--- a/Excel/ItemConfig.xlsx
+++ b/Excel/ItemConfig.xlsx
@@ -708,31 +708,31 @@
     <t>灵珠进阶材料</t>
   </si>
   <si>
-    <t>一阶神兵符</t>
+    <t>1阶神兵符</t>
   </si>
   <si>
     <t>神兵进阶到1阶的材料</t>
   </si>
   <si>
-    <t>二阶神兵符</t>
+    <t>2阶神兵符</t>
   </si>
   <si>
     <t>神兵进阶到2阶的材料</t>
   </si>
   <si>
-    <t>三阶神兵符</t>
+    <t>3阶神兵符</t>
   </si>
   <si>
     <t>神兵进阶到3阶的材料</t>
   </si>
   <si>
-    <t>四阶神兵符</t>
+    <t>4阶神兵符</t>
   </si>
   <si>
     <t>神兵进阶到4阶的材料</t>
   </si>
   <si>
-    <t>五阶神兵符</t>
+    <t>5阶神兵符</t>
   </si>
   <si>
     <t>神兵进阶到5阶的材料</t>

--- a/Excel/ItemConfig.xlsx
+++ b/Excel/ItemConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="1"/>
+    <workbookView windowHeight="17680" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="技能" sheetId="1" r:id="rId1"/>
@@ -1465,12 +1465,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>

--- a/Excel/ItemConfig.xlsx
+++ b/Excel/ItemConfig.xlsx
@@ -229,7 +229,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="642" uniqueCount="344">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="648" uniqueCount="348">
   <si>
     <t>_Id</t>
   </si>
@@ -1254,13 +1254,25 @@
     <t>獠牙</t>
   </si>
   <si>
+    <t>蛮鬃林地珍宝材料</t>
+  </si>
+  <si>
+    <t>图腾</t>
+  </si>
+  <si>
+    <t>酋长重锤</t>
+  </si>
+  <si>
+    <t>‌血花露‌</t>
+  </si>
+  <si>
     <t>熔火地穴珍宝材料</t>
   </si>
   <si>
-    <t>图腾</t>
-  </si>
-  <si>
-    <t>酋长重锤</t>
+    <t>火甲虫</t>
+  </si>
+  <si>
+    <t>炎魔火髓</t>
   </si>
 </sst>
 </file>
@@ -1465,12 +1477,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -7014,7 +7026,7 @@
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C13:D13 C14:C17 C3:E5 C18:D22" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C13:D13 C14:C17 C18:D22 C3:E5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
     <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="M3:N5" errorStyle="warning">
@@ -7868,7 +7880,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N23"/>
+  <dimension ref="A1:N26"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="2"/>
@@ -8524,6 +8536,84 @@
         <v>6</v>
       </c>
     </row>
+    <row r="24" customHeight="1" spans="1:11">
+      <c r="C24" s="3">
+        <v>40000019</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="F24" s="2">
+        <v>6</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="H24" s="2">
+        <v>1</v>
+      </c>
+      <c r="I24" s="2">
+        <v>99999</v>
+      </c>
+      <c r="J24" s="2">
+        <v>0</v>
+      </c>
+      <c r="K24" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" customHeight="1" spans="1:11">
+      <c r="C25" s="3">
+        <v>40000020</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="F25" s="2">
+        <v>6</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="H25" s="2">
+        <v>1</v>
+      </c>
+      <c r="I25" s="2">
+        <v>99999</v>
+      </c>
+      <c r="J25" s="2">
+        <v>0</v>
+      </c>
+      <c r="K25" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26" customHeight="1" spans="1:11">
+      <c r="C26" s="3">
+        <v>40000021</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="F26" s="2">
+        <v>6</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="H26" s="2">
+        <v>1</v>
+      </c>
+      <c r="I26" s="2">
+        <v>99999</v>
+      </c>
+      <c r="J26" s="2">
+        <v>0</v>
+      </c>
+      <c r="K26" s="3">
+        <v>6</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="2">
     <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:E5" errorStyle="warning">

--- a/Excel/ItemConfig.xlsx
+++ b/Excel/ItemConfig.xlsx
@@ -7026,7 +7026,7 @@
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C13:D13 C14:C17 C18:D22 C3:E5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C13:D13 C14:C17 C3:E5 C18:D22" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
     <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="M3:N5" errorStyle="warning">

--- a/Excel/ItemConfig.xlsx
+++ b/Excel/ItemConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="4"/>
+    <workbookView windowWidth="25600" windowHeight="11480" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="技能" sheetId="1" r:id="rId1"/>
@@ -229,7 +229,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="648" uniqueCount="348">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="666" uniqueCount="360">
   <si>
     <t>_Id</t>
   </si>
@@ -1273,6 +1273,53 @@
   </si>
   <si>
     <t>炎魔火髓</t>
+  </si>
+  <si>
+    <t>‌冰蝎爪</t>
+  </si>
+  <si>
+    <t>冰封王陵珍宝材料</t>
+  </si>
+  <si>
+    <t>龙龟蛋</t>
+  </si>
+  <si>
+    <t>冰兽魔核</t>
+  </si>
+  <si>
+    <t>鬼面毒囊</t>
+  </si>
+  <si>
+    <t>暗影祭坛珍宝材料</t>
+  </si>
+  <si>
+    <t>巨蜥毒牙</t>
+  </si>
+  <si>
+    <t>暗影徽记</t>
+  </si>
+  <si>
+    <t>巨熊掌</t>
+  </si>
+  <si>
+    <t>蛮族之地珍宝材料</t>
+  </si>
+  <si>
+    <r>
+      <t>‌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF333333"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>狂暴牛角</t>
+    </r>
+  </si>
+  <si>
+    <t>亲卫令牌</t>
   </si>
 </sst>
 </file>
@@ -1285,7 +1332,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="28">
+  <fonts count="29">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1324,6 +1371,12 @@
       <sz val="9"/>
       <color theme="1"/>
       <name val="等线"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF333333"/>
+      <name val="Arial"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1477,12 +1530,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1812,16 +1865,13 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1830,119 +1880,122 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1954,13 +2007,14 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -2688,7 +2742,7 @@
       <c r="B13" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C13" s="12" t="s">
+      <c r="C13" s="13" t="s">
         <v>49</v>
       </c>
       <c r="D13" s="6" t="s">
@@ -2732,7 +2786,7 @@
       <c r="B14" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C14" s="12" t="s">
+      <c r="C14" s="13" t="s">
         <v>52</v>
       </c>
       <c r="D14" s="6" t="s">
@@ -2776,7 +2830,7 @@
       <c r="B15" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C15" s="12" t="s">
+      <c r="C15" s="13" t="s">
         <v>55</v>
       </c>
       <c r="D15" s="6" t="s">
@@ -2820,7 +2874,7 @@
       <c r="B16" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C16" s="12" t="s">
+      <c r="C16" s="13" t="s">
         <v>58</v>
       </c>
       <c r="D16" s="6" t="s">
@@ -2864,7 +2918,7 @@
       <c r="B17" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C17" s="12" t="s">
+      <c r="C17" s="13" t="s">
         <v>61</v>
       </c>
       <c r="D17" s="6" t="s">
@@ -3174,7 +3228,7 @@
       <c r="B26" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C26" s="12" t="s">
+      <c r="C26" s="13" t="s">
         <v>86</v>
       </c>
       <c r="D26" s="6" t="s">
@@ -3218,7 +3272,7 @@
       <c r="B27" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C27" s="12" t="s">
+      <c r="C27" s="13" t="s">
         <v>89</v>
       </c>
       <c r="D27" s="6" t="s">
@@ -3262,7 +3316,7 @@
       <c r="B28" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C28" s="12" t="s">
+      <c r="C28" s="13" t="s">
         <v>92</v>
       </c>
       <c r="D28" s="6" t="s">
@@ -3306,7 +3360,7 @@
       <c r="B29" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C29" s="12" t="s">
+      <c r="C29" s="13" t="s">
         <v>95</v>
       </c>
       <c r="D29" s="6" t="s">
@@ -3350,7 +3404,7 @@
       <c r="B30" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C30" s="12" t="s">
+      <c r="C30" s="13" t="s">
         <v>98</v>
       </c>
       <c r="D30" s="6" t="s">
@@ -3660,7 +3714,7 @@
       <c r="B39" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C39" s="12" t="s">
+      <c r="C39" s="13" t="s">
         <v>123</v>
       </c>
       <c r="D39" s="6" t="s">
@@ -3704,7 +3758,7 @@
       <c r="B40" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C40" s="12" t="s">
+      <c r="C40" s="13" t="s">
         <v>126</v>
       </c>
       <c r="D40" s="6" t="s">
@@ -3748,7 +3802,7 @@
       <c r="B41" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C41" s="12" t="s">
+      <c r="C41" s="13" t="s">
         <v>129</v>
       </c>
       <c r="D41" s="6" t="s">
@@ -3792,7 +3846,7 @@
       <c r="B42" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C42" s="12" t="s">
+      <c r="C42" s="13" t="s">
         <v>132</v>
       </c>
       <c r="D42" s="6" t="s">
@@ -3836,7 +3890,7 @@
       <c r="B43" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C43" s="12" t="s">
+      <c r="C43" s="13" t="s">
         <v>135</v>
       </c>
       <c r="D43" s="6" t="s">
@@ -4266,10 +4320,10 @@
       </c>
     </row>
     <row r="13" s="6" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C13" s="7"/>
-      <c r="D13" s="7"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
       <c r="E13" s="3"/>
-      <c r="F13" s="7"/>
+      <c r="F13" s="8"/>
       <c r="G13" s="3"/>
       <c r="H13" s="3"/>
       <c r="I13" s="3"/>
@@ -4280,14 +4334,14 @@
       <c r="N13" s="3"/>
     </row>
     <row r="14" s="6" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C14" s="8">
+      <c r="C14" s="9">
         <v>5011</v>
       </c>
-      <c r="D14" s="9" t="s">
+      <c r="D14" s="10" t="s">
         <v>151</v>
       </c>
       <c r="E14" s="2"/>
-      <c r="F14" s="10">
+      <c r="F14" s="11">
         <v>5</v>
       </c>
       <c r="G14" s="3" t="s">
@@ -4314,14 +4368,14 @@
       </c>
     </row>
     <row r="15" s="6" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C15" s="8">
+      <c r="C15" s="9">
         <v>5012</v>
       </c>
-      <c r="D15" s="9" t="s">
+      <c r="D15" s="10" t="s">
         <v>153</v>
       </c>
       <c r="E15" s="2"/>
-      <c r="F15" s="10">
+      <c r="F15" s="11">
         <v>5</v>
       </c>
       <c r="G15" s="3" t="s">
@@ -4348,14 +4402,14 @@
       </c>
     </row>
     <row r="16" s="6" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C16" s="8">
+      <c r="C16" s="9">
         <v>5013</v>
       </c>
-      <c r="D16" s="9" t="s">
+      <c r="D16" s="10" t="s">
         <v>155</v>
       </c>
       <c r="E16" s="3"/>
-      <c r="F16" s="10">
+      <c r="F16" s="11">
         <v>5</v>
       </c>
       <c r="G16" s="3" t="s">
@@ -4382,14 +4436,14 @@
       </c>
     </row>
     <row r="17" s="6" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C17" s="8">
+      <c r="C17" s="9">
         <v>5014</v>
       </c>
-      <c r="D17" s="9" t="s">
+      <c r="D17" s="10" t="s">
         <v>157</v>
       </c>
       <c r="E17" s="3"/>
-      <c r="F17" s="10">
+      <c r="F17" s="11">
         <v>5</v>
       </c>
       <c r="G17" s="3" t="s">
@@ -4416,17 +4470,17 @@
       </c>
     </row>
     <row r="18" s="6" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C18" s="8">
+      <c r="C18" s="9">
         <v>5015</v>
       </c>
-      <c r="D18" s="11" t="s">
+      <c r="D18" s="12" t="s">
         <v>159</v>
       </c>
       <c r="E18" s="3"/>
-      <c r="F18" s="10">
-        <v>5</v>
-      </c>
-      <c r="G18" s="11" t="s">
+      <c r="F18" s="11">
+        <v>5</v>
+      </c>
+      <c r="G18" s="12" t="s">
         <v>160</v>
       </c>
       <c r="H18" s="3">
@@ -4438,10 +4492,10 @@
       <c r="J18" s="3">
         <v>0</v>
       </c>
-      <c r="K18" s="8">
+      <c r="K18" s="9">
         <v>3</v>
       </c>
-      <c r="L18" s="8"/>
+      <c r="L18" s="9"/>
       <c r="M18" s="3">
         <v>0</v>
       </c>
@@ -4450,17 +4504,17 @@
       </c>
     </row>
     <row r="19" s="6" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C19" s="8">
+      <c r="C19" s="9">
         <v>5016</v>
       </c>
-      <c r="D19" s="11" t="s">
+      <c r="D19" s="12" t="s">
         <v>161</v>
       </c>
       <c r="E19" s="3"/>
-      <c r="F19" s="10">
-        <v>5</v>
-      </c>
-      <c r="G19" s="11" t="s">
+      <c r="F19" s="11">
+        <v>5</v>
+      </c>
+      <c r="G19" s="12" t="s">
         <v>162</v>
       </c>
       <c r="H19" s="3">
@@ -4472,10 +4526,10 @@
       <c r="J19" s="3">
         <v>0</v>
       </c>
-      <c r="K19" s="8">
+      <c r="K19" s="9">
         <v>3</v>
       </c>
-      <c r="L19" s="8"/>
+      <c r="L19" s="9"/>
       <c r="M19" s="3">
         <v>0</v>
       </c>
@@ -4484,17 +4538,17 @@
       </c>
     </row>
     <row r="20" s="6" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C20" s="8">
+      <c r="C20" s="9">
         <v>5017</v>
       </c>
-      <c r="D20" s="11" t="s">
+      <c r="D20" s="12" t="s">
         <v>163</v>
       </c>
       <c r="E20" s="3"/>
-      <c r="F20" s="10">
-        <v>5</v>
-      </c>
-      <c r="G20" s="11" t="s">
+      <c r="F20" s="11">
+        <v>5</v>
+      </c>
+      <c r="G20" s="12" t="s">
         <v>164</v>
       </c>
       <c r="H20" s="3">
@@ -4506,10 +4560,10 @@
       <c r="J20" s="3">
         <v>0</v>
       </c>
-      <c r="K20" s="8">
+      <c r="K20" s="9">
         <v>4</v>
       </c>
-      <c r="L20" s="8"/>
+      <c r="L20" s="9"/>
       <c r="M20" s="3">
         <v>0</v>
       </c>
@@ -4518,17 +4572,17 @@
       </c>
     </row>
     <row r="21" s="6" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C21" s="8">
+      <c r="C21" s="9">
         <v>5018</v>
       </c>
-      <c r="D21" s="11" t="s">
+      <c r="D21" s="12" t="s">
         <v>165</v>
       </c>
       <c r="E21" s="3"/>
-      <c r="F21" s="10">
-        <v>5</v>
-      </c>
-      <c r="G21" s="11" t="s">
+      <c r="F21" s="11">
+        <v>5</v>
+      </c>
+      <c r="G21" s="12" t="s">
         <v>166</v>
       </c>
       <c r="H21" s="3">
@@ -4540,10 +4594,10 @@
       <c r="J21" s="3">
         <v>0</v>
       </c>
-      <c r="K21" s="8">
+      <c r="K21" s="9">
         <v>4</v>
       </c>
-      <c r="L21" s="8"/>
+      <c r="L21" s="9"/>
       <c r="M21" s="3">
         <v>0</v>
       </c>
@@ -4552,17 +4606,17 @@
       </c>
     </row>
     <row r="22" s="6" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C22" s="8">
+      <c r="C22" s="9">
         <v>5019</v>
       </c>
-      <c r="D22" s="11" t="s">
+      <c r="D22" s="12" t="s">
         <v>167</v>
       </c>
       <c r="E22" s="3"/>
-      <c r="F22" s="10">
-        <v>5</v>
-      </c>
-      <c r="G22" s="11" t="s">
+      <c r="F22" s="11">
+        <v>5</v>
+      </c>
+      <c r="G22" s="12" t="s">
         <v>168</v>
       </c>
       <c r="H22" s="3">
@@ -4574,10 +4628,10 @@
       <c r="J22" s="3">
         <v>0</v>
       </c>
-      <c r="K22" s="8">
-        <v>5</v>
-      </c>
-      <c r="L22" s="8"/>
+      <c r="K22" s="9">
+        <v>5</v>
+      </c>
+      <c r="L22" s="9"/>
       <c r="M22" s="3">
         <v>0</v>
       </c>
@@ -6477,7 +6531,7 @@
       <c r="C91" s="3">
         <v>8101</v>
       </c>
-      <c r="D91" s="9" t="s">
+      <c r="D91" s="10" t="s">
         <v>268</v>
       </c>
       <c r="E91" s="2"/>
@@ -6510,7 +6564,7 @@
       <c r="C92" s="3">
         <v>8102</v>
       </c>
-      <c r="D92" s="9" t="s">
+      <c r="D92" s="10" t="s">
         <v>270</v>
       </c>
       <c r="E92" s="2"/>
@@ -6543,7 +6597,7 @@
       <c r="C93" s="3">
         <v>8103</v>
       </c>
-      <c r="D93" s="9" t="s">
+      <c r="D93" s="10" t="s">
         <v>271</v>
       </c>
       <c r="E93" s="2"/>
@@ -6576,7 +6630,7 @@
       <c r="C94" s="3">
         <v>8104</v>
       </c>
-      <c r="D94" s="9" t="s">
+      <c r="D94" s="10" t="s">
         <v>272</v>
       </c>
       <c r="E94" s="2"/>
@@ -6609,7 +6663,7 @@
       <c r="C95" s="3">
         <v>8105</v>
       </c>
-      <c r="D95" s="9" t="s">
+      <c r="D95" s="10" t="s">
         <v>273</v>
       </c>
       <c r="E95" s="2"/>
@@ -6642,7 +6696,7 @@
       <c r="C96" s="3">
         <v>8106</v>
       </c>
-      <c r="D96" s="9" t="s">
+      <c r="D96" s="10" t="s">
         <v>274</v>
       </c>
       <c r="E96" s="2"/>
@@ -6675,7 +6729,7 @@
       <c r="C97" s="3">
         <v>8107</v>
       </c>
-      <c r="D97" s="9" t="s">
+      <c r="D97" s="10" t="s">
         <v>275</v>
       </c>
       <c r="E97" s="2"/>
@@ -6708,7 +6762,7 @@
       <c r="C98" s="3">
         <v>8108</v>
       </c>
-      <c r="D98" s="9" t="s">
+      <c r="D98" s="10" t="s">
         <v>276</v>
       </c>
       <c r="E98" s="2"/>
@@ -6741,7 +6795,7 @@
       <c r="C100" s="3">
         <v>8201</v>
       </c>
-      <c r="D100" s="9" t="s">
+      <c r="D100" s="10" t="s">
         <v>277</v>
       </c>
       <c r="F100" s="3">
@@ -6776,7 +6830,7 @@
       <c r="C101" s="3">
         <v>8202</v>
       </c>
-      <c r="D101" s="9" t="s">
+      <c r="D101" s="10" t="s">
         <v>279</v>
       </c>
       <c r="F101" s="3">
@@ -6811,7 +6865,7 @@
       <c r="C102" s="3">
         <v>8203</v>
       </c>
-      <c r="D102" s="9" t="s">
+      <c r="D102" s="10" t="s">
         <v>281</v>
       </c>
       <c r="F102" s="3">
@@ -6846,7 +6900,7 @@
       <c r="C103" s="3">
         <v>8204</v>
       </c>
-      <c r="D103" s="9" t="s">
+      <c r="D103" s="10" t="s">
         <v>283</v>
       </c>
       <c r="F103" s="3">
@@ -6881,7 +6935,7 @@
       <c r="C104" s="3">
         <v>8205</v>
       </c>
-      <c r="D104" s="9" t="s">
+      <c r="D104" s="10" t="s">
         <v>285</v>
       </c>
       <c r="F104" s="3">
@@ -6916,7 +6970,7 @@
       <c r="C105" s="3">
         <v>8206</v>
       </c>
-      <c r="D105" s="9" t="s">
+      <c r="D105" s="10" t="s">
         <v>287</v>
       </c>
       <c r="F105" s="3">
@@ -6951,7 +7005,7 @@
       <c r="C106" s="3">
         <v>8207</v>
       </c>
-      <c r="D106" s="9" t="s">
+      <c r="D106" s="10" t="s">
         <v>289</v>
       </c>
       <c r="F106" s="3">
@@ -6983,46 +7037,46 @@
       </c>
     </row>
     <row r="108" customHeight="1" spans="3:14">
-      <c r="D108" s="9"/>
+      <c r="D108" s="10"/>
     </row>
     <row r="109" customHeight="1" spans="3:14">
-      <c r="D109" s="9"/>
+      <c r="D109" s="10"/>
     </row>
     <row r="110" customHeight="1" spans="3:14">
-      <c r="D110" s="9"/>
+      <c r="D110" s="10"/>
     </row>
     <row r="111" customHeight="1" spans="3:14">
-      <c r="D111" s="9"/>
+      <c r="D111" s="10"/>
     </row>
     <row r="112" customHeight="1" spans="3:14">
-      <c r="D112" s="9"/>
+      <c r="D112" s="10"/>
     </row>
     <row r="113" customHeight="1" spans="4:4">
-      <c r="D113" s="9"/>
+      <c r="D113" s="10"/>
     </row>
     <row r="114" customHeight="1" spans="4:4">
-      <c r="D114" s="9"/>
+      <c r="D114" s="10"/>
     </row>
     <row r="116" customHeight="1" spans="4:4">
-      <c r="D116" s="9"/>
+      <c r="D116" s="10"/>
     </row>
     <row r="117" customHeight="1" spans="4:4">
-      <c r="D117" s="9"/>
+      <c r="D117" s="10"/>
     </row>
     <row r="118" customHeight="1" spans="4:4">
-      <c r="D118" s="9"/>
+      <c r="D118" s="10"/>
     </row>
     <row r="119" customHeight="1" spans="4:4">
-      <c r="D119" s="9"/>
+      <c r="D119" s="10"/>
     </row>
     <row r="120" customHeight="1" spans="4:4">
-      <c r="D120" s="9"/>
+      <c r="D120" s="10"/>
     </row>
     <row r="121" customHeight="1" spans="4:4">
-      <c r="D121" s="9"/>
+      <c r="D121" s="10"/>
     </row>
     <row r="122" customHeight="1" spans="4:4">
-      <c r="D122" s="9"/>
+      <c r="D122" s="10"/>
     </row>
   </sheetData>
   <dataValidations count="2">
@@ -7880,7 +7934,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N26"/>
+  <dimension ref="A1:N35"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="2"/>
@@ -8614,6 +8668,240 @@
         <v>6</v>
       </c>
     </row>
+    <row r="27" customHeight="1" spans="1:11">
+      <c r="C27" s="3">
+        <v>40000022</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="F27" s="2">
+        <v>6</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="H27" s="2">
+        <v>1</v>
+      </c>
+      <c r="I27" s="2">
+        <v>99999</v>
+      </c>
+      <c r="J27" s="2">
+        <v>0</v>
+      </c>
+      <c r="K27" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" customHeight="1" spans="1:11">
+      <c r="C28" s="3">
+        <v>40000023</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="F28" s="2">
+        <v>6</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="H28" s="2">
+        <v>1</v>
+      </c>
+      <c r="I28" s="2">
+        <v>99999</v>
+      </c>
+      <c r="J28" s="2">
+        <v>0</v>
+      </c>
+      <c r="K28" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29" customHeight="1" spans="1:11">
+      <c r="C29" s="3">
+        <v>40000024</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="F29" s="2">
+        <v>6</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="H29" s="2">
+        <v>1</v>
+      </c>
+      <c r="I29" s="2">
+        <v>99999</v>
+      </c>
+      <c r="J29" s="2">
+        <v>0</v>
+      </c>
+      <c r="K29" s="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" customHeight="1" spans="1:11">
+      <c r="C30" s="3">
+        <v>40000025</v>
+      </c>
+      <c r="D30" s="7" t="s">
+        <v>352</v>
+      </c>
+      <c r="F30" s="2">
+        <v>6</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="H30" s="2">
+        <v>1</v>
+      </c>
+      <c r="I30" s="2">
+        <v>99999</v>
+      </c>
+      <c r="J30" s="2">
+        <v>0</v>
+      </c>
+      <c r="K30" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="31" customHeight="1" spans="1:11">
+      <c r="C31" s="3">
+        <v>40000026</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="F31" s="2">
+        <v>6</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="H31" s="2">
+        <v>1</v>
+      </c>
+      <c r="I31" s="2">
+        <v>99999</v>
+      </c>
+      <c r="J31" s="2">
+        <v>0</v>
+      </c>
+      <c r="K31" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32" customHeight="1" spans="1:11">
+      <c r="C32" s="3">
+        <v>40000027</v>
+      </c>
+      <c r="D32" s="7" t="s">
+        <v>355</v>
+      </c>
+      <c r="F32" s="2">
+        <v>6</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="H32" s="2">
+        <v>1</v>
+      </c>
+      <c r="I32" s="2">
+        <v>99999</v>
+      </c>
+      <c r="J32" s="2">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" customHeight="1" spans="3:11">
+      <c r="C33" s="3">
+        <v>40000028</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="F33" s="2">
+        <v>6</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="H33" s="2">
+        <v>1</v>
+      </c>
+      <c r="I33" s="2">
+        <v>99999</v>
+      </c>
+      <c r="J33" s="2">
+        <v>0</v>
+      </c>
+      <c r="K33" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" customHeight="1" spans="3:11">
+      <c r="C34" s="3">
+        <v>40000029</v>
+      </c>
+      <c r="D34" s="7" t="s">
+        <v>358</v>
+      </c>
+      <c r="F34" s="2">
+        <v>6</v>
+      </c>
+      <c r="G34" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="H34" s="2">
+        <v>1</v>
+      </c>
+      <c r="I34" s="2">
+        <v>99999</v>
+      </c>
+      <c r="J34" s="2">
+        <v>0</v>
+      </c>
+      <c r="K34" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="35" customHeight="1" spans="3:11">
+      <c r="C35" s="3">
+        <v>40000030</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="F35" s="2">
+        <v>6</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="H35" s="2">
+        <v>1</v>
+      </c>
+      <c r="I35" s="2">
+        <v>99999</v>
+      </c>
+      <c r="J35" s="2">
+        <v>0</v>
+      </c>
+      <c r="K35" s="3">
+        <v>6</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="2">
     <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:E5" errorStyle="warning">

--- a/Excel/ItemConfig.xlsx
+++ b/Excel/ItemConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="11480" activeTab="4"/>
+    <workbookView windowWidth="25600" windowHeight="12080" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="技能" sheetId="1" r:id="rId1"/>
@@ -1310,9 +1310,9 @@
     </r>
     <r>
       <rPr>
-        <sz val="12"/>
+        <sz val="9"/>
         <color rgb="FF333333"/>
-        <rFont val="Arial"/>
+        <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
       <t>狂暴牛角</t>
@@ -1332,7 +1332,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="29">
+  <fonts count="30">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1374,7 +1374,13 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="12"/>
+      <sz val="9"/>
+      <color rgb="FF333333"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
       <color rgb="FF333333"/>
       <name val="Arial"/>
       <charset val="134"/>
@@ -1865,16 +1871,13 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1883,119 +1886,122 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2008,13 +2014,14 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -2742,7 +2749,7 @@
       <c r="B13" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C13" s="13" t="s">
+      <c r="C13" s="14" t="s">
         <v>49</v>
       </c>
       <c r="D13" s="6" t="s">
@@ -2786,7 +2793,7 @@
       <c r="B14" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C14" s="13" t="s">
+      <c r="C14" s="14" t="s">
         <v>52</v>
       </c>
       <c r="D14" s="6" t="s">
@@ -2830,7 +2837,7 @@
       <c r="B15" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C15" s="13" t="s">
+      <c r="C15" s="14" t="s">
         <v>55</v>
       </c>
       <c r="D15" s="6" t="s">
@@ -2874,7 +2881,7 @@
       <c r="B16" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C16" s="13" t="s">
+      <c r="C16" s="14" t="s">
         <v>58</v>
       </c>
       <c r="D16" s="6" t="s">
@@ -2918,7 +2925,7 @@
       <c r="B17" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C17" s="13" t="s">
+      <c r="C17" s="14" t="s">
         <v>61</v>
       </c>
       <c r="D17" s="6" t="s">
@@ -3228,7 +3235,7 @@
       <c r="B26" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C26" s="13" t="s">
+      <c r="C26" s="14" t="s">
         <v>86</v>
       </c>
       <c r="D26" s="6" t="s">
@@ -3272,7 +3279,7 @@
       <c r="B27" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C27" s="13" t="s">
+      <c r="C27" s="14" t="s">
         <v>89</v>
       </c>
       <c r="D27" s="6" t="s">
@@ -3316,7 +3323,7 @@
       <c r="B28" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C28" s="13" t="s">
+      <c r="C28" s="14" t="s">
         <v>92</v>
       </c>
       <c r="D28" s="6" t="s">
@@ -3360,7 +3367,7 @@
       <c r="B29" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C29" s="13" t="s">
+      <c r="C29" s="14" t="s">
         <v>95</v>
       </c>
       <c r="D29" s="6" t="s">
@@ -3404,7 +3411,7 @@
       <c r="B30" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C30" s="13" t="s">
+      <c r="C30" s="14" t="s">
         <v>98</v>
       </c>
       <c r="D30" s="6" t="s">
@@ -3714,7 +3721,7 @@
       <c r="B39" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C39" s="13" t="s">
+      <c r="C39" s="14" t="s">
         <v>123</v>
       </c>
       <c r="D39" s="6" t="s">
@@ -3758,7 +3765,7 @@
       <c r="B40" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C40" s="13" t="s">
+      <c r="C40" s="14" t="s">
         <v>126</v>
       </c>
       <c r="D40" s="6" t="s">
@@ -3802,7 +3809,7 @@
       <c r="B41" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C41" s="13" t="s">
+      <c r="C41" s="14" t="s">
         <v>129</v>
       </c>
       <c r="D41" s="6" t="s">
@@ -3846,7 +3853,7 @@
       <c r="B42" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C42" s="13" t="s">
+      <c r="C42" s="14" t="s">
         <v>132</v>
       </c>
       <c r="D42" s="6" t="s">
@@ -3890,7 +3897,7 @@
       <c r="B43" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C43" s="13" t="s">
+      <c r="C43" s="14" t="s">
         <v>135</v>
       </c>
       <c r="D43" s="6" t="s">
@@ -4320,10 +4327,10 @@
       </c>
     </row>
     <row r="13" s="6" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C13" s="8"/>
-      <c r="D13" s="8"/>
+      <c r="C13" s="9"/>
+      <c r="D13" s="9"/>
       <c r="E13" s="3"/>
-      <c r="F13" s="8"/>
+      <c r="F13" s="9"/>
       <c r="G13" s="3"/>
       <c r="H13" s="3"/>
       <c r="I13" s="3"/>
@@ -4334,14 +4341,14 @@
       <c r="N13" s="3"/>
     </row>
     <row r="14" s="6" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C14" s="9">
+      <c r="C14" s="10">
         <v>5011</v>
       </c>
-      <c r="D14" s="10" t="s">
+      <c r="D14" s="11" t="s">
         <v>151</v>
       </c>
       <c r="E14" s="2"/>
-      <c r="F14" s="11">
+      <c r="F14" s="12">
         <v>5</v>
       </c>
       <c r="G14" s="3" t="s">
@@ -4368,14 +4375,14 @@
       </c>
     </row>
     <row r="15" s="6" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C15" s="9">
+      <c r="C15" s="10">
         <v>5012</v>
       </c>
-      <c r="D15" s="10" t="s">
+      <c r="D15" s="11" t="s">
         <v>153</v>
       </c>
       <c r="E15" s="2"/>
-      <c r="F15" s="11">
+      <c r="F15" s="12">
         <v>5</v>
       </c>
       <c r="G15" s="3" t="s">
@@ -4402,14 +4409,14 @@
       </c>
     </row>
     <row r="16" s="6" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C16" s="9">
+      <c r="C16" s="10">
         <v>5013</v>
       </c>
-      <c r="D16" s="10" t="s">
+      <c r="D16" s="11" t="s">
         <v>155</v>
       </c>
       <c r="E16" s="3"/>
-      <c r="F16" s="11">
+      <c r="F16" s="12">
         <v>5</v>
       </c>
       <c r="G16" s="3" t="s">
@@ -4436,14 +4443,14 @@
       </c>
     </row>
     <row r="17" s="6" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C17" s="9">
+      <c r="C17" s="10">
         <v>5014</v>
       </c>
-      <c r="D17" s="10" t="s">
+      <c r="D17" s="11" t="s">
         <v>157</v>
       </c>
       <c r="E17" s="3"/>
-      <c r="F17" s="11">
+      <c r="F17" s="12">
         <v>5</v>
       </c>
       <c r="G17" s="3" t="s">
@@ -4470,17 +4477,17 @@
       </c>
     </row>
     <row r="18" s="6" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C18" s="9">
+      <c r="C18" s="10">
         <v>5015</v>
       </c>
-      <c r="D18" s="12" t="s">
+      <c r="D18" s="13" t="s">
         <v>159</v>
       </c>
       <c r="E18" s="3"/>
-      <c r="F18" s="11">
-        <v>5</v>
-      </c>
-      <c r="G18" s="12" t="s">
+      <c r="F18" s="12">
+        <v>5</v>
+      </c>
+      <c r="G18" s="13" t="s">
         <v>160</v>
       </c>
       <c r="H18" s="3">
@@ -4492,10 +4499,10 @@
       <c r="J18" s="3">
         <v>0</v>
       </c>
-      <c r="K18" s="9">
+      <c r="K18" s="10">
         <v>3</v>
       </c>
-      <c r="L18" s="9"/>
+      <c r="L18" s="10"/>
       <c r="M18" s="3">
         <v>0</v>
       </c>
@@ -4504,17 +4511,17 @@
       </c>
     </row>
     <row r="19" s="6" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C19" s="9">
+      <c r="C19" s="10">
         <v>5016</v>
       </c>
-      <c r="D19" s="12" t="s">
+      <c r="D19" s="13" t="s">
         <v>161</v>
       </c>
       <c r="E19" s="3"/>
-      <c r="F19" s="11">
-        <v>5</v>
-      </c>
-      <c r="G19" s="12" t="s">
+      <c r="F19" s="12">
+        <v>5</v>
+      </c>
+      <c r="G19" s="13" t="s">
         <v>162</v>
       </c>
       <c r="H19" s="3">
@@ -4526,10 +4533,10 @@
       <c r="J19" s="3">
         <v>0</v>
       </c>
-      <c r="K19" s="9">
+      <c r="K19" s="10">
         <v>3</v>
       </c>
-      <c r="L19" s="9"/>
+      <c r="L19" s="10"/>
       <c r="M19" s="3">
         <v>0</v>
       </c>
@@ -4538,17 +4545,17 @@
       </c>
     </row>
     <row r="20" s="6" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C20" s="9">
+      <c r="C20" s="10">
         <v>5017</v>
       </c>
-      <c r="D20" s="12" t="s">
+      <c r="D20" s="13" t="s">
         <v>163</v>
       </c>
       <c r="E20" s="3"/>
-      <c r="F20" s="11">
-        <v>5</v>
-      </c>
-      <c r="G20" s="12" t="s">
+      <c r="F20" s="12">
+        <v>5</v>
+      </c>
+      <c r="G20" s="13" t="s">
         <v>164</v>
       </c>
       <c r="H20" s="3">
@@ -4560,10 +4567,10 @@
       <c r="J20" s="3">
         <v>0</v>
       </c>
-      <c r="K20" s="9">
+      <c r="K20" s="10">
         <v>4</v>
       </c>
-      <c r="L20" s="9"/>
+      <c r="L20" s="10"/>
       <c r="M20" s="3">
         <v>0</v>
       </c>
@@ -4572,17 +4579,17 @@
       </c>
     </row>
     <row r="21" s="6" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C21" s="9">
+      <c r="C21" s="10">
         <v>5018</v>
       </c>
-      <c r="D21" s="12" t="s">
+      <c r="D21" s="13" t="s">
         <v>165</v>
       </c>
       <c r="E21" s="3"/>
-      <c r="F21" s="11">
-        <v>5</v>
-      </c>
-      <c r="G21" s="12" t="s">
+      <c r="F21" s="12">
+        <v>5</v>
+      </c>
+      <c r="G21" s="13" t="s">
         <v>166</v>
       </c>
       <c r="H21" s="3">
@@ -4594,10 +4601,10 @@
       <c r="J21" s="3">
         <v>0</v>
       </c>
-      <c r="K21" s="9">
+      <c r="K21" s="10">
         <v>4</v>
       </c>
-      <c r="L21" s="9"/>
+      <c r="L21" s="10"/>
       <c r="M21" s="3">
         <v>0</v>
       </c>
@@ -4606,17 +4613,17 @@
       </c>
     </row>
     <row r="22" s="6" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C22" s="9">
+      <c r="C22" s="10">
         <v>5019</v>
       </c>
-      <c r="D22" s="12" t="s">
+      <c r="D22" s="13" t="s">
         <v>167</v>
       </c>
       <c r="E22" s="3"/>
-      <c r="F22" s="11">
-        <v>5</v>
-      </c>
-      <c r="G22" s="12" t="s">
+      <c r="F22" s="12">
+        <v>5</v>
+      </c>
+      <c r="G22" s="13" t="s">
         <v>168</v>
       </c>
       <c r="H22" s="3">
@@ -4628,10 +4635,10 @@
       <c r="J22" s="3">
         <v>0</v>
       </c>
-      <c r="K22" s="9">
-        <v>5</v>
-      </c>
-      <c r="L22" s="9"/>
+      <c r="K22" s="10">
+        <v>5</v>
+      </c>
+      <c r="L22" s="10"/>
       <c r="M22" s="3">
         <v>0</v>
       </c>
@@ -6531,7 +6538,7 @@
       <c r="C91" s="3">
         <v>8101</v>
       </c>
-      <c r="D91" s="10" t="s">
+      <c r="D91" s="11" t="s">
         <v>268</v>
       </c>
       <c r="E91" s="2"/>
@@ -6564,7 +6571,7 @@
       <c r="C92" s="3">
         <v>8102</v>
       </c>
-      <c r="D92" s="10" t="s">
+      <c r="D92" s="11" t="s">
         <v>270</v>
       </c>
       <c r="E92" s="2"/>
@@ -6597,7 +6604,7 @@
       <c r="C93" s="3">
         <v>8103</v>
       </c>
-      <c r="D93" s="10" t="s">
+      <c r="D93" s="11" t="s">
         <v>271</v>
       </c>
       <c r="E93" s="2"/>
@@ -6630,7 +6637,7 @@
       <c r="C94" s="3">
         <v>8104</v>
       </c>
-      <c r="D94" s="10" t="s">
+      <c r="D94" s="11" t="s">
         <v>272</v>
       </c>
       <c r="E94" s="2"/>
@@ -6663,7 +6670,7 @@
       <c r="C95" s="3">
         <v>8105</v>
       </c>
-      <c r="D95" s="10" t="s">
+      <c r="D95" s="11" t="s">
         <v>273</v>
       </c>
       <c r="E95" s="2"/>
@@ -6696,7 +6703,7 @@
       <c r="C96" s="3">
         <v>8106</v>
       </c>
-      <c r="D96" s="10" t="s">
+      <c r="D96" s="11" t="s">
         <v>274</v>
       </c>
       <c r="E96" s="2"/>
@@ -6729,7 +6736,7 @@
       <c r="C97" s="3">
         <v>8107</v>
       </c>
-      <c r="D97" s="10" t="s">
+      <c r="D97" s="11" t="s">
         <v>275</v>
       </c>
       <c r="E97" s="2"/>
@@ -6762,7 +6769,7 @@
       <c r="C98" s="3">
         <v>8108</v>
       </c>
-      <c r="D98" s="10" t="s">
+      <c r="D98" s="11" t="s">
         <v>276</v>
       </c>
       <c r="E98" s="2"/>
@@ -6795,7 +6802,7 @@
       <c r="C100" s="3">
         <v>8201</v>
       </c>
-      <c r="D100" s="10" t="s">
+      <c r="D100" s="11" t="s">
         <v>277</v>
       </c>
       <c r="F100" s="3">
@@ -6830,7 +6837,7 @@
       <c r="C101" s="3">
         <v>8202</v>
       </c>
-      <c r="D101" s="10" t="s">
+      <c r="D101" s="11" t="s">
         <v>279</v>
       </c>
       <c r="F101" s="3">
@@ -6865,7 +6872,7 @@
       <c r="C102" s="3">
         <v>8203</v>
       </c>
-      <c r="D102" s="10" t="s">
+      <c r="D102" s="11" t="s">
         <v>281</v>
       </c>
       <c r="F102" s="3">
@@ -6900,7 +6907,7 @@
       <c r="C103" s="3">
         <v>8204</v>
       </c>
-      <c r="D103" s="10" t="s">
+      <c r="D103" s="11" t="s">
         <v>283</v>
       </c>
       <c r="F103" s="3">
@@ -6935,7 +6942,7 @@
       <c r="C104" s="3">
         <v>8205</v>
       </c>
-      <c r="D104" s="10" t="s">
+      <c r="D104" s="11" t="s">
         <v>285</v>
       </c>
       <c r="F104" s="3">
@@ -6970,7 +6977,7 @@
       <c r="C105" s="3">
         <v>8206</v>
       </c>
-      <c r="D105" s="10" t="s">
+      <c r="D105" s="11" t="s">
         <v>287</v>
       </c>
       <c r="F105" s="3">
@@ -7005,7 +7012,7 @@
       <c r="C106" s="3">
         <v>8207</v>
       </c>
-      <c r="D106" s="10" t="s">
+      <c r="D106" s="11" t="s">
         <v>289</v>
       </c>
       <c r="F106" s="3">
@@ -7037,46 +7044,46 @@
       </c>
     </row>
     <row r="108" customHeight="1" spans="3:14">
-      <c r="D108" s="10"/>
+      <c r="D108" s="11"/>
     </row>
     <row r="109" customHeight="1" spans="3:14">
-      <c r="D109" s="10"/>
+      <c r="D109" s="11"/>
     </row>
     <row r="110" customHeight="1" spans="3:14">
-      <c r="D110" s="10"/>
+      <c r="D110" s="11"/>
     </row>
     <row r="111" customHeight="1" spans="3:14">
-      <c r="D111" s="10"/>
+      <c r="D111" s="11"/>
     </row>
     <row r="112" customHeight="1" spans="3:14">
-      <c r="D112" s="10"/>
+      <c r="D112" s="11"/>
     </row>
     <row r="113" customHeight="1" spans="4:4">
-      <c r="D113" s="10"/>
+      <c r="D113" s="11"/>
     </row>
     <row r="114" customHeight="1" spans="4:4">
-      <c r="D114" s="10"/>
+      <c r="D114" s="11"/>
     </row>
     <row r="116" customHeight="1" spans="4:4">
-      <c r="D116" s="10"/>
+      <c r="D116" s="11"/>
     </row>
     <row r="117" customHeight="1" spans="4:4">
-      <c r="D117" s="10"/>
+      <c r="D117" s="11"/>
     </row>
     <row r="118" customHeight="1" spans="4:4">
-      <c r="D118" s="10"/>
+      <c r="D118" s="11"/>
     </row>
     <row r="119" customHeight="1" spans="4:4">
-      <c r="D119" s="10"/>
+      <c r="D119" s="11"/>
     </row>
     <row r="120" customHeight="1" spans="4:4">
-      <c r="D120" s="10"/>
+      <c r="D120" s="11"/>
     </row>
     <row r="121" customHeight="1" spans="4:4">
-      <c r="D121" s="10"/>
+      <c r="D121" s="11"/>
     </row>
     <row r="122" customHeight="1" spans="4:4">
-      <c r="D122" s="10"/>
+      <c r="D122" s="11"/>
     </row>
   </sheetData>
   <dataValidations count="2">
@@ -8854,7 +8861,7 @@
       <c r="C34" s="3">
         <v>40000029</v>
       </c>
-      <c r="D34" s="7" t="s">
+      <c r="D34" s="8" t="s">
         <v>358</v>
       </c>
       <c r="F34" s="2">

--- a/Excel/ItemConfig.xlsx
+++ b/Excel/ItemConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="12080" activeTab="4"/>
+    <workbookView windowHeight="17680" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="技能" sheetId="1" r:id="rId1"/>
@@ -229,7 +229,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="666" uniqueCount="360">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="662" uniqueCount="358">
   <si>
     <t>_Id</t>
   </si>
@@ -1002,37 +1002,31 @@
     <t>升级或洗练红装，或者回收为1000精炼石</t>
   </si>
   <si>
-    <t>神技·启蒙</t>
-  </si>
-  <si>
-    <t>激活神技</t>
-  </si>
-  <si>
-    <t>神技·奠基</t>
-  </si>
-  <si>
-    <t>神技·开光</t>
-  </si>
-  <si>
-    <t>神技·融合</t>
-  </si>
-  <si>
-    <t>神技·进阶</t>
-  </si>
-  <si>
-    <t>神技·真意</t>
-  </si>
-  <si>
-    <t>神技·领域</t>
-  </si>
-  <si>
-    <t>神技·掌控</t>
-  </si>
-  <si>
-    <t>神技·道境</t>
-  </si>
-  <si>
-    <t>神技·超脱</t>
+    <t>十年魂环</t>
+  </si>
+  <si>
+    <t>升级对应魂环</t>
+  </si>
+  <si>
+    <t>百年魂环</t>
+  </si>
+  <si>
+    <t>千年魂环</t>
+  </si>
+  <si>
+    <t>万年魂环</t>
+  </si>
+  <si>
+    <t>十万年魂环</t>
+  </si>
+  <si>
+    <t>百万年魂环</t>
+  </si>
+  <si>
+    <t>千万年魂环</t>
+  </si>
+  <si>
+    <t>亿年魂环</t>
   </si>
   <si>
     <t>八蛛魂骨</t>
@@ -1306,6 +1300,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF333333"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
       <t>‌</t>
     </r>
     <r>
@@ -1536,12 +1536,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -3953,7 +3953,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:N122"/>
+  <dimension ref="C1:N119"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="3"/>
@@ -6208,7 +6208,7 @@
       <c r="C80" s="3">
         <v>8001</v>
       </c>
-      <c r="D80" s="3" t="s">
+      <c r="D80" s="2" t="s">
         <v>257</v>
       </c>
       <c r="E80" s="2"/>
@@ -6241,7 +6241,7 @@
       <c r="C81" s="3">
         <v>8002</v>
       </c>
-      <c r="D81" s="3" t="s">
+      <c r="D81" s="2" t="s">
         <v>259</v>
       </c>
       <c r="E81" s="2"/>
@@ -6274,7 +6274,7 @@
       <c r="C82" s="3">
         <v>8003</v>
       </c>
-      <c r="D82" s="3" t="s">
+      <c r="D82" s="2" t="s">
         <v>260</v>
       </c>
       <c r="E82" s="2"/>
@@ -6307,7 +6307,7 @@
       <c r="C83" s="3">
         <v>8004</v>
       </c>
-      <c r="D83" s="3" t="s">
+      <c r="D83" s="2" t="s">
         <v>261</v>
       </c>
       <c r="E83" s="2"/>
@@ -6340,7 +6340,7 @@
       <c r="C84" s="3">
         <v>8005</v>
       </c>
-      <c r="D84" s="3" t="s">
+      <c r="D84" s="2" t="s">
         <v>262</v>
       </c>
       <c r="E84" s="2"/>
@@ -6373,7 +6373,7 @@
       <c r="C85" s="3">
         <v>8006</v>
       </c>
-      <c r="D85" s="3" t="s">
+      <c r="D85" s="2" t="s">
         <v>263</v>
       </c>
       <c r="E85" s="2"/>
@@ -6406,7 +6406,7 @@
       <c r="C86" s="3">
         <v>8007</v>
       </c>
-      <c r="D86" s="3" t="s">
+      <c r="D86" s="2" t="s">
         <v>264</v>
       </c>
       <c r="E86" s="2"/>
@@ -6439,7 +6439,7 @@
       <c r="C87" s="3">
         <v>8008</v>
       </c>
-      <c r="D87" s="3" t="s">
+      <c r="D87" s="2" t="s">
         <v>265</v>
       </c>
       <c r="E87" s="2"/>
@@ -6472,7 +6472,7 @@
       <c r="C88" s="3">
         <v>8009</v>
       </c>
-      <c r="D88" s="3" t="s">
+      <c r="D88" s="11" t="s">
         <v>266</v>
       </c>
       <c r="E88" s="2"/>
@@ -6480,7 +6480,7 @@
         <v>5</v>
       </c>
       <c r="G88" s="3" t="s">
-        <v>258</v>
+        <v>267</v>
       </c>
       <c r="H88" s="3">
         <v>1</v>
@@ -6492,7 +6492,7 @@
         <v>0</v>
       </c>
       <c r="K88" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M88" s="3">
         <v>0</v>
@@ -6505,15 +6505,15 @@
       <c r="C89" s="3">
         <v>8010</v>
       </c>
-      <c r="D89" s="3" t="s">
-        <v>267</v>
+      <c r="D89" s="11" t="s">
+        <v>268</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" s="3">
         <v>5</v>
       </c>
       <c r="G89" s="3" t="s">
-        <v>258</v>
+        <v>267</v>
       </c>
       <c r="H89" s="3">
         <v>1</v>
@@ -6525,28 +6525,61 @@
         <v>0</v>
       </c>
       <c r="K89" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M89" s="3">
         <v>0</v>
       </c>
       <c r="N89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" s="3" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C90" s="3">
+        <v>8011</v>
+      </c>
+      <c r="D90" s="11" t="s">
+        <v>269</v>
+      </c>
+      <c r="E90" s="2"/>
+      <c r="F90" s="3">
+        <v>5</v>
+      </c>
+      <c r="G90" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="H90" s="3">
+        <v>1</v>
+      </c>
+      <c r="I90" s="3">
+        <v>9999999</v>
+      </c>
+      <c r="J90" s="3">
+        <v>0</v>
+      </c>
+      <c r="K90" s="3">
+        <v>7</v>
+      </c>
+      <c r="M90" s="3">
+        <v>0</v>
+      </c>
+      <c r="N90" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="91" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C91" s="3">
-        <v>8101</v>
+        <v>8012</v>
       </c>
       <c r="D91" s="11" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="E91" s="2"/>
       <c r="F91" s="3">
         <v>5</v>
       </c>
       <c r="G91" s="3" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="H91" s="3">
         <v>1</v>
@@ -6569,17 +6602,17 @@
     </row>
     <row r="92" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C92" s="3">
-        <v>8102</v>
+        <v>8013</v>
       </c>
       <c r="D92" s="11" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E92" s="2"/>
       <c r="F92" s="3">
         <v>5</v>
       </c>
       <c r="G92" s="3" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="H92" s="3">
         <v>1</v>
@@ -6602,17 +6635,17 @@
     </row>
     <row r="93" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C93" s="3">
-        <v>8103</v>
+        <v>8014</v>
       </c>
       <c r="D93" s="11" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E93" s="2"/>
       <c r="F93" s="3">
         <v>5</v>
       </c>
       <c r="G93" s="3" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="H93" s="3">
         <v>1</v>
@@ -6635,17 +6668,17 @@
     </row>
     <row r="94" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C94" s="3">
-        <v>8104</v>
+        <v>8015</v>
       </c>
       <c r="D94" s="11" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="E94" s="2"/>
       <c r="F94" s="3">
         <v>5</v>
       </c>
       <c r="G94" s="3" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="H94" s="3">
         <v>1</v>
@@ -6668,17 +6701,17 @@
     </row>
     <row r="95" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C95" s="3">
-        <v>8105</v>
+        <v>8016</v>
       </c>
       <c r="D95" s="11" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E95" s="2"/>
       <c r="F95" s="3">
         <v>5</v>
       </c>
       <c r="G95" s="3" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="H95" s="3">
         <v>1</v>
@@ -6699,64 +6732,33 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" s="3" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C96" s="3">
-        <v>8106</v>
-      </c>
-      <c r="D96" s="11" t="s">
-        <v>274</v>
-      </c>
-      <c r="E96" s="2"/>
-      <c r="F96" s="3">
-        <v>5</v>
-      </c>
-      <c r="G96" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="H96" s="3">
-        <v>1</v>
-      </c>
-      <c r="I96" s="3">
-        <v>9999999</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
-      </c>
-      <c r="K96" s="3">
-        <v>7</v>
-      </c>
-      <c r="M96" s="3">
-        <v>0</v>
-      </c>
-      <c r="N96" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" s="3" customFormat="1" customHeight="1" spans="3:14">
+    <row r="97" customHeight="1" spans="3:14">
       <c r="C97" s="3">
-        <v>8107</v>
+        <v>8201</v>
       </c>
       <c r="D97" s="11" t="s">
         <v>275</v>
       </c>
-      <c r="E97" s="2"/>
       <c r="F97" s="3">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="G97" s="3" t="s">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="H97" s="3">
         <v>1</v>
       </c>
       <c r="I97" s="3">
-        <v>9999999</v>
+        <v>1</v>
       </c>
       <c r="J97" s="3">
         <v>0</v>
       </c>
       <c r="K97" s="3">
-        <v>7</v>
+        <v>1</v>
+      </c>
+      <c r="L97" s="3">
+        <v>0</v>
       </c>
       <c r="M97" s="3">
         <v>0</v>
@@ -6765,51 +6767,88 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" s="3" customFormat="1" customHeight="1" spans="3:14">
+    <row r="98" customHeight="1" spans="3:14">
       <c r="C98" s="3">
-        <v>8108</v>
+        <v>8202</v>
       </c>
       <c r="D98" s="11" t="s">
-        <v>276</v>
-      </c>
-      <c r="E98" s="2"/>
+        <v>277</v>
+      </c>
       <c r="F98" s="3">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="G98" s="3" t="s">
-        <v>269</v>
+        <v>278</v>
       </c>
       <c r="H98" s="3">
         <v>1</v>
       </c>
       <c r="I98" s="3">
-        <v>9999999</v>
+        <v>1</v>
       </c>
       <c r="J98" s="3">
         <v>0</v>
       </c>
       <c r="K98" s="3">
-        <v>7</v>
+        <v>2</v>
+      </c>
+      <c r="L98" s="3">
+        <v>0</v>
       </c>
       <c r="M98" s="3">
         <v>0</v>
       </c>
       <c r="N98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" customHeight="1" spans="3:14">
+      <c r="C99" s="3">
+        <v>8203</v>
+      </c>
+      <c r="D99" s="11" t="s">
+        <v>279</v>
+      </c>
+      <c r="F99" s="3">
+        <v>16</v>
+      </c>
+      <c r="G99" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="H99" s="3">
+        <v>1</v>
+      </c>
+      <c r="I99" s="3">
+        <v>1</v>
+      </c>
+      <c r="J99" s="3">
+        <v>0</v>
+      </c>
+      <c r="K99" s="3">
+        <v>3</v>
+      </c>
+      <c r="L99" s="3">
+        <v>0</v>
+      </c>
+      <c r="M99" s="3">
+        <v>0</v>
+      </c>
+      <c r="N99" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="100" customHeight="1" spans="3:14">
       <c r="C100" s="3">
-        <v>8201</v>
+        <v>8204</v>
       </c>
       <c r="D100" s="11" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="F100" s="3">
         <v>16</v>
       </c>
       <c r="G100" s="3" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="H100" s="3">
         <v>1</v>
@@ -6821,7 +6860,7 @@
         <v>0</v>
       </c>
       <c r="K100" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L100" s="3">
         <v>0</v>
@@ -6835,16 +6874,16 @@
     </row>
     <row r="101" customHeight="1" spans="3:14">
       <c r="C101" s="3">
-        <v>8202</v>
+        <v>8205</v>
       </c>
       <c r="D101" s="11" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="F101" s="3">
         <v>16</v>
       </c>
       <c r="G101" s="3" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="H101" s="3">
         <v>1</v>
@@ -6856,7 +6895,7 @@
         <v>0</v>
       </c>
       <c r="K101" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -6870,16 +6909,16 @@
     </row>
     <row r="102" customHeight="1" spans="3:14">
       <c r="C102" s="3">
-        <v>8203</v>
+        <v>8206</v>
       </c>
       <c r="D102" s="11" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="F102" s="3">
         <v>16</v>
       </c>
       <c r="G102" s="3" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="H102" s="3">
         <v>1</v>
@@ -6891,7 +6930,7 @@
         <v>0</v>
       </c>
       <c r="K102" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L102" s="3">
         <v>0</v>
@@ -6905,16 +6944,16 @@
     </row>
     <row r="103" customHeight="1" spans="3:14">
       <c r="C103" s="3">
-        <v>8204</v>
+        <v>8207</v>
       </c>
       <c r="D103" s="11" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="F103" s="3">
         <v>16</v>
       </c>
       <c r="G103" s="3" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="H103" s="3">
         <v>1</v>
@@ -6926,7 +6965,7 @@
         <v>0</v>
       </c>
       <c r="K103" s="3">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L103" s="3">
         <v>0</v>
@@ -6938,110 +6977,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" customHeight="1" spans="3:14">
-      <c r="C104" s="3">
-        <v>8205</v>
-      </c>
-      <c r="D104" s="11" t="s">
-        <v>285</v>
-      </c>
-      <c r="F104" s="3">
-        <v>16</v>
-      </c>
-      <c r="G104" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="H104" s="3">
-        <v>1</v>
-      </c>
-      <c r="I104" s="3">
-        <v>1</v>
-      </c>
-      <c r="J104" s="3">
-        <v>0</v>
-      </c>
-      <c r="K104" s="3">
-        <v>5</v>
-      </c>
-      <c r="L104" s="3">
-        <v>0</v>
-      </c>
-      <c r="M104" s="3">
-        <v>0</v>
-      </c>
-      <c r="N104" s="3">
-        <v>0</v>
-      </c>
-    </row>
     <row r="105" customHeight="1" spans="3:14">
-      <c r="C105" s="3">
-        <v>8206</v>
-      </c>
-      <c r="D105" s="11" t="s">
-        <v>287</v>
-      </c>
-      <c r="F105" s="3">
-        <v>16</v>
-      </c>
-      <c r="G105" s="3" t="s">
-        <v>288</v>
-      </c>
-      <c r="H105" s="3">
-        <v>1</v>
-      </c>
-      <c r="I105" s="3">
-        <v>1</v>
-      </c>
-      <c r="J105" s="3">
-        <v>0</v>
-      </c>
-      <c r="K105" s="3">
-        <v>6</v>
-      </c>
-      <c r="L105" s="3">
-        <v>0</v>
-      </c>
-      <c r="M105" s="3">
-        <v>0</v>
-      </c>
-      <c r="N105" s="3">
-        <v>0</v>
-      </c>
+      <c r="D105" s="11"/>
     </row>
     <row r="106" customHeight="1" spans="3:14">
-      <c r="C106" s="3">
-        <v>8207</v>
-      </c>
-      <c r="D106" s="11" t="s">
-        <v>289</v>
-      </c>
-      <c r="F106" s="3">
-        <v>16</v>
-      </c>
-      <c r="G106" s="3" t="s">
-        <v>290</v>
-      </c>
-      <c r="H106" s="3">
-        <v>1</v>
-      </c>
-      <c r="I106" s="3">
-        <v>1</v>
-      </c>
-      <c r="J106" s="3">
-        <v>0</v>
-      </c>
-      <c r="K106" s="3">
-        <v>7</v>
-      </c>
-      <c r="L106" s="3">
-        <v>0</v>
-      </c>
-      <c r="M106" s="3">
-        <v>0</v>
-      </c>
-      <c r="N106" s="3">
-        <v>0</v>
-      </c>
+      <c r="D106" s="11"/>
+    </row>
+    <row r="107" customHeight="1" spans="3:14">
+      <c r="D107" s="11"/>
     </row>
     <row r="108" customHeight="1" spans="3:14">
       <c r="D108" s="11"/>
@@ -7055,15 +6998,15 @@
     <row r="111" customHeight="1" spans="3:14">
       <c r="D111" s="11"/>
     </row>
-    <row r="112" customHeight="1" spans="3:14">
-      <c r="D112" s="11"/>
-    </row>
     <row r="113" customHeight="1" spans="4:4">
       <c r="D113" s="11"/>
     </row>
     <row r="114" customHeight="1" spans="4:4">
       <c r="D114" s="11"/>
     </row>
+    <row r="115" customHeight="1" spans="4:4">
+      <c r="D115" s="11"/>
+    </row>
     <row r="116" customHeight="1" spans="4:4">
       <c r="D116" s="11"/>
     </row>
@@ -7075,15 +7018,6 @@
     </row>
     <row r="119" customHeight="1" spans="4:4">
       <c r="D119" s="11"/>
-    </row>
-    <row r="120" customHeight="1" spans="4:4">
-      <c r="D120" s="11"/>
-    </row>
-    <row r="121" customHeight="1" spans="4:4">
-      <c r="D121" s="11"/>
-    </row>
-    <row r="122" customHeight="1" spans="4:4">
-      <c r="D122" s="11"/>
     </row>
   </sheetData>
   <dataValidations count="2">
@@ -7239,14 +7173,14 @@
         <v>9001</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="E6" s="3"/>
       <c r="F6" s="2">
         <v>6</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="H6" s="2">
         <v>1</v>
@@ -7269,14 +7203,14 @@
         <v>9002</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="E7" s="3"/>
       <c r="F7" s="2">
         <v>6</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="H7" s="2">
         <v>1</v>
@@ -7299,14 +7233,14 @@
         <v>9003</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="E8" s="3"/>
       <c r="F8" s="2">
         <v>6</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="H8" s="2">
         <v>1</v>
@@ -7329,14 +7263,14 @@
         <v>9004</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="E9" s="3"/>
       <c r="F9" s="2">
         <v>6</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="H9" s="2">
         <v>1</v>
@@ -7359,14 +7293,14 @@
         <v>9005</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="E10" s="3"/>
       <c r="F10" s="2">
         <v>6</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="H10" s="2">
         <v>1</v>
@@ -7389,14 +7323,14 @@
         <v>9006</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="E11" s="3"/>
       <c r="F11" s="2">
         <v>6</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="H11" s="2">
         <v>1</v>
@@ -7418,14 +7352,14 @@
         <v>9007</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" s="2">
         <v>6</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="H12" s="2">
         <v>1</v>
@@ -7447,14 +7381,14 @@
         <v>9008</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" s="2">
         <v>6</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="H13" s="2">
         <v>1</v>
@@ -7476,14 +7410,14 @@
         <v>9009</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="E14" s="3"/>
       <c r="F14" s="2">
         <v>6</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="H14" s="2">
         <v>1</v>
@@ -7505,14 +7439,14 @@
         <v>9010</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="E15" s="3"/>
       <c r="F15" s="2">
         <v>6</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="H15" s="2">
         <v>1</v>
@@ -7534,14 +7468,14 @@
         <v>9011</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="E16" s="3"/>
       <c r="F16" s="2">
         <v>6</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="H16" s="2">
         <v>1</v>
@@ -7718,14 +7652,14 @@
         <v>10001</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="E6" s="3"/>
       <c r="F6" s="2">
         <v>5</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="H6" s="2">
         <v>1</v>
@@ -7747,14 +7681,14 @@
         <v>10002</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="E7" s="3"/>
       <c r="F7" s="2">
         <v>5</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="H7" s="2">
         <v>1</v>
@@ -7776,14 +7710,14 @@
         <v>10003</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="E8" s="3"/>
       <c r="F8" s="2">
         <v>5</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="H8" s="2">
         <v>1</v>
@@ -7805,14 +7739,14 @@
         <v>10004</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="E9" s="3"/>
       <c r="F9" s="2">
         <v>5</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="H9" s="2">
         <v>1</v>
@@ -8083,16 +8017,16 @@
         <v>40000001</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="F6" s="2">
         <v>6</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="H6" s="2">
         <v>1</v>
@@ -8113,16 +8047,16 @@
         <v>40000002</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="F7" s="2">
         <v>6</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="H7" s="2">
         <v>1</v>
@@ -8143,16 +8077,16 @@
         <v>40000003</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="F8" s="2">
         <v>6</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="H8" s="2">
         <v>1</v>
@@ -8173,16 +8107,16 @@
         <v>40000004</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="F9" s="2">
         <v>6</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="H9" s="2">
         <v>1</v>
@@ -8203,16 +8137,16 @@
         <v>40000005</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="F10" s="2">
         <v>6</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="H10" s="2">
         <v>1</v>
@@ -8233,16 +8167,16 @@
         <v>40000006</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="F11" s="2">
         <v>6</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="H11" s="2">
         <v>1</v>
@@ -8265,16 +8199,16 @@
         <v>40000007</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="F12" s="2">
         <v>6</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="H12" s="2">
         <v>1</v>
@@ -8294,16 +8228,16 @@
         <v>40000008</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="F13" s="2">
         <v>6</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="H13" s="2">
         <v>1</v>
@@ -8323,16 +8257,16 @@
         <v>40000009</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="F14" s="2">
         <v>6</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="H14" s="2">
         <v>1</v>
@@ -8352,16 +8286,16 @@
         <v>40000010</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="F15" s="2">
         <v>6</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="H15" s="2">
         <v>1</v>
@@ -8381,16 +8315,16 @@
         <v>40000011</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="F16" s="2">
         <v>6</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="H16" s="2">
         <v>1</v>
@@ -8411,16 +8345,16 @@
         <v>40000012</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="F17" s="2">
         <v>6</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="H17" s="2">
         <v>1</v>
@@ -8440,14 +8374,14 @@
         <v>40000013</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="E18" s="3"/>
       <c r="F18" s="2">
         <v>6</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="H18" s="2">
         <v>1</v>
@@ -8467,14 +8401,14 @@
         <v>40000014</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="E19" s="3"/>
       <c r="F19" s="2">
         <v>6</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="H19" s="2">
         <v>1</v>
@@ -8494,14 +8428,14 @@
         <v>40000015</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="E20" s="3"/>
       <c r="F20" s="2">
         <v>6</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="H20" s="2">
         <v>1</v>
@@ -8521,14 +8455,14 @@
         <v>40000016</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="E21" s="3"/>
       <c r="F21" s="2">
         <v>6</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="H21" s="2">
         <v>1</v>
@@ -8548,14 +8482,14 @@
         <v>40000017</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="E22" s="3"/>
       <c r="F22" s="2">
         <v>6</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="H22" s="2">
         <v>1</v>
@@ -8575,14 +8509,14 @@
         <v>40000018</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="E23" s="3"/>
       <c r="F23" s="2">
         <v>6</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="H23" s="2">
         <v>1</v>
@@ -8602,13 +8536,13 @@
         <v>40000019</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="F24" s="2">
         <v>6</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="H24" s="2">
         <v>1</v>
@@ -8628,13 +8562,13 @@
         <v>40000020</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="F25" s="2">
         <v>6</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="H25" s="2">
         <v>1</v>
@@ -8654,13 +8588,13 @@
         <v>40000021</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="F26" s="2">
         <v>6</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="H26" s="2">
         <v>1</v>
@@ -8680,13 +8614,13 @@
         <v>40000022</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="F27" s="2">
         <v>6</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="H27" s="2">
         <v>1</v>
@@ -8706,13 +8640,13 @@
         <v>40000023</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="F28" s="2">
         <v>6</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="H28" s="2">
         <v>1</v>
@@ -8732,13 +8666,13 @@
         <v>40000024</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="F29" s="2">
         <v>6</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="H29" s="2">
         <v>1</v>
@@ -8758,13 +8692,13 @@
         <v>40000025</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="F30" s="2">
         <v>6</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="H30" s="2">
         <v>1</v>
@@ -8784,13 +8718,13 @@
         <v>40000026</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="F31" s="2">
         <v>6</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="H31" s="2">
         <v>1</v>
@@ -8810,13 +8744,13 @@
         <v>40000027</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="F32" s="2">
         <v>6</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="H32" s="2">
         <v>1</v>
@@ -8836,13 +8770,13 @@
         <v>40000028</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="F33" s="2">
         <v>6</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="H33" s="2">
         <v>1</v>
@@ -8862,13 +8796,13 @@
         <v>40000029</v>
       </c>
       <c r="D34" s="8" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="F34" s="2">
         <v>6</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="H34" s="2">
         <v>1</v>
@@ -8888,13 +8822,13 @@
         <v>40000030</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="F35" s="2">
         <v>6</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="H35" s="2">
         <v>1</v>

--- a/Excel/ItemConfig.xlsx
+++ b/Excel/ItemConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="1"/>
+    <workbookView windowHeight="17680" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="技能" sheetId="1" r:id="rId1"/>
@@ -229,7 +229,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="662" uniqueCount="358">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="674" uniqueCount="366">
   <si>
     <t>_Id</t>
   </si>
@@ -1320,6 +1320,30 @@
   </si>
   <si>
     <t>亲卫令牌</t>
+  </si>
+  <si>
+    <t>魔瞳</t>
+  </si>
+  <si>
+    <t>虚空裂谷珍宝材料</t>
+  </si>
+  <si>
+    <t>血镰刀</t>
+  </si>
+  <si>
+    <t>神秘法杖</t>
+  </si>
+  <si>
+    <t>犬牙</t>
+  </si>
+  <si>
+    <t>地狱烈焰珍宝材料</t>
+  </si>
+  <si>
+    <t>恶魔利爪</t>
+  </si>
+  <si>
+    <t>深渊巨刃</t>
   </si>
 </sst>
 </file>
@@ -7875,7 +7899,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N35"/>
+  <dimension ref="A1:N42"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="2"/>
@@ -8843,6 +8867,165 @@
         <v>6</v>
       </c>
     </row>
+    <row r="36" customHeight="1" spans="3:11">
+      <c r="C36" s="3">
+        <v>40000031</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="F36" s="2">
+        <v>6</v>
+      </c>
+      <c r="G36" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="H36" s="2">
+        <v>1</v>
+      </c>
+      <c r="I36" s="2">
+        <v>99999</v>
+      </c>
+      <c r="J36" s="2">
+        <v>0</v>
+      </c>
+      <c r="K36" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" customHeight="1" spans="3:11">
+      <c r="C37" s="3">
+        <v>40000032</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="F37" s="2">
+        <v>6</v>
+      </c>
+      <c r="G37" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="H37" s="2">
+        <v>1</v>
+      </c>
+      <c r="I37" s="2">
+        <v>99999</v>
+      </c>
+      <c r="J37" s="2">
+        <v>0</v>
+      </c>
+      <c r="K37" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="38" customHeight="1" spans="3:11">
+      <c r="C38" s="3">
+        <v>40000033</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="F38" s="2">
+        <v>6</v>
+      </c>
+      <c r="G38" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="H38" s="2">
+        <v>1</v>
+      </c>
+      <c r="I38" s="2">
+        <v>99999</v>
+      </c>
+      <c r="J38" s="2">
+        <v>0</v>
+      </c>
+      <c r="K38" s="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39" customHeight="1" spans="3:11">
+      <c r="C39" s="3">
+        <v>40000034</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="F39" s="2">
+        <v>6</v>
+      </c>
+      <c r="G39" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="H39" s="2">
+        <v>1</v>
+      </c>
+      <c r="I39" s="2">
+        <v>99999</v>
+      </c>
+      <c r="J39" s="2">
+        <v>0</v>
+      </c>
+      <c r="K39" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="40" customHeight="1" spans="3:11">
+      <c r="C40" s="3">
+        <v>40000035</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="F40" s="2">
+        <v>6</v>
+      </c>
+      <c r="G40" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="H40" s="2">
+        <v>1</v>
+      </c>
+      <c r="I40" s="2">
+        <v>99999</v>
+      </c>
+      <c r="J40" s="2">
+        <v>0</v>
+      </c>
+      <c r="K40" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="41" customHeight="1" spans="3:11">
+      <c r="C41" s="3">
+        <v>40000036</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="F41" s="2">
+        <v>6</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="H41" s="2">
+        <v>1</v>
+      </c>
+      <c r="I41" s="2">
+        <v>99999</v>
+      </c>
+      <c r="J41" s="2">
+        <v>0</v>
+      </c>
+      <c r="K41" s="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="42" customHeight="1" spans="3:11">
+      <c r="G42" s="3"/>
+    </row>
   </sheetData>
   <dataValidations count="2">
     <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:E5" errorStyle="warning">

--- a/Excel/ItemConfig.xlsx
+++ b/Excel/ItemConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="4"/>
+    <workbookView windowHeight="17680" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="技能" sheetId="1" r:id="rId1"/>
@@ -1017,13 +1017,13 @@
     <t>万年魂环</t>
   </si>
   <si>
-    <t>十万年魂环</t>
-  </si>
-  <si>
-    <t>百万年魂环</t>
-  </si>
-  <si>
-    <t>千万年魂环</t>
+    <t>十万魂环</t>
+  </si>
+  <si>
+    <t>百万魂环</t>
+  </si>
+  <si>
+    <t>千万魂环</t>
   </si>
   <si>
     <t>亿年魂环</t>
